--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -446,7 +446,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -468,7 +467,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -2251,7 +2249,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>gas out 있음/없음</t>
+          <t>gas out 됨/gas out 안됨</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -10126,11 +10124,11 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D230" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
@@ -10155,11 +10153,11 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D231" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
@@ -10402,11 +10400,11 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
@@ -10431,11 +10429,11 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D239" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
@@ -10715,11 +10713,11 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D247" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
@@ -10744,11 +10742,11 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D248" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
@@ -11073,11 +11071,11 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D257" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
@@ -11102,11 +11100,11 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D258" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
@@ -11139,7 +11137,7 @@
         </is>
       </c>
       <c r="D259" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
@@ -11168,7 +11166,7 @@
         </is>
       </c>
       <c r="D260" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
@@ -11197,7 +11195,7 @@
         </is>
       </c>
       <c r="D261" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
@@ -11226,7 +11224,7 @@
         </is>
       </c>
       <c r="D262" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.환자설명" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.도관" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.낙상교육" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소아_질문초안(미확정)" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +35,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +49,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -68,6 +87,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1962,7 +1985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I354"/>
+  <dimension ref="A1:J354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1974,6 +1997,7 @@
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2022,6 +2046,11 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>진단연결</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -2063,6 +2092,11 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2104,6 +2138,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2145,6 +2184,11 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2186,6 +2230,11 @@
           <t>ileus 의심 시</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2227,6 +2276,11 @@
           <t>ileus 의심 시</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2266,6 +2320,11 @@
       <c r="I7" s="2" t="inlineStr">
         <is>
           <t>ileus 의심 시</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -2297,6 +2356,11 @@
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2326,6 +2390,11 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2355,6 +2424,11 @@
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2388,6 +2462,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2429,6 +2508,11 @@
           <t>호흡곤란 여부 확인</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -2470,6 +2554,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -2509,6 +2598,11 @@
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -2540,6 +2634,11 @@
       <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2569,6 +2668,11 @@
       <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2598,6 +2702,11 @@
       <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2631,6 +2740,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2672,6 +2786,11 @@
           <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2713,6 +2832,11 @@
           <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2754,6 +2878,11 @@
           <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2795,6 +2924,11 @@
           <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2836,6 +2970,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2875,6 +3014,11 @@
       <c r="I24" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -2906,6 +3050,11 @@
       <c r="G25" s="2" t="inlineStr"/>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2935,6 +3084,11 @@
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2964,6 +3118,11 @@
       <c r="G27" s="2" t="inlineStr"/>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2997,6 +3156,11 @@
           <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
         </is>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -3030,6 +3194,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3071,6 +3240,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3110,6 +3284,11 @@
       <c r="I31" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -3141,6 +3320,11 @@
       <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3170,6 +3354,11 @@
       <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3199,6 +3388,11 @@
       <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3232,6 +3426,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3273,6 +3472,11 @@
           <t>많지 않을 때</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3314,6 +3518,11 @@
           <t>열 날때</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3355,6 +3564,11 @@
           <t>춥다고 할때</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3396,6 +3610,11 @@
           <t>호흡곤란정도/RR</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3437,6 +3656,11 @@
           <t>사정 때 산소 흡입 시</t>
         </is>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3474,6 +3698,11 @@
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3503,6 +3732,11 @@
       <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3536,6 +3770,11 @@
           <t>결과치 입력</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3569,6 +3808,11 @@
           <t>지금부터 산소 흡입 시작할 떄</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -3602,6 +3846,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -3643,6 +3892,11 @@
           <t>가래 양 많을 떄</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -3680,6 +3934,11 @@
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -3721,6 +3980,11 @@
           <t>가래 못 뱉을 때</t>
         </is>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -3762,6 +4026,11 @@
           <t>열 날때</t>
         </is>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -3803,6 +4072,11 @@
           <t>춥다고 할때</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -3844,6 +4118,11 @@
           <t>호흡곤란 정도/RR</t>
         </is>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -3885,6 +4164,11 @@
           <t>사정 때 산소 흡입 시</t>
         </is>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3922,6 +4206,11 @@
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3951,6 +4240,11 @@
       <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3984,6 +4278,11 @@
           <t>결과치 입력</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -4017,6 +4316,11 @@
           <t>지금부터 산소 흡입 시작할 떄</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -4050,6 +4354,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -4091,6 +4400,11 @@
           <t>가래 양 많을 떄</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4132,6 +4446,11 @@
           <t>쌕쌕거리며 천명음 들릴 때</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4173,6 +4492,11 @@
           <t>열 날때</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4214,6 +4538,11 @@
           <t>춥다고 할때</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -4255,6 +4584,11 @@
           <t>호흡곤란 정도/RR</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -4296,6 +4630,11 @@
           <t>사정 때 산소 흡입 시</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -4333,6 +4672,11 @@
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -4362,6 +4706,11 @@
       <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -4395,6 +4744,11 @@
           <t>결과치 입력</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4428,6 +4782,11 @@
           <t>지금부터 산소 흡입 시작할 떄</t>
         </is>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -4461,6 +4820,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -4502,6 +4866,11 @@
           <t>많지 않을 때</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -4543,6 +4912,11 @@
           <t>열 날때</t>
         </is>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -4584,6 +4958,11 @@
           <t>춥다고 할때</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -4625,6 +5004,11 @@
           <t>호흡곤란정도/RR</t>
         </is>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -4662,6 +5046,11 @@
       </c>
       <c r="H73" s="2" t="inlineStr"/>
       <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -4699,6 +5088,11 @@
       </c>
       <c r="H74" s="2" t="inlineStr"/>
       <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4740,6 +5134,11 @@
           <t>하지부종 여부, Pitting edema 여부, 있을 시 사진 찍어 올리기</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4777,6 +5176,11 @@
       </c>
       <c r="H76" s="2" t="inlineStr"/>
       <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4806,6 +5210,11 @@
       <c r="G77" s="2" t="inlineStr"/>
       <c r="H77" s="2" t="inlineStr"/>
       <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4839,6 +5248,11 @@
           <t>결과치 입력</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4872,6 +5286,11 @@
           <t>지금부터 산소 흡입 시작할 떄</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4905,6 +5324,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4946,6 +5370,7 @@
           <t>많지 않을 때</t>
         </is>
       </c>
+      <c r="J81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4987,6 +5412,7 @@
           <t>열 날때</t>
         </is>
       </c>
+      <c r="J82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5028,6 +5454,7 @@
           <t>춥다고 할때</t>
         </is>
       </c>
+      <c r="J83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5069,6 +5496,7 @@
           <t>호흡곤란정도/RR</t>
         </is>
       </c>
+      <c r="J84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5106,6 +5534,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5143,6 +5572,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5184,6 +5614,7 @@
           <t>하지부종 여부, Pitting edema 여부, 있을 시 사진 찍어 올리기</t>
         </is>
       </c>
+      <c r="J87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5221,6 +5652,7 @@
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5262,6 +5694,7 @@
           <t>호흡곤란 여부 확인</t>
         </is>
       </c>
+      <c r="J89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5303,6 +5736,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5344,6 +5778,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5373,6 +5808,11 @@
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -5402,6 +5842,11 @@
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -5435,6 +5880,7 @@
           <t>결과치 입력</t>
         </is>
       </c>
+      <c r="J94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5468,6 +5914,7 @@
           <t>지금부터 산소 흡입 시작할 떄</t>
         </is>
       </c>
+      <c r="J95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5501,6 +5948,7 @@
           <t>어저러움 여부 확인</t>
         </is>
       </c>
+      <c r="J96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5530,6 +5978,7 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5559,6 +6008,7 @@
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5592,6 +6042,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5633,6 +6084,11 @@
           <t>빈도/정도</t>
         </is>
       </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5670,6 +6126,11 @@
       </c>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5707,6 +6168,11 @@
       </c>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5744,6 +6210,11 @@
       </c>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5781,6 +6252,11 @@
       </c>
       <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5822,6 +6298,11 @@
           <t>시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5859,6 +6340,11 @@
       </c>
       <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5888,6 +6374,11 @@
       <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -5917,6 +6408,11 @@
       <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -5950,6 +6446,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -5991,6 +6492,7 @@
           <t>빈도/정도</t>
         </is>
       </c>
+      <c r="J110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6028,6 +6530,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6065,6 +6568,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6102,6 +6606,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6143,6 +6648,7 @@
           <t>시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6180,6 +6686,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6221,6 +6728,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6250,6 +6758,11 @@
       <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr"/>
       <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6279,6 +6792,11 @@
       <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr"/>
       <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6308,6 +6826,7 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6341,6 +6860,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6370,6 +6890,7 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6399,6 +6920,7 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6432,6 +6954,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6469,6 +6992,11 @@
       </c>
       <c r="H124" s="2" t="inlineStr"/>
       <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -6506,6 +7034,11 @@
       </c>
       <c r="H125" s="2" t="inlineStr"/>
       <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -6547,6 +7080,11 @@
           <t>시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -6584,6 +7122,11 @@
       </c>
       <c r="H127" s="2" t="inlineStr"/>
       <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6613,6 +7156,11 @@
       <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr"/>
       <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -6642,6 +7190,11 @@
       <c r="G129" s="2" t="inlineStr"/>
       <c r="H129" s="2" t="inlineStr"/>
       <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -6675,6 +7228,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -6712,6 +7270,7 @@
       </c>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -6753,6 +7312,7 @@
           <t>시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -6790,6 +7350,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -6831,6 +7392,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -6872,6 +7434,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -6901,6 +7464,11 @@
       <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr"/>
       <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -6930,6 +7498,11 @@
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr"/>
       <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -6959,6 +7532,7 @@
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -6992,6 +7566,7 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
+      <c r="J139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7021,6 +7596,7 @@
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7050,6 +7626,7 @@
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -7083,6 +7660,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -7120,6 +7698,11 @@
       </c>
       <c r="H143" s="2" t="inlineStr"/>
       <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -7157,6 +7740,11 @@
       </c>
       <c r="H144" s="2" t="inlineStr"/>
       <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -7198,6 +7786,11 @@
           <t>뺠간변, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -7239,6 +7832,11 @@
           <t>까만변, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -7276,6 +7874,11 @@
       </c>
       <c r="H147" s="2" t="inlineStr"/>
       <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -7305,6 +7908,11 @@
       <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr"/>
       <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -7334,6 +7942,11 @@
       <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr"/>
       <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -7367,6 +7980,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -7404,6 +8022,7 @@
       </c>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -7445,6 +8064,7 @@
           <t>뺠간변, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -7486,6 +8106,7 @@
           <t>까만변, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -7523,6 +8144,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -7564,6 +8186,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -7605,6 +8228,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -7634,6 +8258,11 @@
       <c r="G157" s="2" t="inlineStr"/>
       <c r="H157" s="2" t="inlineStr"/>
       <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -7663,6 +8292,11 @@
       <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr"/>
       <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -7692,6 +8326,7 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -7725,6 +8360,7 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
+      <c r="J160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -7754,6 +8390,7 @@
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -7783,6 +8420,7 @@
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -7816,6 +8454,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -7853,6 +8492,11 @@
       </c>
       <c r="H164" s="2" t="inlineStr"/>
       <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -7894,6 +8538,11 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -7931,6 +8580,11 @@
       </c>
       <c r="H166" s="2" t="inlineStr"/>
       <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -7960,6 +8614,11 @@
       <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr"/>
       <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -7989,6 +8648,11 @@
       <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr"/>
       <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -8022,6 +8686,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -8059,6 +8728,7 @@
       </c>
       <c r="H170" s="2" t="inlineStr"/>
       <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -8100,6 +8770,7 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -8137,6 +8808,7 @@
       </c>
       <c r="H172" s="2" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -8178,6 +8850,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -8219,6 +8892,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -8248,6 +8922,11 @@
       <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr"/>
       <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -8277,6 +8956,11 @@
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr"/>
       <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -8306,6 +8990,7 @@
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -8335,6 +9020,7 @@
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr"/>
       <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -8364,6 +9050,7 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -8393,6 +9080,7 @@
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -8426,6 +9114,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -8463,6 +9152,11 @@
       </c>
       <c r="H182" s="2" t="inlineStr"/>
       <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -8504,6 +9198,11 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -8541,6 +9240,11 @@
       </c>
       <c r="H184" s="2" t="inlineStr"/>
       <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -8570,6 +9274,11 @@
       <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr"/>
       <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -8599,6 +9308,11 @@
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr"/>
       <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -8632,6 +9346,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -8669,6 +9388,7 @@
       </c>
       <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -8710,6 +9430,7 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -8747,6 +9468,7 @@
       </c>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="2" t="inlineStr"/>
+      <c r="J190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -8788,6 +9510,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -8829,6 +9552,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -8858,6 +9582,11 @@
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -8887,6 +9616,11 @@
       <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="2" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -8916,6 +9650,7 @@
       <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="2" t="inlineStr"/>
+      <c r="J195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -8945,6 +9680,7 @@
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr"/>
       <c r="I196" s="2" t="inlineStr"/>
+      <c r="J196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -8974,6 +9710,7 @@
       <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr"/>
+      <c r="J197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -9003,6 +9740,7 @@
       <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="2" t="inlineStr"/>
+      <c r="J198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -9036,6 +9774,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -9073,6 +9812,11 @@
       </c>
       <c r="H200" s="2" t="inlineStr"/>
       <c r="I200" s="2" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -9114,6 +9858,11 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -9155,6 +9904,11 @@
           <t>헤모글로빈 수치 낮을시</t>
         </is>
       </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -9196,6 +9950,11 @@
           <t>혈소판 수치 낮을시</t>
         </is>
       </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -9237,6 +9996,11 @@
           <t>INR 수치 정상보다 높을시(1.5이상?)</t>
         </is>
       </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -9274,6 +10038,11 @@
       </c>
       <c r="H205" s="2" t="inlineStr"/>
       <c r="I205" s="2" t="inlineStr"/>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -9303,6 +10072,11 @@
       <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr"/>
       <c r="I206" s="2" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -9332,6 +10106,11 @@
       <c r="G207" s="2" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr"/>
       <c r="I207" s="2" t="inlineStr"/>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -9365,6 +10144,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -9402,6 +10186,7 @@
       </c>
       <c r="H209" s="2" t="inlineStr"/>
       <c r="I209" s="2" t="inlineStr"/>
+      <c r="J209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -9443,6 +10228,7 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
+      <c r="J210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -9484,6 +10270,7 @@
           <t>헤모글로빈 수치 낮을시</t>
         </is>
       </c>
+      <c r="J211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -9525,6 +10312,7 @@
           <t>혈소판 수치 낮을시</t>
         </is>
       </c>
+      <c r="J212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -9566,6 +10354,7 @@
           <t>INR 수치 정상보다 높을시(1.5이상?)</t>
         </is>
       </c>
+      <c r="J213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -9603,6 +10392,7 @@
       </c>
       <c r="H214" s="2" t="inlineStr"/>
       <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -9644,6 +10434,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -9685,6 +10476,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -9714,6 +10506,11 @@
       <c r="G217" s="2" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr"/>
       <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -9743,6 +10540,11 @@
       <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr"/>
       <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -9772,6 +10574,7 @@
       <c r="G219" s="2" t="inlineStr"/>
       <c r="H219" s="2" t="inlineStr"/>
       <c r="I219" s="2" t="inlineStr"/>
+      <c r="J219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -9805,6 +10608,7 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
+      <c r="J220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -9834,6 +10638,7 @@
       <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr"/>
       <c r="I221" s="2" t="inlineStr"/>
+      <c r="J221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -9863,6 +10668,7 @@
       <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr"/>
       <c r="I222" s="2" t="inlineStr"/>
+      <c r="J222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -9896,6 +10702,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -9933,6 +10740,11 @@
       </c>
       <c r="H224" s="2" t="inlineStr"/>
       <c r="I224" s="2" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -9970,6 +10782,11 @@
       </c>
       <c r="H225" s="2" t="inlineStr"/>
       <c r="I225" s="2" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -10007,6 +10824,11 @@
       </c>
       <c r="H226" s="2" t="inlineStr"/>
       <c r="I226" s="2" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -10044,6 +10866,11 @@
       </c>
       <c r="H227" s="2" t="inlineStr"/>
       <c r="I227" s="2" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -10081,6 +10908,11 @@
       </c>
       <c r="H228" s="2" t="inlineStr"/>
       <c r="I228" s="2" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -10110,6 +10942,11 @@
       <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr"/>
       <c r="I229" s="2" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -10139,6 +10976,11 @@
       <c r="G230" s="2" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="2" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -10172,6 +11014,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -10209,6 +11056,11 @@
       </c>
       <c r="H232" s="2" t="inlineStr"/>
       <c r="I232" s="2" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -10246,6 +11098,11 @@
       </c>
       <c r="H233" s="2" t="inlineStr"/>
       <c r="I233" s="2" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -10283,6 +11140,11 @@
       </c>
       <c r="H234" s="2" t="inlineStr"/>
       <c r="I234" s="2" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -10320,6 +11182,11 @@
       </c>
       <c r="H235" s="2" t="inlineStr"/>
       <c r="I235" s="2" t="inlineStr"/>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -10357,6 +11224,11 @@
       </c>
       <c r="H236" s="2" t="inlineStr"/>
       <c r="I236" s="2" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -10386,6 +11258,11 @@
       <c r="G237" s="2" t="inlineStr"/>
       <c r="H237" s="2" t="inlineStr"/>
       <c r="I237" s="2" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -10415,6 +11292,11 @@
       <c r="G238" s="2" t="inlineStr"/>
       <c r="H238" s="2" t="inlineStr"/>
       <c r="I238" s="2" t="inlineStr"/>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -10448,6 +11330,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -10485,6 +11372,11 @@
       </c>
       <c r="H240" s="2" t="inlineStr"/>
       <c r="I240" s="2" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -10522,6 +11414,11 @@
       </c>
       <c r="H241" s="2" t="inlineStr"/>
       <c r="I241" s="2" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -10559,6 +11456,11 @@
       </c>
       <c r="H242" s="2" t="inlineStr"/>
       <c r="I242" s="2" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -10596,6 +11498,11 @@
       </c>
       <c r="H243" s="2" t="inlineStr"/>
       <c r="I243" s="2" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -10633,6 +11540,11 @@
       </c>
       <c r="H244" s="2" t="inlineStr"/>
       <c r="I244" s="2" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -10670,6 +11582,11 @@
       </c>
       <c r="H245" s="2" t="inlineStr"/>
       <c r="I245" s="2" t="inlineStr"/>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -10699,6 +11616,11 @@
       <c r="G246" s="2" t="inlineStr"/>
       <c r="H246" s="2" t="inlineStr"/>
       <c r="I246" s="2" t="inlineStr"/>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -10728,6 +11650,11 @@
       <c r="G247" s="2" t="inlineStr"/>
       <c r="H247" s="2" t="inlineStr"/>
       <c r="I247" s="2" t="inlineStr"/>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -10761,6 +11688,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>감염</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -10798,6 +11730,7 @@
       </c>
       <c r="H249" s="2" t="inlineStr"/>
       <c r="I249" s="2" t="inlineStr"/>
+      <c r="J249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -10835,6 +11768,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr"/>
       <c r="I250" s="2" t="inlineStr"/>
+      <c r="J250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -10872,6 +11806,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr"/>
       <c r="I251" s="2" t="inlineStr"/>
+      <c r="J251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -10909,6 +11844,7 @@
       </c>
       <c r="H252" s="2" t="inlineStr"/>
       <c r="I252" s="2" t="inlineStr"/>
+      <c r="J252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -10946,6 +11882,7 @@
       </c>
       <c r="H253" s="2" t="inlineStr"/>
       <c r="I253" s="2" t="inlineStr"/>
+      <c r="J253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -10987,6 +11924,7 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -11028,6 +11966,7 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -11057,6 +11996,11 @@
       <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr"/>
       <c r="I256" s="2" t="inlineStr"/>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -11086,6 +12030,7 @@
       <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr"/>
       <c r="I257" s="2" t="inlineStr"/>
+      <c r="J257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -11119,6 +12064,7 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
+      <c r="J258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -11148,6 +12094,11 @@
       <c r="G259" s="2" t="inlineStr"/>
       <c r="H259" s="2" t="inlineStr"/>
       <c r="I259" s="2" t="inlineStr"/>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -11177,6 +12128,7 @@
       <c r="G260" s="2" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr"/>
       <c r="I260" s="2" t="inlineStr"/>
+      <c r="J260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -11206,6 +12158,7 @@
       <c r="G261" s="2" t="inlineStr"/>
       <c r="H261" s="2" t="inlineStr"/>
       <c r="I261" s="2" t="inlineStr"/>
+      <c r="J261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -11239,6 +12192,7 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -11280,6 +12234,11 @@
           <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -11321,6 +12280,11 @@
           <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -11362,6 +12326,11 @@
           <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
         </is>
       </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -11403,6 +12372,11 @@
           <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
         </is>
       </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -11444,6 +12418,11 @@
           <t>쳉ㅗㄴ 하강</t>
         </is>
       </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -11483,6 +12462,11 @@
       <c r="I268" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>저체온</t>
         </is>
       </c>
     </row>
@@ -11514,6 +12498,11 @@
       <c r="G269" s="2" t="inlineStr"/>
       <c r="H269" s="2" t="inlineStr"/>
       <c r="I269" s="2" t="inlineStr"/>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -11543,6 +12532,11 @@
       <c r="G270" s="2" t="inlineStr"/>
       <c r="H270" s="2" t="inlineStr"/>
       <c r="I270" s="2" t="inlineStr"/>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -11572,6 +12566,11 @@
       <c r="G271" s="2" t="inlineStr"/>
       <c r="H271" s="2" t="inlineStr"/>
       <c r="I271" s="2" t="inlineStr"/>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -11605,6 +12604,11 @@
           <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
         </is>
       </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -11638,6 +12642,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -11679,6 +12688,11 @@
           <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -11720,6 +12734,11 @@
           <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -11761,6 +12780,11 @@
           <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
         </is>
       </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -11802,6 +12826,11 @@
           <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
         </is>
       </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -11841,6 +12870,11 @@
       <c r="I278" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -11872,6 +12906,11 @@
       <c r="G279" s="2" t="inlineStr"/>
       <c r="H279" s="2" t="inlineStr"/>
       <c r="I279" s="2" t="inlineStr"/>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -11905,6 +12944,11 @@
           <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
         </is>
       </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -11938,6 +12982,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -11979,6 +13028,11 @@
           <t>호흡곤란 여부 확인</t>
         </is>
       </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -12016,6 +13070,11 @@
       </c>
       <c r="H283" s="2" t="inlineStr"/>
       <c r="I283" s="2" t="inlineStr"/>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -12057,6 +13116,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -12098,6 +13162,11 @@
           <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
         </is>
       </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -12137,6 +13206,11 @@
       <c r="I286" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
@@ -12168,6 +13242,11 @@
       <c r="G287" s="2" t="inlineStr"/>
       <c r="H287" s="2" t="inlineStr"/>
       <c r="I287" s="2" t="inlineStr"/>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -12197,6 +13276,11 @@
       <c r="G288" s="2" t="inlineStr"/>
       <c r="H288" s="2" t="inlineStr"/>
       <c r="I288" s="2" t="inlineStr"/>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -12230,6 +13314,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -12271,6 +13360,11 @@
           <t>호흡곤란 여부 확인</t>
         </is>
       </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -12308,6 +13402,11 @@
       </c>
       <c r="H291" s="2" t="inlineStr"/>
       <c r="I291" s="2" t="inlineStr"/>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -12349,6 +13448,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -12390,6 +13494,11 @@
           <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
         </is>
       </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -12431,6 +13540,11 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -12472,6 +13586,11 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -12509,6 +13628,11 @@
       </c>
       <c r="H296" s="2" t="inlineStr"/>
       <c r="I296" s="2" t="inlineStr"/>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -12546,6 +13670,11 @@
       </c>
       <c r="H297" s="2" t="inlineStr"/>
       <c r="I297" s="2" t="inlineStr"/>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -12583,6 +13712,11 @@
       </c>
       <c r="H298" s="2" t="inlineStr"/>
       <c r="I298" s="2" t="inlineStr"/>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -12622,6 +13756,11 @@
       <c r="I299" s="2" t="inlineStr">
         <is>
           <t>GCS 15 일때</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
@@ -12653,6 +13792,11 @@
       <c r="G300" s="2" t="inlineStr"/>
       <c r="H300" s="2" t="inlineStr"/>
       <c r="I300" s="2" t="inlineStr"/>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -12682,6 +13826,11 @@
       <c r="G301" s="2" t="inlineStr"/>
       <c r="H301" s="2" t="inlineStr"/>
       <c r="I301" s="2" t="inlineStr"/>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -12715,6 +13864,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -12756,6 +13910,11 @@
           <t>호흡곤란 여부 확인</t>
         </is>
       </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -12793,6 +13952,11 @@
       </c>
       <c r="H304" s="2" t="inlineStr"/>
       <c r="I304" s="2" t="inlineStr"/>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -12830,6 +13994,11 @@
       </c>
       <c r="H305" s="2" t="inlineStr"/>
       <c r="I305" s="2" t="inlineStr"/>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -12871,6 +14040,11 @@
           <t>오심,다뇨,구토, 갈증, 의식변화 등</t>
         </is>
       </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -12908,6 +14082,11 @@
       </c>
       <c r="H307" s="2" t="inlineStr"/>
       <c r="I307" s="2" t="inlineStr"/>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -12937,6 +14116,11 @@
       <c r="G308" s="2" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr"/>
       <c r="I308" s="2" t="inlineStr"/>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -12970,6 +14154,11 @@
           <t>인슐린 투여시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
         </is>
       </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -13003,6 +14192,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -13044,6 +14238,11 @@
           <t>호흡곤란 여부 확인</t>
         </is>
       </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -13081,6 +14280,11 @@
       </c>
       <c r="H312" s="2" t="inlineStr"/>
       <c r="I312" s="2" t="inlineStr"/>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -13118,6 +14322,11 @@
       </c>
       <c r="H313" s="2" t="inlineStr"/>
       <c r="I313" s="2" t="inlineStr"/>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -13159,6 +14368,11 @@
           <t>진전, 빈맥, 발한, 감각이상, 의식변화</t>
         </is>
       </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -13196,6 +14410,11 @@
       </c>
       <c r="H315" s="2" t="inlineStr"/>
       <c r="I315" s="2" t="inlineStr"/>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -13225,6 +14444,11 @@
       <c r="G316" s="2" t="inlineStr"/>
       <c r="H316" s="2" t="inlineStr"/>
       <c r="I316" s="2" t="inlineStr"/>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -13254,6 +14478,11 @@
       <c r="G317" s="2" t="inlineStr"/>
       <c r="H317" s="2" t="inlineStr"/>
       <c r="I317" s="2" t="inlineStr"/>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -13287,6 +14516,11 @@
           <t>D5% 처방시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
         </is>
       </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -13320,6 +14554,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>저혈당</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -13361,6 +14600,11 @@
           <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -13402,6 +14646,11 @@
           <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -13441,6 +14690,11 @@
       <c r="I322" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -13472,6 +14726,11 @@
       <c r="G323" s="2" t="inlineStr"/>
       <c r="H323" s="2" t="inlineStr"/>
       <c r="I323" s="2" t="inlineStr"/>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -13505,6 +14764,11 @@
           <t>airway유지</t>
         </is>
       </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -13534,6 +14798,11 @@
       <c r="G325" s="2" t="inlineStr"/>
       <c r="H325" s="2" t="inlineStr"/>
       <c r="I325" s="2" t="inlineStr"/>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -13567,6 +14836,11 @@
           <t>의사처방시</t>
         </is>
       </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -13600,6 +14874,11 @@
           <t>GCS 15 미만일 떄</t>
         </is>
       </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -13641,6 +14920,11 @@
           <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -13682,6 +14966,11 @@
           <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -13719,6 +15008,11 @@
       </c>
       <c r="H330" s="2" t="inlineStr"/>
       <c r="I330" s="2" t="inlineStr"/>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -13756,6 +15050,11 @@
       </c>
       <c r="H331" s="2" t="inlineStr"/>
       <c r="I331" s="2" t="inlineStr"/>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -13795,6 +15094,11 @@
       <c r="I332" s="2" t="inlineStr">
         <is>
           <t>Active</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -13826,6 +15130,11 @@
       <c r="G333" s="2" t="inlineStr"/>
       <c r="H333" s="2" t="inlineStr"/>
       <c r="I333" s="2" t="inlineStr"/>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -13859,6 +15168,11 @@
           <t>airway유지</t>
         </is>
       </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -13888,6 +15202,11 @@
       <c r="G335" s="2" t="inlineStr"/>
       <c r="H335" s="2" t="inlineStr"/>
       <c r="I335" s="2" t="inlineStr"/>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -13921,6 +15240,11 @@
           <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
         </is>
       </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -13954,6 +15278,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -13995,6 +15324,11 @@
           <t>GCS 15 미만일 떄</t>
         </is>
       </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -14036,6 +15370,11 @@
           <t>보호자 있을시</t>
         </is>
       </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -14077,6 +15416,11 @@
           <t>보호자 없을시</t>
         </is>
       </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -14118,6 +15462,11 @@
           <t>가능하지 않을 떄</t>
         </is>
       </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -14155,6 +15504,11 @@
       </c>
       <c r="H342" s="2" t="inlineStr"/>
       <c r="I342" s="2" t="inlineStr"/>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -14196,6 +15550,11 @@
           <t>Post note에 세부사항 기록하기</t>
         </is>
       </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -14237,6 +15596,11 @@
           <t>보호자 있을시</t>
         </is>
       </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -14278,6 +15642,11 @@
           <t>보호자 없을시</t>
         </is>
       </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -14317,6 +15686,11 @@
       <c r="I346" s="2" t="inlineStr">
         <is>
           <t>active</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
@@ -14348,6 +15722,11 @@
       <c r="G347" s="2" t="inlineStr"/>
       <c r="H347" s="2" t="inlineStr"/>
       <c r="I347" s="2" t="inlineStr"/>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -14381,6 +15760,11 @@
           <t>침대 난간 올려줬을 시</t>
         </is>
       </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -14414,6 +15798,11 @@
           <t>보호자 있을시, 낙상 위험 높을시</t>
         </is>
       </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -14447,6 +15836,11 @@
           <t>보호자 있을시</t>
         </is>
       </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -14480,6 +15874,11 @@
           <t>보호자 없을시</t>
         </is>
       </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -14513,6 +15912,11 @@
           <t>낙상위험 교육</t>
         </is>
       </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -14546,6 +15950,11 @@
           <t>낙상위험 교육</t>
         </is>
       </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -14579,8 +15988,39 @@
           <t>낙상위험 교육</t>
         </is>
       </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>낙상위험</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <dataValidations count="8">
+    <dataValidation sqref="J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J94 J95 J96 J97 J98 J99" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"비효율적 호흡양상,급성통증,공통"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J110 J111 J112 J113 J114 J115 J116 J119 J120 J121 J122 J123" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"출혈,급성통증,공통"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J131 J132 J133 J134 J135 J138 J139 J140 J141 J142" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"출혈,급성통증,공통"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J151 J152 J153 J154 J155 J156 J159 J160 J161 J162 J163" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"출혈,급성통증,공통"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J170 J171 J172 J173 J174 J177 J178 J179 J180 J181" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"출혈,급성통증,공통"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J188 J189 J190 J191 J192 J195 J196 J197 J198 J199" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"출혈,급성통증,공통"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J209 J210 J211 J212 J213 J214 J215 J216 J219 J220 J221 J222 J223" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"출혈위험,급성통증,공통"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J249 J250 J251 J252 J253 J254 J255 J257 J258 J260 J261 J262" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="진단연결" prompt="이 항목이 어느 진단에 속하는지 고르세요 (둘 다면 공통)" type="list">
+      <formula1>"고체온,급성통증,공통"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15316,4 +16756,1224 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>주제</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>진술문(양성·마스터원문)</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>마스터행</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>진술문(음성)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>입력형식</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>질문초안(💬)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>재사용</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>확정(칩스)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>호흡</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>호흡곤란 있음</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2542</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>호흡곤란 없음</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>"숨이 차거나 답답하신가요?"</t>
+        </is>
+      </c>
+      <c r="H2" s="6" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>호흡</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>chest retraction 있음</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2364</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>chest retraction 없음</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>호흡</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>wheezing 있음</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4358</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>wheezing 없음</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>호흡</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>기침 있음</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2467</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>기침 없음</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>"기침하나요?"</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>"기침이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>호흡</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>가래 잘 뱉지 못함</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4010</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>호흡</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>청색증 있음</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2487</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>청색증 없음</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>"입술이나 얼굴이 파래 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>호흡</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>말단 청색증 있음</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>387</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>말단 청색증 없음</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>"손끝·발끝이 파래 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>순환·체온</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>열감 있음</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2693</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>열감 없음</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>"열이 나나요?"</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>순환·체온</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>chilling 있음</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>chilling 없음</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>"춥다고 하거나 몸을 떨었나요?"</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>순환·체온</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>체온 상승함</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1664</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>🩺 체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>순환·체온</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>체온 하강함</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1665</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>🩺 체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>소화·탈수</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>구토함</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>198</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>"토했나요? 몇 번이나 했나요?"</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>소화·탈수</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>오심 있음</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>오심 없음</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>"메스꺼워 하나요?"</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>소화·탈수</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>설사 있음</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2501</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>설사 없음</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>"설사하나요? 몇 번이나 했나요?"</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>"설사하셨나요?"</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>소화·탈수</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>탈수 증상 있음</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1726</v>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>"입술이 마르거나 눈이 꺼져 보이나요? 울어도 눈물이 안 나나요?"</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>소화·탈수</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>소변량 감소함</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>972</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>소화·탈수</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>소변량 없음</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>973</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>"마지막으로 소변 본 게 언제인가요?"</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>소화·탈수</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>복부 통증 있음</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1988</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>복부 통증 없음</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>"배가 아프다고 하나요?"</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>"배가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>신경·의식</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>경련 있음</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>89</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>"경련(발작)을 했나요? 얼마나 오래 했나요?"</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>신경·의식</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>경련과 유사한 증상 보임</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>88</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>신경·의식</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>lethargy 상태임</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3176</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" s="6" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>신경·의식</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>무기력 호소함</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>444</v>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>"기운이 없어 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" s="6" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>신경·의식</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>의식수준 저하됨</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1389</v>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>🩺 의식 수준을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" s="6" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>행동·통증</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>보챔</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>653</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>🩺 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" s="6" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>행동·통증</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>울고 보챔</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1337</v>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>"평소보다 심하게 보채거나 우나요?"</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" s="6" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>행동·통증</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>울음소리 좋음</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1339</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>🩺 울음소리가 우렁찬지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" s="6" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>행동·통증</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>자극 주면 울음</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1447</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>🩺 자극에 반응해 우는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>행동·통증</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>자주 사지 움직이며 보챔</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1488</v>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>행동·통증</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>잠 안자고 울고 보챔</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1510</v>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>"잠을 못 자고 계속 우나요?"</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>행동·통증</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>통증 있음</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1740</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>통증 없음</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>"어디가 아프다고 하나요?"</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>"통증이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>urticaria 있음</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>4287</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>urticaria 없음</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>기저귀 발진 있음</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>250</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>기저귀 발진 없음</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>🩺 기저귀 부위 발진을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>⚠️ 초안 — 칩스 확정 필요</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -39,7 +39,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,11 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -79,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -91,6 +96,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1985,7 +1991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J354"/>
+  <dimension ref="A1:K354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1998,6 +2004,7 @@
     <col width="6" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2049,6 +2056,11 @@
       <c r="J1" s="3" t="inlineStr">
         <is>
           <t>진단연결</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>검토필요</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5382,11 @@
           <t>많지 않을 때</t>
         </is>
       </c>
-      <c r="J81" s="4" t="n"/>
+      <c r="J81" s="7" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -5412,7 +5428,11 @@
           <t>열 날때</t>
         </is>
       </c>
-      <c r="J82" s="4" t="n"/>
+      <c r="J82" s="7" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -5454,7 +5474,16 @@
           <t>춥다고 할때</t>
         </is>
       </c>
-      <c r="J83" s="4" t="n"/>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -5496,7 +5525,16 @@
           <t>호흡곤란정도/RR</t>
         </is>
       </c>
-      <c r="J84" s="4" t="n"/>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5534,7 +5572,11 @@
       </c>
       <c r="H85" s="2" t="inlineStr"/>
       <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="4" t="n"/>
+      <c r="J85" s="7" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5572,7 +5614,11 @@
       </c>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="4" t="n"/>
+      <c r="J86" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -5614,7 +5660,16 @@
           <t>하지부종 여부, Pitting edema 여부, 있을 시 사진 찍어 올리기</t>
         </is>
       </c>
-      <c r="J87" s="4" t="n"/>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -5652,7 +5707,16 @@
       </c>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="4" t="n"/>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5694,7 +5758,16 @@
           <t>호흡곤란 여부 확인</t>
         </is>
       </c>
-      <c r="J89" s="4" t="n"/>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5736,7 +5809,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J90" s="4" t="n"/>
+      <c r="J90" s="7" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -5778,7 +5855,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J91" s="4" t="n"/>
+      <c r="J91" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -5880,7 +5961,11 @@
           <t>결과치 입력</t>
         </is>
       </c>
-      <c r="J94" s="4" t="n"/>
+      <c r="J94" s="7" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -5914,7 +5999,11 @@
           <t>지금부터 산소 흡입 시작할 떄</t>
         </is>
       </c>
-      <c r="J95" s="4" t="n"/>
+      <c r="J95" s="7" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5948,7 +6037,11 @@
           <t>어저러움 여부 확인</t>
         </is>
       </c>
-      <c r="J96" s="4" t="n"/>
+      <c r="J96" s="7" t="inlineStr">
+        <is>
+          <t>비효율적 호흡양상</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5978,7 +6071,11 @@
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="4" t="n"/>
+      <c r="J97" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -6008,7 +6105,11 @@
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="4" t="n"/>
+      <c r="J98" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -6042,7 +6143,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J99" s="4" t="n"/>
+      <c r="J99" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -6492,7 +6597,16 @@
           <t>빈도/정도</t>
         </is>
       </c>
-      <c r="J110" s="4" t="n"/>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6530,7 +6644,16 @@
       </c>
       <c r="H111" s="2" t="inlineStr"/>
       <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="4" t="n"/>
+      <c r="J111" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6568,7 +6691,16 @@
       </c>
       <c r="H112" s="2" t="inlineStr"/>
       <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="4" t="n"/>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6606,7 +6738,16 @@
       </c>
       <c r="H113" s="2" t="inlineStr"/>
       <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="4" t="n"/>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6648,7 +6789,16 @@
           <t>시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
-      <c r="J114" s="4" t="n"/>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6686,7 +6836,11 @@
       </c>
       <c r="H115" s="2" t="inlineStr"/>
       <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="4" t="n"/>
+      <c r="J115" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6728,7 +6882,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J116" s="4" t="n"/>
+      <c r="J116" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6826,7 +6984,11 @@
       <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr"/>
       <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="4" t="n"/>
+      <c r="J119" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6860,7 +7022,11 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J120" s="4" t="n"/>
+      <c r="J120" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6890,7 +7056,11 @@
       <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr"/>
       <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="4" t="n"/>
+      <c r="J121" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6920,7 +7090,11 @@
       <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr"/>
       <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="4" t="n"/>
+      <c r="J122" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6954,7 +7128,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J123" s="4" t="n"/>
+      <c r="J123" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -7270,7 +7448,16 @@
       </c>
       <c r="H131" s="2" t="inlineStr"/>
       <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="4" t="n"/>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7312,7 +7499,16 @@
           <t>시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
-      <c r="J132" s="4" t="n"/>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7350,7 +7546,11 @@
       </c>
       <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="4" t="n"/>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7392,7 +7592,16 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J134" s="4" t="n"/>
+      <c r="J134" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7434,7 +7643,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J135" s="4" t="n"/>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7532,7 +7745,11 @@
       <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr"/>
       <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="4" t="n"/>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7566,7 +7783,11 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
-      <c r="J139" s="4" t="n"/>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7596,7 +7817,11 @@
       <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="4" t="n"/>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7626,7 +7851,11 @@
       <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr"/>
       <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="4" t="n"/>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -7660,7 +7889,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J142" s="4" t="n"/>
+      <c r="J142" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -8022,7 +8255,16 @@
       </c>
       <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="4" t="n"/>
+      <c r="J151" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8064,7 +8306,16 @@
           <t>뺠간변, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
-      <c r="J152" s="4" t="n"/>
+      <c r="J152" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8106,7 +8357,11 @@
           <t>까만변, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
-      <c r="J153" s="4" t="n"/>
+      <c r="J153" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8144,7 +8399,11 @@
       </c>
       <c r="H154" s="2" t="inlineStr"/>
       <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="4" t="n"/>
+      <c r="J154" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8186,7 +8445,16 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J155" s="4" t="n"/>
+      <c r="J155" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8228,7 +8496,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J156" s="4" t="n"/>
+      <c r="J156" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8326,7 +8598,11 @@
       <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr"/>
       <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="4" t="n"/>
+      <c r="J159" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8360,7 +8636,11 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
-      <c r="J160" s="4" t="n"/>
+      <c r="J160" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -8390,7 +8670,11 @@
       <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr"/>
       <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="4" t="n"/>
+      <c r="J161" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -8420,7 +8704,11 @@
       <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr"/>
       <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="4" t="n"/>
+      <c r="J162" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -8454,7 +8742,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J163" s="4" t="n"/>
+      <c r="J163" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -8728,7 +9020,16 @@
       </c>
       <c r="H170" s="2" t="inlineStr"/>
       <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="4" t="n"/>
+      <c r="J170" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -8770,7 +9071,16 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
-      <c r="J171" s="4" t="n"/>
+      <c r="J171" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -8808,7 +9118,11 @@
       </c>
       <c r="H172" s="2" t="inlineStr"/>
       <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="4" t="n"/>
+      <c r="J172" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -8850,7 +9164,16 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J173" s="4" t="n"/>
+      <c r="J173" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -8892,7 +9215,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J174" s="4" t="n"/>
+      <c r="J174" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -8990,7 +9317,11 @@
       <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr"/>
       <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="4" t="n"/>
+      <c r="J177" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -9020,7 +9351,11 @@
       <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr"/>
       <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="4" t="n"/>
+      <c r="J178" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -9050,7 +9385,11 @@
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="4" t="n"/>
+      <c r="J179" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -9080,7 +9419,11 @@
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr"/>
       <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="4" t="n"/>
+      <c r="J180" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -9114,7 +9457,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J181" s="4" t="n"/>
+      <c r="J181" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -9388,7 +9735,16 @@
       </c>
       <c r="H188" s="2" t="inlineStr"/>
       <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="4" t="n"/>
+      <c r="J188" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -9430,7 +9786,16 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
-      <c r="J189" s="4" t="n"/>
+      <c r="J189" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -9468,7 +9833,11 @@
       </c>
       <c r="H190" s="2" t="inlineStr"/>
       <c r="I190" s="2" t="inlineStr"/>
-      <c r="J190" s="4" t="n"/>
+      <c r="J190" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -9510,7 +9879,16 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J191" s="4" t="n"/>
+      <c r="J191" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -9552,7 +9930,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J192" s="4" t="n"/>
+      <c r="J192" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -9650,7 +10032,11 @@
       <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr"/>
       <c r="I195" s="2" t="inlineStr"/>
-      <c r="J195" s="4" t="n"/>
+      <c r="J195" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -9680,7 +10066,11 @@
       <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr"/>
       <c r="I196" s="2" t="inlineStr"/>
-      <c r="J196" s="4" t="n"/>
+      <c r="J196" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -9710,7 +10100,11 @@
       <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr"/>
       <c r="I197" s="2" t="inlineStr"/>
-      <c r="J197" s="4" t="n"/>
+      <c r="J197" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -9740,7 +10134,11 @@
       <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="4" t="n"/>
+      <c r="J198" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -9774,7 +10172,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J199" s="4" t="n"/>
+      <c r="J199" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -10186,7 +10588,16 @@
       </c>
       <c r="H209" s="2" t="inlineStr"/>
       <c r="I209" s="2" t="inlineStr"/>
-      <c r="J209" s="4" t="n"/>
+      <c r="J209" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -10228,7 +10639,16 @@
           <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
         </is>
       </c>
-      <c r="J210" s="4" t="n"/>
+      <c r="J210" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -10270,7 +10690,11 @@
           <t>헤모글로빈 수치 낮을시</t>
         </is>
       </c>
-      <c r="J211" s="4" t="n"/>
+      <c r="J211" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -10312,7 +10736,11 @@
           <t>혈소판 수치 낮을시</t>
         </is>
       </c>
-      <c r="J212" s="4" t="n"/>
+      <c r="J212" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -10354,7 +10782,11 @@
           <t>INR 수치 정상보다 높을시(1.5이상?)</t>
         </is>
       </c>
-      <c r="J213" s="4" t="n"/>
+      <c r="J213" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -10392,7 +10824,11 @@
       </c>
       <c r="H214" s="2" t="inlineStr"/>
       <c r="I214" s="2" t="inlineStr"/>
-      <c r="J214" s="4" t="n"/>
+      <c r="J214" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -10434,7 +10870,16 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J215" s="4" t="n"/>
+      <c r="J215" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -10476,7 +10921,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J216" s="4" t="n"/>
+      <c r="J216" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -10574,7 +11023,11 @@
       <c r="G219" s="2" t="inlineStr"/>
       <c r="H219" s="2" t="inlineStr"/>
       <c r="I219" s="2" t="inlineStr"/>
-      <c r="J219" s="4" t="n"/>
+      <c r="J219" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -10608,7 +11061,11 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
-      <c r="J220" s="4" t="n"/>
+      <c r="J220" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -10638,7 +11095,11 @@
       <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr"/>
       <c r="I221" s="2" t="inlineStr"/>
-      <c r="J221" s="4" t="n"/>
+      <c r="J221" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -10668,7 +11129,11 @@
       <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr"/>
       <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="4" t="n"/>
+      <c r="J222" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -10702,7 +11167,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J223" s="4" t="n"/>
+      <c r="J223" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -11730,7 +12199,16 @@
       </c>
       <c r="H249" s="2" t="inlineStr"/>
       <c r="I249" s="2" t="inlineStr"/>
-      <c r="J249" s="4" t="n"/>
+      <c r="J249" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -11768,7 +12246,16 @@
       </c>
       <c r="H250" s="2" t="inlineStr"/>
       <c r="I250" s="2" t="inlineStr"/>
-      <c r="J250" s="4" t="n"/>
+      <c r="J250" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -11806,7 +12293,11 @@
       </c>
       <c r="H251" s="2" t="inlineStr"/>
       <c r="I251" s="2" t="inlineStr"/>
-      <c r="J251" s="4" t="n"/>
+      <c r="J251" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -11844,7 +12335,11 @@
       </c>
       <c r="H252" s="2" t="inlineStr"/>
       <c r="I252" s="2" t="inlineStr"/>
-      <c r="J252" s="4" t="n"/>
+      <c r="J252" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -11882,7 +12377,11 @@
       </c>
       <c r="H253" s="2" t="inlineStr"/>
       <c r="I253" s="2" t="inlineStr"/>
-      <c r="J253" s="4" t="n"/>
+      <c r="J253" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -11924,7 +12423,16 @@
           <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
-      <c r="J254" s="4" t="n"/>
+      <c r="J254" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -11966,7 +12474,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="J255" s="4" t="n"/>
+      <c r="J255" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -12030,7 +12542,16 @@
       <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr"/>
       <c r="I257" s="2" t="inlineStr"/>
-      <c r="J257" s="4" t="n"/>
+      <c r="J257" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -12064,7 +12585,11 @@
           <t>통증은 없으나 불편할 때 사용</t>
         </is>
       </c>
-      <c r="J258" s="4" t="n"/>
+      <c r="J258" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -12128,7 +12653,11 @@
       <c r="G260" s="2" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr"/>
       <c r="I260" s="2" t="inlineStr"/>
-      <c r="J260" s="4" t="n"/>
+      <c r="J260" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -12158,7 +12687,11 @@
       <c r="G261" s="2" t="inlineStr"/>
       <c r="H261" s="2" t="inlineStr"/>
       <c r="I261" s="2" t="inlineStr"/>
-      <c r="J261" s="4" t="n"/>
+      <c r="J261" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -12192,7 +12725,11 @@
           <t>GCS 15 일때</t>
         </is>
       </c>
-      <c r="J262" s="4" t="n"/>
+      <c r="J262" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -16895,7 +17432,6 @@
           <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" s="6" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
@@ -16932,7 +17468,6 @@
           <t>"쌕쌕거리는 숨소리가 나나요?"</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" s="6" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
@@ -16995,7 +17530,6 @@
       <c r="C6" t="n">
         <v>4010</v>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17006,7 +17540,6 @@
           <t>"가래가 끓는데 잘 못 뱉나요?"</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
@@ -17043,7 +17576,6 @@
           <t>"입술이나 얼굴이 파래 보이나요?"</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" s="6" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
@@ -17080,7 +17612,6 @@
           <t>"손끝·발끝이 파래 보이나요?"</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
@@ -17184,7 +17715,6 @@
       <c r="C11" t="n">
         <v>1664</v>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17221,7 +17751,6 @@
       <c r="C12" t="n">
         <v>1665</v>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17258,7 +17787,6 @@
       <c r="C13" t="n">
         <v>198</v>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17269,7 +17797,6 @@
           <t>"토했나요? 몇 번이나 했나요?"</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" s="6" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
@@ -17306,7 +17833,6 @@
           <t>"메스꺼워 하나요?"</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
@@ -17369,7 +17895,6 @@
       <c r="C16" t="n">
         <v>1726</v>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17380,7 +17905,6 @@
           <t>"입술이 마르거나 눈이 꺼져 보이나요? 울어도 눈물이 안 나나요?"</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" s="6" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
@@ -17402,7 +17926,6 @@
       <c r="C17" t="n">
         <v>972</v>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17413,7 +17936,6 @@
           <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" s="6" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
@@ -17435,7 +17957,6 @@
       <c r="C18" t="n">
         <v>973</v>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17446,7 +17967,6 @@
           <t>"마지막으로 소변 본 게 언제인가요?"</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" s="6" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
@@ -17509,7 +18029,6 @@
       <c r="C20" t="n">
         <v>89</v>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17520,7 +18039,6 @@
           <t>"경련(발작)을 했나요? 얼마나 오래 했나요?"</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" s="6" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
@@ -17542,7 +18060,6 @@
       <c r="C21" t="n">
         <v>88</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17553,7 +18070,6 @@
           <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" s="6" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
@@ -17575,7 +18091,6 @@
       <c r="C22" t="n">
         <v>3176</v>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17586,7 +18101,6 @@
           <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" s="6" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
@@ -17608,7 +18122,6 @@
       <c r="C23" t="n">
         <v>444</v>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17619,7 +18132,6 @@
           <t>"기운이 없어 보이나요?"</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" s="6" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
@@ -17641,7 +18153,6 @@
       <c r="C24" t="n">
         <v>1389</v>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17652,7 +18163,6 @@
           <t>🩺 의식 수준을 확인하세요</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" s="6" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
@@ -17674,7 +18184,6 @@
       <c r="C25" t="n">
         <v>653</v>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17685,7 +18194,6 @@
           <t>🩺 보채는지 관찰하세요</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
       <c r="H25" s="6" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
@@ -17707,7 +18215,6 @@
       <c r="C26" t="n">
         <v>1337</v>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17718,7 +18225,6 @@
           <t>"평소보다 심하게 보채거나 우나요?"</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" s="6" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
@@ -17740,7 +18246,6 @@
       <c r="C27" t="n">
         <v>1339</v>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17751,7 +18256,6 @@
           <t>🩺 울음소리가 우렁찬지 확인하세요</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" s="6" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
@@ -17773,7 +18277,6 @@
       <c r="C28" t="n">
         <v>1447</v>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17784,7 +18287,6 @@
           <t>🩺 자극에 반응해 우는지 확인하세요</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" s="6" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
@@ -17806,7 +18308,6 @@
       <c r="C29" t="n">
         <v>1488</v>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17817,7 +18318,6 @@
           <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" s="6" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
@@ -17839,7 +18339,6 @@
       <c r="C30" t="n">
         <v>1510</v>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17850,7 +18349,6 @@
           <t>"잠을 못 자고 계속 우나요?"</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" s="6" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
@@ -17928,7 +18426,6 @@
           <t>"두드러기가 올라왔나요?"</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" s="6" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
@@ -17965,7 +18462,6 @@
           <t>🩺 기저귀 부위 발진을 확인하세요</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" s="6" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -12542,14 +12542,9 @@
       <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr"/>
       <c r="I257" s="2" t="inlineStr"/>
-      <c r="J257" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="J257" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -17296,18 +17296,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17338,22 +17337,17 @@
       </c>
       <c r="F1" s="5" t="inlineStr">
         <is>
-          <t>질문초안(💬)</t>
+          <t>질문(💬)</t>
         </is>
       </c>
       <c r="G1" s="5" t="inlineStr">
         <is>
-          <t>재사용</t>
+          <t>상태</t>
         </is>
       </c>
       <c r="H1" s="5" t="inlineStr">
         <is>
-          <t>확정(칩스)</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>비고</t>
+          <t>칩스수정</t>
         </is>
       </c>
     </row>
@@ -17388,15 +17382,10 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
-        </is>
-      </c>
-      <c r="H2" s="6" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17427,12 +17416,12 @@
           <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17463,12 +17452,12 @@
           <t>"쌕쌕거리는 숨소리가 나나요?"</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17501,15 +17490,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>"기침이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17525,9 +17509,14 @@
       <c r="C6" t="n">
         <v>4010</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>가래 잘 뱉어냄</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -17535,12 +17524,12 @@
           <t>"가래가 끓는데 잘 못 뱉나요?"</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17571,12 +17560,12 @@
           <t>"입술이나 얼굴이 파래 보이나요?"</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17607,12 +17596,12 @@
           <t>"손끝·발끝이 파래 보이나요?"</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17645,15 +17634,10 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17686,15 +17670,10 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="H10" s="6" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17710,6 +17689,7 @@
       <c r="C11" t="n">
         <v>1664</v>
       </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17722,15 +17702,10 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="H11" s="6" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17746,6 +17721,7 @@
       <c r="C12" t="n">
         <v>1665</v>
       </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17758,15 +17734,10 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17782,9 +17753,14 @@
       <c r="C13" t="n">
         <v>198</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>구토 없음</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -17792,12 +17768,12 @@
           <t>"토했나요? 몇 번이나 했나요?"</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>AI확정 · 형식교정</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17828,12 +17804,12 @@
           <t>"메스꺼워 하나요?"</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17866,15 +17842,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>"설사하셨나요?"</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17884,28 +17855,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>탈수 증상 있음</t>
+          <t>구강건조 있음</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1726</v>
+        <v>2532</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>구강건조 없음</t>
+        </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>"입술이 마르거나 눈이 꺼져 보이나요? 울어도 눈물이 안 나나요?"</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"입술이나 입 안이 말라 있나요?"</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>신규 · 탈수 대체</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17915,28 +17891,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
+          <t>갈증 있음</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>972</v>
+        <v>4091</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>갈증 없음</t>
+        </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
-        </is>
-      </c>
-      <c r="H17" s="6" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"물을 자꾸 찾나요?"</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>신규 · 탈수 대체</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17946,12 +17927,13 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>소변량 없음</t>
+          <t>피부 탄력성 저하됨</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>973</v>
-      </c>
+        <v>1784</v>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17959,15 +17941,15 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>"마지막으로 소변 본 게 언제인가요?"</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>🩺 배나 팔 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>신규 · 탈수 대체</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17977,69 +17959,65 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>복부 통증 있음</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1988</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>복부 통증 없음</t>
-        </is>
-      </c>
+        <v>972</v>
+      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>"배가 아프다고 하나요?"</t>
+          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>"배가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>신경·의식</t>
+          <t>소화·탈수</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>경련 있음</t>
+          <t>복부 통증 있음</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>89</v>
+        <v>1988</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>복부 통증 없음</t>
+        </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>"경련(발작)을 했나요? 얼마나 오래 했나요?"</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"배가 아프다고 하나요?"</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18049,12 +18027,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>경련과 유사한 증상 보임</t>
+          <t>경련 있음</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>88</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18062,15 +18041,15 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"경련(발작)을 했나요? 얼마나 오래 했나요?"</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18080,12 +18059,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lethargy 상태임</t>
+          <t>경련과 유사한 증상 보임</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3176</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18093,15 +18073,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
-        </is>
-      </c>
-      <c r="H22" s="6" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18111,28 +18091,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>무기력 호소함</t>
+          <t>lethargy 상태임</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>444</v>
+        <v>3176</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>의식 명료함</t>
+        </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>"기운이 없어 보이나요?"</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>AI확정 · 형식교정</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18142,28 +18127,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>의식수준 저하됨</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1389</v>
-      </c>
+          <t>울음소리 좋음 / 자극 주면 울음 / 반응 없음</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1339 / 1447 / 482</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>🩺 의식 수준을 확인하세요</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>🩺 아이 반응 정도 — [울음소리 좋음] [자극 주면 울음] [반응 없음]</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>신규 · 3단계</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18179,9 +18167,14 @@
       <c r="C25" t="n">
         <v>653</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>보채지 않음</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -18189,12 +18182,12 @@
           <t>🩺 보채는지 관찰하세요</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>AI확정 · 형식교정</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18210,6 +18203,7 @@
       <c r="C26" t="n">
         <v>1337</v>
       </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18220,12 +18214,12 @@
           <t>"평소보다 심하게 보채거나 우나요?"</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18235,12 +18229,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>울음소리 좋음</t>
+          <t>자주 사지 움직이며 보챔</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1339</v>
-      </c>
+        <v>1488</v>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18248,15 +18243,15 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>🩺 울음소리가 우렁찬지 확인하세요</t>
-        </is>
-      </c>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18266,12 +18261,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>자극 주면 울음</t>
+          <t>잠 안자고 울고 보챔</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1447</v>
-      </c>
+        <v>1510</v>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18279,15 +18275,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>🩺 자극에 반응해 우는지 확인하세요</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"잠을 못 자고 계속 우나요?"</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -18297,77 +18293,87 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>자주 사지 움직이며 보챔</t>
+          <t>통증 있음</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1488</v>
+        <v>1740</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>통증 없음</t>
+        </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
-        </is>
-      </c>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"어디가 아프다고 하나요?"</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>행동·통증</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>잠 안자고 울고 보챔</t>
+          <t>urticaria 있음</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1510</v>
+        <v>4287</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>urticaria 없음</t>
+        </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>"잠을 못 자고 계속 우나요?"</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>행동·통증</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>통증 있음</t>
+          <t>기저귀 발진 있음</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1740</v>
+        <v>250</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>통증 없음</t>
+          <t>기저귀 발진 없음</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -18377,92 +18383,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>"어디가 아프다고 하나요?"</t>
+          <t>🩺 기저귀 부위 발진을 확인하세요</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>"통증이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>피부</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>urticaria 있음</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>4287</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>urticaria 없음</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>"두드러기가 올라왔나요?"</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>피부</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>기저귀 발진 있음</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>250</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>기저귀 발진 없음</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>🩺 기저귀 부위 발진을 확인하세요</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>⚠️ 초안 — 칩스 확정 필요</t>
-        </is>
-      </c>
+          <t>AI확정</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.도관" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.낙상교육" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소아_질문초안(미확정)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.마무리질문" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1991,7 +1992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K354"/>
+  <dimension ref="A1:K348"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -9145,33 +9146,28 @@
       </c>
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>불편감 있음/없음</t>
+          <t>통증 있음</t>
         </is>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>"불편하신 부분이 있으세요?"</t>
+          <t>"통증이 있으세요?"</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr"/>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
-        </is>
-      </c>
-      <c r="J173" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J173" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -9188,36 +9184,24 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>통증 있음</t>
-        </is>
-      </c>
-      <c r="F174" s="2" t="inlineStr">
-        <is>
-          <t>"통증이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr"/>
-      <c r="I174" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J174" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -9238,11 +9222,11 @@
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="F175" s="2" t="inlineStr"/>
@@ -9251,7 +9235,7 @@
       <c r="I175" s="2" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -9268,24 +9252,24 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr"/>
       <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr"/>
       <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="J176" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -9306,11 +9290,11 @@
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>출혈 양상 확인함</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr"/>
@@ -9340,11 +9324,11 @@
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
-          <t>출혈 양상 확인함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr"/>
@@ -9353,7 +9337,7 @@
       <c r="I178" s="2" t="inlineStr"/>
       <c r="J178" s="7" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -9374,11 +9358,11 @@
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E179" s="2" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="F179" s="2" t="inlineStr"/>
@@ -9408,17 +9392,21 @@
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr"/>
       <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr"/>
-      <c r="I180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J180" s="7" t="inlineStr">
         <is>
           <t>급성통증</t>
@@ -9428,38 +9416,42 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>출혈(눈에 보이는 출혈양상)</t>
+          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>질 출혈-통증 있음</t>
+          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)- 통증없음</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr"/>
-      <c r="G181" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H181" s="2" t="inlineStr"/>
-      <c r="I181" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J181" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -9480,16 +9472,16 @@
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
         </is>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오심이나 구토가 있으세요?"</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
@@ -9498,7 +9490,11 @@
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr"/>
-      <c r="I182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
+        </is>
+      </c>
       <c r="J182" t="inlineStr">
         <is>
           <t>출혈</t>
@@ -9522,29 +9518,25 @@
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>출혈 있음</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>"출혈이 있으세요?"</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr"/>
-      <c r="I183" s="2" t="inlineStr">
-        <is>
-          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
-        </is>
-      </c>
+      <c r="I183" s="2" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
           <t>출혈</t>
@@ -9564,27 +9556,19 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>출혈 있음</t>
-        </is>
-      </c>
-      <c r="F184" s="2" t="inlineStr">
-        <is>
-          <t>"출혈이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G184" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr"/>
       <c r="H184" s="2" t="inlineStr"/>
       <c r="I184" s="2" t="inlineStr"/>
       <c r="J184" t="inlineStr">
@@ -9606,7 +9590,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
@@ -9614,7 +9598,7 @@
       </c>
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="F185" s="2" t="inlineStr"/>
@@ -9644,17 +9628,21 @@
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>출혈 양상 확인함</t>
         </is>
       </c>
       <c r="F186" s="2" t="inlineStr"/>
       <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr"/>
-      <c r="I186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J186" t="inlineStr">
         <is>
           <t>출혈</t>
@@ -9669,33 +9657,42 @@
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)- 통증없음</t>
+          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)- 통증있음</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>출혈 양상 확인함</t>
-        </is>
-      </c>
-      <c r="F187" s="2" t="inlineStr"/>
-      <c r="G187" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H187" s="2" t="inlineStr"/>
-      <c r="I187" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>출혈</t>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
         </is>
       </c>
     </row>
@@ -9716,16 +9713,16 @@
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
         </is>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오심이나 구토가 있으세요?"</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
@@ -9734,7 +9731,11 @@
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
-      <c r="I188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
+        </is>
+      </c>
       <c r="J188" s="6" t="inlineStr">
         <is>
           <t>공통</t>
@@ -9763,37 +9764,28 @@
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>출혈 있음</t>
         </is>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>"출혈이 있으세요?"</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr"/>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
-        </is>
-      </c>
-      <c r="J189" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="I189" s="2" t="inlineStr"/>
+      <c r="J189" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -9814,16 +9806,16 @@
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>출혈 있음</t>
+          <t>통증 있음</t>
         </is>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>"출혈이 있으세요?"</t>
+          <t>"통증이 있으세요?"</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
@@ -9832,10 +9824,14 @@
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr"/>
-      <c r="I190" s="2" t="inlineStr"/>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="J190" s="7" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -9852,41 +9848,24 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E191" s="2" t="inlineStr">
         <is>
-          <t>불편감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F191" s="2" t="inlineStr">
-        <is>
-          <t>"불편하신 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr"/>
-      <c r="I191" s="2" t="inlineStr">
-        <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
-        </is>
-      </c>
-      <c r="J191" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="I191" s="2" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -9903,34 +9882,22 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E192" s="2" t="inlineStr">
         <is>
-          <t>통증 있음</t>
-        </is>
-      </c>
-      <c r="F192" s="2" t="inlineStr">
-        <is>
-          <t>"통증이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr"/>
-      <c r="I192" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J192" s="7" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>
@@ -9949,7 +9916,7 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
@@ -9957,14 +9924,14 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr"/>
       <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr"/>
       <c r="I193" s="2" t="inlineStr"/>
-      <c r="J193" t="inlineStr">
+      <c r="J193" s="7" t="inlineStr">
         <is>
           <t>출혈</t>
         </is>
@@ -9983,7 +9950,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
@@ -9991,16 +9958,16 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈 양상 확인함</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr"/>
       <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr"/>
       <c r="I194" s="2" t="inlineStr"/>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="J194" s="7" t="inlineStr">
+        <is>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -10021,11 +9988,11 @@
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr"/>
@@ -10034,7 +10001,7 @@
       <c r="I195" s="2" t="inlineStr"/>
       <c r="J195" s="7" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -10055,11 +10022,11 @@
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>출혈 양상 확인함</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr"/>
@@ -10068,7 +10035,7 @@
       <c r="I196" s="2" t="inlineStr"/>
       <c r="J196" s="7" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -10089,17 +10056,21 @@
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr"/>
       <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr"/>
-      <c r="I197" s="2" t="inlineStr"/>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J197" s="7" t="inlineStr">
         <is>
           <t>급성통증</t>
@@ -10109,72 +10080,88 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)</t>
+          <t>출혈위험(눈에 보이지 않지만 Hemoglobin 낮거나 과거 출혈 경향 있을떄</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)- 통증있음</t>
+          <t>출혈위험 - 통증 없음</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
-        </is>
-      </c>
-      <c r="F198" s="2" t="inlineStr"/>
-      <c r="G198" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="inlineStr"/>
       <c r="I198" s="2" t="inlineStr"/>
-      <c r="J198" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)</t>
+          <t>출혈위험(눈에 보이지 않지만 Hemoglobin 낮거나 과거 출혈 경향 있을떄</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)- 통증있음</t>
+          <t>출혈위험 - 통증 없음</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F199" s="2" t="inlineStr"/>
-      <c r="G199" s="2" t="inlineStr"/>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>"오심이나 구토가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr"/>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J199" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
         </is>
       </c>
     </row>
@@ -10195,25 +10182,29 @@
         </is>
       </c>
       <c r="D200" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>출혈 없음</t>
         </is>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"눈에 보이는 출혈은 없으신가요?"</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr"/>
-      <c r="I200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>헤모글로빈 수치 낮을시</t>
+        </is>
+      </c>
       <c r="J200" t="inlineStr">
         <is>
           <t>출혈위험</t>
@@ -10237,27 +10228,27 @@
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>혈중 hemoglobin 수치 정상 이하임</t>
         </is>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>혈중 Hemoglobin 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr"/>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
+          <t>혈소판 수치 낮을시</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
@@ -10283,16 +10274,16 @@
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E202" s="2" t="inlineStr">
         <is>
-          <t>출혈 없음</t>
+          <t>혈소판 수치 감소함</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>"눈에 보이는 출혈은 없으신가요?"</t>
+          <t>혈소판 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
@@ -10303,7 +10294,7 @@
       <c r="H202" s="2" t="inlineStr"/>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>헤모글로빈 수치 낮을시</t>
+          <t>INR 수치 정상보다 높을시(1.5이상?)</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
@@ -10329,29 +10320,25 @@
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E203" s="2" t="inlineStr">
         <is>
-          <t>혈중 hemoglobin 수치 정상 이하임</t>
+          <t>INR :</t>
         </is>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>혈중 Hemoglobin 수치를 확인하세요</t>
+          <t>INR 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr"/>
-      <c r="I203" s="2" t="inlineStr">
-        <is>
-          <t>혈소판 수치 낮을시</t>
-        </is>
-      </c>
+      <c r="I203" s="2" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>출혈위험</t>
@@ -10371,33 +10358,21 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D204" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E204" s="2" t="inlineStr">
         <is>
-          <t>혈소판 수치 감소함</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>혈소판 수치를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>출혈위험</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr"/>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>INR 수치 정상보다 높을시(1.5이상?)</t>
-        </is>
-      </c>
+      <c r="I204" s="2" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>출혈위험</t>
@@ -10417,27 +10392,19 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>INR :</t>
-        </is>
-      </c>
-      <c r="F205" s="2" t="inlineStr">
-        <is>
-          <t>INR 수치를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>값입력</t>
-        </is>
-      </c>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr"/>
       <c r="H205" s="2" t="inlineStr"/>
       <c r="I205" s="2" t="inlineStr"/>
       <c r="J205" t="inlineStr">
@@ -10459,21 +10426,25 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D206" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>출혈위험</t>
+          <t>출혈 양상 확인함</t>
         </is>
       </c>
       <c r="F206" s="2" t="inlineStr"/>
       <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr"/>
-      <c r="I206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J206" t="inlineStr">
         <is>
           <t>출혈위험</t>
@@ -10488,12 +10459,12 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>출혈위험 - 통증 없음</t>
+          <t>출혈위험-통증 있음</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D207" s="2" t="n">
@@ -10501,16 +10472,29 @@
       </c>
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="F207" s="2" t="inlineStr"/>
-      <c r="G207" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H207" s="2" t="inlineStr"/>
       <c r="I207" s="2" t="inlineStr"/>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>출혈위험</t>
+      <c r="J207" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
         </is>
       </c>
     </row>
@@ -10522,12 +10506,12 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>출혈위험 - 통증 없음</t>
+          <t>출혈위험-통증 있음</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D208" s="2" t="n">
@@ -10535,20 +10519,33 @@
       </c>
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>출혈 양상 확인함</t>
-        </is>
-      </c>
-      <c r="F208" s="2" t="inlineStr"/>
-      <c r="G208" s="2" t="inlineStr"/>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>"오심이나 구토가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H208" s="2" t="inlineStr"/>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J208" t="inlineStr">
-        <is>
-          <t>출혈위험</t>
+          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
+        </is>
+      </c>
+      <c r="J208" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
         </is>
       </c>
     </row>
@@ -10569,33 +10566,32 @@
         </is>
       </c>
       <c r="D209" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>출혈없음</t>
         </is>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"눈에 보이는 출혈은 없으신가요?"</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr"/>
-      <c r="I209" s="2" t="inlineStr"/>
-      <c r="J209" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>헤모글로빈 수치 낮을시</t>
+        </is>
+      </c>
+      <c r="J209" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
         </is>
       </c>
     </row>
@@ -10616,37 +10612,32 @@
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>혈중 hemoglobin 수치 정상 이하임</t>
         </is>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>혈중 Hemoglobin 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>출혈위치, 시작시간, 횟수 post note에 작성, 그림첨부(출혈 양상 실물, 폰사진 있을 시)</t>
-        </is>
-      </c>
-      <c r="J210" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+          <t>혈소판 수치 낮을시</t>
+        </is>
+      </c>
+      <c r="J210" s="7" t="inlineStr">
+        <is>
+          <t>출혈위험</t>
         </is>
       </c>
     </row>
@@ -10667,16 +10658,16 @@
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>출혈없음</t>
+          <t>혈소판 수치 감소함</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>"눈에 보이는 출혈은 없으신가요?"</t>
+          <t>혈소판 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G211" s="2" t="inlineStr">
@@ -10687,7 +10678,7 @@
       <c r="H211" s="2" t="inlineStr"/>
       <c r="I211" s="2" t="inlineStr">
         <is>
-          <t>헤모글로빈 수치 낮을시</t>
+          <t>INR 수치 정상보다 높을시(1.5이상?)</t>
         </is>
       </c>
       <c r="J211" s="7" t="inlineStr">
@@ -10713,29 +10704,25 @@
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>혈중 hemoglobin 수치 정상 이하임</t>
+          <t>INR :</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>혈중 Hemoglobin 수치를 확인하세요</t>
+          <t>INR 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
-      <c r="I212" s="2" t="inlineStr">
-        <is>
-          <t>혈소판 수치 낮을시</t>
-        </is>
-      </c>
+      <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="7" t="inlineStr">
         <is>
           <t>출혈위험</t>
@@ -10759,16 +10746,16 @@
         </is>
       </c>
       <c r="D213" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>혈소판 수치 감소함</t>
+          <t>통증 있음</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
-          <t>혈소판 수치를 확인하세요</t>
+          <t>"통증이 있으세요?"</t>
         </is>
       </c>
       <c r="G213" s="2" t="inlineStr">
@@ -10779,12 +10766,12 @@
       <c r="H213" s="2" t="inlineStr"/>
       <c r="I213" s="2" t="inlineStr">
         <is>
-          <t>INR 수치 정상보다 높을시(1.5이상?)</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J213" s="7" t="inlineStr">
         <is>
-          <t>출혈위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -10801,30 +10788,22 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D214" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>INR :</t>
-        </is>
-      </c>
-      <c r="F214" s="2" t="inlineStr">
-        <is>
-          <t>INR 수치를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>값입력</t>
-        </is>
-      </c>
+          <t>출혈위험</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr"/>
       <c r="H214" s="2" t="inlineStr"/>
       <c r="I214" s="2" t="inlineStr"/>
-      <c r="J214" s="7" t="inlineStr">
+      <c r="J214" t="inlineStr">
         <is>
           <t>출혈위험</t>
         </is>
@@ -10843,41 +10822,24 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>불편감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F215" s="2" t="inlineStr">
-        <is>
-          <t>"불편하신 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr"/>
       <c r="H215" s="2" t="inlineStr"/>
-      <c r="I215" s="2" t="inlineStr">
-        <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
-        </is>
-      </c>
-      <c r="J215" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -10894,36 +10856,24 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>통증 있음</t>
-        </is>
-      </c>
-      <c r="F216" s="2" t="inlineStr">
-        <is>
-          <t>"통증이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr"/>
       <c r="H216" s="2" t="inlineStr"/>
-      <c r="I216" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I216" s="2" t="inlineStr"/>
       <c r="J216" s="7" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈위험</t>
         </is>
       </c>
     </row>
@@ -10940,22 +10890,26 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>출혈위험</t>
+          <t>출혈 양상 확인함</t>
         </is>
       </c>
       <c r="F217" s="2" t="inlineStr"/>
       <c r="G217" s="2" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr"/>
-      <c r="I217" s="2" t="inlineStr"/>
-      <c r="J217" t="inlineStr">
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>통증은 없으나 불편할 때 사용</t>
+        </is>
+      </c>
+      <c r="J217" s="7" t="inlineStr">
         <is>
           <t>출혈위험</t>
         </is>
@@ -10974,22 +10928,22 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D218" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="F218" s="2" t="inlineStr"/>
       <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr"/>
       <c r="I218" s="2" t="inlineStr"/>
-      <c r="J218" t="inlineStr">
+      <c r="J218" s="7" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>
@@ -11012,11 +10966,11 @@
         </is>
       </c>
       <c r="D219" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="F219" s="2" t="inlineStr"/>
@@ -11025,7 +10979,7 @@
       <c r="I219" s="2" t="inlineStr"/>
       <c r="J219" s="7" t="inlineStr">
         <is>
-          <t>출혈위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -11046,11 +11000,11 @@
         </is>
       </c>
       <c r="D220" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E220" s="2" t="inlineStr">
         <is>
-          <t>출혈 양상 확인함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="F220" s="2" t="inlineStr"/>
@@ -11058,118 +11012,138 @@
       <c r="H220" s="2" t="inlineStr"/>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>통증은 없으나 불편할 때 사용</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J220" s="7" t="inlineStr">
         <is>
-          <t>출혈위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>출혈위험(눈에 보이지 않지만 Hemoglobin 낮거나 과거 출혈 경향 있을떄</t>
+          <t>감염</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>출혈위험-통증 있음</t>
+          <t>CRP 수치 정상 이상일때</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D221" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E221" s="2" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
-        </is>
-      </c>
-      <c r="F221" s="2" t="inlineStr"/>
-      <c r="G221" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H221" s="2" t="inlineStr"/>
       <c r="I221" s="2" t="inlineStr"/>
-      <c r="J221" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>감염</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>출혈위험(눈에 보이지 않지만 Hemoglobin 낮거나 과거 출혈 경향 있을떄</t>
+          <t>감염</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>출혈위험-통증 있음</t>
+          <t>CRP 수치 정상 이상일때</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D222" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E222" s="2" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr"/>
-      <c r="G222" s="2" t="inlineStr"/>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>"오심이나 구토가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H222" s="2" t="inlineStr"/>
       <c r="I222" s="2" t="inlineStr"/>
-      <c r="J222" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>감염</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>출혈위험(눈에 보이지 않지만 Hemoglobin 낮거나 과거 출혈 경향 있을떄</t>
+          <t>감염</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>출혈위험-통증 있음</t>
+          <t>CRP 수치 정상 이상일때</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D223" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F223" s="2" t="inlineStr"/>
-      <c r="G223" s="2" t="inlineStr"/>
+          <t>열감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H223" s="2" t="inlineStr"/>
-      <c r="I223" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J223" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="I223" s="2" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>감염</t>
         </is>
       </c>
     </row>
@@ -11190,16 +11164,16 @@
         </is>
       </c>
       <c r="D224" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
@@ -11232,21 +11206,21 @@
         </is>
       </c>
       <c r="D225" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>C-reactive protein 수치 증가함</t>
         </is>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>CRP 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr"/>
@@ -11270,27 +11244,19 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D226" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F226" s="2" t="inlineStr">
-        <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
-        </is>
-      </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>감염</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr"/>
       <c r="I226" s="2" t="inlineStr"/>
       <c r="J226" t="inlineStr">
@@ -11312,27 +11278,19 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D227" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
-        </is>
-      </c>
-      <c r="F227" s="2" t="inlineStr">
-        <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr"/>
       <c r="I227" s="2" t="inlineStr"/>
       <c r="J227" t="inlineStr">
@@ -11354,29 +11312,25 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D228" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>C-reactive protein 수치 증가함</t>
-        </is>
-      </c>
-      <c r="F228" s="2" t="inlineStr">
-        <is>
-          <t>CRP 수치를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr"/>
-      <c r="I228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J228" t="inlineStr">
         <is>
           <t>감염</t>
@@ -11386,17 +11340,17 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>CRP 수치 정상 이상일때</t>
+          <t>CRP 수치 모를때, 감염 위험성 있을떄(배액관, 있을때, 열감 있을 떄)</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D229" s="2" t="n">
@@ -11404,88 +11358,108 @@
       </c>
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>감염</t>
-        </is>
-      </c>
-      <c r="F229" s="2" t="inlineStr"/>
-      <c r="G229" s="2" t="inlineStr"/>
+          <t>Foley catheter 유지중임</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Foley catheter 삽입 여부를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H229" s="2" t="inlineStr"/>
       <c r="I229" s="2" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>CRP 수치 정상 이상일때</t>
+          <t>CRP 수치 모를때, 감염 위험성 있을떄(배액관, 있을때, 열감 있을 떄)</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D230" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="F230" s="2" t="inlineStr"/>
-      <c r="G230" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H230" s="2" t="inlineStr"/>
       <c r="I230" s="2" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>CRP 수치 정상 이상일때</t>
+          <t>CRP 수치 모를때, 감염 위험성 있을떄(배액관, 있을때, 열감 있을 떄)</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D231" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E231" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
-        </is>
-      </c>
-      <c r="F231" s="2" t="inlineStr"/>
-      <c r="G231" s="2" t="inlineStr"/>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>"오심이나 구토가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H231" s="2" t="inlineStr"/>
-      <c r="I231" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
+      <c r="I231" s="2" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -11506,21 +11480,21 @@
         </is>
       </c>
       <c r="D232" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Foley catheter 유지중임</t>
+          <t>열감 있음/없음</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Foley catheter 삽입 여부를 확인하세요</t>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -11548,16 +11522,16 @@
         </is>
       </c>
       <c r="D233" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -11586,27 +11560,19 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D234" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
-        </is>
-      </c>
-      <c r="F234" s="2" t="inlineStr">
-        <is>
-          <t>"오심이나 구토가 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr"/>
       <c r="I234" s="2" t="inlineStr"/>
       <c r="J234" t="inlineStr">
@@ -11628,27 +11594,19 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D235" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F235" s="2" t="inlineStr">
-        <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
-        </is>
-      </c>
-      <c r="G235" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr"/>
       <c r="H235" s="2" t="inlineStr"/>
       <c r="I235" s="2" t="inlineStr"/>
       <c r="J235" t="inlineStr">
@@ -11670,29 +11628,25 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D236" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr"/>
       <c r="H236" s="2" t="inlineStr"/>
-      <c r="I236" s="2" t="inlineStr"/>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J236" t="inlineStr">
         <is>
           <t>감염위험</t>
@@ -11702,17 +11656,17 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>CRP 수치 모를때, 감염 위험성 있을떄(배액관, 있을때, 열감 있을 떄)</t>
+          <t>고체온+통증없음</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D237" s="2" t="n">
@@ -11720,88 +11674,108 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
-        </is>
-      </c>
-      <c r="F237" s="2" t="inlineStr"/>
-      <c r="G237" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H237" s="2" t="inlineStr"/>
       <c r="I237" s="2" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>감염</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>CRP 수치 모를때, 감염 위험성 있을떄(배액관, 있을때, 열감 있을 떄)</t>
+          <t>고체온+통증없음</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="F238" s="2" t="inlineStr"/>
-      <c r="G238" s="2" t="inlineStr"/>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>"오심이나 구토가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H238" s="2" t="inlineStr"/>
       <c r="I238" s="2" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>감염</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>CRP 수치 모를때, 감염 위험성 있을떄(배액관, 있을때, 열감 있을 떄)</t>
+          <t>고체온+통증없음</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D239" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
-        </is>
-      </c>
-      <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
+          <t>열감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H239" s="2" t="inlineStr"/>
-      <c r="I239" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
+      <c r="I239" s="2" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>감염</t>
         </is>
       </c>
     </row>
@@ -11822,16 +11796,16 @@
         </is>
       </c>
       <c r="D240" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -11864,21 +11838,21 @@
         </is>
       </c>
       <c r="D241" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>통증 없음</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>"통증은 없으신가요?"</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr"/>
@@ -11906,21 +11880,21 @@
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
+          <t>체온 상승함</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+          <t>체온을 측정하세요</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr"/>
@@ -11944,27 +11918,19 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D243" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
-        </is>
-      </c>
-      <c r="F243" s="2" t="inlineStr">
-        <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>감염</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr"/>
       <c r="I243" s="2" t="inlineStr"/>
       <c r="J243" t="inlineStr">
@@ -11986,27 +11952,19 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D244" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>통증 없음</t>
-        </is>
-      </c>
-      <c r="F244" s="2" t="inlineStr">
-        <is>
-          <t>"통증은 없으신가요?"</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr"/>
       <c r="H244" s="2" t="inlineStr"/>
       <c r="I244" s="2" t="inlineStr"/>
       <c r="J244" t="inlineStr">
@@ -12028,29 +11986,25 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D245" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>체온 상승함</t>
-        </is>
-      </c>
-      <c r="F245" s="2" t="inlineStr">
-        <is>
-          <t>체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr"/>
-      <c r="I245" s="2" t="inlineStr"/>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J245" t="inlineStr">
         <is>
           <t>감염</t>
@@ -12065,12 +12019,12 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증없음</t>
+          <t>고체온+통증 있음</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D246" s="2" t="n">
@@ -12078,16 +12032,29 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>감염</t>
-        </is>
-      </c>
-      <c r="F246" s="2" t="inlineStr"/>
-      <c r="G246" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H246" s="2" t="inlineStr"/>
       <c r="I246" s="2" t="inlineStr"/>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>감염</t>
+      <c r="J246" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
         </is>
       </c>
     </row>
@@ -12099,29 +12066,42 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증없음</t>
+          <t>고체온+통증 있음</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D247" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="F247" s="2" t="inlineStr"/>
-      <c r="G247" s="2" t="inlineStr"/>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>"오심이나 구토가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H247" s="2" t="inlineStr"/>
       <c r="I247" s="2" t="inlineStr"/>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>감염</t>
+      <c r="J247" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
         </is>
       </c>
     </row>
@@ -12133,33 +12113,37 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증없음</t>
+          <t>고체온+통증 있음</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D248" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
-        </is>
-      </c>
-      <c r="F248" s="2" t="inlineStr"/>
-      <c r="G248" s="2" t="inlineStr"/>
+          <t>열감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H248" s="2" t="inlineStr"/>
-      <c r="I248" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>감염</t>
+      <c r="I248" s="2" t="inlineStr"/>
+      <c r="J248" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12180,16 +12164,16 @@
         </is>
       </c>
       <c r="D249" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -12199,14 +12183,9 @@
       </c>
       <c r="H249" s="2" t="inlineStr"/>
       <c r="I249" s="2" t="inlineStr"/>
-      <c r="J249" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="J249" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12227,33 +12206,28 @@
         </is>
       </c>
       <c r="D250" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>체온 상승함</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>체온을 측정하세요</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr"/>
       <c r="I250" s="2" t="inlineStr"/>
-      <c r="J250" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="J250" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12274,28 +12248,32 @@
         </is>
       </c>
       <c r="D251" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
+          <t>통증 있음</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+          <t>"통증이 있으세요?"</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr"/>
-      <c r="I251" s="2" t="inlineStr"/>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="J251" s="7" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -12312,30 +12290,22 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D252" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
-        </is>
-      </c>
-      <c r="F252" s="2" t="inlineStr">
-        <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G252" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>고체온</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr"/>
+      <c r="G252" s="2" t="inlineStr"/>
       <c r="H252" s="2" t="inlineStr"/>
       <c r="I252" s="2" t="inlineStr"/>
-      <c r="J252" s="7" t="inlineStr">
+      <c r="J252" t="inlineStr">
         <is>
           <t>고체온</t>
         </is>
@@ -12354,27 +12324,19 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D253" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>체온 상승함</t>
-        </is>
-      </c>
-      <c r="F253" s="2" t="inlineStr">
-        <is>
-          <t>체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="G253" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr"/>
       <c r="H253" s="2" t="inlineStr"/>
       <c r="I253" s="2" t="inlineStr"/>
       <c r="J253" s="7" t="inlineStr">
@@ -12396,41 +12358,28 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D254" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>불편감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>"불편하신 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr"/>
+      <c r="G254" s="2" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr"/>
       <c r="I254" s="2" t="inlineStr">
         <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
-        </is>
-      </c>
-      <c r="J254" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+          <t>통증은 없으나 불편할 때 사용</t>
+        </is>
+      </c>
+      <c r="J254" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12447,34 +12396,22 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D255" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>통증 있음</t>
-        </is>
-      </c>
-      <c r="F255" s="2" t="inlineStr">
-        <is>
-          <t>"통증이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G255" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr"/>
       <c r="H255" s="2" t="inlineStr"/>
-      <c r="I255" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J255" s="7" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr"/>
+      <c r="J255" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>
@@ -12493,24 +12430,24 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D256" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr"/>
       <c r="I256" s="2" t="inlineStr"/>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>고체온</t>
+      <c r="J256" s="7" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -12531,11 +12468,11 @@
         </is>
       </c>
       <c r="D257" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr"/>
@@ -12544,7 +12481,7 @@
       <c r="I257" s="2" t="inlineStr"/>
       <c r="J257" s="7" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -12565,11 +12502,11 @@
         </is>
       </c>
       <c r="D258" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr"/>
@@ -12577,152 +12514,196 @@
       <c r="H258" s="2" t="inlineStr"/>
       <c r="I258" s="2" t="inlineStr">
         <is>
-          <t>통증은 없으나 불편할 때 사용</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J258" s="7" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증 있음</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D259" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-      <c r="F259" s="2" t="inlineStr"/>
-      <c r="G259" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H259" s="2" t="inlineStr"/>
-      <c r="I259" s="2" t="inlineStr"/>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+        </is>
+      </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>저체온</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증 있음</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D260" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
-        </is>
-      </c>
-      <c r="F260" s="2" t="inlineStr"/>
-      <c r="G260" s="2" t="inlineStr"/>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
       <c r="H260" s="2" t="inlineStr"/>
-      <c r="I260" s="2" t="inlineStr"/>
-      <c r="J260" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>저체온</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증 있음</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D261" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
-        </is>
-      </c>
-      <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" s="2" t="inlineStr"/>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H261" s="2" t="inlineStr"/>
-      <c r="I261" s="2" t="inlineStr"/>
-      <c r="J261" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>저체온</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증 있음</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D262" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F262" s="2" t="inlineStr"/>
-      <c r="G262" s="2" t="inlineStr"/>
+          <t>감각이상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H262" s="2" t="inlineStr"/>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J262" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>저체온</t>
         </is>
       </c>
     </row>
@@ -12743,16 +12724,16 @@
         </is>
       </c>
       <c r="D263" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>grasp power 강함/약함</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"양손으로 꽉 쥐어보세요" — 근력 확인</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -12763,7 +12744,7 @@
       <c r="H263" s="2" t="inlineStr"/>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>쳉ㅗㄴ 하강</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -12789,27 +12770,27 @@
         </is>
       </c>
       <c r="D264" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>체온 하강함</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>체온을 측정하세요</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -12831,33 +12812,21 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D265" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
-        </is>
-      </c>
-      <c r="F265" s="2" t="inlineStr">
-        <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
-        </is>
-      </c>
-      <c r="G265" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>저체온</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr"/>
+      <c r="G265" s="2" t="inlineStr"/>
       <c r="H265" s="2" t="inlineStr"/>
-      <c r="I265" s="2" t="inlineStr">
-        <is>
-          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
-        </is>
-      </c>
+      <c r="I265" s="2" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>저체온</t>
@@ -12877,33 +12846,21 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D266" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음/없음</t>
-        </is>
-      </c>
-      <c r="F266" s="2" t="inlineStr">
-        <is>
-          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G266" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>저체온의 초기 증상에 대해 설명함</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr"/>
+      <c r="G266" s="2" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr"/>
-      <c r="I266" s="2" t="inlineStr">
-        <is>
-          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
-        </is>
-      </c>
+      <c r="I266" s="2" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
           <t>저체온</t>
@@ -12923,33 +12880,21 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D267" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함/약함</t>
-        </is>
-      </c>
-      <c r="F267" s="2" t="inlineStr">
-        <is>
-          <t>"양손으로 꽉 쥐어보세요" — 근력 확인</t>
-        </is>
-      </c>
-      <c r="G267" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr"/>
+      <c r="G267" s="2" t="inlineStr"/>
       <c r="H267" s="2" t="inlineStr"/>
-      <c r="I267" s="2" t="inlineStr">
-        <is>
-          <t>쳉ㅗㄴ 하강</t>
-        </is>
-      </c>
+      <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>저체온</t>
@@ -12969,31 +12914,23 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D268" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>체온 하강함</t>
-        </is>
-      </c>
-      <c r="F268" s="2" t="inlineStr">
-        <is>
-          <t>체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="G268" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>따뜻한 환경 제공함</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr"/>
+      <c r="G268" s="2" t="inlineStr"/>
       <c r="H268" s="2" t="inlineStr"/>
       <c r="I268" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
@@ -13015,21 +12952,25 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D269" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>사지 근력 평가함</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr"/>
       <c r="G269" s="2" t="inlineStr"/>
       <c r="H269" s="2" t="inlineStr"/>
-      <c r="I269" s="2" t="inlineStr"/>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J269" t="inlineStr">
         <is>
           <t>저체온</t>
@@ -13039,17 +12980,17 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색/뇌출혈 의심</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색뇌출혈 관련</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D270" s="2" t="n">
@@ -13057,33 +12998,45 @@
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>저체온의 초기 증상에 대해 설명함</t>
-        </is>
-      </c>
-      <c r="F270" s="2" t="inlineStr"/>
-      <c r="G270" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H270" s="2" t="inlineStr"/>
-      <c r="I270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+        </is>
+      </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색/뇌출혈 의심</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색뇌출혈 관련</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D271" s="2" t="n">
@@ -13091,33 +13044,45 @@
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
-        </is>
-      </c>
-      <c r="F271" s="2" t="inlineStr"/>
-      <c r="G271" s="2" t="inlineStr"/>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
       <c r="H271" s="2" t="inlineStr"/>
-      <c r="I271" s="2" t="inlineStr"/>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+        </is>
+      </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색/뇌출혈 의심</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색뇌출혈 관련</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D272" s="2" t="n">
@@ -13125,37 +13090,45 @@
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>따뜻한 환경 제공함</t>
-        </is>
-      </c>
-      <c r="F272" s="2" t="inlineStr"/>
-      <c r="G272" s="2" t="inlineStr"/>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H272" s="2" t="inlineStr"/>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색/뇌출혈 의심</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색뇌출혈 관련</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D273" s="2" t="n">
@@ -13163,20 +13136,28 @@
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="F273" s="2" t="inlineStr"/>
-      <c r="G273" s="2" t="inlineStr"/>
+          <t>감각이상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H273" s="2" t="inlineStr"/>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -13197,16 +13178,16 @@
         </is>
       </c>
       <c r="D274" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>grasp power 강함/약함</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"양손으로 꽉 쥐어보세요" — 근력 확인</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -13217,7 +13198,7 @@
       <c r="H274" s="2" t="inlineStr"/>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -13239,33 +13220,21 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D275" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
-        </is>
-      </c>
-      <c r="F275" s="2" t="inlineStr">
-        <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
-        </is>
-      </c>
-      <c r="G275" s="2" t="inlineStr">
-        <is>
-          <t>값입력</t>
-        </is>
-      </c>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr"/>
       <c r="H275" s="2" t="inlineStr"/>
-      <c r="I275" s="2" t="inlineStr">
-        <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
-        </is>
-      </c>
+      <c r="I275" s="2" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>조직관류저하:뇌</t>
@@ -13285,31 +13254,23 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D276" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
-        </is>
-      </c>
-      <c r="F276" s="2" t="inlineStr">
-        <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
-        </is>
-      </c>
-      <c r="G276" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr"/>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
+          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -13331,31 +13292,23 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D277" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음/없음</t>
-        </is>
-      </c>
-      <c r="F277" s="2" t="inlineStr">
-        <is>
-          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G277" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr"/>
       <c r="H277" s="2" t="inlineStr"/>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
@@ -13367,12 +13320,12 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>뇌경색/뇌출혈 의심</t>
+          <t>심근경색 의심</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>뇌경색뇌출혈 관련</t>
+          <t>심근경색의심+통증없음</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -13381,16 +13334,16 @@
         </is>
       </c>
       <c r="D278" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함/약함</t>
+          <t>dizziness 있음/없음</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>"양손으로 꽉 쥐어보세요" — 근력 확인</t>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G278" s="2" t="inlineStr">
@@ -13401,122 +13354,146 @@
       <c r="H278" s="2" t="inlineStr"/>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>뇌경색/뇌출혈 의심</t>
+          <t>심근경색 의심</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>뇌경색뇌출혈 관련</t>
+          <t>심근경색의심+통증없음</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D279" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
-        </is>
-      </c>
-      <c r="F279" s="2" t="inlineStr"/>
-      <c r="G279" s="2" t="inlineStr"/>
+          <t>호흡곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>"숨이 차거나 답답하신가요?"</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H279" s="2" t="inlineStr"/>
       <c r="I279" s="2" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>뇌경색/뇌출혈 의심</t>
+          <t>심근경색 의심</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>뇌경색뇌출혈 관련</t>
+          <t>심근경색의심+통증없음</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D280" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" s="2" t="inlineStr"/>
+          <t>흉부 불편감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>"불편하신 부분이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H280" s="2" t="inlineStr"/>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>뇌경색/뇌출혈 의심</t>
+          <t>심근경색 의심</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>뇌경색뇌출혈 관련</t>
+          <t>심근경색의심+통증없음</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D281" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="F281" s="2" t="inlineStr"/>
-      <c r="G281" s="2" t="inlineStr"/>
+          <t>흉부 통증 없음</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>"흉통은 없으신가요?"</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H281" s="2" t="inlineStr"/>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
@@ -13537,27 +13514,27 @@
         </is>
       </c>
       <c r="D282" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>심전도에서 불규칙한 리듬 관찰됨</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>심전도(ECG) 결과를 확인하세요</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 여부 확인</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
@@ -13579,27 +13556,19 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D283" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
-        </is>
-      </c>
-      <c r="F283" s="2" t="inlineStr">
-        <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
-        </is>
-      </c>
-      <c r="G283" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr"/>
       <c r="I283" s="2" t="inlineStr"/>
       <c r="J283" t="inlineStr">
@@ -13621,33 +13590,21 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D284" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>흉부 불편감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F284" s="2" t="inlineStr">
-        <is>
-          <t>"불편하신 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G284" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>흉부 통증이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr"/>
       <c r="H284" s="2" t="inlineStr"/>
-      <c r="I284" s="2" t="inlineStr">
-        <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
-        </is>
-      </c>
+      <c r="I284" s="2" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -13667,31 +13624,23 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D285" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증 없음</t>
-        </is>
-      </c>
-      <c r="F285" s="2" t="inlineStr">
-        <is>
-          <t>"흉통은 없으신가요?"</t>
-        </is>
-      </c>
-      <c r="G285" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>심전도 변화를 확인함</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr"/>
       <c r="H285" s="2" t="inlineStr"/>
       <c r="I285" s="2" t="inlineStr">
         <is>
-          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
@@ -13708,7 +13657,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증없음</t>
+          <t>심근경색의심+통증있음</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -13717,27 +13666,27 @@
         </is>
       </c>
       <c r="D286" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>심전도에서 불규칙한 리듬 관찰됨</t>
+          <t>dizziness 있음/없음</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>심전도(ECG) 결과를 확인하세요</t>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr"/>
       <c r="I286" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
@@ -13754,24 +13703,32 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증없음</t>
+          <t>심근경색의심+통증있음</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D287" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
-        </is>
-      </c>
-      <c r="F287" s="2" t="inlineStr"/>
-      <c r="G287" s="2" t="inlineStr"/>
+          <t>호흡곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>"숨이 차거나 답답하신가요?"</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H287" s="2" t="inlineStr"/>
       <c r="I287" s="2" t="inlineStr"/>
       <c r="J287" t="inlineStr">
@@ -13788,26 +13745,38 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증없음</t>
+          <t>심근경색의심+통증있음</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D288" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr"/>
+          <t>흉부 불편감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>"불편하신 부분이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H288" s="2" t="inlineStr"/>
-      <c r="I288" s="2" t="inlineStr"/>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+        </is>
+      </c>
       <c r="J288" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -13822,28 +13791,36 @@
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증없음</t>
+          <t>심근경색의심+통증있음</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D289" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
-        </is>
-      </c>
-      <c r="F289" s="2" t="inlineStr"/>
-      <c r="G289" s="2" t="inlineStr"/>
+          <t>흉부 통증 없음</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>"흉통은 없으신가요?"</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H289" s="2" t="inlineStr"/>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
@@ -13869,27 +13846,27 @@
         </is>
       </c>
       <c r="D290" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>심전도에서 불규칙한 리듬 관찰됨</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>심전도(ECG) 결과를 확인하세요</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr"/>
       <c r="I290" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 여부 확인</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
@@ -13915,25 +13892,29 @@
         </is>
       </c>
       <c r="D291" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>흉부 통증 있음</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
+          <t>"가슴이 아프세요?"</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr"/>
-      <c r="I291" s="2" t="inlineStr"/>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="J291" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -13957,29 +13938,25 @@
         </is>
       </c>
       <c r="D292" s="2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>흉부 불편감 있음/없음</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>"불편하신 부분이 있으세요?"</t>
+          <t>확인하세요</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr"/>
-      <c r="I292" s="2" t="inlineStr">
-        <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
-        </is>
-      </c>
+      <c r="I292" s="2" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14003,16 +13980,16 @@
         </is>
       </c>
       <c r="D293" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증 없음</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="F293" s="2" t="inlineStr">
         <is>
-          <t>"흉통은 없으신가요?"</t>
+          <t>확인하세요</t>
         </is>
       </c>
       <c r="G293" s="2" t="inlineStr">
@@ -14021,11 +13998,7 @@
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr"/>
-      <c r="I293" s="2" t="inlineStr">
-        <is>
-          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
-        </is>
-      </c>
+      <c r="I293" s="2" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14049,16 +14022,16 @@
         </is>
       </c>
       <c r="D294" s="2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>심전도에서 불규칙한 리듬 관찰됨</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>심전도(ECG) 결과를 확인하세요</t>
+          <t>확인하세요</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
@@ -14067,11 +14040,7 @@
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr"/>
-      <c r="I294" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I294" s="2" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14095,16 +14064,16 @@
         </is>
       </c>
       <c r="D295" s="2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증 있음</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
         <is>
-          <t>"가슴이 아프세요?"</t>
+          <t>확인하세요</t>
         </is>
       </c>
       <c r="G295" s="2" t="inlineStr">
@@ -14115,7 +14084,7 @@
       <c r="H295" s="2" t="inlineStr"/>
       <c r="I295" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
@@ -14137,27 +14106,19 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D296" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-      <c r="F296" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G296" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr"/>
+      <c r="G296" s="2" t="inlineStr"/>
       <c r="H296" s="2" t="inlineStr"/>
       <c r="I296" s="2" t="inlineStr"/>
       <c r="J296" t="inlineStr">
@@ -14179,27 +14140,19 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D297" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
-        </is>
-      </c>
-      <c r="F297" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G297" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>흉부 통증이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr"/>
+      <c r="G297" s="2" t="inlineStr"/>
       <c r="H297" s="2" t="inlineStr"/>
       <c r="I297" s="2" t="inlineStr"/>
       <c r="J297" t="inlineStr">
@@ -14221,29 +14174,25 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D298" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
-        </is>
-      </c>
-      <c r="F298" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G298" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>심전도 변화를 확인함</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr"/>
+      <c r="G298" s="2" t="inlineStr"/>
       <c r="H298" s="2" t="inlineStr"/>
-      <c r="I298" s="2" t="inlineStr"/>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+        </is>
+      </c>
       <c r="J298" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14253,12 +14202,12 @@
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>심근경색 의심</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증있음</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
@@ -14267,138 +14216,162 @@
         </is>
       </c>
       <c r="D299" s="2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>dizziness 있음/없음</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
-          <t>확인하세요</t>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr"/>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>고혈당</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>심근경색 의심</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증있음</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D300" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
-        </is>
-      </c>
-      <c r="F300" s="2" t="inlineStr"/>
-      <c r="G300" s="2" t="inlineStr"/>
+          <t>호흡곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>"숨이 차거나 답답하신가요?"</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H300" s="2" t="inlineStr"/>
       <c r="I300" s="2" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>고혈당</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>심근경색 의심</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증있음</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D301" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="F301" s="2" t="inlineStr"/>
-      <c r="G301" s="2" t="inlineStr"/>
+          <t>혈당 증가함</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>혈당 수치를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H301" s="2" t="inlineStr"/>
-      <c r="I301" s="2" t="inlineStr"/>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>오심,다뇨,구토, 갈증, 의식변화 등</t>
+        </is>
+      </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>고혈당</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>심근경색 의심</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증있음</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D302" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
-        </is>
-      </c>
-      <c r="F302" s="2" t="inlineStr"/>
-      <c r="G302" s="2" t="inlineStr"/>
+          <t>고혈당 증상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>"갈증이 심하거나 소변이 자주 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H302" s="2" t="inlineStr"/>
-      <c r="I302" s="2" t="inlineStr">
-        <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
-        </is>
-      </c>
+      <c r="I302" s="2" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>고혈당</t>
         </is>
       </c>
     </row>
@@ -14415,7 +14388,7 @@
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D303" s="2" t="n">
@@ -14423,25 +14396,13 @@
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
-        </is>
-      </c>
-      <c r="F303" s="2" t="inlineStr">
-        <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>고혈당</t>
+        </is>
+      </c>
+      <c r="F303" s="2" t="inlineStr"/>
+      <c r="G303" s="2" t="inlineStr"/>
       <c r="H303" s="2" t="inlineStr"/>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 여부 확인</t>
-        </is>
-      </c>
+      <c r="I303" s="2" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>고혈당</t>
@@ -14461,29 +14422,25 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D304" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
-        </is>
-      </c>
-      <c r="F304" s="2" t="inlineStr">
-        <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
-        </is>
-      </c>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr"/>
+      <c r="G304" s="2" t="inlineStr"/>
       <c r="H304" s="2" t="inlineStr"/>
-      <c r="I304" s="2" t="inlineStr"/>
+      <c r="I304" s="2" t="inlineStr">
+        <is>
+          <t>인슐린 투여시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
+        </is>
+      </c>
       <c r="J304" t="inlineStr">
         <is>
           <t>고혈당</t>
@@ -14503,29 +14460,25 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D305" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>불편감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F305" s="2" t="inlineStr">
-        <is>
-          <t>"불편하신 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G305" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>처방에 의해 인슐린 투여함</t>
+        </is>
+      </c>
+      <c r="F305" s="2" t="inlineStr"/>
+      <c r="G305" s="2" t="inlineStr"/>
       <c r="H305" s="2" t="inlineStr"/>
-      <c r="I305" s="2" t="inlineStr"/>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr">
         <is>
           <t>고혈당</t>
@@ -14535,12 +14488,12 @@
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -14549,44 +14502,44 @@
         </is>
       </c>
       <c r="D306" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>혈당 증가함</t>
+          <t>dizziness 있음/없음</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>혈당 수치를 확인하세요</t>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr"/>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>오심,다뇨,구토, 갈증, 의식변화 등</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
@@ -14595,16 +14548,16 @@
         </is>
       </c>
       <c r="D307" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>고혈당 증상 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F307" s="2" t="inlineStr">
         <is>
-          <t>"갈증이 심하거나 소변이 자주 나오세요?"</t>
+          <t>"숨이 차거나 답답하신가요?"</t>
         </is>
       </c>
       <c r="G307" s="2" t="inlineStr">
@@ -14616,117 +14569,129 @@
       <c r="I307" s="2" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D308" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
-        </is>
-      </c>
-      <c r="F308" s="2" t="inlineStr"/>
-      <c r="G308" s="2" t="inlineStr"/>
+          <t>혈당 떨어짐</t>
+        </is>
+      </c>
+      <c r="F308" s="2" t="inlineStr">
+        <is>
+          <t>혈당 수치를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H308" s="2" t="inlineStr"/>
-      <c r="I308" s="2" t="inlineStr"/>
+      <c r="I308" s="2" t="inlineStr">
+        <is>
+          <t>진전, 빈맥, 발한, 감각이상, 의식변화</t>
+        </is>
+      </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D309" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
-        </is>
-      </c>
-      <c r="F309" s="2" t="inlineStr"/>
-      <c r="G309" s="2" t="inlineStr"/>
+          <t>저혈당 증상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F309" s="2" t="inlineStr">
+        <is>
+          <t>"식은땀이 나거나 손이 떨리세요?"</t>
+        </is>
+      </c>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H309" s="2" t="inlineStr"/>
-      <c r="I309" s="2" t="inlineStr">
-        <is>
-          <t>인슐린 투여시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
-        </is>
-      </c>
+      <c r="I309" s="2" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D310" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 인슐린 투여함</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr"/>
       <c r="G310" s="2" t="inlineStr"/>
       <c r="H310" s="2" t="inlineStr"/>
-      <c r="I310" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
+      <c r="I310" s="2" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14708,7 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D311" s="2" t="n">
@@ -14751,25 +14716,13 @@
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
-        </is>
-      </c>
-      <c r="F311" s="2" t="inlineStr">
-        <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr"/>
-      <c r="I311" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 여부 확인</t>
-        </is>
-      </c>
+      <c r="I311" s="2" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>저혈당</t>
@@ -14789,7 +14742,7 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D312" s="2" t="n">
@@ -14797,21 +14750,17 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
-        </is>
-      </c>
-      <c r="F312" s="2" t="inlineStr">
-        <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
-        </is>
-      </c>
-      <c r="G312" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>저혈당 증상(진전, 빈맥, 발한, 감각이상, 의식변화)애 대해 설명함</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr"/>
+      <c r="G312" s="2" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr"/>
-      <c r="I312" s="2" t="inlineStr"/>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>D5% 처방시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
+        </is>
+      </c>
       <c r="J312" t="inlineStr">
         <is>
           <t>저혈당</t>
@@ -14831,7 +14780,7 @@
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D313" s="2" t="n">
@@ -14839,21 +14788,17 @@
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>불편감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F313" s="2" t="inlineStr">
-        <is>
-          <t>"불편하신 부분이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>처방에 의해 D50W 을 투여함</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr"/>
+      <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr"/>
-      <c r="I313" s="2" t="inlineStr"/>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J313" t="inlineStr">
         <is>
           <t>저혈당</t>
@@ -14863,12 +14808,12 @@
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
@@ -14877,16 +14822,16 @@
         </is>
       </c>
       <c r="D314" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>혈당 떨어짐</t>
+          <t>Seizure 있음</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>혈당 수치를 확인하세요</t>
+          <t>발작 양상을 확인하세요</t>
         </is>
       </c>
       <c r="G314" s="2" t="inlineStr">
@@ -14897,24 +14842,24 @@
       <c r="H314" s="2" t="inlineStr"/>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>진전, 빈맥, 발한, 감각이상, 의식변화</t>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
@@ -14923,79 +14868,95 @@
         </is>
       </c>
       <c r="D315" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>저혈당 증상 있음/없음</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F315" s="2" t="inlineStr">
         <is>
-          <t>"식은땀이 나거나 손이 떨리세요?"</t>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
         </is>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr"/>
-      <c r="I315" s="2" t="inlineStr"/>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+        </is>
+      </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D316" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
-        </is>
-      </c>
-      <c r="F316" s="2" t="inlineStr"/>
-      <c r="G316" s="2" t="inlineStr"/>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H316" s="2" t="inlineStr"/>
-      <c r="I316" s="2" t="inlineStr"/>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D317" s="2" t="n">
@@ -15003,7 +14964,7 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr"/>
@@ -15012,19 +14973,19 @@
       <c r="I317" s="2" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
@@ -15033,11 +14994,11 @@
         </is>
       </c>
       <c r="D318" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>저혈당 증상(진전, 빈맥, 발한, 감각이상, 의식변화)애 대해 설명함</t>
+          <t>Seizure 양상을 확인함</t>
         </is>
       </c>
       <c r="F318" s="2" t="inlineStr"/>
@@ -15045,24 +15006,24 @@
       <c r="H318" s="2" t="inlineStr"/>
       <c r="I318" s="2" t="inlineStr">
         <is>
-          <t>D5% 처방시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
+          <t>airway유지</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
@@ -15071,24 +15032,20 @@
         </is>
       </c>
       <c r="D319" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 D50W 을 투여함</t>
+          <t>Seizure시 안전간호 시행함</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
       <c r="G319" s="2" t="inlineStr"/>
       <c r="H319" s="2" t="inlineStr"/>
-      <c r="I319" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
+      <c r="I319" s="2" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -15105,31 +15062,23 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D320" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>Seizure 있음</t>
-        </is>
-      </c>
-      <c r="F320" s="2" t="inlineStr">
-        <is>
-          <t>발작 양상을 확인하세요</t>
-        </is>
-      </c>
-      <c r="G320" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>Seizure의 유발요인을확인함</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr"/>
+      <c r="G320" s="2" t="inlineStr"/>
       <c r="H320" s="2" t="inlineStr"/>
       <c r="I320" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>의사처방시</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
@@ -15151,31 +15100,23 @@
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D321" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
-        </is>
-      </c>
-      <c r="F321" s="2" t="inlineStr">
-        <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
-        </is>
-      </c>
-      <c r="G321" s="2" t="inlineStr">
-        <is>
-          <t>값입력</t>
-        </is>
-      </c>
+          <t>처방에 의해 Lorazepam을 투여함</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr"/>
+      <c r="G321" s="2" t="inlineStr"/>
       <c r="H321" s="2" t="inlineStr"/>
       <c r="I321" s="2" t="inlineStr">
         <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+          <t>GCS 15 미만일 떄</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
@@ -15192,7 +15133,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -15201,16 +15142,16 @@
         </is>
       </c>
       <c r="D322" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>dizziness 있음/없음</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
@@ -15221,7 +15162,7 @@
       <c r="H322" s="2" t="inlineStr"/>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -15238,26 +15179,38 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D323" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="inlineStr"/>
-      <c r="G323" s="2" t="inlineStr"/>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
       <c r="H323" s="2" t="inlineStr"/>
-      <c r="I323" s="2" t="inlineStr"/>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+        </is>
+      </c>
       <c r="J323" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15272,30 +15225,34 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D324" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>Seizure 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F324" s="2" t="inlineStr"/>
-      <c r="G324" s="2" t="inlineStr"/>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H324" s="2" t="inlineStr"/>
-      <c r="I324" s="2" t="inlineStr">
-        <is>
-          <t>airway유지</t>
-        </is>
-      </c>
+      <c r="I324" s="2" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15310,24 +15267,32 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D325" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>Seizure시 안전간호 시행함</t>
-        </is>
-      </c>
-      <c r="F325" s="2" t="inlineStr"/>
-      <c r="G325" s="2" t="inlineStr"/>
+          <t>Seizure 멈춤/없음</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr">
+        <is>
+          <t>발작 양상을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H325" s="2" t="inlineStr"/>
       <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" t="inlineStr">
@@ -15344,28 +15309,36 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D326" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>Seizure의 유발요인을확인함</t>
-        </is>
-      </c>
-      <c r="F326" s="2" t="inlineStr"/>
-      <c r="G326" s="2" t="inlineStr"/>
+          <t>Seizure 유사증상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr">
+        <is>
+          <t>발작 양상을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H326" s="2" t="inlineStr"/>
       <c r="I326" s="2" t="inlineStr">
         <is>
-          <t>의사처방시</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
@@ -15382,30 +15355,26 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D327" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Lorazepam을 투여함</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr"/>
       <c r="G327" s="2" t="inlineStr"/>
       <c r="H327" s="2" t="inlineStr"/>
-      <c r="I327" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 미만일 떄</t>
-        </is>
-      </c>
+      <c r="I327" s="2" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15425,7 +15394,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D328" s="2" t="n">
@@ -15433,23 +15402,15 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
-        </is>
-      </c>
-      <c r="F328" s="2" t="inlineStr">
-        <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G328" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>Seizure 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr"/>
+      <c r="G328" s="2" t="inlineStr"/>
       <c r="H328" s="2" t="inlineStr"/>
       <c r="I328" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>airway유지</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
@@ -15471,7 +15432,7 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D329" s="2" t="n">
@@ -15479,25 +15440,13 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
-        </is>
-      </c>
-      <c r="F329" s="2" t="inlineStr">
-        <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
-        </is>
-      </c>
-      <c r="G329" s="2" t="inlineStr">
-        <is>
-          <t>값입력</t>
-        </is>
-      </c>
+          <t>Seizure시 안전간호 시행함</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr"/>
+      <c r="G329" s="2" t="inlineStr"/>
       <c r="H329" s="2" t="inlineStr"/>
-      <c r="I329" s="2" t="inlineStr">
-        <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
-        </is>
-      </c>
+      <c r="I329" s="2" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15517,7 +15466,7 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D330" s="2" t="n">
@@ -15525,21 +15474,17 @@
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
-        </is>
-      </c>
-      <c r="F330" s="2" t="inlineStr">
-        <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
-        </is>
-      </c>
-      <c r="G330" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>Seizure의 유발요인을확인함</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr"/>
+      <c r="G330" s="2" t="inlineStr"/>
       <c r="H330" s="2" t="inlineStr"/>
-      <c r="I330" s="2" t="inlineStr"/>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+        </is>
+      </c>
       <c r="J330" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15559,7 +15504,7 @@
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D331" s="2" t="n">
@@ -15567,21 +15512,17 @@
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>Seizure 멈춤/없음</t>
-        </is>
-      </c>
-      <c r="F331" s="2" t="inlineStr">
-        <is>
-          <t>발작 양상을 확인하세요</t>
-        </is>
-      </c>
-      <c r="G331" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr"/>
+      <c r="G331" s="2" t="inlineStr"/>
       <c r="H331" s="2" t="inlineStr"/>
-      <c r="I331" s="2" t="inlineStr"/>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J331" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15591,12 +15532,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>의식/낙상 사정</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
+          <t>의식 및 낙상위험 평가</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -15605,214 +15546,258 @@
         </is>
       </c>
       <c r="D332" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>Seizure 유사증상 있음/없음</t>
+          <t>의식 명료함</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>발작 양상을 확인하세요</t>
+          <t>확인하세요</t>
         </is>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr"/>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>GCS 15 미만일 떄</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>의식/낙상 사정</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
+          <t>의식 및 낙상위험 평가</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D333" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="F333" s="2" t="inlineStr"/>
-      <c r="G333" s="2" t="inlineStr"/>
+          <t>의식수준 :</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>확인하세요</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
       <c r="H333" s="2" t="inlineStr"/>
-      <c r="I333" s="2" t="inlineStr"/>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>보호자 있을시</t>
+        </is>
+      </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>의식/낙상 사정</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
+          <t>의식 및 낙상위험 평가</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D334" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>Seizure 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F334" s="2" t="inlineStr"/>
-      <c r="G334" s="2" t="inlineStr"/>
+          <t>보호자 환자 옆에 상주하고 있음</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>확인하세요</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H334" s="2" t="inlineStr"/>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>airway유지</t>
+          <t>보호자 없을시</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>의식/낙상 사정</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
+          <t>의식 및 낙상위험 평가</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D335" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>Seizure시 안전간호 시행함</t>
-        </is>
-      </c>
-      <c r="F335" s="2" t="inlineStr"/>
-      <c r="G335" s="2" t="inlineStr"/>
+          <t>보호자 동행하지 않음</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>확인하세요</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H335" s="2" t="inlineStr"/>
-      <c r="I335" s="2" t="inlineStr"/>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>가능하지 않을 떄</t>
+        </is>
+      </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>의식/낙상 사정</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
+          <t>의식 및 낙상위험 평가</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D336" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>Seizure의 유발요인을확인함</t>
-        </is>
-      </c>
-      <c r="F336" s="2" t="inlineStr"/>
-      <c r="G336" s="2" t="inlineStr"/>
+          <t>Obey command 가능함/ Obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr">
+        <is>
+          <t>확인하세요</t>
+        </is>
+      </c>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H336" s="2" t="inlineStr"/>
-      <c r="I336" s="2" t="inlineStr">
-        <is>
-          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
-        </is>
-      </c>
+      <c r="I336" s="2" t="inlineStr"/>
       <c r="J336" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>의식/낙상 사정</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
+          <t>의식 및 낙상위험 평가</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D337" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="F337" s="2" t="inlineStr"/>
-      <c r="G337" s="2" t="inlineStr"/>
+          <t>시간에대한 지남력 없음/사람에 대한 지남력 없음/ 장소에 대한 지남력 없음</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr">
+        <is>
+          <t>확인하세요</t>
+        </is>
+      </c>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H337" s="2" t="inlineStr"/>
       <c r="I337" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>Post note에 세부사항 기록하기</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
@@ -15833,11 +15818,11 @@
         </is>
       </c>
       <c r="D338" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>의식 명료함</t>
+          <t>시간, 사람, 장소에 대한 지남력 없음</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
@@ -15853,7 +15838,7 @@
       <c r="H338" s="2" t="inlineStr"/>
       <c r="I338" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 미만일 떄</t>
+          <t>보호자 있을시</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
@@ -15879,11 +15864,11 @@
         </is>
       </c>
       <c r="D339" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>의식수준 :</t>
+          <t>보호자 환자 옆에 상주하고 있음</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr">
@@ -15893,13 +15878,13 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr"/>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>보호자 있을시</t>
+          <t>보호자 없을시</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
@@ -15925,11 +15910,11 @@
         </is>
       </c>
       <c r="D340" s="2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>보호자 환자 옆에 상주하고 있음</t>
+          <t>보호자 동행하지 않음</t>
         </is>
       </c>
       <c r="F340" s="2" t="inlineStr">
@@ -15945,7 +15930,7 @@
       <c r="H340" s="2" t="inlineStr"/>
       <c r="I340" s="2" t="inlineStr">
         <is>
-          <t>보호자 없을시</t>
+          <t>active</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
@@ -15967,33 +15952,21 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D341" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>보호자 동행하지 않음</t>
-        </is>
-      </c>
-      <c r="F341" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G341" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>낙상위험</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr"/>
+      <c r="G341" s="2" t="inlineStr"/>
       <c r="H341" s="2" t="inlineStr"/>
-      <c r="I341" s="2" t="inlineStr">
-        <is>
-          <t>가능하지 않을 떄</t>
-        </is>
-      </c>
+      <c r="I341" s="2" t="inlineStr"/>
       <c r="J341" t="inlineStr">
         <is>
           <t>낙상위험</t>
@@ -16013,29 +15986,25 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D342" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>Obey command 가능함/ Obey command 가능하지 않음</t>
-        </is>
-      </c>
-      <c r="F342" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G342" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>낙상방지 교육함</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr"/>
+      <c r="G342" s="2" t="inlineStr"/>
       <c r="H342" s="2" t="inlineStr"/>
-      <c r="I342" s="2" t="inlineStr"/>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>침대 난간 올려줬을 시</t>
+        </is>
+      </c>
       <c r="J342" t="inlineStr">
         <is>
           <t>낙상위험</t>
@@ -16055,31 +16024,23 @@
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D343" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>시간에대한 지남력 없음/사람에 대한 지남력 없음/ 장소에 대한 지남력 없음</t>
-        </is>
-      </c>
-      <c r="F343" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G343" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>침대 난간을 올려줌</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr"/>
+      <c r="G343" s="2" t="inlineStr"/>
       <c r="H343" s="2" t="inlineStr"/>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>Post note에 세부사항 기록하기</t>
+          <t>보호자 있을시, 낙상 위험 높을시</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -16101,27 +16062,19 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D344" s="2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>시간, 사람, 장소에 대한 지남력 없음</t>
-        </is>
-      </c>
-      <c r="F344" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G344" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>보호자와 같이 있게 함</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr"/>
+      <c r="G344" s="2" t="inlineStr"/>
       <c r="H344" s="2" t="inlineStr"/>
       <c r="I344" s="2" t="inlineStr">
         <is>
@@ -16147,27 +16100,19 @@
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D345" s="2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>보호자 환자 옆에 상주하고 있음</t>
-        </is>
-      </c>
-      <c r="F345" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>보호자 동반하도록 설명함</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr"/>
+      <c r="G345" s="2" t="inlineStr"/>
       <c r="H345" s="2" t="inlineStr"/>
       <c r="I345" s="2" t="inlineStr">
         <is>
@@ -16193,31 +16138,23 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D346" s="2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E346" s="2" t="inlineStr">
         <is>
-          <t>보호자 동행하지 않음</t>
-        </is>
-      </c>
-      <c r="F346" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>침대에서 내려오실 때 반드시 간호사 호출하도록 교육함</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr"/>
+      <c r="G346" s="2" t="inlineStr"/>
       <c r="H346" s="2" t="inlineStr"/>
       <c r="I346" s="2" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>낙상위험 교육</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
@@ -16239,21 +16176,25 @@
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D347" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E347" s="2" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>어지러우면 바로 앉고 보호자나 담당간호사에게 알리도록 교육함</t>
         </is>
       </c>
       <c r="F347" s="2" t="inlineStr"/>
       <c r="G347" s="2" t="inlineStr"/>
       <c r="H347" s="2" t="inlineStr"/>
-      <c r="I347" s="2" t="inlineStr"/>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>낙상위험 교육</t>
+        </is>
+      </c>
       <c r="J347" t="inlineStr">
         <is>
           <t>낙상위험</t>
@@ -16277,11 +16218,11 @@
         </is>
       </c>
       <c r="D348" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E348" s="2" t="inlineStr">
         <is>
-          <t>낙상방지 교육함</t>
+          <t>낙상 위험성에 대해 설명함</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr"/>
@@ -16289,238 +16230,10 @@
       <c r="H348" s="2" t="inlineStr"/>
       <c r="I348" s="2" t="inlineStr">
         <is>
-          <t>침대 난간 올려줬을 시</t>
+          <t>낙상위험 교육</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
-        <is>
-          <t>낙상위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 사정</t>
-        </is>
-      </c>
-      <c r="B349" s="2" t="inlineStr">
-        <is>
-          <t>의식 및 낙상위험 평가</t>
-        </is>
-      </c>
-      <c r="C349" s="2" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D349" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E349" s="2" t="inlineStr">
-        <is>
-          <t>침대 난간을 올려줌</t>
-        </is>
-      </c>
-      <c r="F349" s="2" t="inlineStr"/>
-      <c r="G349" s="2" t="inlineStr"/>
-      <c r="H349" s="2" t="inlineStr"/>
-      <c r="I349" s="2" t="inlineStr">
-        <is>
-          <t>보호자 있을시, 낙상 위험 높을시</t>
-        </is>
-      </c>
-      <c r="J349" t="inlineStr">
-        <is>
-          <t>낙상위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 사정</t>
-        </is>
-      </c>
-      <c r="B350" s="2" t="inlineStr">
-        <is>
-          <t>의식 및 낙상위험 평가</t>
-        </is>
-      </c>
-      <c r="C350" s="2" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D350" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E350" s="2" t="inlineStr">
-        <is>
-          <t>보호자와 같이 있게 함</t>
-        </is>
-      </c>
-      <c r="F350" s="2" t="inlineStr"/>
-      <c r="G350" s="2" t="inlineStr"/>
-      <c r="H350" s="2" t="inlineStr"/>
-      <c r="I350" s="2" t="inlineStr">
-        <is>
-          <t>보호자 있을시</t>
-        </is>
-      </c>
-      <c r="J350" t="inlineStr">
-        <is>
-          <t>낙상위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 사정</t>
-        </is>
-      </c>
-      <c r="B351" s="2" t="inlineStr">
-        <is>
-          <t>의식 및 낙상위험 평가</t>
-        </is>
-      </c>
-      <c r="C351" s="2" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D351" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="E351" s="2" t="inlineStr">
-        <is>
-          <t>보호자 동반하도록 설명함</t>
-        </is>
-      </c>
-      <c r="F351" s="2" t="inlineStr"/>
-      <c r="G351" s="2" t="inlineStr"/>
-      <c r="H351" s="2" t="inlineStr"/>
-      <c r="I351" s="2" t="inlineStr">
-        <is>
-          <t>보호자 없을시</t>
-        </is>
-      </c>
-      <c r="J351" t="inlineStr">
-        <is>
-          <t>낙상위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 사정</t>
-        </is>
-      </c>
-      <c r="B352" s="2" t="inlineStr">
-        <is>
-          <t>의식 및 낙상위험 평가</t>
-        </is>
-      </c>
-      <c r="C352" s="2" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D352" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E352" s="2" t="inlineStr">
-        <is>
-          <t>침대에서 내려오실 때 반드시 간호사 호출하도록 교육함</t>
-        </is>
-      </c>
-      <c r="F352" s="2" t="inlineStr"/>
-      <c r="G352" s="2" t="inlineStr"/>
-      <c r="H352" s="2" t="inlineStr"/>
-      <c r="I352" s="2" t="inlineStr">
-        <is>
-          <t>낙상위험 교육</t>
-        </is>
-      </c>
-      <c r="J352" t="inlineStr">
-        <is>
-          <t>낙상위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 사정</t>
-        </is>
-      </c>
-      <c r="B353" s="2" t="inlineStr">
-        <is>
-          <t>의식 및 낙상위험 평가</t>
-        </is>
-      </c>
-      <c r="C353" s="2" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D353" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="E353" s="2" t="inlineStr">
-        <is>
-          <t>어지러우면 바로 앉고 보호자나 담당간호사에게 알리도록 교육함</t>
-        </is>
-      </c>
-      <c r="F353" s="2" t="inlineStr"/>
-      <c r="G353" s="2" t="inlineStr"/>
-      <c r="H353" s="2" t="inlineStr"/>
-      <c r="I353" s="2" t="inlineStr">
-        <is>
-          <t>낙상위험 교육</t>
-        </is>
-      </c>
-      <c r="J353" t="inlineStr">
-        <is>
-          <t>낙상위험</t>
-        </is>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 사정</t>
-        </is>
-      </c>
-      <c r="B354" s="2" t="inlineStr">
-        <is>
-          <t>의식 및 낙상위험 평가</t>
-        </is>
-      </c>
-      <c r="C354" s="2" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D354" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E354" s="2" t="inlineStr">
-        <is>
-          <t>낙상 위험성에 대해 설명함</t>
-        </is>
-      </c>
-      <c r="F354" s="2" t="inlineStr"/>
-      <c r="G354" s="2" t="inlineStr"/>
-      <c r="H354" s="2" t="inlineStr"/>
-      <c r="I354" s="2" t="inlineStr">
-        <is>
-          <t>낙상위험 교육</t>
-        </is>
-      </c>
-      <c r="J354" t="inlineStr">
         <is>
           <t>낙상위험</t>
         </is>
@@ -17385,7 +17098,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17421,7 +17133,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -17457,7 +17168,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -17493,7 +17203,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -17529,7 +17238,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -17565,7 +17273,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -17601,7 +17308,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -17637,7 +17343,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -17673,7 +17378,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -17689,7 +17393,6 @@
       <c r="C11" t="n">
         <v>1664</v>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17705,7 +17408,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17721,7 +17423,6 @@
       <c r="C12" t="n">
         <v>1665</v>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17737,7 +17438,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17773,7 +17473,6 @@
           <t>AI확정 · 형식교정</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17809,7 +17508,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17845,7 +17543,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17881,7 +17578,6 @@
           <t>신규 · 탈수 대체</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17917,7 +17613,6 @@
           <t>신규 · 탈수 대체</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17933,7 +17628,6 @@
       <c r="C18" t="n">
         <v>1784</v>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17949,7 +17643,6 @@
           <t>신규 · 탈수 대체</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17965,7 +17658,6 @@
       <c r="C19" t="n">
         <v>972</v>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>체크</t>
@@ -17981,7 +17673,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -18017,7 +17708,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -18033,7 +17723,6 @@
       <c r="C21" t="n">
         <v>89</v>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18049,7 +17738,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -18065,7 +17753,6 @@
       <c r="C22" t="n">
         <v>88</v>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18081,7 +17768,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -18117,7 +17803,6 @@
           <t>AI확정 · 형식교정</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -18135,7 +17820,6 @@
           <t>1339 / 1447 / 482</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
           <t>선택</t>
@@ -18151,7 +17835,6 @@
           <t>신규 · 3단계</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -18187,7 +17870,6 @@
           <t>AI확정 · 형식교정</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -18203,7 +17885,6 @@
       <c r="C26" t="n">
         <v>1337</v>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18219,7 +17900,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -18235,7 +17915,6 @@
       <c r="C27" t="n">
         <v>1488</v>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18251,7 +17930,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -18267,7 +17945,6 @@
       <c r="C28" t="n">
         <v>1510</v>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>체크</t>
@@ -18283,7 +17960,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -18319,7 +17995,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -18355,7 +18030,6 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -18391,7 +18065,120 @@
           <t>AI확정</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>질문문구(💬)</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>진술문(마스터원문)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>다음동작</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>"그 밖에 더 아프거나 불편한 곳이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>불편감 없음</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>종료 → 의식·낙상으로</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1탭으로 끝</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>"그 밖에 더 아프거나 불편한 곳이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>불편감 있음</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>주호소 화면 다시 표시 + 📌비고 입력</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>추가 사정 유도</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1981,6 +1981,174 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>🌡️ 열나요</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>🤮💩 토하고 설사</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>🫁 숨쉬기 힘들어요</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>⚡ 경련했어요</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1992,7 +2160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K348"/>
+  <dimension ref="A1:K390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16236,6 +16404,1736 @@
       <c r="J348" t="inlineStr">
         <is>
           <t>낙상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D349" t="n">
+        <v>1</v>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>열감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>"열이 나나요?"</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D350" t="n">
+        <v>2</v>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>chilling 있음/없음</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>"춥다고 하거나 몸을 떨었나요?"</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>3</v>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>체온 상승함</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>🩺 체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>4</v>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>lethargy 상태임/의식 명료함</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>5</v>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D354" t="n">
+        <v>6</v>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>구토함/구토 없음</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>"토했나요?"</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>1</v>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D356" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D357" t="n">
+        <v>2</v>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>미온수 목욕 시행함</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D358" t="n">
+        <v>3</v>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>처방에 의해 해열제를 투여함</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D359" t="n">
+        <v>1</v>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>구토함/구토 없음</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>"토했나요? 몇 번이나 했나요?"</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D360" t="n">
+        <v>2</v>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>오심 있음/없음</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>"메스꺼워 하나요?"</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>3</v>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>설사 있음/없음</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>"설사하나요? 몇 번이나 했나요?"</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D362" t="n">
+        <v>4</v>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>구강건조 있음/없음</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>"입술이나 입 안이 말라 있나요?"</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>5</v>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>갈증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>"물을 자꾸 찾나요?"</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>6</v>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>피부 탄력성 저하됨</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>🩺 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D365" t="n">
+        <v>7</v>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>소변량 감소함</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D366" t="n">
+        <v>8</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>복부 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>"배가 아프다고 하나요?"</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>1</v>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>1</v>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>탈수 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D369" t="n">
+        <v>2</v>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>경구수분섭취 격려함</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>소아-구토설사</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D370" t="n">
+        <v>3</v>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>구토 양상 확인함</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D371" t="n">
+        <v>1</v>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>호흡곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D372" t="n">
+        <v>2</v>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>chest retraction 있음/없음</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D373" t="n">
+        <v>3</v>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>wheezing 있음/없음</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>4</v>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>기침 있음/없음</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>"기침하나요?"</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>5</v>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>가래 잘 뱉지 못함/가래 잘 뱉어냄</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D376" t="n">
+        <v>6</v>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>"입술이나 얼굴이 파래 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D377" t="n">
+        <v>7</v>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>말단 청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>"손끝·발끝이 파래 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D378" t="n">
+        <v>1</v>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D379" t="n">
+        <v>1</v>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>호흡곤란이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D380" t="n">
+        <v>2</v>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>산소포화도 monitor 함</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>소아-호흡곤란</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D381" t="n">
+        <v>3</v>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>산소 흡입 시작함</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D382" t="n">
+        <v>1</v>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>경련 있음</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>"경련(발작)을 했나요? 얼마나 오래 했나요?"</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>2</v>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>경련과 유사한 증상 보임</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>3</v>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>lethargy 상태임/의식 명료함</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>"경련 후 축 처져 있나요?"</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D385" t="n">
+        <v>4</v>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>5</v>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>체온 상승함</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>🩺 체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>1</v>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>1</v>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>seizure 양상 확인함</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>2</v>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>seizure의 유발요인을 확인함</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>3</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2149,6 +2149,90 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>🧴 발진·두드러기</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>소아-피부</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>😖 보채고 처져요</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2160,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K390"/>
+  <dimension ref="A1:K408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16690,15 +16774,25 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체온 하강함</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>🩺 체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -16725,7 +16819,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D356" t="n">
@@ -16733,7 +16827,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -16764,11 +16858,11 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>미온수 목욕 시행함</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -16799,11 +16893,11 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>처방에 의해 해열제를 투여함</t>
+          <t>미온수 목욕 시행함</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -16825,30 +16919,20 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>구토함/구토 없음</t>
-        </is>
-      </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>"토했나요? 몇 번이나 했나요?"</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>처방에 의해 해열제를 투여함</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -16858,7 +16942,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -16879,16 +16963,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>오심 있음/없음</t>
+          <t>구토함/구토 없음</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>"메스꺼워 하나요?"</t>
+          <t>"토했나요? 몇 번이나 했나요?"</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -16924,16 +17008,16 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>설사 있음/없음</t>
+          <t>오심 있음/없음</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>"설사하나요? 몇 번이나 했나요?"</t>
+          <t>"메스꺼워 하나요?"</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -16969,16 +17053,16 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>구강건조 있음/없음</t>
+          <t>설사 있음/없음</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>"입술이나 입 안이 말라 있나요?"</t>
+          <t>"설사하나요? 몇 번이나 했나요?"</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -17014,16 +17098,16 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>갈증 있음/없음</t>
+          <t>구강건조 있음/없음</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>"물을 자꾸 찾나요?"</t>
+          <t>"입술이나 입 안이 말라 있나요?"</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -17059,21 +17143,21 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>피부 탄력성 저하됨</t>
+          <t>갈증 있음/없음</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>🩺 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
+          <t>"물을 자꾸 찾나요?"</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -17104,16 +17188,16 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
+          <t>피부 탄력성 저하됨</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
+          <t>🩺 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -17149,21 +17233,21 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>복부 통증 있음/없음</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>"배가 아프다고 하나요?"</t>
+          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -17190,15 +17274,25 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>복부 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>"배가 아프다고 하나요?"</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -17225,7 +17319,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D368" t="n">
@@ -17233,7 +17327,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>탈수 증상이 있는지 확인함</t>
+          <t>체액부족위험</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -17264,11 +17358,11 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>경구수분섭취 격려함</t>
+          <t>탈수 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -17299,11 +17393,11 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>구토 양상 확인함</t>
+          <t>경구수분섭취 격려함</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -17325,30 +17419,20 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D371" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
-        </is>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>구토 양상 확인함</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -17358,7 +17442,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17379,16 +17463,16 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>chest retraction 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
+          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -17424,16 +17508,16 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>wheezing 있음/없음</t>
+          <t>chest retraction 있음/없음</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
+          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -17469,16 +17553,16 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>기침 있음/없음</t>
+          <t>wheezing 있음/없음</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>"기침하나요?"</t>
+          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -17514,16 +17598,16 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>가래 잘 뱉지 못함/가래 잘 뱉어냄</t>
+          <t>기침 있음/없음</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
+          <t>"기침하나요?"</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -17559,16 +17643,16 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>청색증 있음/없음</t>
+          <t>가래 잘 뱉지 못함/가래 잘 뱉어냄</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>"입술이나 얼굴이 파래 보이나요?"</t>
+          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
@@ -17604,16 +17688,16 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>말단 청색증 있음/없음</t>
+          <t>청색증 있음/없음</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>"손끝·발끝이 파래 보이나요?"</t>
+          <t>"입술이나 얼굴이 파래 보이나요?"</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -17645,15 +17729,25 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D378" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>말단 청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>"손끝·발끝이 파래 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -17680,7 +17774,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D379" t="n">
@@ -17688,7 +17782,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>호흡곤란이 있는지 확인함</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -17719,11 +17813,11 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>산소포화도 monitor 함</t>
+          <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -17754,11 +17848,11 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>산소 흡입 시작함</t>
+          <t>산소포화도 monitor 함</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -17780,30 +17874,20 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>경련 있음</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>"경련(발작)을 했나요? 얼마나 오래 했나요?"</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>산소 흡입 시작함</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -17813,7 +17897,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -17834,16 +17918,16 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>경련과 유사한 증상 보임</t>
+          <t>경련 있음</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
+          <t>"경련(발작)을 했나요? 얼마나 오래 했나요?"</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -17879,21 +17963,21 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
+          <t>경련과 유사한 증상 보임</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>"경련 후 축 처져 있나요?"</t>
+          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -17924,21 +18008,21 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
+          <t>"경련 후 축 처져 있나요?"</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -17969,21 +18053,21 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>체온 상승함</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>🩺 체온을 측정하세요</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -18010,15 +18094,25 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D387" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>체온 상승함</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>🩺 체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -18045,7 +18139,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D388" t="n">
@@ -18053,7 +18147,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -18084,11 +18178,11 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>seizure의 유발요인을 확인함</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -18119,21 +18213,741 @@
         </is>
       </c>
       <c r="D390" t="n">
+        <v>2</v>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>seizure의 유발요인을 확인함</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D391" t="n">
         <v>3</v>
       </c>
-      <c r="E390" t="inlineStr">
+      <c r="E391" t="inlineStr">
         <is>
           <t>안전간호를 제공함</t>
         </is>
       </c>
-      <c r="I390" t="inlineStr">
+      <c r="I391" t="inlineStr">
         <is>
           <t>⚠️ 초안</t>
         </is>
       </c>
-      <c r="J390" t="inlineStr">
+      <c r="J391" t="inlineStr">
         <is>
           <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>소아-피부</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D392" t="n">
+        <v>1</v>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>urticaria 있음/없음</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>소아-피부</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>2</v>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>기저귀 발진 있음/없음</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>🩺 기저귀 부위 발진을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>소아-피부</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>1</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>소아-피부</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>1</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>피부 상태를 관찰함</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>소아-피부</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D396" t="n">
+        <v>2</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>긁지 않도록 교육함</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>소아-피부</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>3</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>소양증 감소 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D398" t="n">
+        <v>1</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>보챔/보채지 않음</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>🩺 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>2</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>울고 보챔</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>"평소보다 심하게 보채거나 우나요?"</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>3</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>잠 안자고 울고 보챔</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>"잠을 못 자고 계속 우나요?"</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D401" t="n">
+        <v>4</v>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>자주 사지 움직이며 보챔</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>5</v>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>"어디가 아프다고 하나요?"</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>6</v>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>lethargy 상태임/의식 명료함</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>"축 처져 있거나 반응이 느린가요?"</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>7</v>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D405" t="n">
+        <v>1</v>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D406" t="n">
+        <v>1</v>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>통증 강도 측정함</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D407" t="n">
+        <v>2</v>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>소아-보챔처짐</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>3</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -19275,172 +19275,615 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>도관 진술문</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>도관</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>정식명칭</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>도관 진술문(| 로 구분)</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Foley catheter 유지 중임</t>
-        </is>
-      </c>
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Foley</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Foley catheter</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Foley catheter 유지 중임|Foley catheter 통해 소변 배출되고 있음</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Foley catheter 통해 소변 배출되고 있음</t>
-        </is>
-      </c>
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L-tube</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Levin tube</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Levin tube 유지 중임|Levin tube 통해 배액됨</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Levin tube 유지 중임</t>
-        </is>
-      </c>
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CVC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>중심정맥관</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>중심정맥관 유지 중임</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Levin tube 통해 배액됨</t>
-        </is>
-      </c>
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>A-line</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>arterial line</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>arterial line 유지 중임|arterial line를 통해 혈압 monitor 중임</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>중심정맥관 유지 중임</t>
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>기관내관</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>기관내관</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>기관내관 유지 중임|비강을 통한 기관내관 유지 중임</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>arterial line 유지 중임</t>
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>인공호흡기</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ventilator</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ventilator 적용 중임|home ventilator 적용 중임</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>arterial line를 통해 혈압 monitor 중임</t>
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Hemovac</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>hemovac</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>hemovac 유지 중임|hemovac 통해 배액됨|hemovac 삽입부위 oozing 있음|hemovac 삽입부위 oozing 없음|hemovac 삽입부위 통증 있음|hemovac 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Percutaneous Transhepatic Biliary Drainage 유지 중임</t>
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>JP drain</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Jackson Pratt drain</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jackson Pratt drain 유지 중임|Jackson Pratt drain 통해 배액됨|Jackson Pratt drain 삽입부위 oozing 있음|Jackson Pratt drain 삽입부위 oozing 없음|Jackson Pratt drain 삽입부위 통증 있음|Jackson Pratt drain 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Percutaneous Transhepatic Biliary Drainage 통해 배액됨</t>
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PEG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gastrostomy tube</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>gastrostomy tube 유지 중임|gastrostomy tube로 배액됨|gastrostomy tube 삽입부위 출혈 있음|gastrostomy tube 삽입부위 출혈 없음|gastrostomy tube 삽입부위 oozing 있음|gastrostomy tube 삽입부위 oozing 없음|gastrostomy tube 삽입부위 통증 있음|gastrostomy tube 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>흉관</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>흉관</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>흉관 유지 중임|흉관 통해 배액됨</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>기관절개</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>기관절개관</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>기관절개관 유지 중임</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Chemoport</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>chemoport</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>chemoport 통해 항암제 주입 중임|chemoport 삽입부위 통증 있음|chemoport 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hickman</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Hickman catheter</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hickman catheter 유지 중임|Hickman catheter 삽입부위 통증 있음|Hickman catheter 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PTBD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Percutaneous Transhepatic Biliary Drainage</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Percutaneous Transhepatic Biliary Drainage 유지 중임|Percutaneous Transhepatic Biliary Drainage 통해 배액됨</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PTGBD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Percutaneous Transhepatic Gall bladder Drainage</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Percutaneous Transhepatic Gall bladder Drainage 통해 배액됨</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Percutaneous Drainage 유지 중임</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Percutaneous Drainage 통해 배액됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>흉관 유지 중임</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>흉관 통해 배액됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>장루 통해 변 배출됨</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>장루 통해 변 배출 안됨</t>
-        </is>
-      </c>
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PCD</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Percutaneous Drainage</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Percutaneous Drainage 유지 중임|Percutaneous Drainage 통해 배액됨</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>기관절개관 유지 중임</t>
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>penrose</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>penrose drain</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>penrose drain 유지 중임|penrose drain 삽입부위 oozing 있음|penrose drain 삽입부위 oozing 없음|penrose drain 삽입부위 통증 있음|penrose drain 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PCN</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Percutaneous Nephrostomy tube</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Percutaneous Nephrostomy tube 유지 중임</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>방광루</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cystostomy tube</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>cystostomy tube 유지 중임|cystostomy 유지 중임</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>장루</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>장루</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>장루 통해 변 배출됨|장루 통해 변 배출 안됨|장루 통해 gas out 됨|장루 통해 gas out 안됨</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>공장루</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jejunostomy tube</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>jejunostomy tube로 유지 중임|jejunostomy tube로 배액됨|jejunostomy tube 삽입부위 출혈 있음|jejunostomy tube 삽입부위 출혈 없음|jejunostomy tube 삽입부위 통증 있음|jejunostomy tube 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>EVD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>External Ventricular Drainage</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>External Ventricular Drainage 통해 배액됨|External Ventricular Drainage 삽입부위 oozing 있음|External Ventricular Drainage 삽입부위 oozing 없음|External Ventricular Drainage 삽입부위 통증 있음|External Ventricular Drainage 삽입부위 통증 없음</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>경막외PCA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>epidural Patient Controlled Analgesics</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>epidural Patient Controlled Analgesics 유지 중임</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>★신규</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>상처</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>상처부위</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>상처 dressing 상태임</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>수술상처 dressing 상태임</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>수술상처 출혈 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>수술상처 출혈 없음</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>수술부위</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>수술상처 dressing 상태임|수술상처 출혈 있음|수술상처 출혈 없음</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -14123,7 +14123,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -14140,22 +14140,18 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D291" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>
       </c>
-      <c r="F291" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
+      <c r="F291" s="2" t="n"/>
       <c r="G291" s="2" t="inlineStr">
         <is>
           <t>체크</t>
@@ -14165,7 +14161,7 @@
       <c r="I291" s="2" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -14182,22 +14178,18 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D292" s="2" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
           <t>통증을 인정해줌</t>
         </is>
       </c>
-      <c r="F292" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
+      <c r="F292" s="2" t="n"/>
       <c r="G292" s="2" t="inlineStr">
         <is>
           <t>체크</t>
@@ -14207,7 +14199,7 @@
       <c r="I292" s="2" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -14224,22 +14216,18 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D293" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
           <t>통증을 관찰하기로 함</t>
         </is>
       </c>
-      <c r="F293" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
+      <c r="F293" s="2" t="n"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
           <t>체크</t>
@@ -14249,7 +14237,7 @@
       <c r="I293" s="2" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -14266,22 +14254,18 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D294" s="2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
           <t>통증 양상을 확인함</t>
         </is>
       </c>
-      <c r="F294" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
+      <c r="F294" s="2" t="n"/>
       <c r="G294" s="2" t="inlineStr">
         <is>
           <t>체크</t>
@@ -14295,7 +14279,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14300,7 @@
         </is>
       </c>
       <c r="D295" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
@@ -14350,7 +14334,7 @@
         </is>
       </c>
       <c r="D296" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
@@ -14384,7 +14368,7 @@
         </is>
       </c>
       <c r="D297" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
@@ -19331,7 +19315,6 @@
           <t>Foley catheter 유지 중임|Foley catheter 통해 소변 배출되고 있음</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -19352,7 +19335,6 @@
           <t>Levin tube 유지 중임|Levin tube 통해 배액됨</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19373,7 +19355,6 @@
           <t>중심정맥관 유지 중임</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -19394,7 +19375,6 @@
           <t>arterial line 유지 중임|arterial line를 통해 혈압 monitor 중임</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -19540,7 +19520,6 @@
           <t>흉관 유지 중임|흉관 통해 배액됨</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -19561,7 +19540,6 @@
           <t>기관절개관 유지 중임</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -19632,7 +19610,6 @@
           <t>Percutaneous Transhepatic Biliary Drainage 유지 중임|Percutaneous Transhepatic Biliary Drainage 통해 배액됨</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -19653,7 +19630,6 @@
           <t>Percutaneous Transhepatic Gall bladder Drainage 통해 배액됨</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -19674,7 +19650,6 @@
           <t>Percutaneous Drainage 유지 중임|Percutaneous Drainage 통해 배액됨</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -19720,7 +19695,6 @@
           <t>Percutaneous Nephrostomy tube 유지 중임</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19766,7 +19740,6 @@
           <t>장루 통해 변 배출됨|장루 통해 변 배출 안됨|장루 통해 gas out 됨|장루 통해 gas out 안됨</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -19862,7 +19835,6 @@
           <t>상처 dressing 상태임</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -19883,7 +19855,6 @@
           <t>수술상처 dressing 상태임|수술상처 출혈 있음|수술상처 출혈 없음</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -18846,7 +18846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19378,6 +19378,108 @@
       <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Seizure의 유발요인을 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>"물이나 이온음료를 조금씩 자주 먹여주세요."</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>경구수분섭취 격려함</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>"탈수 증상이 있는지 확인해드릴게요."</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>탈수 증상이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>"토하는 양상을 함께 확인할게요."</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>구토 양상 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>"긁으면 덧날 수 있어요. 손톱을 짧게 깎아주시고 긁지 않게 해주세요."</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>긁지 않도록 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>"가려움을 줄이는 방법을 알려드릴게요."</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>소양증 감소 방법에 대해 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>"피부 상태를 계속 살펴볼게요."</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -2244,7 +2244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K408"/>
+  <dimension ref="A1:K407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -11755,17 +11755,17 @@
       </c>
       <c r="E232" s="2" t="inlineStr">
         <is>
-          <t>Foley catheter 유지중임</t>
+          <t>dizziness있음/없음</t>
         </is>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>Foley catheter 삽입 여부를 확인하세요</t>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr"/>
@@ -11797,12 +11797,12 @@
       </c>
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오심이나 구토가 있으세요?"</t>
         </is>
       </c>
       <c r="G233" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>열감 있음/없음</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
         </is>
       </c>
       <c r="G234" s="2" t="inlineStr">
@@ -11881,12 +11881,12 @@
       </c>
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
         </is>
       </c>
       <c r="G235" s="2" t="inlineStr">
@@ -11915,27 +11915,19 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D236" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
-        </is>
-      </c>
-      <c r="F236" s="2" t="inlineStr">
-        <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G236" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr"/>
+      <c r="G236" s="2" t="inlineStr"/>
       <c r="H236" s="2" t="inlineStr"/>
       <c r="I236" s="2" t="inlineStr"/>
       <c r="J236" t="inlineStr">
@@ -11957,7 +11949,7 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D237" s="2" t="n">
@@ -11965,7 +11957,7 @@
       </c>
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="F237" s="2" t="inlineStr"/>
@@ -11995,17 +11987,21 @@
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="F238" s="2" t="inlineStr"/>
       <c r="G238" s="2" t="inlineStr"/>
       <c r="H238" s="2" t="inlineStr"/>
-      <c r="I238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J238" t="inlineStr">
         <is>
           <t>감염위험</t>
@@ -12015,38 +12011,42 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>CRP 수치 모를때, 감염 위험성 있을떄(배액관, 있을때, 열감 있을 떄)</t>
+          <t>고체온+통증없음</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D239" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
-        </is>
-      </c>
-      <c r="F239" s="2" t="inlineStr"/>
-      <c r="G239" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H239" s="2" t="inlineStr"/>
-      <c r="I239" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
+      <c r="I239" s="2" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>감염</t>
         </is>
       </c>
     </row>
@@ -12067,16 +12067,16 @@
         </is>
       </c>
       <c r="D240" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
         </is>
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오심이나 구토가 있으세요?"</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
@@ -12109,16 +12109,16 @@
         </is>
       </c>
       <c r="D241" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>열감 있음/없음</t>
         </is>
       </c>
       <c r="F241" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
@@ -12151,16 +12151,16 @@
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
@@ -12193,16 +12193,16 @@
         </is>
       </c>
       <c r="D243" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
+          <t>통증 있음/통증 없음</t>
         </is>
       </c>
       <c r="F243" s="2" t="inlineStr">
         <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
+          <t>"통증이 있으세요?"</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
@@ -12235,21 +12235,21 @@
         </is>
       </c>
       <c r="D244" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E244" s="2" t="inlineStr">
         <is>
-          <t>통증 있음/통증 없음</t>
+          <t>체온 상승함</t>
         </is>
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>"통증이 있으세요?"</t>
+          <t>체온을 측정하세요</t>
         </is>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr"/>
@@ -12273,27 +12273,19 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D245" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E245" s="2" t="inlineStr">
         <is>
-          <t>체온 상승함</t>
-        </is>
-      </c>
-      <c r="F245" s="2" t="inlineStr">
-        <is>
-          <t>체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="G245" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>감염</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr"/>
       <c r="I245" s="2" t="inlineStr"/>
       <c r="J245" t="inlineStr">
@@ -12315,7 +12307,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D246" s="2" t="n">
@@ -12323,7 +12315,7 @@
       </c>
       <c r="E246" s="2" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="F246" s="2" t="inlineStr"/>
@@ -12353,17 +12345,21 @@
         </is>
       </c>
       <c r="D247" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E247" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="F247" s="2" t="inlineStr"/>
       <c r="G247" s="2" t="inlineStr"/>
       <c r="H247" s="2" t="inlineStr"/>
-      <c r="I247" s="2" t="inlineStr"/>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J247" t="inlineStr">
         <is>
           <t>감염</t>
@@ -12378,33 +12374,42 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증없음</t>
+          <t>고체온+통증 있음</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D248" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E248" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
-        </is>
-      </c>
-      <c r="F248" s="2" t="inlineStr"/>
-      <c r="G248" s="2" t="inlineStr"/>
+          <t>dizziness있음/없음</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H248" s="2" t="inlineStr"/>
-      <c r="I248" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>감염</t>
+      <c r="I248" s="2" t="inlineStr"/>
+      <c r="J248" s="6" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>⚠️ 확인</t>
         </is>
       </c>
     </row>
@@ -12425,16 +12430,16 @@
         </is>
       </c>
       <c r="D249" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E249" s="2" t="inlineStr">
         <is>
-          <t>dizziness있음/없음</t>
+          <t>오심, 구토 없음/오심, 구토 있음</t>
         </is>
       </c>
       <c r="F249" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"오심이나 구토가 있으세요?"</t>
         </is>
       </c>
       <c r="G249" s="2" t="inlineStr">
@@ -12472,16 +12477,16 @@
         </is>
       </c>
       <c r="D250" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E250" s="2" t="inlineStr">
         <is>
-          <t>오심, 구토 없음/오심, 구토 있음</t>
+          <t>열감 있음/없음</t>
         </is>
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>"오심이나 구토가 있으세요?"</t>
+          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
         </is>
       </c>
       <c r="G250" s="2" t="inlineStr">
@@ -12491,14 +12496,9 @@
       </c>
       <c r="H250" s="2" t="inlineStr"/>
       <c r="I250" s="2" t="inlineStr"/>
-      <c r="J250" s="6" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>⚠️ 확인</t>
+      <c r="J250" s="7" t="inlineStr">
+        <is>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12519,16 +12519,16 @@
         </is>
       </c>
       <c r="D251" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E251" s="2" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F251" s="2" t="inlineStr">
         <is>
-          <t>"몸이 뜨겁거나 열이 나는 것 같으세요?"</t>
+          <t>"오한(춥고 떨림)이 있으세요?"</t>
         </is>
       </c>
       <c r="G251" s="2" t="inlineStr">
@@ -12561,21 +12561,21 @@
         </is>
       </c>
       <c r="D252" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E252" s="2" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
+          <t>체온 상승함</t>
         </is>
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>"오한(춥고 떨림)이 있으세요?"</t>
+          <t>체온을 측정하세요</t>
         </is>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr"/>
@@ -12603,28 +12603,32 @@
         </is>
       </c>
       <c r="D253" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E253" s="2" t="inlineStr">
         <is>
-          <t>체온 상승함</t>
+          <t>통증 있음/통증 없음</t>
         </is>
       </c>
       <c r="F253" s="2" t="inlineStr">
         <is>
-          <t>체온을 측정하세요</t>
+          <t>"통증이 있으세요?"</t>
         </is>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr"/>
-      <c r="I253" s="2" t="inlineStr"/>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="J253" s="7" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -12641,36 +12645,24 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D254" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E254" s="2" t="inlineStr">
         <is>
-          <t>통증 있음/통증 없음</t>
-        </is>
-      </c>
-      <c r="F254" s="2" t="inlineStr">
-        <is>
-          <t>"통증이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>고체온</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr"/>
+      <c r="G254" s="2" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr"/>
-      <c r="I254" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="J254" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+      <c r="I254" s="2" t="inlineStr"/>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12679,7 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D255" s="2" t="n">
@@ -12695,14 +12687,14 @@
       </c>
       <c r="E255" s="2" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="F255" s="2" t="inlineStr"/>
       <c r="G255" s="2" t="inlineStr"/>
       <c r="H255" s="2" t="inlineStr"/>
       <c r="I255" s="2" t="inlineStr"/>
-      <c r="J255" t="inlineStr">
+      <c r="J255" s="7" t="inlineStr">
         <is>
           <t>고체온</t>
         </is>
@@ -12725,17 +12717,21 @@
         </is>
       </c>
       <c r="D256" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E256" s="2" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="F256" s="2" t="inlineStr"/>
       <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr"/>
-      <c r="I256" s="2" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>통증은 없으나 불편할 때 사용</t>
+        </is>
+      </c>
       <c r="J256" s="7" t="inlineStr">
         <is>
           <t>고체온</t>
@@ -12755,7 +12751,7 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D257" s="2" t="n">
@@ -12763,20 +12759,16 @@
       </c>
       <c r="E257" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="F257" s="2" t="inlineStr"/>
       <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr"/>
-      <c r="I257" s="2" t="inlineStr">
-        <is>
-          <t>통증은 없으나 불편할 때 사용</t>
-        </is>
-      </c>
-      <c r="J257" s="7" t="inlineStr">
-        <is>
-          <t>고체온</t>
+      <c r="I257" s="2" t="inlineStr"/>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -12793,22 +12785,22 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D258" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E258" s="2" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="F258" s="2" t="inlineStr"/>
       <c r="G258" s="2" t="inlineStr"/>
       <c r="H258" s="2" t="inlineStr"/>
       <c r="I258" s="2" t="inlineStr"/>
-      <c r="J258" t="inlineStr">
+      <c r="J258" s="7" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>
@@ -12831,11 +12823,11 @@
         </is>
       </c>
       <c r="D259" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E259" s="2" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="F259" s="2" t="inlineStr"/>
@@ -12865,17 +12857,21 @@
         </is>
       </c>
       <c r="D260" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E260" s="2" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="F260" s="2" t="inlineStr"/>
       <c r="G260" s="2" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr"/>
-      <c r="I260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J260" s="7" t="inlineStr">
         <is>
           <t>급성통증</t>
@@ -12885,38 +12881,46 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>고체온+통증 있음</t>
+          <t>저체온</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D261" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E261" s="2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F261" s="2" t="inlineStr"/>
-      <c r="G261" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H261" s="2" t="inlineStr"/>
       <c r="I261" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
-      <c r="J261" s="7" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>저체온</t>
         </is>
       </c>
     </row>
@@ -12937,27 +12941,27 @@
         </is>
       </c>
       <c r="D262" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
       <c r="I262" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
@@ -12983,27 +12987,27 @@
         </is>
       </c>
       <c r="D263" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr"/>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -13029,27 +13033,27 @@
         </is>
       </c>
       <c r="D264" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E264" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>감각이상 있음/없음</t>
         </is>
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
         </is>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr"/>
       <c r="I264" s="2" t="inlineStr">
         <is>
-          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
+          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
@@ -13075,16 +13079,16 @@
         </is>
       </c>
       <c r="D265" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E265" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음/없음</t>
+          <t>grasp power 강함/약함</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
         <is>
-          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
+          <t>"제 손을 양손으로 꽉 쥐어보시겠어요?"</t>
         </is>
       </c>
       <c r="G265" s="2" t="inlineStr">
@@ -13095,7 +13099,7 @@
       <c r="H265" s="2" t="inlineStr"/>
       <c r="I265" s="2" t="inlineStr">
         <is>
-          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
+          <t>쳉ㅗㄴ 하강</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
@@ -13121,27 +13125,27 @@
         </is>
       </c>
       <c r="D266" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함/약함</t>
+          <t>체온 하강함</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>"제 손을 양손으로 꽉 쥐어보시겠어요?"</t>
+          <t>체온을 측정하세요</t>
         </is>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr"/>
       <c r="I266" s="2" t="inlineStr">
         <is>
-          <t>쳉ㅗㄴ 하강</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
@@ -13163,33 +13167,21 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D267" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>체온 하강함</t>
-        </is>
-      </c>
-      <c r="F267" s="2" t="inlineStr">
-        <is>
-          <t>체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="G267" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>저체온</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr"/>
+      <c r="G267" s="2" t="inlineStr"/>
       <c r="H267" s="2" t="inlineStr"/>
-      <c r="I267" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I267" s="2" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>저체온</t>
@@ -13209,7 +13201,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D268" s="2" t="n">
@@ -13217,7 +13209,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>저체온의 초기 증상에 대해 설명함</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr"/>
@@ -13247,11 +13239,11 @@
         </is>
       </c>
       <c r="D269" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E269" s="2" t="inlineStr">
         <is>
-          <t>저체온의 초기 증상에 대해 설명함</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr"/>
@@ -13281,17 +13273,21 @@
         </is>
       </c>
       <c r="D270" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E270" s="2" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>담요를 덮어줌</t>
         </is>
       </c>
       <c r="F270" s="2" t="inlineStr"/>
       <c r="G270" s="2" t="inlineStr"/>
       <c r="H270" s="2" t="inlineStr"/>
-      <c r="I270" s="2" t="inlineStr"/>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+        </is>
+      </c>
       <c r="J270" t="inlineStr">
         <is>
           <t>저체온</t>
@@ -13315,11 +13311,11 @@
         </is>
       </c>
       <c r="D271" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E271" s="2" t="inlineStr">
         <is>
-          <t>담요를 덮어줌</t>
+          <t>사지 근력 평가함</t>
         </is>
       </c>
       <c r="F271" s="2" t="inlineStr"/>
@@ -13327,7 +13323,7 @@
       <c r="H271" s="2" t="inlineStr"/>
       <c r="I271" s="2" t="inlineStr">
         <is>
-          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
@@ -13339,38 +13335,46 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색/뇌출혈 의심</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>뇌경색뇌출혈 관련</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D272" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E272" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="F272" s="2" t="inlineStr"/>
-      <c r="G272" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H272" s="2" t="inlineStr"/>
       <c r="I272" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>저체온</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -13391,27 +13395,27 @@
         </is>
       </c>
       <c r="D273" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E273" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr"/>
       <c r="I273" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
@@ -13437,27 +13441,27 @@
         </is>
       </c>
       <c r="D274" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -13483,27 +13487,27 @@
         </is>
       </c>
       <c r="D275" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E275" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>감각이상 있음/없음</t>
         </is>
       </c>
       <c r="F275" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
         </is>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr"/>
       <c r="I275" s="2" t="inlineStr">
         <is>
-          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
+          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
@@ -13529,16 +13533,16 @@
         </is>
       </c>
       <c r="D276" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E276" s="2" t="inlineStr">
         <is>
-          <t>감각이상 있음/없음</t>
+          <t>grasp power 강함/약함</t>
         </is>
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
+          <t>"제 손을 양손으로 꽉 쥐어보시겠어요?"</t>
         </is>
       </c>
       <c r="G276" s="2" t="inlineStr">
@@ -13549,7 +13553,7 @@
       <c r="H276" s="2" t="inlineStr"/>
       <c r="I276" s="2" t="inlineStr">
         <is>
-          <t>쥐는 함 양손 강한지, 약한지, 양쪽 손 쥐는 힘 같은지 다른지 따라 추가기록 +  post note 기록</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
@@ -13571,33 +13575,21 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D277" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E277" s="2" t="inlineStr">
         <is>
-          <t>grasp power 강함/약함</t>
-        </is>
-      </c>
-      <c r="F277" s="2" t="inlineStr">
-        <is>
-          <t>"제 손을 양손으로 꽉 쥐어보시겠어요?"</t>
-        </is>
-      </c>
-      <c r="G277" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr"/>
       <c r="H277" s="2" t="inlineStr"/>
-      <c r="I277" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I277" s="2" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>조직관류저하:뇌</t>
@@ -13617,7 +13609,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D278" s="2" t="n">
@@ -13625,13 +13617,17 @@
       </c>
       <c r="E278" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="F278" s="2" t="inlineStr"/>
       <c r="G278" s="2" t="inlineStr"/>
       <c r="H278" s="2" t="inlineStr"/>
-      <c r="I278" s="2" t="inlineStr"/>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+        </is>
+      </c>
       <c r="J278" t="inlineStr">
         <is>
           <t>조직관류저하:뇌</t>
@@ -13655,11 +13651,11 @@
         </is>
       </c>
       <c r="D279" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E279" s="2" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>사지 근력 평가함</t>
         </is>
       </c>
       <c r="F279" s="2" t="inlineStr"/>
@@ -13667,7 +13663,7 @@
       <c r="H279" s="2" t="inlineStr"/>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
@@ -13679,38 +13675,46 @@
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>뇌경색/뇌출혈 의심</t>
+          <t>심근경색 의심</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>뇌경색뇌출혈 관련</t>
+          <t>심근경색의심+통증없음</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D280" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E280" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="F280" s="2" t="inlineStr"/>
-      <c r="G280" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H280" s="2" t="inlineStr"/>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
@@ -13731,16 +13735,16 @@
         </is>
       </c>
       <c r="D281" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E281" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F281" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"숨이 차거나 답답하신가요?"</t>
         </is>
       </c>
       <c r="G281" s="2" t="inlineStr">
@@ -13749,11 +13753,7 @@
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr"/>
-      <c r="I281" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 여부 확인</t>
-        </is>
-      </c>
+      <c r="I281" s="2" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -13777,16 +13777,16 @@
         </is>
       </c>
       <c r="D282" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E282" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>흉부 불편감 있음/없음</t>
         </is>
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
+          <t>"가슴이 답답하거나 불편하신가요?"</t>
         </is>
       </c>
       <c r="G282" s="2" t="inlineStr">
@@ -13795,7 +13795,11 @@
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
-      <c r="I282" s="2" t="inlineStr"/>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+        </is>
+      </c>
       <c r="J282" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -13819,16 +13823,16 @@
         </is>
       </c>
       <c r="D283" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E283" s="2" t="inlineStr">
         <is>
-          <t>흉부 불편감 있음/없음</t>
+          <t>흉부 통증 있음/흉부 통증 없음</t>
         </is>
       </c>
       <c r="F283" s="2" t="inlineStr">
         <is>
-          <t>"가슴이 답답하거나 불편하신가요?"</t>
+          <t>"가슴이 아프세요?"</t>
         </is>
       </c>
       <c r="G283" s="2" t="inlineStr">
@@ -13839,7 +13843,7 @@
       <c r="H283" s="2" t="inlineStr"/>
       <c r="I283" s="2" t="inlineStr">
         <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
@@ -13865,27 +13869,27 @@
         </is>
       </c>
       <c r="D284" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증 있음/흉부 통증 없음</t>
+          <t>불규칙 맥박 촉지됨</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>"가슴이 아프세요?"</t>
+          <t>심전도(ECG) 결과를 확인하세요</t>
         </is>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
       <c r="I284" s="2" t="inlineStr">
         <is>
-          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
@@ -13907,33 +13911,21 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D285" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E285" s="2" t="inlineStr">
         <is>
-          <t>불규칙 맥박 촉지됨</t>
-        </is>
-      </c>
-      <c r="F285" s="2" t="inlineStr">
-        <is>
-          <t>심전도(ECG) 결과를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G285" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr"/>
       <c r="H285" s="2" t="inlineStr"/>
-      <c r="I285" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I285" s="2" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -13953,7 +13945,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D286" s="2" t="n">
@@ -13961,7 +13953,7 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>흉부 통증이 있는지 확인함</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr"/>
@@ -13991,17 +13983,21 @@
         </is>
       </c>
       <c r="D287" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E287" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
+          <t>심전도 변화를 확인함</t>
         </is>
       </c>
       <c r="F287" s="2" t="inlineStr"/>
       <c r="G287" s="2" t="inlineStr"/>
       <c r="H287" s="2" t="inlineStr"/>
-      <c r="I287" s="2" t="inlineStr"/>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J287" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14016,28 +14012,36 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증없음</t>
+          <t>심근경색의심+통증있음</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D288" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E288" s="2" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
-        </is>
-      </c>
-      <c r="F288" s="2" t="inlineStr"/>
-      <c r="G288" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H288" s="2" t="inlineStr"/>
       <c r="I288" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -14063,16 +14067,16 @@
         </is>
       </c>
       <c r="D289" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E289" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F289" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"숨이 차거나 답답하신가요?"</t>
         </is>
       </c>
       <c r="G289" s="2" t="inlineStr">
@@ -14081,11 +14085,7 @@
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr"/>
-      <c r="I289" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 여부 확인</t>
-        </is>
-      </c>
+      <c r="I289" s="2" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14109,16 +14109,16 @@
         </is>
       </c>
       <c r="D290" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E290" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>흉부 불편감 있음/없음</t>
         </is>
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
+          <t>"가슴이 답답하거나 불편하신가요?"</t>
         </is>
       </c>
       <c r="G290" s="2" t="inlineStr">
@@ -14127,7 +14127,11 @@
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr"/>
-      <c r="I290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+        </is>
+      </c>
       <c r="J290" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14151,16 +14155,16 @@
         </is>
       </c>
       <c r="D291" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E291" s="2" t="inlineStr">
         <is>
-          <t>흉부 불편감 있음/없음</t>
+          <t>흉부 통증 있음/흉부 통증 없음</t>
         </is>
       </c>
       <c r="F291" s="2" t="inlineStr">
         <is>
-          <t>"가슴이 답답하거나 불편하신가요?"</t>
+          <t>"가슴이 아프세요?"</t>
         </is>
       </c>
       <c r="G291" s="2" t="inlineStr">
@@ -14171,12 +14175,12 @@
       <c r="H291" s="2" t="inlineStr"/>
       <c r="I291" s="2" t="inlineStr">
         <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -14197,32 +14201,32 @@
         </is>
       </c>
       <c r="D292" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E292" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증 있음/흉부 통증 없음</t>
+          <t>불규칙 맥박 촉지됨</t>
         </is>
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>"가슴이 아프세요?"</t>
+          <t>심전도(ECG) 결과를 확인하세요</t>
         </is>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr"/>
       <c r="I292" s="2" t="inlineStr">
         <is>
-          <t>ECG에서 ST elevation 이나 depression, 부정맥 있음 post note에 기록.</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
@@ -14239,36 +14243,28 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D293" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E293" s="2" t="inlineStr">
         <is>
-          <t>불규칙 맥박 촉지됨</t>
-        </is>
-      </c>
-      <c r="F293" s="2" t="inlineStr">
-        <is>
-          <t>심전도(ECG) 결과를 확인하세요</t>
-        </is>
-      </c>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="n"/>
       <c r="G293" s="2" t="inlineStr">
         <is>
           <t>체크</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr"/>
-      <c r="I293" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I293" s="2" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -14285,7 +14281,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D294" s="2" t="n">
@@ -14293,7 +14289,7 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="F294" s="2" t="n"/>
@@ -14327,11 +14323,11 @@
         </is>
       </c>
       <c r="D295" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="F295" s="2" t="n"/>
@@ -14365,11 +14361,11 @@
         </is>
       </c>
       <c r="D296" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E296" s="2" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="F296" s="2" t="n"/>
@@ -14379,7 +14375,11 @@
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr"/>
-      <c r="I296" s="2" t="inlineStr"/>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>GCS 15 일때</t>
+        </is>
+      </c>
       <c r="J296" t="inlineStr">
         <is>
           <t>급성통증</t>
@@ -14399,32 +14399,24 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D297" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E297" s="2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="F297" s="2" t="n"/>
-      <c r="G297" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr"/>
+      <c r="G297" s="2" t="inlineStr"/>
       <c r="H297" s="2" t="inlineStr"/>
-      <c r="I297" s="2" t="inlineStr">
-        <is>
-          <t>GCS 15 일때</t>
-        </is>
-      </c>
+      <c r="I297" s="2" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>조직관류저하:심폐계</t>
         </is>
       </c>
     </row>
@@ -14441,15 +14433,15 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D298" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>흉부 통증이 있는지 확인함</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr"/>
@@ -14479,17 +14471,21 @@
         </is>
       </c>
       <c r="D299" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E299" s="2" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
+          <t>심전도 변화를 확인함</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr"/>
       <c r="G299" s="2" t="inlineStr"/>
       <c r="H299" s="2" t="inlineStr"/>
-      <c r="I299" s="2" t="inlineStr"/>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+        </is>
+      </c>
       <c r="J299" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
@@ -14499,38 +14495,46 @@
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>심근경색 의심</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>심근경색의심+통증있음</t>
+          <t>고혈당</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D300" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E300" s="2" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
-        </is>
-      </c>
-      <c r="F300" s="2" t="inlineStr"/>
-      <c r="G300" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H300" s="2" t="inlineStr"/>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>강도/ 빈도/ 양상/ 기간/ 부위</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>조직관류저하:심폐계</t>
+          <t>고혈당</t>
         </is>
       </c>
     </row>
@@ -14551,16 +14555,16 @@
         </is>
       </c>
       <c r="D301" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E301" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F301" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"숨이 차거나 답답하신가요?"</t>
         </is>
       </c>
       <c r="G301" s="2" t="inlineStr">
@@ -14569,11 +14573,7 @@
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr"/>
-      <c r="I301" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 여부 확인</t>
-        </is>
-      </c>
+      <c r="I301" s="2" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>고혈당</t>
@@ -14597,25 +14597,29 @@
         </is>
       </c>
       <c r="D302" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E302" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>혈당 증가함</t>
         </is>
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
+          <t>혈당 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr"/>
-      <c r="I302" s="2" t="inlineStr"/>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>오심,다뇨,구토, 갈증, 의식변화 등</t>
+        </is>
+      </c>
       <c r="J302" t="inlineStr">
         <is>
           <t>고혈당</t>
@@ -14639,29 +14643,25 @@
         </is>
       </c>
       <c r="D303" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E303" s="2" t="inlineStr">
         <is>
-          <t>혈당 증가함</t>
+          <t>고혈당 증상 있음/없음</t>
         </is>
       </c>
       <c r="F303" s="2" t="inlineStr">
         <is>
-          <t>혈당 수치를 확인하세요</t>
+          <t>"갈증이 심하거나 소변이 자주 나오세요?"</t>
         </is>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr"/>
-      <c r="I303" s="2" t="inlineStr">
-        <is>
-          <t>오심,다뇨,구토, 갈증, 의식변화 등</t>
-        </is>
-      </c>
+      <c r="I303" s="2" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>고혈당</t>
@@ -14681,27 +14681,19 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D304" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E304" s="2" t="inlineStr">
         <is>
-          <t>고혈당 증상 있음/없음</t>
-        </is>
-      </c>
-      <c r="F304" s="2" t="inlineStr">
-        <is>
-          <t>"갈증이 심하거나 소변이 자주 나오세요?"</t>
-        </is>
-      </c>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>고혈당</t>
+        </is>
+      </c>
+      <c r="F304" s="2" t="inlineStr"/>
+      <c r="G304" s="2" t="inlineStr"/>
       <c r="H304" s="2" t="inlineStr"/>
       <c r="I304" s="2" t="inlineStr"/>
       <c r="J304" t="inlineStr">
@@ -14723,7 +14715,7 @@
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D305" s="2" t="n">
@@ -14731,13 +14723,17 @@
       </c>
       <c r="E305" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="F305" s="2" t="inlineStr"/>
       <c r="G305" s="2" t="inlineStr"/>
       <c r="H305" s="2" t="inlineStr"/>
-      <c r="I305" s="2" t="inlineStr"/>
+      <c r="I305" s="2" t="inlineStr">
+        <is>
+          <t>인슐린 투여시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
+        </is>
+      </c>
       <c r="J305" t="inlineStr">
         <is>
           <t>고혈당</t>
@@ -14761,11 +14757,11 @@
         </is>
       </c>
       <c r="D306" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E306" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>처방에 의해 인슐린 투여함</t>
         </is>
       </c>
       <c r="F306" s="2" t="inlineStr"/>
@@ -14773,7 +14769,7 @@
       <c r="H306" s="2" t="inlineStr"/>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>인슐린 투여시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
@@ -14785,38 +14781,46 @@
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D307" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E307" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 인슐린 투여함</t>
-        </is>
-      </c>
-      <c r="F307" s="2" t="inlineStr"/>
-      <c r="G307" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F307" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H307" s="2" t="inlineStr"/>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>호흡곤란 여부 확인</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>고혈당</t>
+          <t>저혈당</t>
         </is>
       </c>
     </row>
@@ -14837,16 +14841,16 @@
         </is>
       </c>
       <c r="D308" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E308" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>"숨이 차거나 답답하신가요?"</t>
         </is>
       </c>
       <c r="G308" s="2" t="inlineStr">
@@ -14855,11 +14859,7 @@
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr"/>
-      <c r="I308" s="2" t="inlineStr">
-        <is>
-          <t>호흡곤란 여부 확인</t>
-        </is>
-      </c>
+      <c r="I308" s="2" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>저혈당</t>
@@ -14883,25 +14883,29 @@
         </is>
       </c>
       <c r="D309" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E309" s="2" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>혈당 떨어짐</t>
         </is>
       </c>
       <c r="F309" s="2" t="inlineStr">
         <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
+          <t>혈당 수치를 확인하세요</t>
         </is>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr"/>
-      <c r="I309" s="2" t="inlineStr"/>
+      <c r="I309" s="2" t="inlineStr">
+        <is>
+          <t>진전, 빈맥, 발한, 감각이상, 의식변화</t>
+        </is>
+      </c>
       <c r="J309" t="inlineStr">
         <is>
           <t>저혈당</t>
@@ -14925,29 +14929,25 @@
         </is>
       </c>
       <c r="D310" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E310" s="2" t="inlineStr">
         <is>
-          <t>혈당 떨어짐</t>
+          <t>저혈당 증상 있음/없음</t>
         </is>
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>혈당 수치를 확인하세요</t>
+          <t>"식은땀이 나거나 손이 떨리세요?"</t>
         </is>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr"/>
-      <c r="I310" s="2" t="inlineStr">
-        <is>
-          <t>진전, 빈맥, 발한, 감각이상, 의식변화</t>
-        </is>
-      </c>
+      <c r="I310" s="2" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>저혈당</t>
@@ -14967,27 +14967,19 @@
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D311" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E311" s="2" t="inlineStr">
         <is>
-          <t>저혈당 증상 있음/없음</t>
-        </is>
-      </c>
-      <c r="F311" s="2" t="inlineStr">
-        <is>
-          <t>"식은땀이 나거나 손이 떨리세요?"</t>
-        </is>
-      </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>저혈당</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr"/>
       <c r="I311" s="2" t="inlineStr"/>
       <c r="J311" t="inlineStr">
@@ -15009,7 +15001,7 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D312" s="2" t="n">
@@ -15017,7 +15009,7 @@
       </c>
       <c r="E312" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="F312" s="2" t="inlineStr"/>
@@ -15047,17 +15039,21 @@
         </is>
       </c>
       <c r="D313" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E313" s="2" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>저혈당 증상(진전, 빈맥, 발한, 감각이상, 의식변화)에 대해 설명함</t>
         </is>
       </c>
       <c r="F313" s="2" t="inlineStr"/>
       <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr"/>
-      <c r="I313" s="2" t="inlineStr"/>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>D5% 처방시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
+        </is>
+      </c>
       <c r="J313" t="inlineStr">
         <is>
           <t>저혈당</t>
@@ -15081,11 +15077,11 @@
         </is>
       </c>
       <c r="D314" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E314" s="2" t="inlineStr">
         <is>
-          <t>저혈당 증상(진전, 빈맥, 발한, 감각이상, 의식변화)에 대해 설명함</t>
+          <t>처방에 의해 D50W 을 투여함</t>
         </is>
       </c>
       <c r="F314" s="2" t="inlineStr"/>
@@ -15093,7 +15089,7 @@
       <c r="H314" s="2" t="inlineStr"/>
       <c r="I314" s="2" t="inlineStr">
         <is>
-          <t>D5% 처방시 용량, 경로, 주입속도, 오더형태, 의사명 기입</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
@@ -15105,38 +15101,46 @@
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D315" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E315" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 D50W 을 투여함</t>
-        </is>
-      </c>
-      <c r="F315" s="2" t="inlineStr"/>
-      <c r="G315" s="2" t="inlineStr"/>
+          <t>Seizure 있음</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>발작 양상을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H315" s="2" t="inlineStr"/>
       <c r="I315" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>저혈당</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -15157,27 +15161,27 @@
         </is>
       </c>
       <c r="D316" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E316" s="2" t="inlineStr">
         <is>
-          <t>Seizure 있음</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>발작 양상을 확인하세요</t>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr"/>
       <c r="I316" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
@@ -15203,27 +15207,27 @@
         </is>
       </c>
       <c r="D317" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr"/>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
@@ -15245,33 +15249,21 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D318" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E318" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
-        </is>
-      </c>
-      <c r="F318" s="2" t="inlineStr">
-        <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
-        </is>
-      </c>
-      <c r="G318" s="2" t="inlineStr">
-        <is>
-          <t>선택</t>
-        </is>
-      </c>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr"/>
+      <c r="G318" s="2" t="inlineStr"/>
       <c r="H318" s="2" t="inlineStr"/>
-      <c r="I318" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I318" s="2" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15291,7 +15283,7 @@
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D319" s="2" t="n">
@@ -15299,13 +15291,17 @@
       </c>
       <c r="E319" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="F319" s="2" t="inlineStr"/>
       <c r="G319" s="2" t="inlineStr"/>
       <c r="H319" s="2" t="inlineStr"/>
-      <c r="I319" s="2" t="inlineStr"/>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>airway유지</t>
+        </is>
+      </c>
       <c r="J319" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15329,21 +15325,17 @@
         </is>
       </c>
       <c r="D320" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E320" s="2" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="F320" s="2" t="inlineStr"/>
       <c r="G320" s="2" t="inlineStr"/>
       <c r="H320" s="2" t="inlineStr"/>
-      <c r="I320" s="2" t="inlineStr">
-        <is>
-          <t>airway유지</t>
-        </is>
-      </c>
+      <c r="I320" s="2" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15367,17 +15359,21 @@
         </is>
       </c>
       <c r="D321" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E321" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>seizure의 유발요인을 확인함</t>
         </is>
       </c>
       <c r="F321" s="2" t="inlineStr"/>
       <c r="G321" s="2" t="inlineStr"/>
       <c r="H321" s="2" t="inlineStr"/>
-      <c r="I321" s="2" t="inlineStr"/>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>의사처방시</t>
+        </is>
+      </c>
       <c r="J321" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15401,11 +15397,11 @@
         </is>
       </c>
       <c r="D322" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E322" s="2" t="inlineStr">
         <is>
-          <t>seizure의 유발요인을 확인함</t>
+          <t>처방에 의해 Lorazepam을 투여함</t>
         </is>
       </c>
       <c r="F322" s="2" t="inlineStr"/>
@@ -15413,7 +15409,7 @@
       <c r="H322" s="2" t="inlineStr"/>
       <c r="I322" s="2" t="inlineStr">
         <is>
-          <t>의사처방시</t>
+          <t>GCS 15 미만일 떄</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
@@ -15430,28 +15426,36 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D323" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E323" s="2" t="inlineStr">
         <is>
-          <t>처방에 의해 Lorazepam을 투여함</t>
-        </is>
-      </c>
-      <c r="F323" s="2" t="inlineStr"/>
-      <c r="G323" s="2" t="inlineStr"/>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
       <c r="H323" s="2" t="inlineStr"/>
       <c r="I323" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 미만일 떄</t>
+          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
@@ -15477,27 +15481,27 @@
         </is>
       </c>
       <c r="D324" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E324" s="2" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr"/>
       <c r="I324" s="2" t="inlineStr">
         <is>
-          <t>Rt/Lt/대칭여부/Rt모양/Lt모양</t>
+          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
@@ -15523,29 +15527,25 @@
         </is>
       </c>
       <c r="D325" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr"/>
-      <c r="I325" s="2" t="inlineStr">
-        <is>
-          <t>두통 환자 동공크기 여부 변화 반드시 확인(뇌출혈, 뇌경색 등 감별 위함)</t>
-        </is>
-      </c>
+      <c r="I325" s="2" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15569,21 +15569,21 @@
         </is>
       </c>
       <c r="D326" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E326" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>Seizure 멈춤/없음</t>
         </is>
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>"발작이 멈췄나요?"</t>
         </is>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr"/>
@@ -15611,16 +15611,16 @@
         </is>
       </c>
       <c r="D327" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E327" s="2" t="inlineStr">
         <is>
-          <t>Seizure 멈춤/없음</t>
+          <t>Seizure 유사증상 있음/없음</t>
         </is>
       </c>
       <c r="F327" s="2" t="inlineStr">
         <is>
-          <t>"발작이 멈췄나요?"</t>
+          <t>"발작과 비슷한 증상이 있었나요?"</t>
         </is>
       </c>
       <c r="G327" s="2" t="inlineStr">
@@ -15629,7 +15629,11 @@
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr"/>
-      <c r="I327" s="2" t="inlineStr"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
       <c r="J327" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15649,33 +15653,21 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D328" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>Seizure 유사증상 있음/없음</t>
-        </is>
-      </c>
-      <c r="F328" s="2" t="inlineStr">
-        <is>
-          <t>"발작과 비슷한 증상이 있었나요?"</t>
-        </is>
-      </c>
-      <c r="G328" s="2" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr"/>
+      <c r="G328" s="2" t="inlineStr"/>
       <c r="H328" s="2" t="inlineStr"/>
-      <c r="I328" s="2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
+      <c r="I328" s="2" t="inlineStr"/>
       <c r="J328" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15695,7 +15687,7 @@
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D329" s="2" t="n">
@@ -15703,13 +15695,17 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr"/>
       <c r="G329" s="2" t="inlineStr"/>
       <c r="H329" s="2" t="inlineStr"/>
-      <c r="I329" s="2" t="inlineStr"/>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>airway유지</t>
+        </is>
+      </c>
       <c r="J329" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15733,21 +15729,17 @@
         </is>
       </c>
       <c r="D330" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E330" s="2" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="F330" s="2" t="inlineStr"/>
       <c r="G330" s="2" t="inlineStr"/>
       <c r="H330" s="2" t="inlineStr"/>
-      <c r="I330" s="2" t="inlineStr">
-        <is>
-          <t>airway유지</t>
-        </is>
-      </c>
+      <c r="I330" s="2" t="inlineStr"/>
       <c r="J330" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15771,17 +15763,21 @@
         </is>
       </c>
       <c r="D331" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E331" s="2" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>seizure의 유발요인을 확인함</t>
         </is>
       </c>
       <c r="F331" s="2" t="inlineStr"/>
       <c r="G331" s="2" t="inlineStr"/>
       <c r="H331" s="2" t="inlineStr"/>
-      <c r="I331" s="2" t="inlineStr"/>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+        </is>
+      </c>
       <c r="J331" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -15805,11 +15801,11 @@
         </is>
       </c>
       <c r="D332" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E332" s="2" t="inlineStr">
         <is>
-          <t>seizure의 유발요인을 확인함</t>
+          <t>사지 근력 평가함</t>
         </is>
       </c>
       <c r="F332" s="2" t="inlineStr"/>
@@ -15817,7 +15813,7 @@
       <c r="H332" s="2" t="inlineStr"/>
       <c r="I332" s="2" t="inlineStr">
         <is>
-          <t>LLE/LUE/RLE/RUE(좌하지, 좌상지, 우하지, 우상지) 5점 : 손으로 눌러도 버티거나 더 강함 4점 : 힘은 있으나 손으로 누르면 내려감, 3점: 들기는 하나 손으로 내리면 슥 내려감, 2점 겨우 손을 들긴 하지만 곧바로 내려감, 1점 :손가락을 꼼지락 하는 정도, 0점 : 움직임 없음</t>
+          <t>GCS 15 일때</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
@@ -15829,38 +15825,46 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>의식/낙상 사정</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>이미 Seizure를 하고 멈춘뒤 내원할 때</t>
+          <t>의식 및 낙상위험 평가</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D333" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E333" s="2" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
-        </is>
-      </c>
-      <c r="F333" s="2" t="inlineStr"/>
-      <c r="G333" s="2" t="inlineStr"/>
+          <t>의식 명료함</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>확인하세요</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
       <c r="H333" s="2" t="inlineStr"/>
       <c r="I333" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 일때</t>
+          <t>GCS 15 미만일 떄</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>낙상위험</t>
         </is>
       </c>
     </row>
@@ -15881,11 +15885,11 @@
         </is>
       </c>
       <c r="D334" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E334" s="2" t="inlineStr">
         <is>
-          <t>의식 명료함</t>
+          <t>의식수준 :</t>
         </is>
       </c>
       <c r="F334" s="2" t="inlineStr">
@@ -15895,13 +15899,13 @@
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr"/>
       <c r="I334" s="2" t="inlineStr">
         <is>
-          <t>GCS 15 미만일 떄</t>
+          <t>보호자 있을시</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
@@ -15927,11 +15931,11 @@
         </is>
       </c>
       <c r="D335" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E335" s="2" t="inlineStr">
         <is>
-          <t>의식수준 :</t>
+          <t>보호자 환자 옆에 상주하고 있음</t>
         </is>
       </c>
       <c r="F335" s="2" t="inlineStr">
@@ -15941,13 +15945,13 @@
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr"/>
       <c r="I335" s="2" t="inlineStr">
         <is>
-          <t>보호자 있을시</t>
+          <t>보호자 없을시</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
@@ -15973,11 +15977,11 @@
         </is>
       </c>
       <c r="D336" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E336" s="2" t="inlineStr">
         <is>
-          <t>보호자 환자 옆에 상주하고 있음</t>
+          <t>보호자 동행하지 않음</t>
         </is>
       </c>
       <c r="F336" s="2" t="inlineStr">
@@ -15993,7 +15997,7 @@
       <c r="H336" s="2" t="inlineStr"/>
       <c r="I336" s="2" t="inlineStr">
         <is>
-          <t>보호자 없을시</t>
+          <t>가능하지 않을 떄</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
@@ -16019,11 +16023,11 @@
         </is>
       </c>
       <c r="D337" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E337" s="2" t="inlineStr">
         <is>
-          <t>보호자 동행하지 않음</t>
+          <t>Obey command 가능함/ Obey command 가능하지 않음</t>
         </is>
       </c>
       <c r="F337" s="2" t="inlineStr">
@@ -16033,15 +16037,11 @@
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr"/>
-      <c r="I337" s="2" t="inlineStr">
-        <is>
-          <t>가능하지 않을 떄</t>
-        </is>
-      </c>
+      <c r="I337" s="2" t="inlineStr"/>
       <c r="J337" t="inlineStr">
         <is>
           <t>낙상위험</t>
@@ -16065,11 +16065,11 @@
         </is>
       </c>
       <c r="D338" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E338" s="2" t="inlineStr">
         <is>
-          <t>Obey command 가능함/ Obey command 가능하지 않음</t>
+          <t>시간에대한 지남력 없음/사람에 대한 지남력 없음/ 장소에 대한 지남력 없음</t>
         </is>
       </c>
       <c r="F338" s="2" t="inlineStr">
@@ -16079,11 +16079,15 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr"/>
-      <c r="I338" s="2" t="inlineStr"/>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>Post note에 세부사항 기록하기</t>
+        </is>
+      </c>
       <c r="J338" t="inlineStr">
         <is>
           <t>낙상위험</t>
@@ -16107,11 +16111,11 @@
         </is>
       </c>
       <c r="D339" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E339" s="2" t="inlineStr">
         <is>
-          <t>시간에대한 지남력 없음/사람에 대한 지남력 없음/ 장소에 대한 지남력 없음</t>
+          <t>시간, 사람, 장소에 대한 지남력 없음</t>
         </is>
       </c>
       <c r="F339" s="2" t="inlineStr">
@@ -16121,13 +16125,13 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr"/>
       <c r="I339" s="2" t="inlineStr">
         <is>
-          <t>Post note에 세부사항 기록하기</t>
+          <t>보호자 있을시</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
@@ -16149,33 +16153,21 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D340" s="2" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E340" s="2" t="inlineStr">
         <is>
-          <t>시간, 사람, 장소에 대한 지남력 없음</t>
-        </is>
-      </c>
-      <c r="F340" s="2" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G340" s="2" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
+          <t>낙상위험</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr"/>
+      <c r="G340" s="2" t="inlineStr"/>
       <c r="H340" s="2" t="inlineStr"/>
-      <c r="I340" s="2" t="inlineStr">
-        <is>
-          <t>보호자 있을시</t>
-        </is>
-      </c>
+      <c r="I340" s="2" t="inlineStr"/>
       <c r="J340" t="inlineStr">
         <is>
           <t>낙상위험</t>
@@ -16195,7 +16187,7 @@
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D341" s="2" t="n">
@@ -16203,13 +16195,17 @@
       </c>
       <c r="E341" s="2" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>낙상방지 교육함</t>
         </is>
       </c>
       <c r="F341" s="2" t="inlineStr"/>
       <c r="G341" s="2" t="inlineStr"/>
       <c r="H341" s="2" t="inlineStr"/>
-      <c r="I341" s="2" t="inlineStr"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>침대 난간 올려줬을 시</t>
+        </is>
+      </c>
       <c r="J341" t="inlineStr">
         <is>
           <t>낙상위험</t>
@@ -16233,11 +16229,11 @@
         </is>
       </c>
       <c r="D342" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E342" s="2" t="inlineStr">
         <is>
-          <t>낙상방지 교육함</t>
+          <t>침대 난간을 올려줌</t>
         </is>
       </c>
       <c r="F342" s="2" t="inlineStr"/>
@@ -16245,7 +16241,7 @@
       <c r="H342" s="2" t="inlineStr"/>
       <c r="I342" s="2" t="inlineStr">
         <is>
-          <t>침대 난간 올려줬을 시</t>
+          <t>보호자 있을시, 낙상 위험 높을시</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
@@ -16271,11 +16267,11 @@
         </is>
       </c>
       <c r="D343" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E343" s="2" t="inlineStr">
         <is>
-          <t>침대 난간을 올려줌</t>
+          <t>보호자와 같이 있게 함</t>
         </is>
       </c>
       <c r="F343" s="2" t="inlineStr"/>
@@ -16283,7 +16279,7 @@
       <c r="H343" s="2" t="inlineStr"/>
       <c r="I343" s="2" t="inlineStr">
         <is>
-          <t>보호자 있을시, 낙상 위험 높을시</t>
+          <t>보호자 있을시</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
@@ -16309,11 +16305,11 @@
         </is>
       </c>
       <c r="D344" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E344" s="2" t="inlineStr">
         <is>
-          <t>보호자와 같이 있게 함</t>
+          <t>보호자 동반하도록 설명함</t>
         </is>
       </c>
       <c r="F344" s="2" t="inlineStr"/>
@@ -16321,7 +16317,7 @@
       <c r="H344" s="2" t="inlineStr"/>
       <c r="I344" s="2" t="inlineStr">
         <is>
-          <t>보호자 있을시</t>
+          <t>보호자 없을시</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
@@ -16347,11 +16343,11 @@
         </is>
       </c>
       <c r="D345" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E345" s="2" t="inlineStr">
         <is>
-          <t>보호자 동반하도록 설명함</t>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="F345" s="2" t="inlineStr"/>
@@ -16359,7 +16355,7 @@
       <c r="H345" s="2" t="inlineStr"/>
       <c r="I345" s="2" t="inlineStr">
         <is>
-          <t>보호자 없을시</t>
+          <t>낙상위험 교육</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
@@ -16369,40 +16365,47 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="inlineStr">
-        <is>
-          <t>의식/낙상 사정</t>
-        </is>
-      </c>
-      <c r="B346" s="2" t="inlineStr">
-        <is>
-          <t>의식 및 낙상위험 평가</t>
-        </is>
-      </c>
-      <c r="C346" s="2" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D346" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="E346" s="2" t="inlineStr">
-        <is>
-          <t>손상을 예방하는 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="F346" s="2" t="inlineStr"/>
-      <c r="G346" s="2" t="inlineStr"/>
-      <c r="H346" s="2" t="inlineStr"/>
-      <c r="I346" s="2" t="inlineStr">
-        <is>
-          <t>낙상위험 교육</t>
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>소아-발열</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D346" t="n">
+        <v>1</v>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>열감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>"열이 나나요?"</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -16423,16 +16426,16 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>"열이 나나요?"</t>
+          <t>"춥다고 하거나 몸을 떨었나요?"</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -16468,21 +16471,21 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
+          <t>체온 상승함/체온 하강함</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>"춥다고 하거나 몸을 떨었나요?"</t>
+          <t>🩺 체온을 측정하세요</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -16513,21 +16516,21 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>체온 상승함/체온 하강함</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>🩺 체온을 측정하세요</t>
+          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -16558,21 +16561,21 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -16603,21 +16606,21 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
+          <t>구토함/구토 없음</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
+          <t>"토했나요?"</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -16644,25 +16647,15 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D352" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>구토함/구토 없음</t>
-        </is>
-      </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>"토했나요?"</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -16689,7 +16682,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D353" t="n">
@@ -16697,7 +16690,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -16728,11 +16721,11 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>미온수 목욕 시행함</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -16763,11 +16756,11 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>미온수 목욕 시행함</t>
+          <t>처방에 의해 해열제를 투여함</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -16789,30 +16782,40 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D356" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>처방에 의해 해열제를 투여함</t>
+          <t>구토함/구토 없음</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>"토했나요?"</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>횟수는 📌비고에 기재</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -16833,16 +16836,16 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>구토함/구토 없음</t>
+          <t>오심 있음/없음</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>"토했나요?"</t>
+          <t>"메스꺼워 하나요?"</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -16852,7 +16855,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>횟수는 📌비고에 기재</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
@@ -16878,16 +16881,16 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>오심 있음/없음</t>
+          <t>설사 있음/없음</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>"메스꺼워 하나요?"</t>
+          <t>"설사하나요?"</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -16897,7 +16900,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>횟수는 📌비고에 기재</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
@@ -16923,16 +16926,16 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>설사 있음/없음</t>
+          <t>구강건조 있음/없음</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>"설사하나요?"</t>
+          <t>"입술이나 입 안이 말라 있나요?"</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -16942,7 +16945,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>횟수는 📌비고에 기재</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
@@ -16968,16 +16971,16 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>구강건조 있음/없음</t>
+          <t>갈증 있음/없음</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>"입술이나 입 안이 말라 있나요?"</t>
+          <t>"물을 자꾸 찾나요?"</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -17013,21 +17016,21 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>갈증 있음/없음</t>
+          <t>피부 탄력성 저하됨</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>"물을 자꾸 찾나요?"</t>
+          <t>🩺 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -17058,16 +17061,16 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>피부 탄력성 저하됨</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>🩺 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
+          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -17103,21 +17106,21 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
+          <t>복부 통증 있음/없음</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
+          <t>"배가 아프다고 하나요?"</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -17144,25 +17147,15 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D364" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>복부 통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>"배가 아프다고 하나요?"</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>체액부족위험</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -17189,7 +17182,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D365" t="n">
@@ -17197,7 +17190,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>탈수 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -17228,11 +17221,11 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>탈수 증상이 있는지 확인함</t>
+          <t>경구수분섭취 격려함</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -17263,11 +17256,11 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>경구수분섭취 격려함</t>
+          <t>구토 양상 확인함</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -17289,20 +17282,30 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>구토 양상 확인함</t>
+          <t>호흡곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -17312,7 +17315,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -17333,16 +17336,16 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>chest retraction 있음/없음</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
+          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
@@ -17378,16 +17381,16 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>chest retraction 있음/없음</t>
+          <t>wheezing 있음/없음</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
+          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -17423,16 +17426,16 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>wheezing 있음/없음</t>
+          <t>기침 있음/없음</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
+          <t>"기침하나요?"</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -17468,16 +17471,16 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>기침 있음/없음</t>
+          <t>가래 잘 뱉지 못함/가래 잘 뱉어냄</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>"기침하나요?"</t>
+          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -17513,16 +17516,16 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>가래 잘 뱉지 못함/가래 잘 뱉어냄</t>
+          <t>청색증 있음/없음</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
+          <t>"입술이나 얼굴이 파래 보이나요?"</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -17558,16 +17561,16 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>청색증 있음/없음</t>
+          <t>말단 청색증 있음/없음</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>"입술이나 얼굴이 파래 보이나요?"</t>
+          <t>"손끝·발끝이 파래 보이나요?"</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
@@ -17599,25 +17602,15 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>말단 청색증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>"손끝·발끝이 파래 보이나요?"</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -17644,7 +17637,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -17652,7 +17645,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -17683,11 +17676,11 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>호흡곤란이 있는지 확인함</t>
+          <t>산소포화도 monitor 함</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -17718,11 +17711,11 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>산소포화도 monitor 함</t>
+          <t>산소 흡입 시작함</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -17744,30 +17737,40 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>산소 흡입 시작함</t>
+          <t>경련 있음</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>"경련(발작)을 했나요?"</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>지속시간은 📌비고에 기재</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -17788,16 +17791,16 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>경련 있음</t>
+          <t>경련과 유사한 증상 보임</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>"경련(발작)을 했나요?"</t>
+          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
@@ -17807,7 +17810,7 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>지속시간은 📌비고에 기재</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
@@ -17833,21 +17836,21 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>경련과 유사한 증상 보임</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
+          <t>"경련 후 축 처져 있나요?"</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -17878,21 +17881,21 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>"경련 후 축 처져 있나요?"</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -17923,21 +17926,21 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
+          <t>체온 상승함</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
+          <t>🩺 체온을 측정하세요</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -17964,25 +17967,15 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D384" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>체온 상승함</t>
-        </is>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>🩺 체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="G384" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -18009,7 +18002,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D385" t="n">
@@ -18017,7 +18010,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -18048,11 +18041,11 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>seizure의 유발요인을 확인함</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -18083,11 +18076,11 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>seizure의 유발요인을 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -18109,20 +18102,30 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>urticaria 있음/없음</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -18132,7 +18135,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -18153,16 +18156,16 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>urticaria 있음/없음</t>
+          <t>기저귀 발진 있음/없음</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>"두드러기가 올라왔나요?"</t>
+          <t>🩺 기저귀 부위 발진을 확인하세요</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
@@ -18198,16 +18201,16 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>기저귀 발진 있음/없음</t>
+          <t>가려움증 있음/가려움증 없음</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>🩺 기저귀 부위 발진을 확인하세요</t>
+          <t>"가려워하나요?"</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -18217,7 +18220,7 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ 보강</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
@@ -18243,16 +18246,16 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>가려움증 있음/가려움증 없음</t>
+          <t>bullae 있음/bullae 없음</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>"가려워하나요?"</t>
+          <t>🩺 물집이 잡혔는지 확인하세요</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
@@ -18288,16 +18291,16 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>bullae 있음/bullae 없음</t>
+          <t>열감 있음/열감 없음</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>🩺 물집이 잡혔는지 확인하세요</t>
+          <t>"열이 나나요?"</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -18329,30 +18332,20 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D393" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>열감 있음/열감 없음</t>
-        </is>
-      </c>
-      <c r="F393" t="inlineStr">
-        <is>
-          <t>"열이 나나요?"</t>
-        </is>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>⚠️ 보강</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
@@ -18374,7 +18367,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D394" t="n">
@@ -18382,7 +18375,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -18413,11 +18406,11 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>긁지 않도록 교육함</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -18448,11 +18441,11 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
+          <t>소양증 감소 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -18474,20 +18467,30 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
+          <t>보챔/보채지 않음</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>🩺 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -18497,7 +18500,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -18518,21 +18521,21 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>보챔/보채지 않음</t>
+          <t>울고 보챔</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>🩺 보채는지 관찰하세요</t>
+          <t>"평소보다 심하게 보채거나 우나요?"</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -18563,16 +18566,16 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>울고 보챔</t>
+          <t>잠 안자고 울고 보챔</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>"평소보다 심하게 보채거나 우나요?"</t>
+          <t>"잠을 못 자고 계속 우나요?"</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -18608,16 +18611,16 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>잠 안자고 울고 보챔</t>
+          <t>자주 사지 움직이며 보챔</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>"잠을 못 자고 계속 우나요?"</t>
+          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -18653,26 +18656,26 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>자주 사지 움직이며 보챔</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
+          <t>"아파하나요?"</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>부위는 📌비고에 기재</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
@@ -18698,16 +18701,16 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>"아파하나요?"</t>
+          <t>"축 처져 있거나 반응이 느린가요?"</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -18717,7 +18720,7 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>부위는 📌비고에 기재</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
@@ -18743,21 +18746,21 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>"축 처져 있거나 반응이 느린가요?"</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -18784,25 +18787,15 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
-        </is>
-      </c>
-      <c r="F404" t="inlineStr">
-        <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G404" t="inlineStr">
-        <is>
-          <t>선택</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -18829,7 +18822,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D405" t="n">
@@ -18837,7 +18830,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 강도 측정함</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -18868,11 +18861,11 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>통증 강도 측정함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -18903,11 +18896,11 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -18916,41 +18909,6 @@
         </is>
       </c>
       <c r="J407" t="inlineStr">
-        <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>소아</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>소아-보챔처짐</t>
-        </is>
-      </c>
-      <c r="C408" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D408" t="n">
-        <v>3</v>
-      </c>
-      <c r="E408" t="inlineStr">
-        <is>
-          <t>통증을 인정해줌</t>
-        </is>
-      </c>
-      <c r="I408" t="inlineStr">
-        <is>
-          <t>⚠️ 초안</t>
-        </is>
-      </c>
-      <c r="J408" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2233,6 +2233,358 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B_소화기</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>🤮💩</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B_비뇨기</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>🚽</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B_이비인후</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>👂</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B_어지럼</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>💫</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B_중독</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>💊</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B_골절외상</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B_안과</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>👁️</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B_피부</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>🧴</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B_의식섬망</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>🌀</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B_정신과</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>😰</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B_혈압</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>🩺</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2244,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K407"/>
+  <dimension ref="A1:K544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -18911,6 +19263,5131 @@
       <c r="J407" t="inlineStr">
         <is>
           <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>1</v>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D409" t="n">
+        <v>2</v>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>설사 있음/설사 없음</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>"설사하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D410" t="n">
+        <v>3</v>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>탈수 증상 있음</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>🩺 탈수 증상(입마름·소변감소)</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D411" t="n">
+        <v>4</v>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>변비 있음/변비 없음</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>"변을 못 보거나 불편하세요?"</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D412" t="n">
+        <v>1</v>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D413" t="n">
+        <v>1</v>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>탈수 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D414" t="n">
+        <v>2</v>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>금식 하도록 교육함</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>⚠️ 마스터 없음 — 시간 붙은 것만 존재(2시간/6시간…). 칩스 확인</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D415" t="n">
+        <v>2</v>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>변비</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>변비</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D416" t="n">
+        <v>3</v>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>변비 유발 식품을 피하도록 교육함</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>변비</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>4</v>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>대변 양상 확인함</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>변비</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D418" t="n">
+        <v>1</v>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>배뇨곤란 있음/배뇨곤란 없음</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>"소변보기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D419" t="n">
+        <v>2</v>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>요정체 있음/요정체 없음</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>"소변이 막힌 느낌이세요?"</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>3</v>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>잔뇨감 있음/잔뇨감 없음</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D421" t="n">
+        <v>4</v>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>혈뇨 있음/혈뇨 없음</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>"소변에 피가 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>5</v>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>소변량 감소함</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>🩺 소변량 감소</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>1</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>1</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>요정체가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>2</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>단순도뇨 시행함</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>3</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>혈뇨가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>1</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>귀분비물 있음/귀분비물 없음</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>"귀에서 분비물이 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>2</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>이명 있음/이명 없음</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>"귀울림(이명)이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>3</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>청력 이상 있음</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>"잘 안 들리세요?"</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>4</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>코막힘 있음/코막힘 없음</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>"코가 막히세요?"</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>5</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>콧물 있음/콧물 없음</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>"콧물이 나세요?"</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>6</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>연하곤란 있음/연하곤란 없음</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>"삼키기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>1</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>1</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>2</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>청력장애가 있는지 사정함</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>3</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>1</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>2</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>3</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D440" t="n">
+        <v>4</v>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>prompt/sluggish/hippus</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D441" t="n">
+        <v>5</v>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>감각이상 있음/감각이상 없음</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D442" t="n">
+        <v>6</v>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>grasp power 약함/grasp power 강함</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D443" t="n">
+        <v>7</v>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>vertigo 있음/vertigo 없음</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D444" t="n">
+        <v>8</v>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>syncope 있음/syncope 없음</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D445" t="n">
+        <v>9</v>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D446" t="n">
+        <v>1</v>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D447" t="n">
+        <v>1</v>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D448" t="n">
+        <v>2</v>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D449" t="n">
+        <v>3</v>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D450" t="n">
+        <v>2</v>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>4</v>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>5</v>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>6</v>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>조직관류 증진 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>7</v>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>1</v>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>음독 함 ★</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>★ 칩스확정 — 마스터 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>2</v>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>"토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>3</v>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>4</v>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>5</v>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>prompt/sluggish/hippus</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>6</v>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>감각이상 있음/감각이상 없음</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>7</v>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>grasp power 약함/grasp power 강함</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>8</v>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>1</v>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>1</v>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>위세척에 대해 설명함</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>2</v>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>처방에 의해 해독제를 투여함</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>3</v>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>4</v>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>1</v>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>골절 있음</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>"부러진 곳(골절)이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>2</v>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>골절부위 edema 있음/골절부위 edema 없음</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>"다친 곳이 붓나요?"</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>3</v>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>골절부위 tingling sense 있음/골절부위 tingling sense 없음</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>"저릿하거나 감각이 이상하세요?"</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>4</v>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>찰과상 있음/찰과상 없음</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>5</v>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>출혈 있음/출혈 없음</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>"피가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>1</v>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>1</v>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>골절부위 압박붕대 감아줌</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>2</v>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>골절부위 올려줌</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>2</v>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>골절외상</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>3</v>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>sensory motor circulation 확인함</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>1</v>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>시력감퇴 있음/시력감퇴 없음</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>"예전보다 잘 안 보이세요?"</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>2</v>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>시야결손 있음/시야결손 없음</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>"시야 일부가 가려지세요?"</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>3</v>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>복시 있음/복시 없음</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>4</v>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>결막충혈 있음/결막충혈 없음</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>"눈이 충혈되었나요?"</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>5</v>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>이물질 관찰됨</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>6</v>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>결막출혈 있음/결막출혈 없음</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>1</v>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>★ 칩스확정 — 마스터는 통합형(시각,청각,촉각…)</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>1</v>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>2</v>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>2</v>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>3</v>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>이물질 제거함</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>4</v>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>안연고 점안 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>3</v>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>5</v>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>6</v>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>1</v>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>가려움증 있음/가려움증 없음</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>2</v>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>urticaria 있음/urticaria 없음</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>3</v>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>bullae 있음/bullae 없음</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>"물집이 잡혔나요?"</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>1</v>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>1</v>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>긁지 않도록 교육함</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>2</v>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>소양증 감소 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>2</v>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>3</v>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>피부 상태를 관찰함</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>1</v>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>2</v>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>3</v>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>prompt/sluggish/hippus</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>🩺 빛 반사</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>4</v>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>감각이상 있음/감각이상 없음</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>5</v>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>grasp power 약함/grasp power 강함</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>6</v>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>7</v>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>사람에 대한 지남력 없음/사람에 대한 지남력 있음</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>8</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>섬망 있음/섬망 없음</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>9</v>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>환각 있음/환각 없음</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>"없는 것이 보이거나 들리세요?"</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>10</v>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>flapping tremor 있음/flapping tremor 없음</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>🩺 손떨림(flapping tremor)</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>1</v>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>1</v>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>2</v>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>2</v>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>3</v>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>알코올 섭취 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>4</v>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>금단 증상을 설명함</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>5</v>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>1</v>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>구체적 자살계획을 언급함/자해나 자살시도를 부인함</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>2</v>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>자살을 시도함</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>3</v>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>자살 충동 있음</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>자살 충동 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>4</v>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>공격적 행동함/타인에 대한 공격적 행동을 보이지 않음</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>🩺 공격적 행동(관찰)</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>5</v>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>공황상태 있음/공황상태 없음</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>"심하게 불안하거나 공황 상태이세요?"</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>1</v>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>1</v>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>2</v>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>2</v>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>3</v>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>진정시킴</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>4</v>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>억제대 적용 중임</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>3</v>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>5</v>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>불안을 감소시켜 줌</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>정신과</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>6</v>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>경청해줌</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>1</v>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>혈압(mmHg) :</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>2</v>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>혈압 상승됨</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>🩺 혈압 상승됨 (고혈압)</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>3</v>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>혈압 저하됨</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>🩺 혈압 저하됨 (저혈압)</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>4</v>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>고혈압으로 인한 증상 있음/고혈압으로 인한 증상 없음</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>5</v>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>체위성 저혈압 있음</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>1</v>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>1</v>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>혈압 측정함</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>2</v>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Non Invasive BP monitor 시작함</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>3</v>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>혈압관리 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>2</v>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>4</v>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>혈압 측정함</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>5</v>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>혈압</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>6</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -18951,7 +24428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -19585,6 +25062,737 @@
       <c r="C37" t="inlineStr">
         <is>
           <t>피부 상태를 관찰함</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>"필요하면 잠시 금식하시도록 안내드릴게요"</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>금식 하도록 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>변비</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>"변비 유발 식품을 피하도록 알려드릴게요"</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>변비 유발 식품을 피하도록 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>변비</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>"대변 상태를 확인하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>대변 양상 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>"소변이 막혔는지 확인하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>요정체가 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>"소변줄로 빼드릴게요"</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>단순도뇨 시행함</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>"소변에 피가 있는지 확인하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>혈뇨가 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>"청력에 문제가 있는지 살펴보겠습니다"</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>청력장애가 있는지 사정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>"삼키기 편한 음식을 안내드릴게요"</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>"안전하게 부축해 드릴게요"</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>"넘어져 다치지 않게 안내드릴게요"</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>"어지러우면 혈당부터 확인합니다"</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>"여기는 병원이고 지금은 낮이에요"</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>"뇌 혈류를 돕는 방법을 안내드릴게요"</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>조직관류 증진 방법에 대해 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>"혈당도 확인하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>"위세척에 대해 설명드릴게요"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>위세척에 대해 설명함</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>"처방된 해독제를 투여하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>처방에 의해 해독제를 투여함</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>"안전하게 지켜드릴게요"</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>"신경학적 증상을 확인하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>"압박붕대로 감아드릴게요"</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>골절부위 압박붕대 감아줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>"부기 가라앉게 올려드릴게요"</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>골절부위 올려줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>"감각·움직임·혈색을 자주 확인하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>sensory motor circulation 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>"안 보이실 때 안전하게 부축해 드릴게요"</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>"눈 보호를 위해 안대를 해드릴게요"</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>"눈에 들어간 것을 조심히 빼드릴게요"</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>이물질 제거함</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>"안연고 넣는 방법을 알려드릴게요"</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>안연고 점안 방법에 대해 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>"눈을 보호하기 위해 안대를 적용하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>안대 적용함</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>"피부 상태를 살펴보겠습니다"</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>피부 상태를 관찰함</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>"안전하게 지켜드릴게요"</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>"음주 습관을 여쭤볼게요"</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>알코올 섭취 양상을 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>"금단 증상을 설명드릴게요"</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>금단 증상을 설명함</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>"안전하게 지켜드릴게요"</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>"안전하게 지켜드릴게요"</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>"자주 살펴보고 필요한 준비를 해두겠습니다"</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>"진정하실 수 있게 돕겠습니다"</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>진정시킴</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>"안전을 위해 보호대를 적용하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>억제대 적용 중임</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>"천천히 호흡해 보세요"</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>불안을 감소시켜 줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>"편하게 말씀하세요, 듣고 있어요"</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>경청해줌</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>"혈압을 측정하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>혈압 측정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>"혈압을 계속 지켜보겠습니다"</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Non Invasive BP monitor 시작함</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>"혈압 관리법을 안내드릴게요"</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>혈압관리 방법에 대해 교육함</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>"혈압을 측정하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>혈압 측정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>"일어설 때 어지러운지 확인하겠습니다"</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>"안전하게 부축해 드릴게요"</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -13302,7 +13302,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
@@ -13343,12 +13343,12 @@
       </c>
       <c r="E263" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F263" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G263" s="2" t="inlineStr">
@@ -13359,7 +13359,7 @@
       <c r="H263" s="2" t="inlineStr"/>
       <c r="I263" s="2" t="inlineStr">
         <is>
-          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="F273" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G273" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G274" s="2" t="inlineStr">
@@ -13813,7 +13813,7 @@
       <c r="H274" s="2" t="inlineStr"/>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>머리~얼굴~팔~다리~몸통 양쪽 만져가면서 감각 저하가 있는지 감별</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G316" s="2" t="inlineStr">
@@ -15563,12 +15563,12 @@
       </c>
       <c r="E317" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F317" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G317" s="2" t="inlineStr">
@@ -15579,7 +15579,7 @@
       <c r="H317" s="2" t="inlineStr"/>
       <c r="I317" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>동공 크기를 확인하세요 (Rt/Lt)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
@@ -15883,12 +15883,12 @@
       </c>
       <c r="E325" s="2" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt/sluggish/hippus 함</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
         <is>
-          <t>빛 반사를 확인하세요 (prompt/sluggish/hippus)</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
@@ -15897,7 +15897,11 @@
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr"/>
-      <c r="I325" s="2" t="inlineStr"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>★ 칩스확정 — 마스터 없음</t>
+        </is>
+      </c>
       <c r="J325" t="inlineStr">
         <is>
           <t>신체손상위험</t>
@@ -20462,7 +20466,7 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
@@ -20497,12 +20501,12 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>prompt/sluggish/hippus</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
@@ -20512,7 +20516,7 @@
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
     </row>
@@ -21097,7 +21101,7 @@
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>"토하셨어요?"</t>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -21177,7 +21181,7 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -21212,12 +21216,12 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>prompt/sluggish/hippus</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -21227,7 +21231,7 @@
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
     </row>
@@ -22817,7 +22821,7 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>🩺 동공 크기 (Rt / Lt · mm)</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -22852,12 +22856,12 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>prompt/sluggish/hippus</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>🩺 빛 반사</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -22867,7 +22871,7 @@
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
     </row>
@@ -23137,7 +23141,7 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>🩺 손떨림(flapping tremor)</t>
+          <t>🩺 양손을 앞으로 뻗고 손목을 젖히게 해보세요 — 파닥이듯 떨리나요?</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.낙상교육" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소아_질문초안(미확정)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.마무리질문" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.통증공통" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -85,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -98,6 +99,9 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -27763,4 +27767,1567 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>과정</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>진술문(마스터원문)</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>질문문구(💬)</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>입력형식</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>그룹</t>
+        </is>
+      </c>
+      <c r="I1" s="8" t="inlineStr">
+        <is>
+          <t>조건</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>진통제 원함/진통제를 원하지 않음</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>"진통제를 맞고 싶으세요?"</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>아파도 참는 환자가 많아 반드시 묻는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>처방에 의해 진통제를 투여함</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>💊 진통제를 투여했나요?</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>투여후</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>의사 처방이 난 뒤에 누른다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>진통제 투여 후 통증 감소됨/진통제 투여하였으나 통증 지속됨</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>"진통제 맞고 통증이 좀 나아지셨어요?"</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>투여후</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>진통제 투여 후 부작용 있음/없음</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>"진통제 맞고 메스껍거나 어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>투여후</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P&amp;E조건</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>통증부위를 사정함</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>부위를 하나라도 고르면</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P&amp;E조건</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>통증 강도 측정함</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>강도</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>강도를 입력하면</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P&amp;E조건</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>양상을 하나라도 고르면</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P&amp;E조건</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>진통제 투여 후 통증 강도 측정함</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>투여후강도</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>투여 후 강도를 다시 재면</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>가슴</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>🫃</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>목</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>🧣</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>허리</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>🔙</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>팔</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>💪</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>다리</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>🦵</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>엉덩이</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>🍑</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>anterior chest</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>가슴</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>epigastric site</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>가슴</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mediastinal site</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>가슴</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>substernal site</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>가슴</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LLQ</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LUQ</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>RLQ</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RUQ</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>9</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>periumbilical area</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>세부부위</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>전체</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>도구</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NRS</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>숫자 0~10 · 성인</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>도구</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FPRS</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>얼굴 그림 · 소아/노인</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>도구</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FLACC</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>행동 관찰 · 영유아</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>도구</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NIPS</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>신생아</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>도구</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>5</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CNPS</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>비언어 성인</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>뻐근한</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>날카로운</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>둔한</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>욱신·쑤시는</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>5</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>타는 듯한</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>저리는 듯한</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>7</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>칼로 베인 듯한</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>양상</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>표현 못함</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>빈도</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>발작적으로 갑자기</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>빈도</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>지속적</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>빈도</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>표현 못함</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>빈도</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>양호함</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>약함</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SMC</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>평가불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>통증진단</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>이 진단이 있는 경로에 통증 사정 위젯을 띄운다</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>통증진단</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>만성통증</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>기간이 아래 기준 이상이면 이 진단으로 바꾼다</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>기간기준</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>만성통증 기준(개월) — IASP/ICD-11 국제표준</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SMC진단</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>이 진단이 있으면 부위와 무관하게 SMC를 연다(골절·외상)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>오늘·며칠 전</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1개월 미만</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1~3개월</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3개월 이상</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>만성</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>이 구간이면 만성통증으로 넘긴다</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>기간</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>모름</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>A&amp;E조건</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>만성 통증 있음</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>만성</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>기간이 3개월 이상일 때만 기록된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>A&amp;E조건</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>문항</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>sensory, motor, circulation intact 함</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>🩺 감각·운동·순환이 모두 정상인가요?</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SMC정상</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소아_질문초안(미확정)" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.마무리질문" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.통증공통" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.신경학공통" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.추천근거" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -548,6 +550,237 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>진술문(마스터원문)</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>질문문구(💬)</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>입력형식</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>★ 마스터 없음 · 칩스확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>감각이상 있음/없음</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>"몸에 감각이 이상한 부분이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>grasp power 강함/약함</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>"제 손을 양손으로 꽉 쥐어보시겠어요?"</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>이상소견 진술문</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>오심, 구토 있음</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>토했으면 이상 — 엑셀엔 「없음」이 먼저 적혀 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>obey command 가능하지 않음</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>지시를 못 따르면 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>사람에 대한 지남력 없음</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>지남력은 없는 게 이상</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>grasp power 약함</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>악력은 약한 게 이상 — 두통 경로는 「강함」이 먼저 적혀 있다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -12289,7 +12522,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -12329,7 +12562,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12602,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12642,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12663,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -12470,7 +12703,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -12489,7 +12722,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12747,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12549,7 +12782,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12817,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>감염</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
@@ -29136,12 +29369,6 @@
           <t>오늘·며칠 전</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -29162,12 +29389,6 @@
           <t>1개월 미만</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -29188,12 +29409,6 @@
           <t>1~3개월</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -29214,15 +29429,11 @@
           <t>3개월 이상</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>만성</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>이 구간이면 만성통증으로 넘긴다</t>
@@ -29248,12 +29459,6 @@
           <t>모름</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -29269,15 +29474,11 @@
       <c r="C58" t="n">
         <v>1</v>
       </c>
-      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
           <t>만성 통증 있음</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>만성</t>
@@ -29303,7 +29504,6 @@
       <c r="C59" t="n">
         <v>2</v>
       </c>
-      <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
           <t>sensory, motor, circulation intact 함</t>
@@ -29319,13 +29519,11 @@
           <t>체크</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>SMC정상</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -18,6 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.통증공통" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.신경학공통" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.추천근거" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.후속사정" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -773,6 +774,168 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>악력은 약한 게 이상 — 두통 경로는 「강함」이 먼저 적혀 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>빛 반사 확인결과 sluggish 함 ★</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>빛 반사는 prompt(즉시)가 정상이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>빛 반사 확인결과 hippus 함 ★</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>순서</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>발동조건</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>생략조건</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>과정</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>진술문(마스터원문)</t>
+        </is>
+      </c>
+      <c r="F1" s="8" t="inlineStr">
+        <is>
+          <t>질문문구(💬)</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>입력형식</t>
+        </is>
+      </c>
+      <c r="H1" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>신경학이상</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>혈당 증가함/혈당 떨어짐/혈당 정상 범위임</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🩺 혈당을 재세요 — 신경학적 이상이 있으면 먼저 확인합니다</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>되돌릴 수 있는 원인부터 본다. 이미 혈당을 묻는 경로에서는 뜨지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>신경학이상</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>혈당 검사 시행함</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>위 문항에 답하면 함께 기록된다</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -19,6 +19,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.신경학공통" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.추천근거" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.후속사정" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.평가자동" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -931,11 +932,449 @@
           <t>혈당 검사 시행함</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>위 문항에 답하면 함께 기록된다</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>진술문(마스터원문)</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>쓰는 경로</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>출혈양상 확인함</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>호흡곤란이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>seizure 양상 확인함</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>흉부 통증이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>심전도 변화를 확인함</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>탈수 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>피부 상태를 관찰함</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>혈압 측정함</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>구토 양상 확인함</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>통증 강도 측정함</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>대변 양상 확인함</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>요정체가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>혈뇨가 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sensory motor circulation 확인함</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>알코올 섭취 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>— 아래는 애매해서 수동으로 두었다. 자동으로 돌리려면 위로 옮기세요 —</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>(수동) 산소포화도 monitor 함</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>기계를 붙이는 행위에 가깝다</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>(수동) seizure의 유발요인을 확인함</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>따로 물어봐야 안다</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>(수동) 통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>20</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>사정이 아니라 계획이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>(수동) 청력장애가 있는지 사정함</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>별도 검사가 필요하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>(수동) 체위성 저혈압 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>기립 혈압을 따로 재야 한다</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1289,19 +1289,13 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>— 아래는 애매해서 수동으로 두었다. 자동으로 돌리려면 위로 옮기세요 —</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -20197,6 +20191,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -20237,6 +20236,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -20277,6 +20281,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -20317,6 +20326,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>변비</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -22457,6 +22471,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -22497,6 +22516,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -22537,6 +22561,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
@@ -22577,6 +22606,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -22617,6 +22651,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
@@ -23682,6 +23721,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
@@ -23722,6 +23766,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
@@ -23762,6 +23811,11 @@
           <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -23802,6 +23856,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
@@ -23842,6 +23901,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
@@ -23882,6 +23946,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
@@ -23922,6 +23991,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -23962,6 +24036,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
@@ -24002,6 +24081,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -24042,6 +24126,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>알코올금단증</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -24327,6 +24416,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
@@ -24367,6 +24461,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -24407,6 +24506,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>자살위험</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -24447,6 +24551,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>폭력위험:타인</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
@@ -24487,6 +24596,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>불안</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -24842,6 +24956,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
@@ -24882,6 +25001,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
@@ -24922,6 +25046,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
@@ -24962,6 +25091,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>고혈압</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -25000,6 +25134,11 @@
       <c r="I564" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>저혈압</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1289,7 +1289,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
@@ -3429,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K572"/>
+  <dimension ref="A1:K569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -21301,6 +21300,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -21341,6 +21345,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
@@ -21381,6 +21390,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
@@ -21421,6 +21435,11 @@
           <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
@@ -21461,6 +21480,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -21501,6 +21525,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -21541,6 +21570,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -21581,6 +21615,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -21621,6 +21660,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -22871,6 +22915,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -22911,6 +22960,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
@@ -22951,6 +23005,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>감각지각장애 : 시각</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
@@ -22991,6 +23050,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -23031,6 +23095,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
@@ -23071,6 +23140,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>안위변화</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -23285,25 +23359,35 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>가려움증 있음/가려움증 없음</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -23313,32 +23397,42 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
+          <t>urticaria 있음/urticaria 없음</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -23348,32 +23442,42 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D520" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>bullae 있음/bullae 없음</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>"물집이 잡혔나요?"</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -23383,7 +23487,7 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
@@ -23400,7 +23504,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D521" t="n">
@@ -23408,22 +23512,17 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>가려움증 있음/가려움증 없음</t>
-        </is>
-      </c>
-      <c r="F521" t="inlineStr">
-        <is>
-          <t>"피부가 가려우세요?"</t>
-        </is>
-      </c>
-      <c r="G521" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -23440,30 +23539,25 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>urticaria 있음/urticaria 없음</t>
-        </is>
-      </c>
-      <c r="F522" t="inlineStr">
-        <is>
-          <t>"두드러기가 올라왔나요?"</t>
-        </is>
-      </c>
-      <c r="G522" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>긁지 않도록 교육함</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -23480,30 +23574,25 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>bullae 있음/bullae 없음</t>
-        </is>
-      </c>
-      <c r="F523" t="inlineStr">
-        <is>
-          <t>"물집이 잡혔나요?"</t>
-        </is>
-      </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>소양증 감소 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -23524,11 +23613,11 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -23538,7 +23627,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
@@ -23559,11 +23648,11 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -23573,32 +23662,42 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -23608,24 +23707,24 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D527" t="n">
@@ -23633,7 +23732,17 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -23643,24 +23752,24 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D528" t="n">
@@ -23668,17 +23777,27 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>선택</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -23699,16 +23818,16 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>dizziness 있음/dizziness 없음</t>
+          <t>감각이상 있음/감각이상 없음</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -23744,21 +23863,21 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>grasp power 약함/grasp power 강함</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -23789,26 +23908,26 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J531" t="inlineStr">
@@ -23834,16 +23953,16 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>감각이상 있음/감각이상 없음</t>
+          <t>사람에 대한 지남력 없음/사람에 대한 지남력 있음</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -23879,16 +23998,16 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>grasp power 약함/grasp power 강함</t>
+          <t>섬망 있음/섬망 없음</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -23903,7 +24022,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -23924,16 +24043,16 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음/obey command 가능함</t>
+          <t>환각 있음/환각 없음</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+          <t>"없는 것이 보이거나 들리세요?"</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -23948,7 +24067,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -23969,16 +24088,16 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>사람에 대한 지남력 없음/사람에 대한 지남력 있음</t>
+          <t>flapping tremor 있음/flapping tremor 없음</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+          <t>🩺 양손을 앞으로 뻗고 손목을 젖히게 해보세요 — 파닥이듯 떨리나요?</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -23993,7 +24112,7 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -24010,25 +24129,15 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D536" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>섬망 있음/섬망 없음</t>
-        </is>
-      </c>
-      <c r="F536" t="inlineStr">
-        <is>
-          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
-        </is>
-      </c>
-      <c r="G536" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24038,7 +24147,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -24055,25 +24164,15 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>환각 있음/환각 없음</t>
-        </is>
-      </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>"없는 것이 보이거나 들리세요?"</t>
-        </is>
-      </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -24083,7 +24182,7 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -24100,25 +24199,15 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>flapping tremor 있음/flapping tremor 없음</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>🩺 양손을 앞으로 뻗고 손목을 젖히게 해보세요 — 파닥이듯 떨리나요?</t>
-        </is>
-      </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -24128,7 +24217,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -24149,11 +24238,11 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -24163,7 +24252,7 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -24184,11 +24273,11 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>알코올 섭취 양상을 확인함</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24198,7 +24287,7 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -24219,11 +24308,11 @@
         </is>
       </c>
       <c r="D541" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>금단 증상을 설명함</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24233,7 +24322,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -24250,15 +24339,15 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D542" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -24275,25 +24364,35 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>알코올 섭취 양상을 확인함</t>
+          <t>구체적 자살계획을 언급함/자해나 자살시도를 부인함</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -24303,32 +24402,42 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D544" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>금단 증상을 설명함</t>
+          <t>자살을 시도함</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -24338,32 +24447,42 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>자살 충동 있음</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>자살 충동 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -24373,7 +24492,7 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
@@ -24394,16 +24513,16 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>구체적 자살계획을 언급함/자해나 자살시도를 부인함</t>
+          <t>공격적 행동함/타인에 대한 공격적 행동을 보이지 않음</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
+          <t>🩺 공격적 행동(관찰)</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -24418,7 +24537,7 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
@@ -24439,21 +24558,21 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>자살을 시도함</t>
+          <t>공황상태 있음/공황상태 없음</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+          <t>"심하게 불안하거나 공황 상태이세요?"</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -24463,7 +24582,7 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
@@ -24480,25 +24599,15 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>자살 충동 있음</t>
-        </is>
-      </c>
-      <c r="F548" t="inlineStr">
-        <is>
-          <t>자살 충동 (구체적 사항 비고에 기재)</t>
-        </is>
-      </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>자살위험</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -24525,25 +24634,15 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>공격적 행동함/타인에 대한 공격적 행동을 보이지 않음</t>
-        </is>
-      </c>
-      <c r="F549" t="inlineStr">
-        <is>
-          <t>🩺 공격적 행동(관찰)</t>
-        </is>
-      </c>
-      <c r="G549" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -24553,7 +24652,7 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
@@ -24570,25 +24669,15 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D550" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>공황상태 있음/공황상태 없음</t>
-        </is>
-      </c>
-      <c r="F550" t="inlineStr">
-        <is>
-          <t>"심하게 불안하거나 공황 상태이세요?"</t>
-        </is>
-      </c>
-      <c r="G550" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -24598,7 +24687,7 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
@@ -24619,11 +24708,11 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -24633,7 +24722,7 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
@@ -24654,11 +24743,11 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>진정시킴</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -24668,7 +24757,7 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
@@ -24689,11 +24778,11 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
+          <t>억제대 적용 중임</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -24703,7 +24792,7 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
@@ -24724,11 +24813,11 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>불안</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -24738,7 +24827,7 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
@@ -24759,11 +24848,11 @@
         </is>
       </c>
       <c r="D555" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>진정시킴</t>
+          <t>불안을 감소시켜 줌</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -24773,7 +24862,7 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
@@ -24794,11 +24883,11 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>억제대 적용 중임</t>
+          <t>경청해줌</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -24808,32 +24897,42 @@
       </c>
       <c r="J556" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D557" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>혈압(mmHg) :</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -24843,32 +24942,42 @@
       </c>
       <c r="J557" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>불안을 감소시켜 줌</t>
+          <t>혈압 상승됨</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>🩺 혈압 상승됨 (고혈압)</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -24878,32 +24987,42 @@
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>경청해줌</t>
+          <t>혈압 저하됨</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>🩺 혈압 저하됨 (저혈압)</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -24913,7 +25032,7 @@
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -24934,21 +25053,21 @@
         </is>
       </c>
       <c r="D560" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>혈압(mmHg) :</t>
+          <t>고혈압으로 인한 증상 있음/고혈압으로 인한 증상 없음</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
+          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -24958,7 +25077,7 @@
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
@@ -24979,16 +25098,16 @@
         </is>
       </c>
       <c r="D561" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>혈압 상승됨</t>
+          <t>체위성 저혈압 있음</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>🩺 혈압 상승됨 (고혈압)</t>
+          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
@@ -25003,7 +25122,7 @@
       </c>
       <c r="J561" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -25020,25 +25139,15 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>혈압 저하됨</t>
-        </is>
-      </c>
-      <c r="F562" t="inlineStr">
-        <is>
-          <t>🩺 혈압 저하됨 (저혈압)</t>
-        </is>
-      </c>
-      <c r="G562" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>고혈압</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -25048,7 +25157,7 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
@@ -25065,25 +25174,15 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>고혈압으로 인한 증상 있음/고혈압으로 인한 증상 없음</t>
-        </is>
-      </c>
-      <c r="F563" t="inlineStr">
-        <is>
-          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G563" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -25110,25 +25209,15 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D564" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>체위성 저혈압 있음</t>
-        </is>
-      </c>
-      <c r="F564" t="inlineStr">
-        <is>
-          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
-        </is>
-      </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>Non Invasive BP monitor 시작함</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -25138,7 +25227,7 @@
       </c>
       <c r="J564" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
@@ -25155,15 +25244,15 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>혈압관리 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -25190,15 +25279,15 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
+          <t>저혈압</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -25208,7 +25297,7 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -25229,11 +25318,11 @@
         </is>
       </c>
       <c r="D567" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Non Invasive BP monitor 시작함</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -25243,7 +25332,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -25264,11 +25353,11 @@
         </is>
       </c>
       <c r="D568" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>혈압관리 방법에 대해 교육함</t>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -25278,7 +25367,7 @@
       </c>
       <c r="J568" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -25295,15 +25384,15 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D569" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -25312,111 +25401,6 @@
         </is>
       </c>
       <c r="J569" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B570" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C570" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D570" t="n">
-        <v>4</v>
-      </c>
-      <c r="E570" t="inlineStr">
-        <is>
-          <t>혈압 측정함</t>
-        </is>
-      </c>
-      <c r="I570" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J570" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B571" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C571" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D571" t="n">
-        <v>5</v>
-      </c>
-      <c r="E571" t="inlineStr">
-        <is>
-          <t>체위성 저혈압 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="I571" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J571" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B572" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C572" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D572" t="n">
-        <v>6</v>
-      </c>
-      <c r="E572" t="inlineStr">
-        <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="I572" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J572" t="inlineStr">
         <is>
           <t>저혈압</t>
         </is>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -25753,7 +25753,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>따뜻한 환경 제공함</t>
+          <t>담요를 덮어줌</t>
         </is>
       </c>
     </row>
@@ -25957,7 +25957,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Seizure 양상을 확인함</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
     </row>
@@ -29574,6 +29574,11 @@
           <t>FPRS</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
           <t>얼굴 그림 · 소아/노인</t>
@@ -29599,6 +29604,11 @@
           <t>FLACC</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
           <t>행동 관찰 · 영유아</t>
@@ -29622,6 +29632,11 @@
       <c r="D31" t="inlineStr">
         <is>
           <t>NIPS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>소아</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -558,7 +558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,31 @@
       <c r="D6" t="inlineStr">
         <is>
           <t>토글</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>의식수준 :</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>🩺 의식수준을 적으세요 (alert · drowsy · stupor · coma)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>값입력</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GCS로 안 되는 서술을 남길 때</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K569"/>
+  <dimension ref="A1:K556"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16949,12 +16974,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -16967,39 +16992,39 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>의식 명료함</t>
+          <t>열감 있음/없음</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>확인하세요</t>
+          <t>"열이 나나요?"</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>GCS 15 미만일 떄</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -17012,39 +17037,39 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>의식수준 :</t>
+          <t>chilling 있음/없음</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>확인하세요</t>
+          <t>"춥다고 하거나 몸을 떨었나요?"</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>보호자 있을시</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -17057,39 +17082,39 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>보호자 환자 옆에 상주하고 있음</t>
+          <t>체온 상승함/체온 하강함</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>확인하세요</t>
+          <t>🩺 체온을 측정하세요</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>보호자 없을시</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -17102,39 +17127,39 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>보호자 동행하지 않음</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>확인하세요</t>
+          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>가능하지 않을 떄</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -17147,34 +17172,39 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Obey command 가능함/ Obey command 가능하지 않음</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>확인하세요</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -17187,89 +17217,79 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>시간에대한 지남력 없음/사람에 대한 지남력 없음/ 장소에 대한 지남력 없음</t>
+          <t>구토함/구토 없음</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>확인하세요</t>
+          <t>"토했나요?"</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Post note에 세부사항 기록하기</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D363" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>시간, 사람, 장소에 대한 지남력 없음</t>
-        </is>
-      </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>확인하세요</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>고체온</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>보호자 있을시</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D364" t="n">
@@ -17277,24 +17297,29 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -17303,33 +17328,33 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>낙상방지 교육함</t>
+          <t>미온수 목욕 시행함</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>침대 난간 올려줬을 시</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-발열</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -17338,126 +17363,156 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>침대 난간을 올려줌</t>
+          <t>처방에 의해 해열제를 투여함</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>보호자 있을시, 낙상 위험 높을시</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>고체온</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D367" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>보호자와 같이 있게 함</t>
+          <t>구토함/구토 없음</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>"토했나요?"</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>보호자 있을시</t>
+          <t>횟수는 📌비고에 기재</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D368" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>보호자 동반하도록 설명함</t>
+          <t>오심 있음/없음</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>"메스꺼워 하나요?"</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>보호자 없을시</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>의식/낙상 사정</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>의식 및 낙상위험 평가</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D369" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>손상을 예방하는 방법에 대해 교육함</t>
+          <t>설사 있음/없음</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>"설사하나요?"</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>낙상위험 교육</t>
+          <t>횟수는 📌비고에 기재</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>낙상위험</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17469,7 +17524,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -17478,16 +17533,16 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
+          <t>구강건조 있음/없음</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>"열이 나나요?"</t>
+          <t>"입술이나 입 안이 말라 있나요?"</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -17502,7 +17557,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17569,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -17523,16 +17578,16 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>chilling 있음/없음</t>
+          <t>갈증 있음/없음</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>"춥다고 하거나 몸을 떨었나요?"</t>
+          <t>"물을 자꾸 찾나요?"</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -17547,7 +17602,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17559,7 +17614,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -17568,21 +17623,21 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>체온 상승함/체온 하강함</t>
+          <t>피부 탄력성 저하됨</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>🩺 체온을 측정하세요</t>
+          <t>🩺 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -17592,7 +17647,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17659,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -17613,21 +17668,21 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>"아이가 축 처져 있거나 반응이 느린가요?"</t>
+          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -17637,7 +17692,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17649,7 +17704,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -17658,21 +17713,21 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
+          <t>복부 통증 있음/없음</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
+          <t>"배가 아프다고 하나요?"</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -17682,7 +17737,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -17694,30 +17749,20 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D375" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>구토함/구토 없음</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>"토했나요?"</t>
-        </is>
-      </c>
-      <c r="G375" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>체액부족위험</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -17727,7 +17772,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17739,12 +17784,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D376" t="n">
@@ -17752,7 +17797,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>탈수 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -17762,7 +17807,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17774,7 +17819,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -17783,11 +17828,11 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>경구수분섭취 격려함</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -17797,7 +17842,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17809,7 +17854,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -17818,11 +17863,11 @@
         </is>
       </c>
       <c r="D378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>미온수 목욕 시행함</t>
+          <t>구토 양상 확인함</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -17832,7 +17877,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -17844,30 +17889,30 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>소아-발열</t>
+          <t>소아-구토설사</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D379" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>처방에 의해 해열제를 투여함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ 통증 진단 추가</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>고체온</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -17884,35 +17929,25 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D380" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>구토함/구토 없음</t>
-        </is>
-      </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>"토했나요?"</t>
-        </is>
-      </c>
-      <c r="G380" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>횟수는 📌비고에 기재</t>
+          <t>⚠️ 통증 진단 추가</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -17929,35 +17964,25 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D381" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>오심 있음/없음</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>"메스꺼워 하나요?"</t>
-        </is>
-      </c>
-      <c r="G381" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ 통증 진단 추가</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -17974,35 +17999,25 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D382" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>설사 있음/없음</t>
-        </is>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>"설사하나요?"</t>
-        </is>
-      </c>
-      <c r="G382" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>횟수는 📌비고에 기재</t>
+          <t>⚠️ 통증 진단 추가</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -18014,7 +18029,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -18023,16 +18038,16 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>구강건조 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>"입술이나 입 안이 말라 있나요?"</t>
+          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -18047,7 +18062,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18074,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -18068,16 +18083,16 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>갈증 있음/없음</t>
+          <t>chest retraction 있음/없음</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>"물을 자꾸 찾나요?"</t>
+          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
@@ -18092,7 +18107,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18119,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -18113,21 +18128,21 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>피부 탄력성 저하됨</t>
+          <t>wheezing 있음/없음</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>🩺 피부를 집었다 놓았을 때 천천히 돌아오나요?</t>
+          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -18137,7 +18152,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18149,7 +18164,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -18158,21 +18173,21 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
+          <t>기침 있음/없음</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>"소변(기저귀)이 평소보다 줄었나요?"</t>
+          <t>"기침하나요?"</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -18182,7 +18197,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18194,7 +18209,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -18203,16 +18218,16 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>복부 통증 있음/없음</t>
+          <t>가래 잘 뱉지 못함/가래 잘 뱉어냄</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>"배가 아프다고 하나요?"</t>
+          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
@@ -18227,7 +18242,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18239,20 +18254,30 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D388" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>"입술이나 얼굴이 파래 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -18262,7 +18287,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18274,20 +18299,30 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D389" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>탈수 증상이 있는지 확인함</t>
+          <t>말단 청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>"손끝·발끝이 파래 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -18297,7 +18332,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18309,20 +18344,20 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D390" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>경구수분섭취 격려함</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -18332,7 +18367,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18379,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -18353,11 +18388,11 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>구토 양상 확인함</t>
+          <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -18367,7 +18402,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18379,12 +18414,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D392" t="n">
@@ -18392,17 +18427,17 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>산소포화도 monitor 함</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>⚠️ 통증 진단 추가</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18449,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-호흡곤란</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -18423,21 +18458,21 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>산소 흡입 시작함</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>⚠️ 통증 진단 추가</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -18449,30 +18484,40 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D394" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>경련 있음</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>"경련(발작)을 했나요?"</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
         <is>
-          <t>⚠️ 통증 진단 추가</t>
+          <t>지속시간은 📌비고에 기재</t>
         </is>
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18484,30 +18529,40 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>소아-구토설사</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D395" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>경련과 유사한 증상 보임</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>⚠️ 통증 진단 추가</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18519,7 +18574,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -18528,16 +18583,16 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>"아이가 숨쉬기 힘들어 보이나요?"</t>
+          <t>"경련 후 축 처져 있나요?"</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
@@ -18552,7 +18607,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18564,7 +18619,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -18573,21 +18628,21 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>chest retraction 있음/없음</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>"숨쉴 때 갈비뼈 사이나 목이 쑥 들어가나요?"</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -18597,7 +18652,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18609,7 +18664,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -18618,21 +18673,21 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>wheezing 있음/없음</t>
+          <t>체온 상승함</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>"쌕쌕거리는 숨소리가 나나요?"</t>
+          <t>🩺 체온을 측정하세요</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -18642,7 +18697,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18654,30 +18709,20 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D399" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>기침 있음/없음</t>
-        </is>
-      </c>
-      <c r="F399" t="inlineStr">
-        <is>
-          <t>"기침하나요?"</t>
-        </is>
-      </c>
-      <c r="G399" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -18687,7 +18732,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18699,30 +18744,20 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D400" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>가래 잘 뱉지 못함/가래 잘 뱉어냄</t>
-        </is>
-      </c>
-      <c r="F400" t="inlineStr">
-        <is>
-          <t>"가래가 끓는데 잘 못 뱉나요?"</t>
-        </is>
-      </c>
-      <c r="G400" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -18732,7 +18767,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18744,30 +18779,20 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D401" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>청색증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F401" t="inlineStr">
-        <is>
-          <t>"입술이나 얼굴이 파래 보이나요?"</t>
-        </is>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>seizure의 유발요인을 확인함</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -18777,7 +18802,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18789,30 +18814,20 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D402" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>말단 청색증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F402" t="inlineStr">
-        <is>
-          <t>"손끝·발끝이 파래 보이나요?"</t>
-        </is>
-      </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -18822,7 +18837,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -18834,12 +18849,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D403" t="n">
@@ -18847,7 +18862,17 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>urticaria 있음/없음</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -18857,7 +18882,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -18869,20 +18894,30 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D404" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>호흡곤란이 있는지 확인함</t>
+          <t>기저귀 발진 있음/없음</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>🩺 기저귀 부위 발진을 확인하세요</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -18892,7 +18927,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -18904,30 +18939,40 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D405" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>산소포화도 monitor 함</t>
+          <t>가려움증 있음/가려움증 없음</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>"가려워하나요?"</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ 보강</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -18939,30 +18984,40 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>소아-호흡곤란</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D406" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>산소 흡입 시작함</t>
+          <t>bullae 있음/bullae 없음</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>🩺 물집이 잡혔는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ 보강</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -18974,7 +19029,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -18983,31 +19038,31 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>경련 있음</t>
+          <t>열감 있음/열감 없음</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>"경련(발작)을 했나요?"</t>
+          <t>"열이 나나요?"</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>지속시간은 📌비고에 기재</t>
+          <t>⚠️ 보강</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -19019,30 +19074,20 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>경련과 유사한 증상 보임</t>
-        </is>
-      </c>
-      <c r="F408" t="inlineStr">
-        <is>
-          <t>🩺 경련과 비슷한 움직임이 있는지 관찰하세요</t>
-        </is>
-      </c>
-      <c r="G408" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -19052,7 +19097,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -19064,30 +19109,20 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D409" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
-        </is>
-      </c>
-      <c r="F409" t="inlineStr">
-        <is>
-          <t>"경련 후 축 처져 있나요?"</t>
-        </is>
-      </c>
-      <c r="G409" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -19097,7 +19132,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -19109,30 +19144,20 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D410" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
-        </is>
-      </c>
-      <c r="F410" t="inlineStr">
-        <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G410" t="inlineStr">
-        <is>
-          <t>선택</t>
+          <t>긁지 않도록 교육함</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -19142,7 +19167,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -19154,30 +19179,20 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-피부</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D411" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>체온 상승함</t>
-        </is>
-      </c>
-      <c r="F411" t="inlineStr">
-        <is>
-          <t>🩺 체온을 측정하세요</t>
-        </is>
-      </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>소양증 감소 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -19187,7 +19202,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -19199,12 +19214,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D412" t="n">
@@ -19212,7 +19227,17 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>보챔/보채지 않음</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>🩺 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -19222,7 +19247,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19234,20 +19259,30 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>울고 보챔</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>"평소보다 심하게 보채거나 우나요?"</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -19257,7 +19292,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19269,20 +19304,30 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D414" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>seizure의 유발요인을 확인함</t>
+          <t>잠 안자고 울고 보챔</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>"잠을 못 자고 계속 우나요?"</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -19292,7 +19337,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19304,20 +19349,30 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>소아-경련</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D415" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>자주 사지 움직이며 보챔</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -19327,7 +19382,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19339,7 +19394,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -19348,16 +19403,16 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>urticaria 있음/없음</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>"두드러기가 올라왔나요?"</t>
+          <t>"아파하나요?"</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
@@ -19367,12 +19422,12 @@
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>부위는 📌비고에 기재</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19384,7 +19439,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -19393,16 +19448,16 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>기저귀 발진 있음/없음</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>🩺 기저귀 부위 발진을 확인하세요</t>
+          <t>"축 처져 있거나 반응이 느린가요?"</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
@@ -19417,7 +19472,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19429,7 +19484,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -19438,31 +19493,31 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>가려움증 있음/가려움증 없음</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>"가려워하나요?"</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>⚠️ 보강</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19474,40 +19529,30 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>bullae 있음/bullae 없음</t>
-        </is>
-      </c>
-      <c r="F419" t="inlineStr">
-        <is>
-          <t>🩺 물집이 잡혔는지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G419" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>⚠️ 보강</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19519,40 +19564,30 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D420" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>열감 있음/열감 없음</t>
-        </is>
-      </c>
-      <c r="F420" t="inlineStr">
-        <is>
-          <t>"열이 나나요?"</t>
-        </is>
-      </c>
-      <c r="G420" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>통증 강도 측정함</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>⚠️ 보강</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19564,20 +19599,20 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -19587,7 +19622,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -19599,7 +19634,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소아-보챔처짐</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -19608,11 +19643,11 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -19622,89 +19657,109 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D423" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>소아-피부</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D424" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
+          <t>설사 있음/설사 없음</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>"설사하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -19713,43 +19768,43 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>보챔/보채지 않음</t>
+          <t>탈수 증상 있음</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>🩺 보채는지 관찰하세요</t>
+          <t>🩺 탈수 증상(입마름·소변감소)</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -19758,308 +19813,258 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>울고 보챔</t>
+          <t>변비 있음/변비 없음</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>"평소보다 심하게 보채거나 우나요?"</t>
+          <t>"변을 못 보거나 불편하세요?"</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>잠 안자고 울고 보챔</t>
-        </is>
-      </c>
-      <c r="F427" t="inlineStr">
-        <is>
-          <t>"잠을 못 자고 계속 우나요?"</t>
-        </is>
-      </c>
-      <c r="G427" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>체액부족위험</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>자주 사지 움직이며 보챔</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr">
-        <is>
-          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
-        </is>
-      </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>탈수 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D429" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F429" t="inlineStr">
-        <is>
-          <t>"아파하나요?"</t>
-        </is>
-      </c>
-      <c r="G429" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>금식 하도록 교육함</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>부위는 📌비고에 기재</t>
+          <t>⚠️ 마스터 없음 — 시간 붙은 것만 존재(2시간/6시간…). 칩스 확인</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
-        </is>
-      </c>
-      <c r="F430" t="inlineStr">
-        <is>
-          <t>"축 처져 있거나 반응이 느린가요?"</t>
-        </is>
-      </c>
-      <c r="G430" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>변비</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
-        </is>
-      </c>
-      <c r="F431" t="inlineStr">
-        <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G431" t="inlineStr">
-        <is>
-          <t>선택</t>
+          <t>변비 유발 식품을 피하도록 교육함</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>대변 양상 확인함</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D433" t="n">
@@ -20067,34 +20072,39 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>통증 강도 측정함</t>
+          <t>배뇨곤란 있음/배뇨곤란 없음</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>"소변보기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
-        </is>
-      </c>
-      <c r="J433" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D434" t="n">
@@ -20102,34 +20112,39 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>요정체 있음/요정체 없음</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>"소변이 막힌 느낌이세요?"</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
-        </is>
-      </c>
-      <c r="J434" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D435" t="n">
@@ -20137,29 +20152,34 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>잔뇨감 있음/잔뇨감 없음</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
-        </is>
-      </c>
-      <c r="J435" t="inlineStr">
-        <is>
-          <t>급성통증</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -20168,16 +20188,16 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>오심, 구토 있음/오심, 구토 없음</t>
+          <t>혈뇨 있음/혈뇨 없음</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
+          <t>"소변에 피가 보이나요?"</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
@@ -20188,23 +20208,18 @@
       <c r="I436" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J436" t="inlineStr">
-        <is>
-          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -20213,66 +20228,51 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>설사 있음/설사 없음</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>"설사하셨어요?"</t>
+          <t>🩺 소변량 감소</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J437" t="inlineStr">
-        <is>
-          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>탈수 증상 있음</t>
-        </is>
-      </c>
-      <c r="F438" t="inlineStr">
-        <is>
-          <t>🩺 탈수 증상(입마름·소변감소)</t>
-        </is>
-      </c>
-      <c r="G438" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>배뇨장애</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -20282,42 +20282,32 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>배뇨장애</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D439" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>변비 있음/변비 없음</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>"변을 못 보거나 불편하세요?"</t>
-        </is>
-      </c>
-      <c r="G439" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>요정체가 있는지 확인함</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -20327,32 +20317,32 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>변비</t>
+          <t>배뇨장애</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>단순도뇨 시행함</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -20362,19 +20352,19 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>배뇨장애</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -20383,11 +20373,11 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>탈수 증상이 있는지 확인함</t>
+          <t>혈뇨가 있는지 확인함</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -20397,59 +20387,64 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>배뇨장애</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D442" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>금식 하도록 교육함</t>
+          <t>귀분비물 있음/귀분비물 없음</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>"귀에서 분비물이 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>⚠️ 마스터 없음 — 시간 붙은 것만 존재(2시간/6시간…). 칩스 확인</t>
-        </is>
-      </c>
-      <c r="J442" t="inlineStr">
-        <is>
-          <t>체액부족위험</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D443" t="n">
@@ -20457,34 +20452,39 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>변비</t>
+          <t>이명 있음/이명 없음</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>"귀울림(이명)이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J443" t="inlineStr">
-        <is>
-          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D444" t="n">
@@ -20492,34 +20492,39 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>변비 유발 식품을 피하도록 교육함</t>
+          <t>청력 이상 있음</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>"잘 안 들리세요?"</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J444" t="inlineStr">
-        <is>
-          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D445" t="n">
@@ -20527,29 +20532,34 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>대변 양상 확인함</t>
+          <t>코막힘 있음/코막힘 없음</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>"코가 막히세요?"</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -20558,16 +20568,16 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>배뇨곤란 있음/배뇨곤란 없음</t>
+          <t>콧물 있음/콧물 없음</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>"소변보기 힘드세요?"</t>
+          <t>"콧물이 나세요?"</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
@@ -20584,12 +20594,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -20598,16 +20608,16 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>요정체 있음/요정체 없음</t>
+          <t>연하곤란 있음/연하곤란 없음</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>"소변이 막힌 느낌이세요?"</t>
+          <t>"삼키기 힘드세요?"</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
@@ -20624,145 +20634,130 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>잔뇨감 있음/잔뇨감 없음</t>
-        </is>
-      </c>
-      <c r="F448" t="inlineStr">
-        <is>
-          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
-        </is>
-      </c>
-      <c r="G448" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D449" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>혈뇨 있음/혈뇨 없음</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>"소변에 피가 보이나요?"</t>
-        </is>
-      </c>
-      <c r="G449" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
-        </is>
-      </c>
-      <c r="F450" t="inlineStr">
-        <is>
-          <t>🩺 소변량 감소</t>
-        </is>
-      </c>
-      <c r="G450" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>청력장애가 있는지 사정함</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
+          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -20772,24 +20767,24 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D452" t="n">
@@ -20797,7 +20792,17 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>요정체가 있는지 확인함</t>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -20807,24 +20812,24 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D453" t="n">
@@ -20832,7 +20837,17 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>단순도뇨 시행함</t>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -20842,24 +20857,24 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D454" t="n">
@@ -20867,7 +20882,17 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>혈뇨가 있는지 확인함</t>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -20877,19 +20902,19 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -20898,38 +20923,43 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>귀분비물 있음/귀분비물 없음</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>"귀에서 분비물이 나오세요?"</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -20938,16 +20968,16 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>이명 있음/이명 없음</t>
+          <t>감각이상 있음/감각이상 없음</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>"귀울림(이명)이 있으세요?"</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -20958,18 +20988,23 @@
       <c r="I456" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -20978,38 +21013,43 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>청력 이상 있음</t>
+          <t>grasp power 약함/grasp power 강함</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>"잘 안 들리세요?"</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -21018,16 +21058,16 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>코막힘 있음/코막힘 없음</t>
+          <t>vertigo 있음/vertigo 없음</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>"코가 막히세요?"</t>
+          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -21038,18 +21078,23 @@
       <c r="I458" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -21058,16 +21103,16 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>콧물 있음/콧물 없음</t>
+          <t>syncope 있음/syncope 없음</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>"콧물이 나세요?"</t>
+          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
@@ -21078,18 +21123,23 @@
       <c r="I459" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -21098,16 +21148,16 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>연하곤란 있음/연하곤란 없음</t>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>"삼키기 힘드세요?"</t>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
@@ -21118,18 +21168,23 @@
       <c r="I460" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -21142,7 +21197,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -21152,19 +21207,19 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -21177,7 +21232,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -21187,19 +21242,19 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -21212,7 +21267,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>청력장애가 있는지 사정함</t>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -21222,19 +21277,19 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -21247,7 +21302,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -21257,7 +21312,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -21274,25 +21329,15 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>오심, 구토 있음/오심, 구토 없음</t>
-        </is>
-      </c>
-      <c r="F465" t="inlineStr">
-        <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
-        </is>
-      </c>
-      <c r="G465" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -21302,7 +21347,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -21319,25 +21364,15 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>dizziness 있음/dizziness 없음</t>
-        </is>
-      </c>
-      <c r="F466" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
-      <c r="G466" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -21347,7 +21382,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -21364,25 +21399,15 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
-        </is>
-      </c>
-      <c r="F467" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
-        </is>
-      </c>
-      <c r="G467" t="inlineStr">
-        <is>
-          <t>값입력</t>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -21409,30 +21434,20 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
-        </is>
-      </c>
-      <c r="F468" t="inlineStr">
-        <is>
-          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
-        </is>
-      </c>
-      <c r="G468" t="inlineStr">
-        <is>
-          <t>선택</t>
+          <t>조직관류 증진 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
@@ -21454,25 +21469,15 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>감각이상 있음/감각이상 없음</t>
-        </is>
-      </c>
-      <c r="F469" t="inlineStr">
-        <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
-      <c r="G469" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -21489,12 +21494,12 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -21503,43 +21508,38 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>grasp power 약함/grasp power 강함</t>
+          <t>음독 함 ★</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J470" t="inlineStr">
-        <is>
-          <t>조직관류저하:뇌</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -21548,16 +21548,16 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>vertigo 있음/vertigo 없음</t>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
@@ -21568,23 +21568,18 @@
       <c r="I471" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J471" t="inlineStr">
-        <is>
-          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -21593,16 +21588,16 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>syncope 있음/syncope 없음</t>
+          <t>dizziness 있음/dizziness 없음</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
@@ -21613,23 +21608,18 @@
       <c r="I472" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J472" t="inlineStr">
-        <is>
-          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -21638,183 +21628,198 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음/obey command 가능함</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J473" t="inlineStr">
-        <is>
-          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>선택</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J474" t="inlineStr">
-        <is>
-          <t>신체손상위험</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>감각이상 있음/감각이상 없음</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J475" t="inlineStr">
-        <is>
-          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>손상을 예방하는 방법에 대해 교육함</t>
+          <t>grasp power 약함/grasp power 강함</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J476" t="inlineStr">
-        <is>
-          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J477" t="inlineStr">
-        <is>
-          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -21823,11 +21828,11 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>중독위험</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -21837,19 +21842,19 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -21858,11 +21863,11 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>위세척에 대해 설명함</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -21872,19 +21877,19 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -21893,11 +21898,11 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>처방에 의해 해독제를 투여함</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -21907,19 +21912,19 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -21928,11 +21933,11 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>조직관류 증진 방법에 대해 교육함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -21942,19 +21947,19 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -21963,11 +21968,11 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -21977,19 +21982,19 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -22002,12 +22007,12 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>음독 함 ★</t>
+          <t>골절 있음</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
+          <t>"부러진 곳(골절)이 있으세요?"</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -22017,19 +22022,24 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -22042,12 +22052,12 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>오심, 구토 있음/오심, 구토 없음</t>
+          <t>골절부위 edema 있음/골절부위 edema 없음</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
+          <t>"다친 곳이 붓나요?"</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -22058,18 +22068,23 @@
       <c r="I484" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -22082,12 +22097,12 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>dizziness 있음/dizziness 없음</t>
+          <t>골절부위 tingling sense 있음/골절부위 tingling sense 없음</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>"저릿하거나 감각이 이상하세요?"</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -22098,18 +22113,23 @@
       <c r="I485" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -22122,34 +22142,39 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>찰과상 있음/찰과상 없음</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -22162,154 +22187,144 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+          <t>출혈 있음/출혈 없음</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+          <t>"피가 나나요?"</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>감각이상 있음/감각이상 없음</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>grasp power 약함/grasp power 강함</t>
-        </is>
-      </c>
-      <c r="F489" t="inlineStr">
-        <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
-        </is>
-      </c>
-      <c r="G489" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>골절부위 압박붕대 감아줌</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음/obey command 가능함</t>
-        </is>
-      </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G490" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>골절부위 올려줌</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -22318,11 +22333,11 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -22332,19 +22347,19 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>골절외상</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -22353,11 +22368,11 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>위세척에 대해 설명함</t>
+          <t>sensory motor circulation 확인함</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -22367,32 +22382,42 @@
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>처방에 의해 해독제를 투여함</t>
+          <t>시력감퇴 있음/시력감퇴 없음</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>"예전보다 잘 안 보이세요?"</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -22402,32 +22427,42 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>시야결손 있음/시야결손 없음</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>"시야 일부가 가려지세요?"</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -22437,32 +22472,42 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D495" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>복시 있음/복시 없음</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -22472,19 +22517,19 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -22493,21 +22538,21 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>골절 있음</t>
+          <t>결막충혈 있음/결막충혈 없음</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>"부러진 곳(골절)이 있으세요?"</t>
+          <t>"눈이 충혈되었나요?"</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -22517,19 +22562,19 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -22538,21 +22583,21 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>골절부위 edema 있음/골절부위 edema 없음</t>
+          <t>이물질 관찰됨</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>"다친 곳이 붓나요?"</t>
+          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -22562,19 +22607,19 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -22583,16 +22628,16 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>골절부위 tingling sense 있음/골절부위 tingling sense 없음</t>
+          <t>결막출혈 있음/결막출혈 없음</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>"저릿하거나 감각이 이상하세요?"</t>
+          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -22607,87 +22652,67 @@
       </c>
       <c r="J498" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>찰과상 있음/찰과상 없음</t>
-        </is>
-      </c>
-      <c r="F499" t="inlineStr">
-        <is>
-          <t>"긁힌 상처(찰과상)가 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G499" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터는 통합형(시각,청각,촉각…)</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D500" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>출혈 있음/출혈 없음</t>
-        </is>
-      </c>
-      <c r="F500" t="inlineStr">
-        <is>
-          <t>"피가 나나요?"</t>
-        </is>
-      </c>
-      <c r="G500" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -22697,32 +22722,32 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>안대 적용함</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -22732,32 +22757,32 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>골절부위 압박붕대 감아줌</t>
+          <t>안위변화</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -22767,19 +22792,19 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -22788,11 +22813,11 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>골절부위 올려줌</t>
+          <t>이물질 제거함</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -22802,32 +22827,32 @@
       </c>
       <c r="J503" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
+          <t>안연고 점안 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -22837,32 +22862,42 @@
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>골절외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D505" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>sensory motor circulation 확인함</t>
+          <t>가려움증 있음/가려움증 없음</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -22872,19 +22907,19 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -22893,16 +22928,16 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>시력감퇴 있음/시력감퇴 없음</t>
+          <t>urticaria 있음/urticaria 없음</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>"예전보다 잘 안 보이세요?"</t>
+          <t>"두드러기가 올라왔나요?"</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -22917,19 +22952,19 @@
       </c>
       <c r="J506" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -22938,16 +22973,16 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>시야결손 있음/시야결손 없음</t>
+          <t>bullae 있음/bullae 없음</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>"시야 일부가 가려지세요?"</t>
+          <t>"물집이 잡혔나요?"</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -22962,42 +22997,32 @@
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D508" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>복시 있음/복시 없음</t>
-        </is>
-      </c>
-      <c r="F508" t="inlineStr">
-        <is>
-          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
-        </is>
-      </c>
-      <c r="G508" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -23007,42 +23032,32 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D509" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>결막충혈 있음/결막충혈 없음</t>
-        </is>
-      </c>
-      <c r="F509" t="inlineStr">
-        <is>
-          <t>"눈이 충혈되었나요?"</t>
-        </is>
-      </c>
-      <c r="G509" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>긁지 않도록 교육함</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -23052,42 +23067,32 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D510" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>이물질 관찰됨</t>
-        </is>
-      </c>
-      <c r="F510" t="inlineStr">
-        <is>
-          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
-        </is>
-      </c>
-      <c r="G510" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>소양증 감소 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -23097,42 +23102,32 @@
       </c>
       <c r="J510" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>결막출혈 있음/결막출혈 없음</t>
-        </is>
-      </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
-        </is>
-      </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -23142,59 +23137,59 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터는 통합형(시각,청각,촉각…)</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D513" t="n">
@@ -23202,7 +23197,17 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -23212,24 +23217,24 @@
       </c>
       <c r="J513" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D514" t="n">
@@ -23237,7 +23242,17 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -23247,67 +23262,87 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>선택</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>이물질 제거함</t>
+          <t>감각이상 있음/감각이상 없음</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -23317,32 +23352,42 @@
       </c>
       <c r="J516" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D517" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>안연고 점안 방법에 대해 교육함</t>
+          <t>grasp power 약함/grasp power 강함</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -23352,19 +23397,19 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -23373,16 +23418,16 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>가려움증 있음/가려움증 없음</t>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>"피부가 가려우세요?"</t>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -23397,19 +23442,19 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -23418,16 +23463,16 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>urticaria 있음/urticaria 없음</t>
+          <t>사람에 대한 지남력 없음/사람에 대한 지남력 있음</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>"두드러기가 올라왔나요?"</t>
+          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -23442,19 +23487,19 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -23463,16 +23508,16 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>bullae 있음/bullae 없음</t>
+          <t>섬망 있음/섬망 없음</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>"물집이 잡혔나요?"</t>
+          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -23487,32 +23532,42 @@
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D521" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>환각 있음/환각 없음</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>"없는 것이 보이거나 들리세요?"</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -23522,32 +23577,42 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D522" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
+          <t>flapping tremor 있음/flapping tremor 없음</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>🩺 양손을 앞으로 뻗고 손목을 젖히게 해보세요 — 파닥이듯 떨리나요?</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -23557,32 +23622,32 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -23592,32 +23657,32 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -23627,19 +23692,19 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -23648,11 +23713,11 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -23662,7 +23727,7 @@
       </c>
       <c r="J525" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -23679,25 +23744,15 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>dizziness 있음/dizziness 없음</t>
-        </is>
-      </c>
-      <c r="F526" t="inlineStr">
-        <is>
-          <t>"어지러우세요?"</t>
-        </is>
-      </c>
-      <c r="G526" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>알코올금단증</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -23707,7 +23762,7 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -23724,25 +23779,15 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
-        </is>
-      </c>
-      <c r="F527" t="inlineStr">
-        <is>
-          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
-        </is>
-      </c>
-      <c r="G527" t="inlineStr">
-        <is>
-          <t>값입력</t>
+          <t>알코올 섭취 양상을 확인함</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -23752,7 +23797,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -23769,35 +23814,25 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
-        </is>
-      </c>
-      <c r="F528" t="inlineStr">
-        <is>
-          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
-        </is>
-      </c>
-      <c r="G528" t="inlineStr">
-        <is>
-          <t>선택</t>
+          <t>금단 증상을 설명함</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -23814,25 +23849,15 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D529" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>감각이상 있음/감각이상 없음</t>
-        </is>
-      </c>
-      <c r="F529" t="inlineStr">
-        <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
-        </is>
-      </c>
-      <c r="G529" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -23842,19 +23867,19 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -23863,16 +23888,16 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>grasp power 약함/grasp power 강함</t>
+          <t>구체적 자살계획을 언급함/자해나 자살시도를 부인함</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -23887,19 +23912,19 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -23908,21 +23933,21 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음/obey command 가능함</t>
+          <t>자살을 시도함</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+          <t>자살 시도 (구체적 사항 비고에 기재)</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -23932,19 +23957,19 @@
       </c>
       <c r="J531" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -23953,21 +23978,21 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>사람에 대한 지남력 없음/사람에 대한 지남력 있음</t>
+          <t>자살 충동 있음</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+          <t>자살 충동 (구체적 사항 비고에 기재)</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -23977,19 +24002,19 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -23998,16 +24023,16 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>섬망 있음/섬망 없음</t>
+          <t>공격적 행동함/타인에 대한 공격적 행동을 보이지 않음</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
+          <t>🩺 공격적 행동(관찰)</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -24022,19 +24047,19 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -24043,16 +24068,16 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>환각 있음/환각 없음</t>
+          <t>공황상태 있음/공황상태 없음</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>"없는 것이 보이거나 들리세요?"</t>
+          <t>"심하게 불안하거나 공황 상태이세요?"</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -24067,42 +24092,32 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D535" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>flapping tremor 있음/flapping tremor 없음</t>
-        </is>
-      </c>
-      <c r="F535" t="inlineStr">
-        <is>
-          <t>🩺 양손을 앞으로 뻗고 손목을 젖히게 해보세요 — 파닥이듯 떨리나요?</t>
-        </is>
-      </c>
-      <c r="G535" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>자살위험</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -24112,24 +24127,24 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D536" t="n">
@@ -24137,7 +24152,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24147,19 +24162,19 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -24168,11 +24183,11 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -24182,24 +24197,24 @@
       </c>
       <c r="J537" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D538" t="n">
@@ -24207,7 +24222,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -24217,32 +24232,32 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>진정시킴</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -24252,19 +24267,19 @@
       </c>
       <c r="J539" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -24273,11 +24288,11 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>알코올 섭취 양상을 확인함</t>
+          <t>억제대 적용 중임</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24287,32 +24302,32 @@
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D541" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>금단 증상을 설명함</t>
+          <t>불안</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24322,19 +24337,19 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -24347,7 +24362,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>불안을 감소시켜 줌</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -24357,7 +24372,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
@@ -24374,25 +24389,15 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>구체적 자살계획을 언급함/자해나 자살시도를 부인함</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G543" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>경청해줌</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -24402,19 +24407,19 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -24423,21 +24428,21 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>자살을 시도함</t>
+          <t>혈압(mmHg) :</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -24447,19 +24452,19 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -24468,16 +24473,16 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>자살 충동 있음</t>
+          <t>혈압 상승됨</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>자살 충동 (구체적 사항 비고에 기재)</t>
+          <t>🩺 혈압 상승됨 (고혈압)</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -24492,19 +24497,19 @@
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -24513,21 +24518,21 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>공격적 행동함/타인에 대한 공격적 행동을 보이지 않음</t>
+          <t>혈압 저하됨</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>🩺 공격적 행동(관찰)</t>
+          <t>🩺 혈압 저하됨 (저혈압)</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -24537,19 +24542,19 @@
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -24558,16 +24563,16 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>공황상태 있음/공황상태 없음</t>
+          <t>고혈압으로 인한 증상 있음/고혈압으로 인한 증상 없음</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>"심하게 불안하거나 공황 상태이세요?"</t>
+          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -24582,32 +24587,42 @@
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>체위성 저혈압 있음</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -24617,24 +24632,24 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D549" t="n">
@@ -24642,7 +24657,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>고혈압</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -24652,19 +24667,19 @@
       </c>
       <c r="J549" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -24673,11 +24688,11 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -24687,24 +24702,24 @@
       </c>
       <c r="J550" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D551" t="n">
@@ -24712,7 +24727,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>Non Invasive BP monitor 시작함</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -24722,19 +24737,19 @@
       </c>
       <c r="J551" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -24747,7 +24762,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>진정시킴</t>
+          <t>혈압관리 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -24757,32 +24772,32 @@
       </c>
       <c r="J552" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>억제대 적용 중임</t>
+          <t>저혈압</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -24792,32 +24807,32 @@
       </c>
       <c r="J553" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -24827,19 +24842,19 @@
       </c>
       <c r="J554" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -24852,7 +24867,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>불안을 감소시켜 줌</t>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -24862,19 +24877,19 @@
       </c>
       <c r="J555" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -24887,7 +24902,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>경청해줌</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -24896,511 +24911,6 @@
         </is>
       </c>
       <c r="J556" t="inlineStr">
-        <is>
-          <t>불안</t>
-        </is>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C557" t="inlineStr">
-        <is>
-          <t>A&amp;E</t>
-        </is>
-      </c>
-      <c r="D557" t="n">
-        <v>1</v>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>혈압(mmHg) :</t>
-        </is>
-      </c>
-      <c r="F557" t="inlineStr">
-        <is>
-          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
-        </is>
-      </c>
-      <c r="G557" t="inlineStr">
-        <is>
-          <t>값입력</t>
-        </is>
-      </c>
-      <c r="I557" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J557" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B558" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C558" t="inlineStr">
-        <is>
-          <t>A&amp;E</t>
-        </is>
-      </c>
-      <c r="D558" t="n">
-        <v>2</v>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>혈압 상승됨</t>
-        </is>
-      </c>
-      <c r="F558" t="inlineStr">
-        <is>
-          <t>🩺 혈압 상승됨 (고혈압)</t>
-        </is>
-      </c>
-      <c r="G558" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J558" t="inlineStr">
-        <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B559" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C559" t="inlineStr">
-        <is>
-          <t>A&amp;E</t>
-        </is>
-      </c>
-      <c r="D559" t="n">
-        <v>3</v>
-      </c>
-      <c r="E559" t="inlineStr">
-        <is>
-          <t>혈압 저하됨</t>
-        </is>
-      </c>
-      <c r="F559" t="inlineStr">
-        <is>
-          <t>🩺 혈압 저하됨 (저혈압)</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
-      <c r="I559" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J559" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B560" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C560" t="inlineStr">
-        <is>
-          <t>A&amp;E</t>
-        </is>
-      </c>
-      <c r="D560" t="n">
-        <v>4</v>
-      </c>
-      <c r="E560" t="inlineStr">
-        <is>
-          <t>고혈압으로 인한 증상 있음/고혈압으로 인한 증상 없음</t>
-        </is>
-      </c>
-      <c r="F560" t="inlineStr">
-        <is>
-          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G560" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J560" t="inlineStr">
-        <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B561" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C561" t="inlineStr">
-        <is>
-          <t>A&amp;E</t>
-        </is>
-      </c>
-      <c r="D561" t="n">
-        <v>5</v>
-      </c>
-      <c r="E561" t="inlineStr">
-        <is>
-          <t>체위성 저혈압 있음</t>
-        </is>
-      </c>
-      <c r="F561" t="inlineStr">
-        <is>
-          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
-        </is>
-      </c>
-      <c r="G561" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
-      <c r="I561" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J561" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B562" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C562" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D562" t="n">
-        <v>1</v>
-      </c>
-      <c r="E562" t="inlineStr">
-        <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-      <c r="I562" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J562" t="inlineStr">
-        <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B563" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C563" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D563" t="n">
-        <v>1</v>
-      </c>
-      <c r="E563" t="inlineStr">
-        <is>
-          <t>혈압 측정함</t>
-        </is>
-      </c>
-      <c r="I563" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J563" t="inlineStr">
-        <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B564" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D564" t="n">
-        <v>2</v>
-      </c>
-      <c r="E564" t="inlineStr">
-        <is>
-          <t>Non Invasive BP monitor 시작함</t>
-        </is>
-      </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J564" t="inlineStr">
-        <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B565" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C565" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D565" t="n">
-        <v>3</v>
-      </c>
-      <c r="E565" t="inlineStr">
-        <is>
-          <t>혈압관리 방법에 대해 교육함</t>
-        </is>
-      </c>
-      <c r="I565" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J565" t="inlineStr">
-        <is>
-          <t>고혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B566" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C566" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D566" t="n">
-        <v>2</v>
-      </c>
-      <c r="E566" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-      <c r="I566" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J566" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B567" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D567" t="n">
-        <v>4</v>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>혈압 측정함</t>
-        </is>
-      </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J567" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B568" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D568" t="n">
-        <v>5</v>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>체위성 저혈압 증상이 있는지 확인함</t>
-        </is>
-      </c>
-      <c r="I568" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J568" t="inlineStr">
-        <is>
-          <t>저혈압</t>
-        </is>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="B569" t="inlineStr">
-        <is>
-          <t>혈압</t>
-        </is>
-      </c>
-      <c r="C569" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D569" t="n">
-        <v>6</v>
-      </c>
-      <c r="E569" t="inlineStr">
-        <is>
-          <t>안전간호를 제공함</t>
-        </is>
-      </c>
-      <c r="I569" t="inlineStr">
-        <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J569" t="inlineStr">
         <is>
           <t>저혈압</t>
         </is>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1407,7 +1407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3442,6 +3442,114 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>anaphylaxis</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>🐝</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>burn</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>😪</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3453,7 +3561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K556"/>
+  <dimension ref="A1:K611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -24913,6 +25021,2121 @@
       <c r="J556" t="inlineStr">
         <is>
           <t>저혈압</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>7</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>인후 불편감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>"목이 아프거나 불편하세요?"</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>8</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>인후 충혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>🩺 목 안이 붉은지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>2</v>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>4</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>5</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>6</v>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>7</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>인후 상태를 확인함</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>7</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>안구통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>"눈이 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>3</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>5</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>6</v>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>안과</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>7</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>6</v>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>옆구리 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>"옆구리(허리 옆)가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>2</v>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>4</v>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>5</v>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>비뇨기</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>6</v>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>1</v>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>전신 허약감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>"온몸에 기운이 없으세요?"</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>2</v>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>사지 허약감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>"팔다리에 힘이 없으세요?"</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>3</v>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>피로 호소함/피로하지 않다고 함</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>"많이 피곤하세요?"</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>4</v>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>dizziness 있음/없음</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>1</v>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>1</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>피로 정도를 확인함</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>2</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>24시간 피로 수준을 사정함</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>전신 쇠약</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>3</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>활동의 지속성장애</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>1</v>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>알레르기 있음/없음</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>"약이나 음식에 알레르기가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>2</v>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>urticaria 있음/없음</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>3</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>가려움증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>4</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>호흡곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>"숨이 차거나 답답하신가요?"</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>5</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>wheezing 있음/없음</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>🩺 쌕쌕거리는 숨소리를 청진하세요</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>6</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>연하곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>"목이 붓거나 삼키기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>7</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>🩺 입술·얼굴이 파란지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>8</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>혈압 저하됨</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>🩺 혈압이 떨어졌는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>1</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>1</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>알레르기원을 확인함</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>2</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>알레르기 과거력이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>3</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>전신 알레르기 반응이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>4</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>알레르기원에 노출되지 않도록 교육함</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>알레르기반응</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D595" t="n">
+        <v>2</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D596" t="n">
+        <v>5</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>산소 흡입 시작함</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D597" t="n">
+        <v>6</v>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>IV 주입경로 확보하여 수액 주입함</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D598" t="n">
+        <v>1</v>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>화상 입음</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>"화상을 입으셨나요?"</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D599" t="n">
+        <v>2</v>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>bullae 있음/없음</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>🩺 물집이 잡혔는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D600" t="n">
+        <v>3</v>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>"화상 부위가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D601" t="n">
+        <v>1</v>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D602" t="n">
+        <v>1</v>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>화상부위 세척함</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D603" t="n">
+        <v>2</v>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>화상부위 오염물 제거함</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D604" t="n">
+        <v>3</v>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>화상 dressing 함</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D605" t="n">
+        <v>2</v>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D606" t="n">
+        <v>4</v>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D607" t="n">
+        <v>5</v>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>흡입 화상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D608" t="n">
+        <v>3</v>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D609" t="n">
+        <v>6</v>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D610" t="n">
+        <v>7</v>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>화상</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D611" t="n">
+        <v>8</v>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>커버리지 보완 260802</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -974,7 +974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1002,11 +1002,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>기도개방 상태를 확인함</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -1017,11 +1017,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>출혈양상 확인함</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1047,11 +1047,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>호흡곤란이 있는지 확인함</t>
+          <t>출혈양상 확인함</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,11 +1062,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1077,11 +1077,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1092,11 +1092,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1107,11 +1107,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>사지 근력 평가함</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seizure 양상 확인함</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1137,11 +1137,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>흉부 통증이 있는지 확인함</t>
+          <t>seizure 양상 확인함</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>심전도 변화를 확인함</t>
+          <t>흉부 통증이 있는지 확인함</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1167,7 +1167,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>탈수 증상이 있는지 확인함</t>
+          <t>심전도 변화를 확인함</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1182,7 +1182,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>탈수 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1197,7 +1197,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1212,11 +1212,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>구토 양상 확인함</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>통증 강도 측정함</t>
+          <t>구토 양상 확인함</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1242,7 +1242,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대변 양상 확인함</t>
+          <t>통증 강도 측정함</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1257,7 +1257,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>요정체가 있는지 확인함</t>
+          <t>대변 양상 확인함</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1272,7 +1272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>혈뇨가 있는지 확인함</t>
+          <t>요정체가 있는지 확인함</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1287,7 +1287,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>sensory motor circulation 확인함</t>
+          <t>혈뇨가 있는지 확인함</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1302,7 +1302,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>알코올 섭취 양상을 확인함</t>
+          <t>sensory motor circulation 확인함</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1314,83 +1314,99 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>— 아래는 애매해서 수동으로 두었다. 자동으로 돌리려면 위로 옮기세요 —</t>
-        </is>
-      </c>
-    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>알코올 섭취 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>사정을 했으면 반드시 참 — 자동 기록</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>(수동) 산소포화도 monitor 함</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>8</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>기계를 붙이는 행위에 가깝다</t>
+          <t>— 아래는 애매해서 수동으로 두었다. 자동으로 돌리려면 위로 옮기세요 —</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>(수동) seizure의 유발요인을 확인함</t>
+          <t>(수동) 산소포화도 monitor 함</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>따로 물어봐야 안다</t>
+          <t>기계를 붙이는 행위에 가깝다</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>(수동) 통증을 관찰하기로 함</t>
+          <t>(수동) seizure의 유발요인을 확인함</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>사정이 아니라 계획이다</t>
+          <t>따로 물어봐야 안다</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>(수동) 청력장애가 있는지 사정함</t>
+          <t>(수동) 통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>별도 검사가 필요하다</t>
+          <t>사정이 아니라 계획이다</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>(수동) 체위성 저혈압 증상이 있는지 확인함</t>
+          <t>(수동) 청력장애가 있는지 사정함</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
+        <is>
+          <t>별도 검사가 필요하다</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>(수동) 체위성 저혈압 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>기립 혈압을 따로 재야 한다</t>
         </is>
@@ -3458,10 +3474,6 @@
           <t>🐝</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>아나필락시스</t>
@@ -3494,10 +3506,6 @@
           <t>🔥</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>화상</t>
@@ -3530,10 +3538,6 @@
           <t>😪</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>전신 쇠약</t>
@@ -3561,7 +3565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K611"/>
+  <dimension ref="A1:K613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -26566,7 +26570,7 @@
         </is>
       </c>
       <c r="D596" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E596" t="inlineStr">
         <is>
@@ -26601,7 +26605,7 @@
         </is>
       </c>
       <c r="D597" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E597" t="inlineStr">
         <is>
@@ -27136,6 +27140,76 @@
       <c r="J611" t="inlineStr">
         <is>
           <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D612" t="n">
+        <v>1</v>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>기도개방 상태를 확인함</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>확인형 — 산소·수액은 안 할 수도 있다</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>아나필락시스</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>2</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>호흡곤란이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>확인형 — 산소·수액은 안 할 수도 있다</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>기도개방유지불능</t>
         </is>
       </c>
     </row>
@@ -30562,9 +30636,14 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>통증있음</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>아파도 참는 환자가 많아 반드시 묻는다</t>
+          <t>통증이 확인됐을 때만 묻는다 — 통증 없는 환자에게 물으면 이상하다</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1329,7 +1329,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -1423,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3554,6 +3553,314 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ob</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>임신·산과</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>🤰</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>임신 상태가 어떻게 되세요?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>🤰 임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ob</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>임신·산과</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>🤰</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>임신 상태가 어떻게 되세요?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>🤰 임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ob</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>임신·산과</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>🤰</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>임신 상태가 어떻게 되세요?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>👶 출산 후 6주 이내</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>ob</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>임신·산과</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>🤰</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>임신 상태가 어떻게 되세요?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>🚺 임신 아님</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>🟡 노랗게 보여요</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>🍼 잘 못 먹어요</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>peds</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>아이가 어디가 불편해서 왔나요?</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>😮‍💨 숨을 멈췄어요</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3565,7 +3872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K613"/>
+  <dimension ref="A1:K693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -27210,6 +27517,3106 @@
       <c r="J613" t="inlineStr">
         <is>
           <t>기도개방유지불능</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>1</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>질 출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>"질에서 피가 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>2</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>자궁수축 있음/없음</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>"배가 규칙적으로 뭉치세요?"</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>3</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>질 분비물 있음/없음</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>"평소와 다른 분비물이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>4</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>복부 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>"배가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>1</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>1</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>2</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>출혈양상 확인함</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>2</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>3</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>질 분비물 양상 관찰함</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>3</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>4</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>5</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>임신 20주 미만</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>6</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>1</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>태동 있음/태동 없음</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>"아기가 움직이는 게 느껴지세요?"</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>2</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>자궁수축 있음/없음</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>"배가 규칙적으로 뭉치세요?"</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>3</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>양막파열 있음/없음</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>"양수가 터진 것 같으세요?"</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>4</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>양수 leakage 있음/없음</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>🩺 양수가 새는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>5</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>질 출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>"질에서 피가 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>6</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>복부 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>"배가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>1</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>1</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>분만 진행 상태 확인함</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>2</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>양수 양상 관찰함</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>3</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>양막 파열 시간 확인함</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>모체와태아상태위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>2</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>4</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>5</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>출혈양상 확인함</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>3</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D641" t="n">
+        <v>6</v>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D642" t="n">
+        <v>7</v>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>임신 20주 이상</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D643" t="n">
+        <v>8</v>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D644" t="n">
+        <v>1</v>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>오로 있음</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>🩺 오로가 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D645" t="n">
+        <v>2</v>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>질 출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>"평소보다 피가 많이 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D646" t="n">
+        <v>3</v>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>열감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>"열이 나거나 오한이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D647" t="n">
+        <v>4</v>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>복부 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>"배가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D648" t="n">
+        <v>1</v>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D649" t="n">
+        <v>1</v>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>오로 관찰함</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D650" t="n">
+        <v>2</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D651" t="n">
+        <v>2</v>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D652" t="n">
+        <v>3</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D653" t="n">
+        <v>4</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D654" t="n">
+        <v>3</v>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D655" t="n">
+        <v>5</v>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D656" t="n">
+        <v>6</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>출산 후 (6주 이내)</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D657" t="n">
+        <v>7</v>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D658" t="n">
+        <v>1</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>질 분비물 있음/없음</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>"평소와 다른 분비물이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D659" t="n">
+        <v>2</v>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>질 출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>"질에서 피가 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D660" t="n">
+        <v>3</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>무월경 있음</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>🩺 생리가 없는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D661" t="n">
+        <v>4</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>월경불순이 있다고 함</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>🩺 생리가 불규칙한지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D662" t="n">
+        <v>5</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>복부 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>"아랫배가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D663" t="n">
+        <v>1</v>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D664" t="n">
+        <v>1</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>질 분비물 양상 관찰함</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D665" t="n">
+        <v>2</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>월경력 확인함</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D666" t="n">
+        <v>2</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D667" t="n">
+        <v>3</v>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>출혈양상 확인함</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D668" t="n">
+        <v>3</v>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D669" t="n">
+        <v>4</v>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D670" t="n">
+        <v>5</v>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>산과</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>부인과 (임신 아님)</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D671" t="n">
+        <v>6</v>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D672" t="n">
+        <v>1</v>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>황달 있음/없음</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>"아기 피부가 노랗게 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D673" t="n">
+        <v>2</v>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>공막의 황달 있음/없음</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>🩺 눈 흰자가 노란지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D674" t="n">
+        <v>3</v>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>수유 잘함/보충수유 필요함</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>"젖을 잘 먹나요?"</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D675" t="n">
+        <v>4</v>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>lethargy 상태임/의식 명료함</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>"아이가 축 처져 있나요?"</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D676" t="n">
+        <v>1</v>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D677" t="n">
+        <v>1</v>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>황달이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>소아-황달</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D678" t="n">
+        <v>2</v>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>수유 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D679" t="n">
+        <v>1</v>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>수유 잘함/보충수유 필요함</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>"젖을 잘 먹나요?"</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D680" t="n">
+        <v>2</v>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>수유 후 구토 보임/수유 후 구토 없음</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>"먹고 나서 토하나요?"</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D681" t="n">
+        <v>3</v>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>수유 후 역류 보임/수유 후 역류 없음</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>"먹고 나서 올리나요?"</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D682" t="n">
+        <v>4</v>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>수유 후 만족감 있음</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>🩺 먹고 나서 편안해 보이는지 관찰하세요</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D683" t="n">
+        <v>1</v>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D684" t="n">
+        <v>1</v>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>수유 중 아기의 피로 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>소아-수유곤란</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D685" t="n">
+        <v>2</v>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>수유 방법에 대해 교육함</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D686" t="n">
+        <v>1</v>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>무호흡 있음/없음</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>"숨을 멈춘 적이 있나요?"</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D687" t="n">
+        <v>2</v>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>"입술이나 얼굴이 파래졌나요?"</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D688" t="n">
+        <v>3</v>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>apnea alarm 울림/apnea alarm 울리지 않음</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>🩺 무호흡 알람이 울렸는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D689" t="n">
+        <v>1</v>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D690" t="n">
+        <v>1</v>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>호흡곤란이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D691" t="n">
+        <v>2</v>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>산소포화도 monitor 함</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D692" t="n">
+        <v>3</v>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>무호흡 monitor 시작함</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>소아-무호흡</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D693" t="n">
+        <v>4</v>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>무호흡 지속 시간 측정함</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1422,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3273,27 +3273,37 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>어디를 다치셨어요?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>🦴 팔·다리 (골절)</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
           <t>골절외상</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>🤕</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>골절외상</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>골절외상</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>외상 부위 구분 260802</t>
         </is>
       </c>
     </row>
@@ -3579,8 +3589,6 @@
           <t>🤰 임신 20주 미만</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
           <t>산과</t>
@@ -3623,8 +3631,6 @@
           <t>🤰 임신 20주 이상</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>산과</t>
@@ -3667,8 +3673,6 @@
           <t>👶 출산 후 6주 이내</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>산과</t>
@@ -3711,8 +3715,6 @@
           <t>🚺 임신 아님</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>산과</t>
@@ -3755,8 +3757,6 @@
           <t>🟡 노랗게 보여요</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>소아</t>
@@ -3799,8 +3799,6 @@
           <t>🍼 잘 못 먹어요</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
           <t>소아</t>
@@ -3843,8 +3841,6 @@
           <t>😮‍💨 숨을 멈췄어요</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
           <t>소아</t>
@@ -3858,6 +3854,270 @@
       <c r="J62" t="inlineStr">
         <is>
           <t>커버리지 2차 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>trauma</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>어디를 다치셨어요?</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>🧠 머리</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>trauma</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>어디를 다치셨어요?</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>😐 얼굴</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>trauma</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>어디를 다치셨어요?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>🧣 목·척추</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>trauma</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>어디를 다치셨어요?</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>🫀 가슴</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>trauma</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>어디를 다치셨어요?</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>🫃 배</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>trauma</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>어디를 다치셨어요?</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>🚨 여러 곳</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
         </is>
       </c>
     </row>
@@ -3872,7 +4132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K693"/>
+  <dimension ref="A1:K771"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -30617,6 +30877,2976 @@
       <c r="J693" t="inlineStr">
         <is>
           <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D694" t="n">
+        <v>1</v>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>신체손상 있음</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>🩺 머리에 손상이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D695" t="n">
+        <v>2</v>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>"머리에서 피가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D696" t="n">
+        <v>3</v>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>찰과상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>🩺 긁힌 상처를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D697" t="n">
+        <v>4</v>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>두통 있음/두통 없음</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>"머리가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D698" t="n">
+        <v>5</v>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>"메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>1</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>1</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>신경학적 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>2</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>2</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>3</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>상처 관찰함</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>3</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>4</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>4</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>5</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>6</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>외상-두부</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>7</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>1</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>늑골 골절 있음/늑골 골절 없음</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>🩺 늑골 골절이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>2</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>다발성 늑골 골절 있음</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>🩺 여러 대가 부러졌는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>3</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>호흡곤란 있음/없음</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>"숨쉬기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>4</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>흉부 통증 있음/흉부 통증 없음</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>"가슴이 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>1</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>1</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>호흡곤란이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>2</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>산소포화도 monitor 함</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>2</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>3</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>상처 관찰함</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>3</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>4</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>5</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>외상-흉부</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>6</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>1</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>복부 압통 있음/복부 압통 없음</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>🩺 배를 눌렀을 때 아파하는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>2</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>🩺 출혈이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D725" t="n">
+        <v>3</v>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>"메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D726" t="n">
+        <v>4</v>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>복부 통증 있음/복부 통증 없음</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>"배가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D727" t="n">
+        <v>1</v>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D728" t="n">
+        <v>1</v>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D729" t="n">
+        <v>2</v>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>상처 관찰함</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D730" t="n">
+        <v>2</v>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D731" t="n">
+        <v>3</v>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D732" t="n">
+        <v>4</v>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>외상-복부</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D733" t="n">
+        <v>5</v>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D734" t="n">
+        <v>1</v>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>경부 강직 있음/경부 강직 없음</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>"목이 뻣뻣하거나 움직이기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D735" t="n">
+        <v>2</v>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>경부 swelling 있음/경부 swelling 없음</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>🩺 목이 부었는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D736" t="n">
+        <v>3</v>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>감각이상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>"팔다리가 저리거나 감각이 이상하세요?"</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D737" t="n">
+        <v>4</v>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>grasp power 강함/약함</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>"제 손을 양손으로 꽉 쥐어보시겠어요?"</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D738" t="n">
+        <v>1</v>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D739" t="n">
+        <v>1</v>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D740" t="n">
+        <v>2</v>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D741" t="n">
+        <v>2</v>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>sensory motor circulation 확인함</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>말초신경혈관기능장애위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D742" t="n">
+        <v>3</v>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D743" t="n">
+        <v>3</v>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D744" t="n">
+        <v>4</v>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>외상-목/척추</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D745" t="n">
+        <v>5</v>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D746" t="n">
+        <v>1</v>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>안면부종 있음</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>🩺 얼굴이 부었는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>2</v>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>"얼굴에서 피가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>3</v>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>찰과상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>🩺 긁힌 상처를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>1</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>1</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>상처 관찰함</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>2</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>상처 dressing 함</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>조직손상</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>2</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>3</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>3</v>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>4</v>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>5</v>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>외상-안면</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>6</v>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>1</v>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>신체손상 있음</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>🩺 여러 곳을 다쳤는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>2</v>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>골절 있음</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>🩺 골절이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>3</v>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>🩺 출혈이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>4</v>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>찰과상 있음/없음</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>🩺 긁힌 상처를 확인하세요</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>1</v>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>1</v>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>상처 관찰함</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>2</v>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>안전간호를 제공함</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>2</v>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>3</v>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>출혈 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>4</v>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>출혈양상 확인함</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>3</v>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D769" t="n">
+        <v>5</v>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D770" t="n">
+        <v>6</v>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>외상</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>외상-다발성</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D771" t="n">
+        <v>7</v>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>외상 부위 구분 260802</t>
+        </is>
+      </c>
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>급성통증</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -20,7 +20,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.추천근거" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.후속사정" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.평가자동" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.외상부위" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.부위상세" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1423,611 +1423,1186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
           <t>순서</t>
         </is>
       </c>
-      <c r="B1" s="8" t="inlineStr">
-        <is>
-          <t>부위</t>
-        </is>
-      </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
           <t>아이콘</t>
         </is>
       </c>
-      <c r="D1" s="8" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>진단연결</t>
         </is>
       </c>
-      <c r="E1" s="8" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>과정</t>
         </is>
       </c>
-      <c r="F1" s="8" t="inlineStr">
+      <c r="G1" s="8" t="inlineStr">
         <is>
           <t>진술문(마스터원문)</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>질문문구(💬)</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>입력형식</t>
         </is>
       </c>
-      <c r="I1" s="8" t="inlineStr">
+      <c r="J1" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>머리</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>🧠</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>조직관류저하:뇌</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>오심, 구토 있음/오심, 구토 없음</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>"메스껍거나 토하셨어요?"</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>뇌손상 징후</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>머리</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>🧠</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>조직관류저하:뇌</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>P&amp;E</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>얼굴</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>😐</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>조직손상</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>안면부종 있음</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>🩺 얼굴이 부었는지 확인하세요</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>체크</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>2</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>얼굴</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>😐</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>조직손상</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>P&amp;E</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>상처 dressing 함</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>3</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>목·척추</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>🧣</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>경부 강직 있음/경부 강직 없음</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>"목이 뻣뻣하거나 움직이기 힘드세요?"</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>3</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>목·척추</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>🧣</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>감각이상 있음/없음</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>"팔다리가 저리거나 감각이 이상하세요?"</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>3</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>목·척추</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>🧣</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>P&amp;E</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>sensory motor circulation 확인함</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>4</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>가슴</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>🫀</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>비효율적호흡양상</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>늑골 골절 있음/늑골 골절 없음</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>🩺 늑골 골절이 있는지 확인하세요</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>4</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>가슴</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>🫀</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>비효율적호흡양상</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>호흡곤란 있음/없음</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>"숨쉬기 힘드세요?"</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>4</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>가슴</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>🫀</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>비효율적호흡양상</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>P&amp;E</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>4</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>가슴</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>🫀</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>비효율적호흡양상</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>P&amp;E</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>산소포화도 monitor 함</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>5</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>배</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>🫃</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>출혈</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>복부 압통 있음/복부 압통 없음</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>🩺 배를 눌렀을 때 아파하는지 확인하세요</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>6</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>팔·다리</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>🦴</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>골절 있음</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>🩺 골절이 있는지 확인하세요</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>체크</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>6</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>팔·다리</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>🦴</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>A&amp;E</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>골절부위 tingling sense 있음/없음</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>"저릿하거나 감각이 이상하세요?"</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>토글</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>외상부위</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>6</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>팔·다리</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>🦴</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>P&amp;E</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>sensory motor circulation 확인함</t>
         </is>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>물림</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>🐕</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>🩺 물린 상처를 확인하세요</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>동물·사람</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>물림</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>🐕</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>감염 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>쏘임</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>🐝</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>redness 있음/redness 없음</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>🩺 쏘인 부위가 붉은지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>벌·곤충</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>쏘임</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>🐝</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>쏘인부위 침 제거함</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>열상</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>🔪</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>🩺 찢어진 상처를 확인하세요</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>열상</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>🔪</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>상처 dressing 함</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>발진</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>redness 있음/redness 없음</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>🩺 발진이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>봉와직염 의심</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>🟥</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>edema 있음/edema 없음</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>🩺 부어 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>봉와직염 의심</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>🟥</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>열감 있음/열감 없음</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>🩺 만졌을 때 뜨거운지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>멍 (외상 없이)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>🟣</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ecchymosis 있음/ecchymosis 없음</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>🩺 멍이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>출혈경향 의심</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>이물질</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>📌</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>이물질 관찰됨</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>🩺 박힌 것이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4476,7 +5051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L698"/>
+  <dimension ref="A1:L707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -23539,6 +24114,11 @@
           <t>피부손상위험</t>
         </is>
       </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
@@ -23584,6 +24164,11 @@
           <t>피부손상</t>
         </is>
       </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
@@ -23629,6 +24214,11 @@
           <t>피부손상</t>
         </is>
       </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -31429,6 +32019,372 @@
           <t>급성통증</t>
         </is>
       </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D699" t="n">
+        <v>4</v>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>🩺 피부가 상했는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D700" t="n">
+        <v>5</v>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>"피가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D701" t="n">
+        <v>6</v>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>"그 부위가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D702" t="n">
+        <v>3</v>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D703" t="n">
+        <v>4</v>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>피부 상태를 관찰함</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D704" t="n">
+        <v>4</v>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D705" t="n">
+        <v>5</v>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>통증을 인정해줌</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>6</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>통증 양상을 확인함</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>피부</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>7</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>통증을 관찰하기로 함</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>피부 확장 260802</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="8">

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1423,7 +1423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2194,9 +2194,6 @@
           <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2282,9 +2279,6 @@
           <t>쏘인부위 침 제거함</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2330,7 +2324,6 @@
           <t>체크</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2366,9 +2359,6 @@
           <t>상처 dressing 함</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2414,7 +2404,6 @@
           <t>토글</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2460,7 +2449,6 @@
           <t>토글</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2506,7 +2494,6 @@
           <t>토글</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2602,7 +2589,800 @@
           <t>체크</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>열사병</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>🥵</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>체온 상승함</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>🩺 체온을 측정하세요</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>더운 환경 노출</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>열사병</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>🥵</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>미온수 목욕 시행함</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>열사병</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>🥵</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>고체온</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>덥거나 추운 환경에 노출되지 않도록 함</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>햇볕 노출</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>☀️</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>햇볕에 노출된 부위가 빨갛게 됨</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>🩺 햇볕에 탄 부위를 확인하세요</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>일사병·일광화상</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>동상</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>🧊</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>🩺 언 부위를 확인하세요</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>동상</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>🧊</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>동상입지 않도록 교육함</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>익수</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>🌊</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>호흡곤란 있음/호흡곤란 없음</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>"숨쉬기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>물에 빠짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>익수</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>🌊</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>호흡곤란이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>익수</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>🌊</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>산소포화도 monitor 함</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>추운 환경 노출</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>🥶</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>저체온</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>덥거나 추운 환경에 노출되지 않도록 함</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>8</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>화학물질 노출</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>🩺 닿은 부위를 확인하세요</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>화학물질 노출</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>상처 관찰함</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>9</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>전기 손상</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>🩺 전류가 드나든 자리를 확인하세요</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>입구·출구 상처</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>9</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>전기 손상</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>상처 dressing 함</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>유해물질 흡입</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>호흡곤란 있음/호흡곤란 없음</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>"숨쉬기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>유해물질 흡입</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>호흡곤란이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>유해물질 흡입</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>💨</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>비효율적호흡양상</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>산소포화도 monitor 함</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>먹음(음독)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>💊</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>피부 접촉</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>✋</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>🩺 닿은 부위를 확인하세요</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14749,6 +15529,11 @@
           <t>공통</t>
         </is>
       </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14789,6 +15574,11 @@
           <t>공통</t>
         </is>
       </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14829,6 +15619,11 @@
           <t>고체온</t>
         </is>
       </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14869,6 +15664,11 @@
           <t>고체온</t>
         </is>
       </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14909,6 +15709,11 @@
           <t>급성통증</t>
         </is>
       </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14949,6 +15754,11 @@
           <t>고체온</t>
         </is>
       </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15224,6 +16034,11 @@
           <t>공통</t>
         </is>
       </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15264,6 +16079,11 @@
           <t>공통</t>
         </is>
       </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15304,6 +16124,11 @@
           <t>고체온</t>
         </is>
       </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15344,6 +16169,11 @@
           <t>고체온</t>
         </is>
       </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15384,6 +16214,11 @@
           <t>고체온</t>
         </is>
       </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15429,6 +16264,11 @@
           <t>급성통증</t>
         </is>
       </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>온열노출</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15694,6 +16534,11 @@
           <t>저체온</t>
         </is>
       </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15739,6 +16584,11 @@
           <t>저체온</t>
         </is>
       </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15784,6 +16634,11 @@
           <t>저체온</t>
         </is>
       </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15829,6 +16684,11 @@
           <t>저체온</t>
         </is>
       </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15874,6 +16734,11 @@
           <t>저체온</t>
         </is>
       </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -15919,6 +16784,11 @@
           <t>저체온</t>
         </is>
       </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>한랭노출</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -23134,6 +24004,11 @@
           <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -23174,6 +24049,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -23214,6 +24094,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -23254,6 +24139,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -23294,6 +24184,11 @@
           <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -23334,6 +24229,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -23374,6 +24274,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
@@ -23414,6 +24319,11 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>노출경로</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
@@ -32204,7 +33114,6 @@
           <t>감염위험</t>
         </is>
       </c>
-      <c r="L702" t="inlineStr"/>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
@@ -32240,7 +33149,6 @@
           <t>감염위험</t>
         </is>
       </c>
-      <c r="L703" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
@@ -32276,7 +33184,6 @@
           <t>급성통증</t>
         </is>
       </c>
-      <c r="L704" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
@@ -32312,7 +33219,6 @@
           <t>급성통증</t>
         </is>
       </c>
-      <c r="L705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
@@ -32348,7 +33254,6 @@
           <t>급성통증</t>
         </is>
       </c>
-      <c r="L706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
@@ -32384,7 +33289,6 @@
           <t>급성통증</t>
         </is>
       </c>
-      <c r="L707" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="8">

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -737,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -825,6 +825,42 @@
       <c r="B7" t="inlineStr">
         <is>
           <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>보챔</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>보채는 아기는 통증을 의심한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>울고 보챔</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>잠 안자고 울고 보챔</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>〃 — 가장 강한 단계</t>
         </is>
       </c>
     </row>
@@ -2674,9 +2710,6 @@
           <t>미온수 목욕 시행함</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2712,9 +2745,6 @@
           <t>덥거나 추운 환경에 노출되지 않도록 함</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2810,7 +2840,6 @@
           <t>체크</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2846,9 +2875,6 @@
           <t>동상입지 않도록 교육함</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2934,9 +2960,6 @@
           <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2972,9 +2995,6 @@
           <t>산소포화도 monitor 함</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3010,9 +3030,6 @@
           <t>덥거나 추운 환경에 노출되지 않도록 함</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3058,7 +3075,6 @@
           <t>체크</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3094,9 +3110,6 @@
           <t>상처 관찰함</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3182,9 +3195,6 @@
           <t>상처 dressing 함</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3230,7 +3240,6 @@
           <t>토글</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3266,9 +3275,6 @@
           <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3304,9 +3310,6 @@
           <t>산소포화도 monitor 함</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3332,11 +3335,6 @@
           <t>중독위험</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3382,7 +3380,6 @@
           <t>체크</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5831,7 +5828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L707"/>
+  <dimension ref="A1:L705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -21701,22 +21698,22 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>보챔/보채지 않음</t>
+          <t>보채지 않음/보챔/울고 보챔/잠 안자고 울고 보챔</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>🩺 보채는지 관찰하세요</t>
+          <t>🩺 보채는 정도를 고르세요</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>정도 3단계를 한 문항으로 260802</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
@@ -21746,12 +21743,12 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>울고 보챔</t>
+          <t>자주 사지 움직이며 보챔</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>"평소보다 심하게 보채거나 우나요?"</t>
+          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
@@ -21791,22 +21788,22 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>잠 안자고 울고 보챔</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>"잠을 못 자고 계속 우나요?"</t>
+          <t>"아파하나요?"</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>부위는 📌비고에 기재</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
@@ -21836,17 +21833,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>자주 사지 움직이며 보챔</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>🩺 팔다리를 자주 움직이며 보채는지 관찰하세요</t>
+          <t>"축 처져 있거나 반응이 느린가요?"</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -21881,22 +21878,22 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>"아파하나요?"</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>부위는 📌비고에 기재</t>
+          <t>⚠️ 초안</t>
         </is>
       </c>
       <c r="J416" t="inlineStr">
@@ -21918,25 +21915,15 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
-        </is>
-      </c>
-      <c r="F417" t="inlineStr">
-        <is>
-          <t>"축 처져 있거나 반응이 느린가요?"</t>
-        </is>
-      </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -21963,25 +21950,15 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D418" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
-        </is>
-      </c>
-      <c r="F418" t="inlineStr">
-        <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G418" t="inlineStr">
-        <is>
-          <t>선택</t>
+          <t>통증 강도 측정함</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -22008,15 +21985,15 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -22047,11 +22024,11 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>통증 강도 측정함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -22068,70 +22045,90 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>소아-보챔처짐</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D422" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>설사 있음/설사 없음</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>"설사하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>⚠️ 초안</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -22152,21 +22149,21 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>오심, 구토 있음/오심, 구토 없음</t>
+          <t>탈수 증상 있음</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
+          <t>🩺 탈수 증상(입마름·소변감소)</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -22197,16 +22194,16 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>설사 있음/설사 없음</t>
+          <t>변비 있음/변비 없음</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>"설사하셨어요?"</t>
+          <t>"변을 못 보거나 불편하세요?"</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
@@ -22221,7 +22218,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>변비</t>
         </is>
       </c>
     </row>
@@ -22238,25 +22235,15 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D425" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>탈수 증상 있음</t>
-        </is>
-      </c>
-      <c r="F425" t="inlineStr">
-        <is>
-          <t>🩺 탈수 증상(입마름·소변감소)</t>
-        </is>
-      </c>
-      <c r="G425" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>체액부족위험</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -22283,25 +22270,15 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D426" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>변비 있음/변비 없음</t>
-        </is>
-      </c>
-      <c r="F426" t="inlineStr">
-        <is>
-          <t>"변을 못 보거나 불편하세요?"</t>
-        </is>
-      </c>
-      <c r="G426" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>탈수 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -22311,7 +22288,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>변비</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
@@ -22328,20 +22305,20 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>금식 하도록 교육함</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>⚠️ 마스터 없음 — 시간 붙은 것만 존재(2시간/6시간…). 칩스 확인</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
@@ -22363,15 +22340,15 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>탈수 증상이 있는지 확인함</t>
+          <t>변비</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -22381,7 +22358,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>변비</t>
         </is>
       </c>
     </row>
@@ -22402,21 +22379,21 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>금식 하도록 교육함</t>
+          <t>변비 유발 식품을 피하도록 교육함</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>⚠️ 마스터 없음 — 시간 붙은 것만 존재(2시간/6시간…). 칩스 확인</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>변비</t>
         </is>
       </c>
     </row>
@@ -22433,15 +22410,15 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>변비</t>
+          <t>대변 양상 확인함</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -22458,70 +22435,80 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D431" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>변비 유발 식품을 피하도록 교육함</t>
+          <t>배뇨곤란 있음/배뇨곤란 없음</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>"소변보기 힘드세요?"</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J431" t="inlineStr">
-        <is>
-          <t>변비</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D432" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>대변 양상 확인함</t>
+          <t>요정체 있음/요정체 없음</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>"소변이 막힌 느낌이세요?"</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J432" t="inlineStr">
-        <is>
-          <t>변비</t>
         </is>
       </c>
     </row>
@@ -22542,16 +22529,16 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>배뇨곤란 있음/배뇨곤란 없음</t>
+          <t>잔뇨감 있음/잔뇨감 없음</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>"소변보기 힘드세요?"</t>
+          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -22582,16 +22569,16 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>요정체 있음/요정체 없음</t>
+          <t>혈뇨 있음/혈뇨 없음</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>"소변이 막힌 느낌이세요?"</t>
+          <t>"소변에 피가 보이나요?"</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
@@ -22622,21 +22609,21 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>잔뇨감 있음/잔뇨감 없음</t>
+          <t>소변량 감소함</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>"다 본 뒤에도 남은 느낌(잔뇨)?"</t>
+          <t>🩺 소변량 감소</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -22658,30 +22645,25 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D436" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>혈뇨 있음/혈뇨 없음</t>
-        </is>
-      </c>
-      <c r="F436" t="inlineStr">
-        <is>
-          <t>"소변에 피가 보이나요?"</t>
-        </is>
-      </c>
-      <c r="G436" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>배뇨장애</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
         </is>
       </c>
     </row>
@@ -22698,30 +22680,25 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D437" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>소변량 감소함</t>
-        </is>
-      </c>
-      <c r="F437" t="inlineStr">
-        <is>
-          <t>🩺 소변량 감소</t>
-        </is>
-      </c>
-      <c r="G437" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>요정체가 있는지 확인함</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
         </is>
       </c>
     </row>
@@ -22738,15 +22715,15 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>배뇨장애</t>
+          <t>단순도뇨 시행함</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -22777,11 +22754,11 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>요정체가 있는지 확인함</t>
+          <t>혈뇨가 있는지 확인함</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -22798,70 +22775,80 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D440" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>단순도뇨 시행함</t>
+          <t>귀분비물 있음/귀분비물 없음</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>"귀에서 분비물이 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>배뇨장애</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D441" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>혈뇨가 있는지 확인함</t>
+          <t>이명 있음/이명 없음</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>"귀울림(이명)이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>배뇨장애</t>
         </is>
       </c>
     </row>
@@ -22882,21 +22869,21 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>귀분비물 있음/귀분비물 없음</t>
+          <t>청력 이상 있음</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>"귀에서 분비물이 나오세요?"</t>
+          <t>"잘 안 들리세요?"</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -22922,16 +22909,16 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>이명 있음/이명 없음</t>
+          <t>코막힘 있음/코막힘 없음</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>"귀울림(이명)이 있으세요?"</t>
+          <t>"코가 막히세요?"</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
@@ -22962,21 +22949,21 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>청력 이상 있음</t>
+          <t>콧물 있음/콧물 없음</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>"잘 안 들리세요?"</t>
+          <t>"콧물이 나세요?"</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -23002,16 +22989,16 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>코막힘 있음/코막힘 없음</t>
+          <t>연하곤란 있음/연하곤란 없음</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>"코가 막히세요?"</t>
+          <t>"삼키기 힘드세요?"</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
@@ -23038,30 +23025,25 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D446" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>콧물 있음/콧물 없음</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>"콧물이 나세요?"</t>
-        </is>
-      </c>
-      <c r="G446" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -23078,30 +23060,25 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D447" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>연하곤란 있음/연하곤란 없음</t>
-        </is>
-      </c>
-      <c r="F447" t="inlineStr">
-        <is>
-          <t>"삼키기 힘드세요?"</t>
-        </is>
-      </c>
-      <c r="G447" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -23118,15 +23095,15 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>청력장애가 있는지 사정함</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -23157,11 +23134,11 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -23178,25 +23155,35 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D450" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>청력장애가 있는지 사정함</t>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -23206,32 +23193,42 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D451" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 음식을 섭취하도록 교육함</t>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -23241,7 +23238,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -23262,21 +23259,21 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>오심, 구토 있음/오심, 구토 없음</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -23286,7 +23283,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -23307,31 +23304,31 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>dizziness 있음/dizziness 없음</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -23352,21 +23349,21 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>감각이상 있음/감각이상 없음</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -23397,26 +23394,26 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+          <t>grasp power 약함/grasp power 강함</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
@@ -23442,16 +23439,16 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>감각이상 있음/감각이상 없음</t>
+          <t>vertigo 있음/vertigo 없음</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
@@ -23466,7 +23463,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -23487,16 +23484,16 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>grasp power 약함/grasp power 강함</t>
+          <t>syncope 있음/syncope 없음</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
@@ -23511,7 +23508,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -23532,16 +23529,16 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>vertigo 있음/vertigo 없음</t>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>"빙글빙글 도는 느낌이 있으세요?"</t>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
@@ -23556,7 +23553,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -23573,25 +23570,15 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D459" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>syncope 있음/syncope 없음</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>"잠깐 정신을 잃으신 적 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G459" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -23618,25 +23605,15 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D460" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음/obey command 가능함</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G460" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -23646,7 +23623,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -23663,15 +23640,15 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>손상을 예방하는 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -23702,11 +23679,11 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -23733,7 +23710,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D463" t="n">
@@ -23741,7 +23718,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>손상을 예방하는 방법에 대해 교육함</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -23751,7 +23728,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -23772,11 +23749,11 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -23786,7 +23763,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -23803,15 +23780,15 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -23842,11 +23819,11 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>조직관류 증진 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -23877,11 +23854,11 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>혈당 검사 시행함</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -23898,60 +23875,80 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>조직관류 증진 방법에 대해 교육함</t>
+          <t>음독 함 ★</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="J468" t="inlineStr">
-        <is>
-          <t>조직관류저하:뇌</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>노출경로</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>혈당 검사 시행함</t>
+          <t>오심, 구토 있음/오심, 구토 없음</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>"속이 메스껍거나 토하셨어요?"</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -23959,9 +23956,9 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="J469" t="inlineStr">
-        <is>
-          <t>조직관류저하:뇌</t>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>노출경로</t>
         </is>
       </c>
     </row>
@@ -23982,26 +23979,26 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>음독 함 ★</t>
+          <t>dizziness 있음/dizziness 없음</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>"약물·다른 것을 삼키셨어요? (무엇을 드셨는지 비고에 기재)"</t>
+          <t>"어지러우세요?"</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="L470" t="inlineStr">
@@ -24027,21 +24024,21 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>오심, 구토 있음/오심, 구토 없음</t>
+          <t>동공크기 :</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>"속이 메스껍거나 토하셨어요?"</t>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -24072,26 +24069,26 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>dizziness 있음/dizziness 없음</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -24117,21 +24114,21 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>감각이상 있음/감각이상 없음</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -24162,26 +24159,26 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+          <t>grasp power 약함/grasp power 강함</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -24207,16 +24204,16 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>감각이상 있음/감각이상 없음</t>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
@@ -24248,25 +24245,15 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>grasp power 약함/grasp power 강함</t>
-        </is>
-      </c>
-      <c r="F476" t="inlineStr">
-        <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
-        </is>
-      </c>
-      <c r="G476" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>중독위험</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -24274,9 +24261,9 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t>노출경로</t>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
@@ -24293,25 +24280,15 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음/obey command 가능함</t>
-        </is>
-      </c>
-      <c r="F477" t="inlineStr">
-        <is>
-          <t>"제가 말씀드리는 대로 따라 해보실 수 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G477" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>위세척에 대해 설명함</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -24319,9 +24296,9 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t>노출경로</t>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
@@ -24338,15 +24315,15 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>처방에 의해 해독제를 투여함</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -24377,11 +24354,11 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>위세척에 대해 설명함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
@@ -24412,11 +24389,11 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>처방에 의해 해독제를 투여함</t>
+          <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -24433,25 +24410,35 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>시력감퇴 있음/시력감퇴 없음</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>"예전보다 잘 안 보이세요?"</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -24461,32 +24448,42 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D482" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>신경학적 증상이 있는지 확인함</t>
+          <t>시야결손 있음/시야결손 없음</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>"시야 일부가 가려지세요?"</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -24496,7 +24493,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
@@ -24517,16 +24514,16 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>시력감퇴 있음/시력감퇴 없음</t>
+          <t>복시 있음/복시 없음</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>"예전보다 잘 안 보이세요?"</t>
+          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -24562,16 +24559,16 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>시야결손 있음/시야결손 없음</t>
+          <t>결막충혈 있음/결막충혈 없음</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>"시야 일부가 가려지세요?"</t>
+          <t>"눈이 충혈되었나요?"</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -24586,7 +24583,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
@@ -24607,21 +24604,21 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>복시 있음/복시 없음</t>
+          <t>이물질 관찰됨</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>"사물이 두 개로 겹쳐 보이세요?"</t>
+          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -24631,7 +24628,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
@@ -24652,16 +24649,16 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>결막충혈 있음/결막충혈 없음</t>
+          <t>결막출혈 있음/결막출혈 없음</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>"눈이 충혈되었나요?"</t>
+          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -24693,35 +24690,25 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D487" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>이물질 관찰됨</t>
-        </is>
-      </c>
-      <c r="F487" t="inlineStr">
-        <is>
-          <t>"눈에 뭐가 들어간 느낌이세요?"</t>
-        </is>
-      </c>
-      <c r="G487" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터는 통합형(시각,청각,촉각…)</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
@@ -24738,25 +24725,15 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D488" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>결막출혈 있음/결막출혈 없음</t>
-        </is>
-      </c>
-      <c r="F488" t="inlineStr">
-        <is>
-          <t>"눈에 출혈(붉은 것)이 있나요?"</t>
-        </is>
-      </c>
-      <c r="G488" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -24766,7 +24743,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>감각지각장애 : 시각</t>
         </is>
       </c>
     </row>
@@ -24783,20 +24760,20 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>안대 적용함</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터는 통합형(시각,청각,촉각…)</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
@@ -24818,15 +24795,15 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D490" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>안위변화</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -24836,7 +24813,7 @@
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
@@ -24857,11 +24834,11 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>안대 적용함</t>
+          <t>이물질 제거함</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -24871,7 +24848,7 @@
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>안위변화</t>
         </is>
       </c>
     </row>
@@ -24888,15 +24865,15 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D492" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>안연고 점안 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -24913,25 +24890,35 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D493" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>이물질 제거함</t>
+          <t>가려움증 있음/가려움증 없음</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>"피부가 가려우세요?"</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -24941,32 +24928,47 @@
       </c>
       <c r="J493" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>피부손상위험</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>피부상황</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D494" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>안연고 점안 방법에 대해 교육함</t>
+          <t>urticaria 있음/urticaria 없음</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -24976,7 +24978,12 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>안위변화</t>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>피부상황</t>
         </is>
       </c>
     </row>
@@ -24997,16 +25004,16 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>가려움증 있음/가려움증 없음</t>
+          <t>bullae 있음/bullae 없음</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>"피부가 가려우세요?"</t>
+          <t>"물집이 잡혔나요?"</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -25021,7 +25028,7 @@
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="L495" t="inlineStr">
@@ -25043,25 +25050,15 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D496" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>urticaria 있음/urticaria 없음</t>
-        </is>
-      </c>
-      <c r="F496" t="inlineStr">
-        <is>
-          <t>"두드러기가 올라왔나요?"</t>
-        </is>
-      </c>
-      <c r="G496" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부손상위험</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -25071,12 +25068,7 @@
       </c>
       <c r="J496" t="inlineStr">
         <is>
-          <t>피부손상</t>
-        </is>
-      </c>
-      <c r="L496" t="inlineStr">
-        <is>
-          <t>피부상황</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -25093,25 +25085,15 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D497" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>bullae 있음/bullae 없음</t>
-        </is>
-      </c>
-      <c r="F497" t="inlineStr">
-        <is>
-          <t>"물집이 잡혔나요?"</t>
-        </is>
-      </c>
-      <c r="G497" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>긁지 않도록 교육함</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -25121,12 +25103,7 @@
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>피부손상</t>
-        </is>
-      </c>
-      <c r="L497" t="inlineStr">
-        <is>
-          <t>피부상황</t>
+          <t>피부손상위험</t>
         </is>
       </c>
     </row>
@@ -25143,15 +25120,15 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>소양증 감소 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -25178,15 +25155,15 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>긁지 않도록 교육함</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -25196,7 +25173,7 @@
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
@@ -25217,11 +25194,11 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>소양증 감소 방법에 대해 교육함</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -25231,32 +25208,42 @@
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>피부손상위험</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>dizziness 있음/dizziness 없음</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>"어지러우세요?"</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -25266,32 +25253,42 @@
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D502" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>동공크기 :</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -25301,7 +25298,7 @@
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -25322,26 +25319,26 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>dizziness 있음/dizziness 없음</t>
+          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>"어지러우세요?"</t>
+          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
       <c r="J503" t="inlineStr">
@@ -25367,21 +25364,21 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>동공크기 :</t>
+          <t>감각이상 있음/감각이상 없음</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>🩺 동공 크기를 확인하세요 — 실물 동공자로 재세요</t>
+          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -25412,26 +25409,26 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>빛 반사 확인결과 prompt 함 ★/빛 반사 확인결과 sluggish 함 ★/빛 반사 확인결과 hippus 함 ★</t>
+          <t>grasp power 약함/grasp power 강함</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>🩺 펜라이트를 비춰 동공 반응을 확인하세요 (prompt 즉시 · sluggish 느림 · hippus 떨림)</t>
+          <t>"손에 힘이 빠지거나 약하세요?"</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터 없음</t>
+          <t>⚠️ V4 이관</t>
         </is>
       </c>
       <c r="J505" t="inlineStr">
@@ -25457,16 +25454,16 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>감각이상 있음/감각이상 없음</t>
+          <t>obey command 가능하지 않음/obey command 가능함</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>"한쪽이 저리거나 감각이 둔하세요?"</t>
+          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -25502,16 +25499,16 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>grasp power 약함/grasp power 강함</t>
+          <t>사람에 대한 지남력 없음/사람에 대한 지남력 있음</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>"손에 힘이 빠지거나 약하세요?"</t>
+          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -25547,16 +25544,16 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>obey command 가능하지 않음/obey command 가능함</t>
+          <t>섬망 있음/섬망 없음</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>"제가 말씀드리는 대로 한번 따라 해보실 수 있으세요?"</t>
+          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -25571,7 +25568,7 @@
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -25592,16 +25589,16 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>사람에 대한 지남력 없음/사람에 대한 지남력 있음</t>
+          <t>환각 있음/환각 없음</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>"여기가 어디인지, 옆에 누가 계신지 아시겠어요?"</t>
+          <t>"없는 것이 보이거나 들리세요?"</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -25616,7 +25613,7 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -25637,16 +25634,16 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>섬망 있음/섬망 없음</t>
+          <t>flapping tremor 있음/flapping tremor 없음</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>"평소와 달리 헛것을 보거나 혼란스러워 보이세요?"</t>
+          <t>🩺 양손을 앞으로 뻗고 손목을 젖히게 해보세요 — 파닥이듯 떨리나요?</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -25678,25 +25675,15 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D511" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>환각 있음/환각 없음</t>
-        </is>
-      </c>
-      <c r="F511" t="inlineStr">
-        <is>
-          <t>"없는 것이 보이거나 들리세요?"</t>
-        </is>
-      </c>
-      <c r="G511" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -25706,7 +25693,7 @@
       </c>
       <c r="J511" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -25723,25 +25710,15 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D512" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>flapping tremor 있음/flapping tremor 없음</t>
-        </is>
-      </c>
-      <c r="F512" t="inlineStr">
-        <is>
-          <t>🩺 양손을 앞으로 뻗고 손목을 젖히게 해보세요 — 파닥이듯 떨리나요?</t>
-        </is>
-      </c>
-      <c r="G512" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -25751,7 +25728,7 @@
       </c>
       <c r="J512" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
@@ -25768,15 +25745,15 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D513" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -25803,15 +25780,15 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D514" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>사람, 시간, 장소에 대한 지남력을 줌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -25821,7 +25798,7 @@
       </c>
       <c r="J514" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -25842,11 +25819,11 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>알코올 섭취 양상을 확인함</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -25856,7 +25833,7 @@
       </c>
       <c r="J515" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>알코올금단증</t>
         </is>
       </c>
     </row>
@@ -25873,15 +25850,15 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D516" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>금단 증상을 설명함</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -25912,11 +25889,11 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>알코올 섭취 양상을 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -25933,25 +25910,35 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D518" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>금단 증상을 설명함</t>
+          <t>구체적 자살계획을 언급함/자해나 자살시도를 부인함</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -25961,32 +25948,42 @@
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>정신과</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D519" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>자살을 시도함</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -25996,7 +25993,7 @@
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>알코올금단증</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
@@ -26017,21 +26014,21 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>구체적 자살계획을 언급함/자해나 자살시도를 부인함</t>
+          <t>자살 충동 있음</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>"죽고 싶은 생각이나 계획이 있으세요?"</t>
+          <t>자살 충동 (구체적 사항 비고에 기재)</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -26062,21 +26059,21 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>자살을 시도함</t>
+          <t>공격적 행동함/타인에 대한 공격적 행동을 보이지 않음</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>자살 시도 (구체적 사항 비고에 기재)</t>
+          <t>🩺 공격적 행동(관찰)</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -26086,7 +26083,7 @@
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
@@ -26107,21 +26104,21 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>자살 충동 있음</t>
+          <t>공황상태 있음/공황상태 없음</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>자살 충동 (구체적 사항 비고에 기재)</t>
+          <t>"심하게 불안하거나 공황 상태이세요?"</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -26131,7 +26128,7 @@
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
@@ -26148,25 +26145,15 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D523" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>공격적 행동함/타인에 대한 공격적 행동을 보이지 않음</t>
-        </is>
-      </c>
-      <c r="F523" t="inlineStr">
-        <is>
-          <t>🩺 공격적 행동(관찰)</t>
-        </is>
-      </c>
-      <c r="G523" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>자살위험</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -26176,7 +26163,7 @@
       </c>
       <c r="J523" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
@@ -26193,25 +26180,15 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D524" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>공황상태 있음/공황상태 없음</t>
-        </is>
-      </c>
-      <c r="F524" t="inlineStr">
-        <is>
-          <t>"심하게 불안하거나 공황 상태이세요?"</t>
-        </is>
-      </c>
-      <c r="G524" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -26221,7 +26198,7 @@
       </c>
       <c r="J524" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>자살위험</t>
         </is>
       </c>
     </row>
@@ -26238,15 +26215,15 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D525" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -26273,15 +26250,15 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -26291,7 +26268,7 @@
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
@@ -26312,11 +26289,11 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>자살 시도에 대해 자주 사정하고 응급 처치 준비해 둠</t>
+          <t>진정시킴</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -26326,7 +26303,7 @@
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>자살위험</t>
+          <t>폭력위험:타인</t>
         </is>
       </c>
     </row>
@@ -26343,15 +26320,15 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D528" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>억제대 적용 중임</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -26378,7 +26355,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D529" t="n">
@@ -26386,7 +26363,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>진정시킴</t>
+          <t>불안</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -26396,7 +26373,7 @@
       </c>
       <c r="J529" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
@@ -26417,11 +26394,11 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>억제대 적용 중임</t>
+          <t>불안을 감소시켜 줌</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -26431,7 +26408,7 @@
       </c>
       <c r="J530" t="inlineStr">
         <is>
-          <t>폭력위험:타인</t>
+          <t>불안</t>
         </is>
       </c>
     </row>
@@ -26448,15 +26425,15 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D531" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>경청해줌</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -26473,25 +26450,35 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D532" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>불안을 감소시켜 줌</t>
+          <t>혈압(mmHg) :</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>값입력</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -26501,32 +26488,42 @@
       </c>
       <c r="J532" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>정신과</t>
+          <t>혈압</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D533" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>경청해줌</t>
+          <t>혈압 상승됨</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>🩺 혈압 상승됨 (고혈압)</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -26536,7 +26533,7 @@
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>불안</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
@@ -26557,21 +26554,21 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>혈압(mmHg) :</t>
+          <t>혈압 저하됨</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>🩺 혈압 측정 (수축기 / 이완기 · mmHg)</t>
+          <t>🩺 혈압 저하됨 (저혈압)</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>값입력</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -26581,7 +26578,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -26602,21 +26599,21 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>혈압 상승됨</t>
+          <t>고혈압으로 인한 증상 있음/고혈압으로 인한 증상 없음</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>🩺 혈압 상승됨 (고혈압)</t>
+          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -26647,16 +26644,16 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>혈압 저하됨</t>
+          <t>체위성 저혈압 있음</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>🩺 혈압 저하됨 (저혈압)</t>
+          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -26688,25 +26685,15 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D537" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>고혈압으로 인한 증상 있음/고혈압으로 인한 증상 없음</t>
-        </is>
-      </c>
-      <c r="F537" t="inlineStr">
-        <is>
-          <t>"두통·어지럼 등 불편한 증상 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G537" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>고혈압</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -26733,25 +26720,15 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D538" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>체위성 저혈압 있음</t>
-        </is>
-      </c>
-      <c r="F538" t="inlineStr">
-        <is>
-          <t>"일어설 때 핑 돌거나 어지러우세요?"</t>
-        </is>
-      </c>
-      <c r="G538" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -26761,7 +26738,7 @@
       </c>
       <c r="J538" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>고혈압</t>
         </is>
       </c>
     </row>
@@ -26778,15 +26755,15 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D539" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>Non Invasive BP monitor 시작함</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -26817,11 +26794,11 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
+          <t>혈압관리 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -26848,7 +26825,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D541" t="n">
@@ -26856,7 +26833,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Non Invasive BP monitor 시작함</t>
+          <t>저혈압</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -26866,7 +26843,7 @@
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -26887,11 +26864,11 @@
         </is>
       </c>
       <c r="D542" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>혈압관리 방법에 대해 교육함</t>
+          <t>혈압 측정함</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -26901,7 +26878,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>고혈압</t>
+          <t>저혈압</t>
         </is>
       </c>
     </row>
@@ -26918,15 +26895,15 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D543" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>체위성 저혈압 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -26957,11 +26934,11 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>혈압 측정함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -26978,70 +26955,90 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>혈압</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>혈압</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D545" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>체위성 저혈압 증상이 있는지 확인함</t>
+          <t>인후 불편감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>"목이 아프거나 불편하세요?"</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>커버리지 보완 260802</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>혈압</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>혈압</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D546" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>인후 충혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>🩺 목 안이 붉은지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>커버리지 보완 260802</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -27058,25 +27055,15 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D547" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>인후 불편감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F547" t="inlineStr">
-        <is>
-          <t>"목이 아프거나 불편하세요?"</t>
-        </is>
-      </c>
-      <c r="G547" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -27103,25 +27090,15 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D548" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>인후 충혈 있음/없음</t>
-        </is>
-      </c>
-      <c r="F548" t="inlineStr">
-        <is>
-          <t>🩺 목 안이 붉은지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G548" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -27148,15 +27125,15 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D549" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -27187,11 +27164,11 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -27222,11 +27199,11 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>인후 상태를 확인함</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -27243,25 +27220,35 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D552" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>안구통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>"눈이 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -27278,25 +27265,25 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>안과</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D553" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>인후 상태를 확인함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -27323,25 +27310,15 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D554" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>안구통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F554" t="inlineStr">
-        <is>
-          <t>"눈이 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G554" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -27368,15 +27345,15 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D555" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -27407,11 +27384,11 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -27428,17 +27405,17 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D557" t="n">
@@ -27446,7 +27423,17 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>옆구리 통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>"옆구리(허리 옆)가 아프세요?"</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -27463,25 +27450,25 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>안과</t>
+          <t>비뇨기</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D558" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -27508,25 +27495,15 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D559" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>옆구리 통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F559" t="inlineStr">
-        <is>
-          <t>"옆구리(허리 옆)가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G559" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -27553,15 +27530,15 @@
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D560" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -27592,11 +27569,11 @@
         </is>
       </c>
       <c r="D561" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -27613,25 +27590,35 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>전신 쇠약</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>전신 쇠약</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D562" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>전신 허약감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>"온몸에 기운이 없으세요?"</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -27641,32 +27628,42 @@
       </c>
       <c r="J562" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>활동의 지속성장애</t>
         </is>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>전신 쇠약</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>비뇨기</t>
+          <t>전신 쇠약</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D563" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>사지 허약감 있음/없음</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>"팔다리에 힘이 없으세요?"</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -27676,7 +27673,7 @@
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>활동의 지속성장애</t>
         </is>
       </c>
     </row>
@@ -27697,16 +27694,16 @@
         </is>
       </c>
       <c r="D564" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>전신 허약감 있음/없음</t>
+          <t>피로 호소함/피로하지 않다고 함</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>"온몸에 기운이 없으세요?"</t>
+          <t>"많이 피곤하세요?"</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -27742,16 +27739,16 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>사지 허약감 있음/없음</t>
+          <t>dizziness 있음/없음</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>"팔다리에 힘이 없으세요?"</t>
+          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -27766,7 +27763,7 @@
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>활동의 지속성장애</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -27783,25 +27780,15 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D566" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>피로 호소함/피로하지 않다고 함</t>
-        </is>
-      </c>
-      <c r="F566" t="inlineStr">
-        <is>
-          <t>"많이 피곤하세요?"</t>
-        </is>
-      </c>
-      <c r="G566" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>활동의 지속성장애</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -27828,25 +27815,15 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D567" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>dizziness 있음/없음</t>
-        </is>
-      </c>
-      <c r="F567" t="inlineStr">
-        <is>
-          <t>"어지럽거나 핑 도는 느낌이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G567" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피로 정도를 확인함</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -27856,7 +27833,7 @@
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>활동의 지속성장애</t>
         </is>
       </c>
     </row>
@@ -27873,15 +27850,15 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D568" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>활동의 지속성장애</t>
+          <t>24시간 피로 수준을 사정함</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -27912,11 +27889,11 @@
         </is>
       </c>
       <c r="D569" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>피로 정도를 확인함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -27933,25 +27910,35 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>전신 쇠약</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>전신 쇠약</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D570" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>24시간 피로 수준을 사정함</t>
+          <t>알레르기 있음/없음</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>"약이나 음식에 알레르기가 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -27961,32 +27948,42 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>활동의 지속성장애</t>
+          <t>알레르기반응</t>
         </is>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>전신 쇠약</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>전신 쇠약</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D571" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>urticaria 있음/없음</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>"두드러기가 올라왔나요?"</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -27996,7 +27993,7 @@
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>활동의 지속성장애</t>
+          <t>알레르기반응</t>
         </is>
       </c>
     </row>
@@ -28017,16 +28014,16 @@
         </is>
       </c>
       <c r="D572" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>알레르기 있음/없음</t>
+          <t>가려움증 있음/없음</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>"약이나 음식에 알레르기가 있으세요?"</t>
+          <t>"피부가 가려우세요?"</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -28062,16 +28059,16 @@
         </is>
       </c>
       <c r="D573" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>urticaria 있음/없음</t>
+          <t>호흡곤란 있음/없음</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>"두드러기가 올라왔나요?"</t>
+          <t>"숨이 차거나 답답하신가요?"</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -28086,7 +28083,7 @@
       </c>
       <c r="J573" t="inlineStr">
         <is>
-          <t>알레르기반응</t>
+          <t>기도개방유지불능</t>
         </is>
       </c>
     </row>
@@ -28107,16 +28104,16 @@
         </is>
       </c>
       <c r="D574" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>가려움증 있음/없음</t>
+          <t>wheezing 있음/없음</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>"피부가 가려우세요?"</t>
+          <t>🩺 쌕쌕거리는 숨소리를 청진하세요</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -28131,7 +28128,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>알레르기반응</t>
+          <t>기도개방유지불능</t>
         </is>
       </c>
     </row>
@@ -28152,16 +28149,16 @@
         </is>
       </c>
       <c r="D575" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>호흡곤란 있음/없음</t>
+          <t>연하곤란 있음/없음</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>"숨이 차거나 답답하신가요?"</t>
+          <t>"목이 붓거나 삼키기 힘드세요?"</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -28197,16 +28194,16 @@
         </is>
       </c>
       <c r="D576" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>wheezing 있음/없음</t>
+          <t>청색증 있음/없음</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>🩺 쌕쌕거리는 숨소리를 청진하세요</t>
+          <t>🩺 입술·얼굴이 파란지 확인하세요</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -28242,21 +28239,21 @@
         </is>
       </c>
       <c r="D577" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>연하곤란 있음/없음</t>
+          <t>혈압 저하됨</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>"목이 붓거나 삼키기 힘드세요?"</t>
+          <t>🩺 혈압이 떨어졌는지 확인하세요</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -28266,7 +28263,7 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>기도개방유지불능</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -28283,25 +28280,15 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D578" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>청색증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F578" t="inlineStr">
-        <is>
-          <t>🩺 입술·얼굴이 파란지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G578" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>알레르기반응</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -28311,7 +28298,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>기도개방유지불능</t>
+          <t>알레르기반응</t>
         </is>
       </c>
     </row>
@@ -28328,25 +28315,15 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D579" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>혈압 저하됨</t>
-        </is>
-      </c>
-      <c r="F579" t="inlineStr">
-        <is>
-          <t>🩺 혈압이 떨어졌는지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G579" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>알레르기원을 확인함</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -28356,7 +28333,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>알레르기반응</t>
         </is>
       </c>
     </row>
@@ -28373,15 +28350,15 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D580" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>알레르기반응</t>
+          <t>알레르기 과거력이 있는지 확인함</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -28412,11 +28389,11 @@
         </is>
       </c>
       <c r="D581" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>알레르기원을 확인함</t>
+          <t>전신 알레르기 반응이 있는지 확인함</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -28447,11 +28424,11 @@
         </is>
       </c>
       <c r="D582" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>알레르기 과거력이 있는지 확인함</t>
+          <t>알레르기원에 노출되지 않도록 교육함</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -28478,15 +28455,15 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D583" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>전신 알레르기 반응이 있는지 확인함</t>
+          <t>기도개방유지불능</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -28496,7 +28473,7 @@
       </c>
       <c r="J583" t="inlineStr">
         <is>
-          <t>알레르기반응</t>
+          <t>기도개방유지불능</t>
         </is>
       </c>
     </row>
@@ -28517,11 +28494,11 @@
         </is>
       </c>
       <c r="D584" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>알레르기원에 노출되지 않도록 교육함</t>
+          <t>산소 흡입 시작함</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -28531,7 +28508,7 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>알레르기반응</t>
+          <t>기도개방유지불능</t>
         </is>
       </c>
     </row>
@@ -28548,15 +28525,15 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D585" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>기도개방유지불능</t>
+          <t>IV 주입경로 확보하여 수액 주입함</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -28573,25 +28550,35 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>화상</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>화상</t>
         </is>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D586" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>산소 흡입 시작함</t>
+          <t>화상 입음</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>"화상을 입으셨나요?"</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -28601,32 +28588,42 @@
       </c>
       <c r="J586" t="inlineStr">
         <is>
-          <t>기도개방유지불능</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>화상</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>화상</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D587" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>IV 주입경로 확보하여 수액 주입함</t>
+          <t>bullae 있음/없음</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>🩺 물집이 잡혔는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -28636,7 +28633,7 @@
       </c>
       <c r="J587" t="inlineStr">
         <is>
-          <t>기도개방유지불능</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
@@ -28657,21 +28654,21 @@
         </is>
       </c>
       <c r="D588" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>화상 입음</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>"화상을 입으셨나요?"</t>
+          <t>"화상 부위가 아프세요?"</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -28681,7 +28678,7 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -28698,25 +28695,15 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D589" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>bullae 있음/없음</t>
-        </is>
-      </c>
-      <c r="F589" t="inlineStr">
-        <is>
-          <t>🩺 물집이 잡혔는지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G589" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부손상</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -28743,25 +28730,15 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D590" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F590" t="inlineStr">
-        <is>
-          <t>"화상 부위가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G590" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>화상부위 세척함</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -28771,7 +28748,7 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>피부손상</t>
         </is>
       </c>
     </row>
@@ -28788,15 +28765,15 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D591" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>화상부위 오염물 제거함</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -28827,11 +28804,11 @@
         </is>
       </c>
       <c r="D592" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>화상부위 세척함</t>
+          <t>화상 dressing 함</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -28858,7 +28835,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D593" t="n">
@@ -28866,7 +28843,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>화상부위 오염물 제거함</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -28876,7 +28853,7 @@
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -28897,11 +28874,11 @@
         </is>
       </c>
       <c r="D594" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>화상 dressing 함</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -28911,7 +28888,7 @@
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -28928,15 +28905,15 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D595" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>흡입 화상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -28963,15 +28940,15 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D596" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -28981,7 +28958,7 @@
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -29002,11 +28979,11 @@
         </is>
       </c>
       <c r="D597" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>흡입 화상이 있는지 확인함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
@@ -29016,7 +28993,7 @@
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -29033,15 +29010,15 @@
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D598" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -29072,11 +29049,11 @@
         </is>
       </c>
       <c r="D599" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -29093,12 +29070,12 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>화상</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>화상</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -29107,33 +29084,33 @@
         </is>
       </c>
       <c r="D600" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>기도개방 상태를 확인함</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>커버리지 보완 260802</t>
+          <t>확인형 — 산소·수액은 안 할 수도 있다</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>기도개방유지불능</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>화상</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>화상</t>
+          <t>아나필락시스</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
@@ -29142,38 +29119,38 @@
         </is>
       </c>
       <c r="D601" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>커버리지 보완 260802</t>
+          <t>확인형 — 산소·수액은 안 할 수도 있다</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>기도개방유지불능</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>산과</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>임신 20주 미만</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D602" t="n">
@@ -29181,34 +29158,44 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>기도개방 상태를 확인함</t>
+          <t>질 출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>"질에서 피가 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>확인형 — 산소·수액은 안 할 수도 있다</t>
+          <t>커버리지 2차 260802</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>기도개방유지불능</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>산과</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>아나필락시스</t>
+          <t>임신 20주 미만</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D603" t="n">
@@ -29216,17 +29203,27 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>호흡곤란이 있는지 확인함</t>
+          <t>자궁수축 있음/없음</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>"배가 규칙적으로 뭉치세요?"</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>확인형 — 산소·수액은 안 할 수도 있다</t>
+          <t>커버리지 2차 260802</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>기도개방유지불능</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -29247,16 +29244,16 @@
         </is>
       </c>
       <c r="D604" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>질 출혈 있음/없음</t>
+          <t>질 분비물 있음/없음</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>"질에서 피가 나오세요?"</t>
+          <t>"평소와 다른 분비물이 있으세요?"</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -29271,7 +29268,7 @@
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -29292,16 +29289,16 @@
         </is>
       </c>
       <c r="D605" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>자궁수축 있음/없음</t>
+          <t>복부 통증 있음/없음</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>"배가 규칙적으로 뭉치세요?"</t>
+          <t>"배가 아프세요?"</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
@@ -29316,7 +29313,7 @@
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -29333,25 +29330,15 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D606" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>질 분비물 있음/없음</t>
-        </is>
-      </c>
-      <c r="F606" t="inlineStr">
-        <is>
-          <t>"평소와 다른 분비물이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G606" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -29361,7 +29348,7 @@
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -29378,25 +29365,15 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D607" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>복부 통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F607" t="inlineStr">
-        <is>
-          <t>"배가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G607" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -29406,7 +29383,7 @@
       </c>
       <c r="J607" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -29423,15 +29400,15 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D608" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>출혈양상 확인함</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -29458,15 +29435,15 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D609" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -29476,7 +29453,7 @@
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -29497,11 +29474,11 @@
         </is>
       </c>
       <c r="D610" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>출혈양상 확인함</t>
+          <t>질 분비물 양상 관찰함</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -29511,7 +29488,7 @@
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -29532,11 +29509,11 @@
         </is>
       </c>
       <c r="D611" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -29546,7 +29523,7 @@
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -29567,11 +29544,11 @@
         </is>
       </c>
       <c r="D612" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>질 분비물 양상 관찰함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -29581,7 +29558,7 @@
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -29598,15 +29575,15 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D613" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
@@ -29637,11 +29614,11 @@
         </is>
       </c>
       <c r="D614" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -29663,20 +29640,30 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>임신 20주 미만</t>
+          <t>임신 20주 이상</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D615" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>태동 있음/태동 없음</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>"아기가 움직이는 게 느껴지세요?"</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -29686,7 +29673,7 @@
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>모체와태아상태위험</t>
         </is>
       </c>
     </row>
@@ -29698,20 +29685,30 @@
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>임신 20주 미만</t>
+          <t>임신 20주 이상</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D616" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>자궁수축 있음/없음</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>"배가 규칙적으로 뭉치세요?"</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -29721,7 +29718,7 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>모체와태아상태위험</t>
         </is>
       </c>
     </row>
@@ -29742,16 +29739,16 @@
         </is>
       </c>
       <c r="D617" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>태동 있음/태동 없음</t>
+          <t>양막파열 있음/없음</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>"아기가 움직이는 게 느껴지세요?"</t>
+          <t>"양수가 터진 것 같으세요?"</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -29787,16 +29784,16 @@
         </is>
       </c>
       <c r="D618" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>자궁수축 있음/없음</t>
+          <t>양수 leakage 있음/없음</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>"배가 규칙적으로 뭉치세요?"</t>
+          <t>🩺 양수가 새는지 확인하세요</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -29832,16 +29829,16 @@
         </is>
       </c>
       <c r="D619" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>양막파열 있음/없음</t>
+          <t>질 출혈 있음/없음</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>"양수가 터진 것 같으세요?"</t>
+          <t>"질에서 피가 나오세요?"</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -29856,7 +29853,7 @@
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>모체와태아상태위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -29877,16 +29874,16 @@
         </is>
       </c>
       <c r="D620" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>양수 leakage 있음/없음</t>
+          <t>복부 통증 있음/없음</t>
         </is>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>🩺 양수가 새는지 확인하세요</t>
+          <t>"배가 아프세요?"</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -29901,7 +29898,7 @@
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>모체와태아상태위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -29918,25 +29915,15 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D621" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>질 출혈 있음/없음</t>
-        </is>
-      </c>
-      <c r="F621" t="inlineStr">
-        <is>
-          <t>"질에서 피가 나오세요?"</t>
-        </is>
-      </c>
-      <c r="G621" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>모체와태아상태위험</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -29946,7 +29933,7 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>모체와태아상태위험</t>
         </is>
       </c>
     </row>
@@ -29963,25 +29950,15 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D622" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>복부 통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F622" t="inlineStr">
-        <is>
-          <t>"배가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G622" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>분만 진행 상태 확인함</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -29991,7 +29968,7 @@
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>모체와태아상태위험</t>
         </is>
       </c>
     </row>
@@ -30008,15 +29985,15 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D623" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>모체와태아상태위험</t>
+          <t>양수 양상 관찰함</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -30047,11 +30024,11 @@
         </is>
       </c>
       <c r="D624" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>분만 진행 상태 확인함</t>
+          <t>양막 파열 시간 확인함</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -30078,7 +30055,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D625" t="n">
@@ -30086,7 +30063,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>양수 양상 관찰함</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -30096,7 +30073,7 @@
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>모체와태아상태위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -30117,11 +30094,11 @@
         </is>
       </c>
       <c r="D626" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>양막 파열 시간 확인함</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -30131,7 +30108,7 @@
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>모체와태아상태위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -30148,15 +30125,15 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D627" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>출혈양상 확인함</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -30183,15 +30160,15 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D628" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -30201,7 +30178,7 @@
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -30222,11 +30199,11 @@
         </is>
       </c>
       <c r="D629" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>출혈양상 확인함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -30236,7 +30213,7 @@
       </c>
       <c r="J629" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -30253,15 +30230,15 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D630" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -30292,11 +30269,11 @@
         </is>
       </c>
       <c r="D631" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
@@ -30318,20 +30295,30 @@
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>임신 20주 이상</t>
+          <t>출산 후 (6주 이내)</t>
         </is>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D632" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>오로 있음</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>🩺 오로가 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -30341,7 +30328,7 @@
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -30353,20 +30340,30 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>임신 20주 이상</t>
+          <t>출산 후 (6주 이내)</t>
         </is>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D633" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>질 출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>"평소보다 피가 많이 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -30376,7 +30373,7 @@
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -30397,21 +30394,21 @@
         </is>
       </c>
       <c r="D634" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>오로 있음</t>
+          <t>열감 있음/없음</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>🩺 오로가 있는지 확인하세요</t>
+          <t>"열이 나거나 오한이 있으세요?"</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -30421,7 +30418,7 @@
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -30442,16 +30439,16 @@
         </is>
       </c>
       <c r="D635" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>질 출혈 있음/없음</t>
+          <t>복부 통증 있음/없음</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>"평소보다 피가 많이 나오세요?"</t>
+          <t>"배가 아프세요?"</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -30466,7 +30463,7 @@
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -30483,25 +30480,15 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D636" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>열감 있음/없음</t>
-        </is>
-      </c>
-      <c r="F636" t="inlineStr">
-        <is>
-          <t>"열이 나거나 오한이 있으세요?"</t>
-        </is>
-      </c>
-      <c r="G636" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -30511,7 +30498,7 @@
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -30528,25 +30515,15 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D637" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>복부 통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F637" t="inlineStr">
-        <is>
-          <t>"배가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G637" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>오로 관찰함</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -30556,7 +30533,7 @@
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -30573,15 +30550,15 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D638" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -30608,15 +30585,15 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D639" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>오로 관찰함</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -30626,7 +30603,7 @@
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -30647,11 +30624,11 @@
         </is>
       </c>
       <c r="D640" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -30661,7 +30638,7 @@
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -30678,15 +30655,15 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D641" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -30713,7 +30690,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D642" t="n">
@@ -30721,7 +30698,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>감염 증상이 있는지 확인함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
@@ -30731,7 +30708,7 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -30752,11 +30729,11 @@
         </is>
       </c>
       <c r="D643" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>체온 측정함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -30766,7 +30743,7 @@
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -30783,15 +30760,15 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D644" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
@@ -30822,11 +30799,11 @@
         </is>
       </c>
       <c r="D645" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -30848,20 +30825,30 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>출산 후 (6주 이내)</t>
+          <t>부인과 (임신 아님)</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D646" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>질 분비물 있음/없음</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>"평소와 다른 분비물이 있으세요?"</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -30871,7 +30858,7 @@
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -30883,20 +30870,30 @@
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>출산 후 (6주 이내)</t>
+          <t>부인과 (임신 아님)</t>
         </is>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D647" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>질 출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>"질에서 피가 나오세요?"</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -30906,7 +30903,7 @@
       </c>
       <c r="J647" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -30927,21 +30924,21 @@
         </is>
       </c>
       <c r="D648" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>질 분비물 있음/없음</t>
+          <t>무월경 있음</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>"평소와 다른 분비물이 있으세요?"</t>
+          <t>🩺 생리가 없는지 확인하세요</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -30951,7 +30948,7 @@
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -30972,21 +30969,21 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>질 출혈 있음/없음</t>
+          <t>월경불순이 있다고 함</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>"질에서 피가 나오세요?"</t>
+          <t>🩺 생리가 불규칙한지 확인하세요</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -30996,7 +30993,7 @@
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>공통</t>
         </is>
       </c>
     </row>
@@ -31017,21 +31014,21 @@
         </is>
       </c>
       <c r="D650" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>무월경 있음</t>
+          <t>복부 통증 있음/없음</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>🩺 생리가 없는지 확인하세요</t>
+          <t>"아랫배가 아프세요?"</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -31041,7 +31038,7 @@
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -31058,25 +31055,15 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D651" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>월경불순이 있다고 함</t>
-        </is>
-      </c>
-      <c r="F651" t="inlineStr">
-        <is>
-          <t>🩺 생리가 불규칙한지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G651" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -31086,7 +31073,7 @@
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -31103,25 +31090,15 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D652" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>복부 통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F652" t="inlineStr">
-        <is>
-          <t>"아랫배가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G652" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>질 분비물 양상 관찰함</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
@@ -31131,7 +31108,7 @@
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -31148,15 +31125,15 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D653" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>월경력 확인함</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -31183,15 +31160,15 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D654" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>질 분비물 양상 관찰함</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -31201,7 +31178,7 @@
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -31222,11 +31199,11 @@
         </is>
       </c>
       <c r="D655" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>월경력 확인함</t>
+          <t>출혈양상 확인함</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
@@ -31236,7 +31213,7 @@
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -31257,11 +31234,11 @@
         </is>
       </c>
       <c r="D656" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -31271,7 +31248,7 @@
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -31292,11 +31269,11 @@
         </is>
       </c>
       <c r="D657" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>출혈양상 확인함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -31306,7 +31283,7 @@
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -31323,15 +31300,15 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D658" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -31362,11 +31339,11 @@
         </is>
       </c>
       <c r="D659" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -31383,25 +31360,35 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>산과</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
         <is>
-          <t>부인과 (임신 아님)</t>
+          <t>소아-황달</t>
         </is>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D660" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>황달 있음/없음</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>"아기 피부가 노랗게 보이나요?"</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -31411,32 +31398,42 @@
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>비효율적수유</t>
         </is>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>산과</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
         <is>
-          <t>부인과 (임신 아님)</t>
+          <t>소아-황달</t>
         </is>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D661" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>공막의 황달 있음/없음</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>🩺 눈 흰자가 노란지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -31446,7 +31443,7 @@
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>비효율적수유</t>
         </is>
       </c>
     </row>
@@ -31467,16 +31464,16 @@
         </is>
       </c>
       <c r="D662" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>황달 있음/없음</t>
+          <t>수유 잘함/보충수유 필요함</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>"아기 피부가 노랗게 보이나요?"</t>
+          <t>"젖을 잘 먹나요?"</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -31512,16 +31509,16 @@
         </is>
       </c>
       <c r="D663" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>공막의 황달 있음/없음</t>
+          <t>lethargy 상태임/의식 명료함</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>🩺 눈 흰자가 노란지 확인하세요</t>
+          <t>"아이가 축 처져 있나요?"</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -31553,25 +31550,15 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D664" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>수유 잘함/보충수유 필요함</t>
-        </is>
-      </c>
-      <c r="F664" t="inlineStr">
-        <is>
-          <t>"젖을 잘 먹나요?"</t>
-        </is>
-      </c>
-      <c r="G664" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>비효율적수유</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -31598,25 +31585,15 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D665" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>lethargy 상태임/의식 명료함</t>
-        </is>
-      </c>
-      <c r="F665" t="inlineStr">
-        <is>
-          <t>"아이가 축 처져 있나요?"</t>
-        </is>
-      </c>
-      <c r="G665" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>황달이 있는지 확인함</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -31643,15 +31620,15 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D666" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>비효율적수유</t>
+          <t>수유 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -31673,12 +31650,12 @@
       </c>
       <c r="B667" t="inlineStr">
         <is>
-          <t>소아-황달</t>
+          <t>소아-수유곤란</t>
         </is>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D667" t="n">
@@ -31686,7 +31663,17 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>황달이 있는지 확인함</t>
+          <t>수유 잘함/보충수유 필요함</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>"젖을 잘 먹나요?"</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -31708,12 +31695,12 @@
       </c>
       <c r="B668" t="inlineStr">
         <is>
-          <t>소아-황달</t>
+          <t>소아-수유곤란</t>
         </is>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D668" t="n">
@@ -31721,7 +31708,17 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>수유 방법에 대해 교육함</t>
+          <t>수유 후 구토 보임/수유 후 구토 없음</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>"먹고 나서 토하나요?"</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -31752,16 +31749,16 @@
         </is>
       </c>
       <c r="D669" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>수유 잘함/보충수유 필요함</t>
+          <t>수유 후 역류 보임/수유 후 역류 없음</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>"젖을 잘 먹나요?"</t>
+          <t>"먹고 나서 올리나요?"</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -31797,21 +31794,21 @@
         </is>
       </c>
       <c r="D670" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>수유 후 구토 보임/수유 후 구토 없음</t>
+          <t>수유 후 만족감 있음</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>"먹고 나서 토하나요?"</t>
+          <t>🩺 먹고 나서 편안해 보이는지 관찰하세요</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -31838,25 +31835,15 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D671" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>수유 후 역류 보임/수유 후 역류 없음</t>
-        </is>
-      </c>
-      <c r="F671" t="inlineStr">
-        <is>
-          <t>"먹고 나서 올리나요?"</t>
-        </is>
-      </c>
-      <c r="G671" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>비효율적수유</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -31883,25 +31870,15 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D672" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>수유 후 만족감 있음</t>
-        </is>
-      </c>
-      <c r="F672" t="inlineStr">
-        <is>
-          <t>🩺 먹고 나서 편안해 보이는지 관찰하세요</t>
-        </is>
-      </c>
-      <c r="G672" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>수유 중 아기의 피로 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -31928,15 +31905,15 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D673" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>비효율적수유</t>
+          <t>수유 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -31958,12 +31935,12 @@
       </c>
       <c r="B674" t="inlineStr">
         <is>
-          <t>소아-수유곤란</t>
+          <t>소아-무호흡</t>
         </is>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D674" t="n">
@@ -31971,7 +31948,17 @@
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>수유 중 아기의 피로 증상이 있는지 확인함</t>
+          <t>무호흡 있음/없음</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>"숨을 멈춘 적이 있나요?"</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -31981,7 +31968,7 @@
       </c>
       <c r="J674" t="inlineStr">
         <is>
-          <t>비효율적수유</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -31993,12 +31980,12 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>소아-수유곤란</t>
+          <t>소아-무호흡</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D675" t="n">
@@ -32006,7 +31993,17 @@
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>수유 방법에 대해 교육함</t>
+          <t>청색증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>"입술이나 얼굴이 파래졌나요?"</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -32016,7 +32013,7 @@
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>비효율적수유</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -32037,16 +32034,16 @@
         </is>
       </c>
       <c r="D676" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>무호흡 있음/없음</t>
+          <t>apnea alarm 울림/apnea alarm 울리지 않음</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>"숨을 멈춘 적이 있나요?"</t>
+          <t>🩺 무호흡 알람이 울렸는지 확인하세요</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -32078,25 +32075,15 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D677" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>청색증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F677" t="inlineStr">
-        <is>
-          <t>"입술이나 얼굴이 파래졌나요?"</t>
-        </is>
-      </c>
-      <c r="G677" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -32123,25 +32110,15 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D678" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>apnea alarm 울림/apnea alarm 울리지 않음</t>
-        </is>
-      </c>
-      <c r="F678" t="inlineStr">
-        <is>
-          <t>🩺 무호흡 알람이 울렸는지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G678" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -32168,15 +32145,15 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D679" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>산소포화도 monitor 함</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -32207,11 +32184,11 @@
         </is>
       </c>
       <c r="D680" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>호흡곤란이 있는지 확인함</t>
+          <t>무호흡 monitor 시작함</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -32242,11 +32219,11 @@
         </is>
       </c>
       <c r="D681" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>산소포화도 monitor 함</t>
+          <t>무호흡 지속 시간 측정함</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
@@ -32263,70 +32240,100 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>외상</t>
         </is>
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>소아-무호흡</t>
+          <t>외상</t>
         </is>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D682" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>무호흡 monitor 시작함</t>
+          <t>신체손상 있음</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>🩺 다친 곳이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>커버리지 2차 260802</t>
+          <t>외상 1경로 통합 260802</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>외상부위</t>
         </is>
       </c>
     </row>
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>외상</t>
         </is>
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>소아-무호흡</t>
+          <t>외상</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D683" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>무호흡 지속 시간 측정함</t>
+          <t>출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>"피가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>커버리지 2차 260802</t>
+          <t>외상 1경로 통합 260802</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>외상부위</t>
         </is>
       </c>
     </row>
@@ -32347,21 +32354,21 @@
         </is>
       </c>
       <c r="D684" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>신체손상 있음</t>
+          <t>찰과상 있음/없음</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>🩺 다친 곳이 있는지 확인하세요</t>
+          <t>🩺 긁힌 상처를 확인하세요</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -32397,16 +32404,16 @@
         </is>
       </c>
       <c r="D685" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>출혈 있음/없음</t>
+          <t>edema 있음/없음</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>"피가 나나요?"</t>
+          <t>🩺 다친 곳이 부었는지 확인하세요</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
@@ -32421,7 +32428,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="L685" t="inlineStr">
@@ -32447,16 +32454,16 @@
         </is>
       </c>
       <c r="D686" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>찰과상 있음/없음</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>🩺 긁힌 상처를 확인하세요</t>
+          <t>"다친 곳이 아프세요?"</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -32471,7 +32478,7 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
@@ -32493,25 +32500,15 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D687" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>edema 있음/없음</t>
-        </is>
-      </c>
-      <c r="F687" t="inlineStr">
-        <is>
-          <t>🩺 다친 곳이 부었는지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G687" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -32522,11 +32519,6 @@
       <c r="J687" t="inlineStr">
         <is>
           <t>신체손상위험</t>
-        </is>
-      </c>
-      <c r="L687" t="inlineStr">
-        <is>
-          <t>외상부위</t>
         </is>
       </c>
     </row>
@@ -32543,25 +32535,15 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D688" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F688" t="inlineStr">
-        <is>
-          <t>"다친 곳이 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G688" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>상처 관찰함</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -32571,12 +32553,7 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-      <c r="L688" t="inlineStr">
-        <is>
-          <t>외상부위</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -32593,15 +32570,15 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D689" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -32628,15 +32605,15 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D690" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>상처 관찰함</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -32646,7 +32623,7 @@
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -32667,11 +32644,11 @@
         </is>
       </c>
       <c r="D691" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -32681,7 +32658,7 @@
       </c>
       <c r="J691" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -32698,15 +32675,15 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D692" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>출혈양상 확인함</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -32733,7 +32710,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D693" t="n">
@@ -32741,7 +32718,7 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -32751,7 +32728,7 @@
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -32772,11 +32749,11 @@
         </is>
       </c>
       <c r="D694" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>출혈양상 확인함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -32786,7 +32763,7 @@
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -32803,15 +32780,15 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D695" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -32842,11 +32819,11 @@
         </is>
       </c>
       <c r="D696" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -32863,70 +32840,100 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D697" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>🩺 피부가 상했는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>외상 1경로 통합 260802</t>
+          <t>피부 확장 260802</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr">
+        <is>
+          <t>피부상황</t>
         </is>
       </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D698" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>출혈 있음/없음</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>"피가 나나요?"</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>외상 1경로 통합 260802</t>
+          <t>피부 확장 260802</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr">
+        <is>
+          <t>피부상황</t>
         </is>
       </c>
     </row>
@@ -32947,21 +32954,21 @@
         </is>
       </c>
       <c r="D699" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>피부 손상 있음</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>🩺 피부가 상했는지 확인하세요</t>
+          <t>"그 부위가 아프세요?"</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -32971,7 +32978,7 @@
       </c>
       <c r="J699" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="L699" t="inlineStr">
@@ -32993,25 +33000,15 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D700" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>출혈 있음/없음</t>
-        </is>
-      </c>
-      <c r="F700" t="inlineStr">
-        <is>
-          <t>"피가 나나요?"</t>
-        </is>
-      </c>
-      <c r="G700" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -33021,12 +33018,7 @@
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>피부손상</t>
-        </is>
-      </c>
-      <c r="L700" t="inlineStr">
-        <is>
-          <t>피부상황</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -33043,25 +33035,15 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D701" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F701" t="inlineStr">
-        <is>
-          <t>"그 부위가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G701" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -33071,12 +33053,7 @@
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-      <c r="L701" t="inlineStr">
-        <is>
-          <t>피부상황</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -33097,11 +33074,11 @@
         </is>
       </c>
       <c r="D702" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -33111,7 +33088,7 @@
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -33132,11 +33109,11 @@
         </is>
       </c>
       <c r="D703" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -33146,7 +33123,7 @@
       </c>
       <c r="J703" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -33163,15 +33140,15 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D704" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -33202,11 +33179,11 @@
         </is>
       </c>
       <c r="D705" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -33215,76 +33192,6 @@
         </is>
       </c>
       <c r="J705" t="inlineStr">
-        <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr">
-        <is>
-          <t>피부</t>
-        </is>
-      </c>
-      <c r="B706" t="inlineStr">
-        <is>
-          <t>피부</t>
-        </is>
-      </c>
-      <c r="C706" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D706" t="n">
-        <v>6</v>
-      </c>
-      <c r="E706" t="inlineStr">
-        <is>
-          <t>통증 양상을 확인함</t>
-        </is>
-      </c>
-      <c r="I706" t="inlineStr">
-        <is>
-          <t>피부 확장 260802</t>
-        </is>
-      </c>
-      <c r="J706" t="inlineStr">
-        <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr">
-        <is>
-          <t>피부</t>
-        </is>
-      </c>
-      <c r="B707" t="inlineStr">
-        <is>
-          <t>피부</t>
-        </is>
-      </c>
-      <c r="C707" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D707" t="n">
-        <v>7</v>
-      </c>
-      <c r="E707" t="inlineStr">
-        <is>
-          <t>통증을 관찰하기로 함</t>
-        </is>
-      </c>
-      <c r="I707" t="inlineStr">
-        <is>
-          <t>피부 확장 260802</t>
-        </is>
-      </c>
-      <c r="J707" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -15526,11 +15526,6 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15571,11 +15566,6 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -15616,11 +15606,6 @@
           <t>고체온</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -15661,11 +15646,6 @@
           <t>고체온</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15706,11 +15686,6 @@
           <t>급성통증</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -16031,11 +16006,6 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16076,11 +16046,6 @@
           <t>공통</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -16121,11 +16086,6 @@
           <t>고체온</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -16166,11 +16126,6 @@
           <t>고체온</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16261,11 +16216,6 @@
           <t>급성통증</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr">
-        <is>
-          <t>온열노출</t>
-        </is>
-      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16531,11 +16481,6 @@
           <t>저체온</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t>한랭노출</t>
-        </is>
-      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -16581,11 +16526,6 @@
           <t>저체온</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t>한랭노출</t>
-        </is>
-      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -16631,11 +16571,6 @@
           <t>저체온</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t>한랭노출</t>
-        </is>
-      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16681,11 +16616,6 @@
           <t>저체온</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t>한랭노출</t>
-        </is>
-      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16731,11 +16661,6 @@
           <t>저체온</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t>한랭노출</t>
-        </is>
-      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -23956,11 +23881,6 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t>노출경로</t>
-        </is>
-      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -24001,11 +23921,6 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="L470" t="inlineStr">
-        <is>
-          <t>노출경로</t>
-        </is>
-      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -24046,11 +23961,6 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t>노출경로</t>
-        </is>
-      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -24091,11 +24001,6 @@
           <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t>노출경로</t>
-        </is>
-      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -24136,11 +24041,6 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t>노출경로</t>
-        </is>
-      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -24181,11 +24081,6 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
-      <c r="L474" t="inlineStr">
-        <is>
-          <t>노출경로</t>
-        </is>
-      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -24224,11 +24119,6 @@
       <c r="I475" t="inlineStr">
         <is>
           <t>⚠️ V4 이관</t>
-        </is>
-      </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t>노출경로</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -11979,7 +11979,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -12424,7 +12424,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -12469,7 +12469,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -12554,7 +12554,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -15624,7 +15624,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -15664,7 +15664,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -16064,7 +16064,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -16104,7 +16104,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -17299,7 +17299,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -19839,7 +19839,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -21709,7 +21709,7 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -22454,7 +22454,7 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -24449,7 +24449,7 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -24844,7 +24844,7 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         </is>
       </c>
       <c r="D586" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E586" t="inlineStr">
         <is>
@@ -28499,7 +28499,7 @@
         </is>
       </c>
       <c r="D587" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E587" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         </is>
       </c>
       <c r="D588" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E588" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         </is>
       </c>
       <c r="D602" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E602" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         </is>
       </c>
       <c r="D603" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E603" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         </is>
       </c>
       <c r="D604" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E604" t="inlineStr">
         <is>
@@ -29179,7 +29179,7 @@
         </is>
       </c>
       <c r="D605" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E605" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         </is>
       </c>
       <c r="D615" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E615" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         </is>
       </c>
       <c r="D616" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E616" t="inlineStr">
         <is>
@@ -29629,7 +29629,7 @@
         </is>
       </c>
       <c r="D617" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E617" t="inlineStr">
         <is>
@@ -29674,7 +29674,7 @@
         </is>
       </c>
       <c r="D618" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E618" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         </is>
       </c>
       <c r="D619" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E619" t="inlineStr">
         <is>
@@ -29764,7 +29764,7 @@
         </is>
       </c>
       <c r="D620" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E620" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         </is>
       </c>
       <c r="D632" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E632" t="inlineStr">
         <is>
@@ -30239,7 +30239,7 @@
         </is>
       </c>
       <c r="D633" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         </is>
       </c>
       <c r="D634" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E634" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         </is>
       </c>
       <c r="D635" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E635" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         </is>
       </c>
       <c r="D646" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E646" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         </is>
       </c>
       <c r="D647" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E647" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         </is>
       </c>
       <c r="D648" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E648" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         </is>
       </c>
       <c r="D649" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E649" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         </is>
       </c>
       <c r="D650" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E650" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         </is>
       </c>
       <c r="D682" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E682" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         </is>
       </c>
       <c r="D683" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E683" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         </is>
       </c>
       <c r="D684" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E684" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         </is>
       </c>
       <c r="D685" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E685" t="inlineStr">
         <is>
@@ -32344,7 +32344,7 @@
         </is>
       </c>
       <c r="D686" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E686" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         </is>
       </c>
       <c r="D697" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E697" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         </is>
       </c>
       <c r="D698" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E698" t="inlineStr">
         <is>
@@ -32844,7 +32844,7 @@
         </is>
       </c>
       <c r="D699" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E699" t="inlineStr">
         <is>
@@ -36414,7 +36414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -36493,31 +36493,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>진통제 원함/진통제를 원하지 않음</t>
+          <t>처방에 의해 진통제를 투여함</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>"진통제를 맞고 싶으세요?"</t>
+          <t>💊 진통제를 투여했나요?</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>통증있음</t>
+          <t>투여후</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>통증이 확인됐을 때만 묻는다 — 통증 없는 환자에게 물으면 이상하다</t>
+          <t>의사 처방이 난 뒤에 누른다</t>
         </is>
       </c>
     </row>
@@ -36533,31 +36533,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>처방에 의해 진통제를 투여함</t>
+          <t>진통제 투여 후 통증 감소됨/진통제 투여하였으나 통증 지속됨</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>💊 진통제를 투여했나요?</t>
+          <t>"진통제 맞고 통증이 좀 나아지셨어요?"</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>투여후</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>의사 처방이 난 뒤에 누른다</t>
         </is>
       </c>
     </row>
@@ -36573,21 +36568,21 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>진통제 투여 후 통증 감소됨/진통제 투여하였으나 통증 지속됨</t>
+          <t>진통제 투여 후 부작용 있음/없음</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>"진통제 맞고 통증이 좀 나아지셨어요?"</t>
+          <t>"진통제 맞고 메스껍거나 어지러우세요?"</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>선택</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -36599,7 +36594,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E조건</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -36608,26 +36603,21 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>진통제 투여 후 부작용 있음/없음</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>"진통제 맞고 메스껍거나 어지러우세요?"</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>투여후</t>
+          <t>통증부위를 사정함</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>부위</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>부위를 하나라도 고르면</t>
         </is>
       </c>
     </row>
@@ -36643,21 +36633,21 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>통증부위를 사정함</t>
+          <t>통증 강도 측정함</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>부위</t>
+          <t>강도</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>부위를 하나라도 고르면</t>
+          <t>강도를 입력하면</t>
         </is>
       </c>
     </row>
@@ -36673,21 +36663,21 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>통증 강도 측정함</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>강도</t>
+          <t>양상</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>강도를 입력하면</t>
+          <t>양상을 하나라도 고르면</t>
         </is>
       </c>
     </row>
@@ -36703,51 +36693,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>진통제 투여 후 통증 강도 측정함</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>양상</t>
+          <t>투여후강도</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>양상을 하나라도 고르면</t>
+          <t>투여 후 강도를 다시 재면</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P&amp;E조건</t>
+          <t>값</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>문항</t>
+          <t>부위</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>진통제 투여 후 통증 강도 측정함</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>투여후강도</t>
+        <v>1</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>머리</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>투여 후 강도를 다시 재면</t>
+          <t>🧠</t>
         </is>
       </c>
     </row>
@@ -36763,16 +36748,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>머리</t>
+          <t>가슴</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>🧠</t>
+          <t>🫀</t>
         </is>
       </c>
     </row>
@@ -36788,16 +36773,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>가슴</t>
+          <t>배</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>🫀</t>
+          <t>🫃</t>
         </is>
       </c>
     </row>
@@ -36813,16 +36798,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>목</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>🫃</t>
+          <t>🧣</t>
         </is>
       </c>
     </row>
@@ -36838,16 +36823,21 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>목</t>
+          <t>허리</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>🧣</t>
+          <t>🔙</t>
         </is>
       </c>
     </row>
@@ -36863,11 +36853,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>허리</t>
+          <t>팔</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -36877,7 +36867,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>🔙</t>
+          <t>💪</t>
         </is>
       </c>
     </row>
@@ -36893,11 +36883,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>팔</t>
+          <t>다리</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -36907,7 +36897,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>💪</t>
+          <t>🦵</t>
         </is>
       </c>
     </row>
@@ -36923,21 +36913,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>다리</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>SMC</t>
+          <t>엉덩이</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>🦵</t>
+          <t>🍑</t>
         </is>
       </c>
     </row>
@@ -36949,20 +36934,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>부위</t>
+          <t>세부부위</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>엉덩이</t>
+          <t>anterior chest</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>🍑</t>
+          <t>가슴</t>
         </is>
       </c>
     </row>
@@ -36978,11 +36963,11 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>anterior chest</t>
+          <t>epigastric site</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -37003,11 +36988,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>epigastric site</t>
+          <t>mediastinal site</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -37028,11 +37013,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>mediastinal site</t>
+          <t>substernal site</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -37053,16 +37038,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>substernal site</t>
+          <t>LLQ</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>가슴</t>
+          <t>배</t>
         </is>
       </c>
     </row>
@@ -37078,11 +37063,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LLQ</t>
+          <t>LUQ</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -37103,11 +37088,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LUQ</t>
+          <t>RLQ</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -37128,11 +37113,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>RLQ</t>
+          <t>RUQ</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -37153,11 +37138,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>RUQ</t>
+          <t>periumbilical area</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -37178,11 +37163,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>periumbilical area</t>
+          <t>전체</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -37199,20 +37184,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>세부부위</t>
+          <t>도구</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>전체</t>
+          <t>NRS</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>배</t>
+          <t>숫자 0~10 · 성인</t>
         </is>
       </c>
     </row>
@@ -37228,16 +37213,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NRS</t>
+          <t>FPRS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>소아</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>숫자 0~10 · 성인</t>
+          <t>얼굴 그림 · 소아/노인</t>
         </is>
       </c>
     </row>
@@ -37253,11 +37243,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FPRS</t>
+          <t>FLACC</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -37267,7 +37257,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>얼굴 그림 · 소아/노인</t>
+          <t>행동 관찰 · 영유아</t>
         </is>
       </c>
     </row>
@@ -37283,11 +37273,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FLACC</t>
+          <t>NIPS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -37297,7 +37287,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>행동 관찰 · 영유아</t>
+          <t>신생아</t>
         </is>
       </c>
     </row>
@@ -37313,21 +37303,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NIPS</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>소아</t>
+          <t>CNPS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>신생아</t>
+          <t>비언어 성인</t>
         </is>
       </c>
     </row>
@@ -37339,20 +37324,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>도구</t>
+          <t>양상</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CNPS</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>비언어 성인</t>
+          <t>뻐근한</t>
         </is>
       </c>
     </row>
@@ -37368,11 +37348,11 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>뻐근한</t>
+          <t>날카로운</t>
         </is>
       </c>
     </row>
@@ -37388,11 +37368,11 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>날카로운</t>
+          <t>둔한</t>
         </is>
       </c>
     </row>
@@ -37408,11 +37388,11 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>둔한</t>
+          <t>욱신·쑤시는</t>
         </is>
       </c>
     </row>
@@ -37428,11 +37408,11 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>욱신·쑤시는</t>
+          <t>타는 듯한</t>
         </is>
       </c>
     </row>
@@ -37448,11 +37428,11 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>타는 듯한</t>
+          <t>저리는 듯한</t>
         </is>
       </c>
     </row>
@@ -37468,11 +37448,11 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>저리는 듯한</t>
+          <t>칼로 베인 듯한</t>
         </is>
       </c>
     </row>
@@ -37488,11 +37468,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>칼로 베인 듯한</t>
+          <t>표현 못함</t>
         </is>
       </c>
     </row>
@@ -37504,15 +37484,15 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>양상</t>
+          <t>빈도</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>표현 못함</t>
+          <t>발작적으로 갑자기</t>
         </is>
       </c>
     </row>
@@ -37528,11 +37508,11 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>발작적으로 갑자기</t>
+          <t>지속적</t>
         </is>
       </c>
     </row>
@@ -37548,11 +37528,11 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>지속적</t>
+          <t>표현 못함</t>
         </is>
       </c>
     </row>
@@ -37568,11 +37548,11 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>표현 못함</t>
+          <t>기타</t>
         </is>
       </c>
     </row>
@@ -37584,15 +37564,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>빈도</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>양호함</t>
         </is>
       </c>
     </row>
@@ -37608,11 +37588,11 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>양호함</t>
+          <t>약함</t>
         </is>
       </c>
     </row>
@@ -37628,11 +37608,11 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>약함</t>
+          <t>없음</t>
         </is>
       </c>
     </row>
@@ -37648,11 +37628,11 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>평가불가</t>
         </is>
       </c>
     </row>
@@ -37664,15 +37644,20 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>통증진단</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>평가불가</t>
+          <t>급성통증</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>이 진단이 있는 경로에 통증 사정 위젯을 띄운다</t>
         </is>
       </c>
     </row>
@@ -37688,16 +37673,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>만성통증</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>이 진단이 있는 경로에 통증 사정 위젯을 띄운다</t>
+          <t>기간이 아래 기준 이상이면 이 진단으로 바꾼다</t>
         </is>
       </c>
     </row>
@@ -37709,20 +37694,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>통증진단</t>
+          <t>기간기준</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>만성통증</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>기간이 아래 기준 이상이면 이 진단으로 바꾼다</t>
+          <t>만성통증 기준(개월) — IASP/ICD-11 국제표준</t>
         </is>
       </c>
     </row>
@@ -37734,7 +37719,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>기간기준</t>
+          <t>SMC진단</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -37742,12 +37727,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>말초신경혈관기능장애위험</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>만성통증 기준(개월) — IASP/ICD-11 국제표준</t>
+          <t>이 진단이 있으면 부위와 무관하게 SMC를 연다(골절·외상)</t>
         </is>
       </c>
     </row>
@@ -37759,7 +37744,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SMC진단</t>
+          <t>기간</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -37767,12 +37752,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>말초신경혈관기능장애위험</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>이 진단이 있으면 부위와 무관하게 SMC를 연다(골절·외상)</t>
+          <t>오늘·며칠 전</t>
         </is>
       </c>
     </row>
@@ -37788,11 +37768,11 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>오늘·며칠 전</t>
+          <t>1개월 미만</t>
         </is>
       </c>
     </row>
@@ -37808,11 +37788,11 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1개월 미만</t>
+          <t>1~3개월</t>
         </is>
       </c>
     </row>
@@ -37828,11 +37808,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>1~3개월</t>
+          <t>3개월 이상</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>만성</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>이 구간이면 만성통증으로 넘긴다</t>
         </is>
       </c>
     </row>
@@ -37848,41 +37838,41 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3개월 이상</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>만성</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>이 구간이면 만성통증으로 넘긴다</t>
+          <t>모름</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>값</t>
+          <t>A&amp;E조건</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>기간</t>
+          <t>문항</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>모름</t>
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>만성 통증 있음</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>만성</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>기간이 3개월 이상일 때만 기록된다</t>
         </is>
       </c>
     </row>
@@ -37898,56 +37888,116 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>만성 통증 있음</t>
+          <t>sensory, motor, circulation intact 함</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>🩺 감각·운동·순환이 모두 정상인가요?</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>만성</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>기간이 3개월 이상일 때만 기록된다</t>
+          <t>SMC정상</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A&amp;E조건</t>
+          <t>값</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>문항</t>
+          <t>부위자동</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>가슴</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>흉부 통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>부위자동</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
         <v>2</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>sensory, motor, circulation intact 함</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>🩺 감각·운동·순환이 모두 정상인가요?</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>체크</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>SMC정상</t>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>배</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>복부 통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>부위자동</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>머리</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>두통</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -5828,7 +5828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L705"/>
+  <dimension ref="A1:L706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -22714,7 +22714,7 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -22874,7 +22874,7 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -22914,7 +22914,7 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -26904,7 +26904,7 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -33082,6 +33082,51 @@
         </is>
       </c>
       <c r="J705" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>이비인후</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D706" t="n">
+        <v>1</v>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>"아프세요?"</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>통증 문항 260802</t>
+        </is>
+      </c>
+      <c r="J706" t="inlineStr">
         <is>
           <t>급성통증</t>
         </is>
@@ -37930,11 +37975,6 @@
           <t>가슴</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>흉부 통증</t>
@@ -37960,11 +38000,6 @@
           <t>배</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>복부 통증</t>
@@ -37990,11 +38025,6 @@
           <t>머리</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>두통</t>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -5828,7 +5828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L706"/>
+  <dimension ref="A1:L716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -17393,17 +17393,17 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>불규칙 맥박 촉지됨</t>
+          <t>normal sinus rhythm 임/ST elevation 보임/ST 분절 하강 보임/T wave inversion 보임</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>심전도(ECG) 결과를 확인하세요</t>
+          <t>🩺 심전도(ECG) 판독 결과를 고르세요</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -17414,6 +17414,11 @@
       <c r="J304" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>심전도 항목 신설 — 칩스 확인 필요</t>
         </is>
       </c>
     </row>
@@ -17848,17 +17853,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>불규칙 맥박 촉지됨</t>
+          <t>normal sinus rhythm 임/ST elevation 보임/ST 분절 하강 보임/T wave inversion 보임</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>심전도(ECG) 결과를 확인하세요</t>
+          <t>🩺 심전도(ECG) 판독 결과를 고르세요</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -17869,6 +17874,11 @@
       <c r="J316" t="inlineStr">
         <is>
           <t>조직관류저하:심폐계</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>심전도 항목 신설 — 칩스 확인 필요</t>
         </is>
       </c>
     </row>
@@ -22396,6 +22406,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -22436,6 +22456,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -22476,6 +22506,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -22516,6 +22556,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -22556,6 +22606,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>배뇨장애</t>
+        </is>
+      </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -22736,6 +22796,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -22776,6 +22846,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -22816,6 +22896,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -22856,6 +22946,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -22896,6 +22996,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -22936,6 +23046,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -23836,6 +23956,16 @@
           <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>노출경로</t>
@@ -23881,6 +24011,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
@@ -23921,6 +24061,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
@@ -23961,6 +24111,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
@@ -24001,6 +24161,16 @@
           <t>★ 칩스확정 — 마스터 없음</t>
         </is>
       </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -24041,6 +24211,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
@@ -24081,6 +24261,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
@@ -24121,6 +24311,16 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>진단연결 자동보정 — 칩스 확인 필요</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
@@ -33129,6 +33329,386 @@
       <c r="J706" t="inlineStr">
         <is>
           <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증없음</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D707" t="n">
+        <v>6</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>부정맥 있음/부정맥 없음</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>🩺 심전도에 부정맥이 보이나요?</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>심전도 판독 결과</t>
+        </is>
+      </c>
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증없음</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D708" t="n">
+        <v>3</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증없음</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D709" t="n">
+        <v>6</v>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>부정맥이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증없음</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D710" t="n">
+        <v>7</v>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>부정맥으로 인한 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증없음</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D711" t="n">
+        <v>8</v>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>EKG monitor 시작함</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증있음</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D712" t="n">
+        <v>6</v>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>부정맥 있음/부정맥 없음</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>🩺 심전도에 부정맥이 보이나요?</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>심전도 판독 결과</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증있음</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D713" t="n">
+        <v>3</v>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증있음</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D714" t="n">
+        <v>6</v>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>부정맥이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증있음</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D715" t="n">
+        <v>7</v>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>부정맥으로 인한 증상이 있는지 확인함</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>심근경색 의심</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>심근경색의심+통증있음</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D716" t="n">
+        <v>8</v>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>EKG monitor 시작함</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -3392,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3458,6 +3458,21 @@
           <t>비고</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>카테고리순서</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>카테고리</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>카테고리아이콘</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -3498,6 +3513,19 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>통증</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>😣</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3538,6 +3566,19 @@
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>통증</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>😣</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3578,6 +3619,19 @@
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>통증</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>😣</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3618,6 +3672,19 @@
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>통증</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>😣</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3658,6 +3725,19 @@
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -3698,6 +3778,19 @@
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -3738,6 +3831,19 @@
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -3778,6 +3884,19 @@
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -3818,16 +3937,29 @@
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3837,7 +3969,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -3847,7 +3979,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>흉통 동반?</t>
+          <t>통증 동반?</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3866,16 +3998,29 @@
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -3885,7 +4030,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3895,7 +4040,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>흉통 동반?</t>
+          <t>통증 동반?</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3914,16 +4059,29 @@
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3933,7 +4091,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -3943,7 +4101,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>복통 동반?</t>
+          <t>통증 동반?</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3962,16 +4120,29 @@
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3981,7 +4152,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -3991,7 +4162,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>복통 동반?</t>
+          <t>통증 동반?</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4010,16 +4181,29 @@
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -4029,7 +4213,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4039,7 +4223,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>복통 동반?</t>
+          <t>통증 동반?</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4058,16 +4242,29 @@
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -4077,7 +4274,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -4087,7 +4284,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>복통 동반?</t>
+          <t>통증 동반?</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4106,16 +4303,29 @@
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -4125,7 +4335,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -4154,16 +4364,29 @@
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>bleed1</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>출혈 (눈에 보임)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -4173,7 +4396,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>출혈 종류?</t>
+          <t>어디서 피가 나나요?</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -4202,35 +4425,56 @@
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>bleed2</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>출혈 (외상·코피)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>🩹</t>
+          <t>🩸</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>어디서 피가 나나요?</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>외상 · 코피 · 상처 · 수술</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>통증 동반?</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>통증 없음</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)</t>
@@ -4242,35 +4486,56 @@
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>bleed2</t>
+          <t>bleed</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>출혈 (외상·코피)</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>🩹</t>
+          <t>🩸</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>어디서 피가 나나요?</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>외상 · 코피 · 상처 · 수술</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>통증 동반?</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>통증 있음</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>출혈(기타 외상 출혈-코피, 상처 출혈, 수술 출혈)</t>
@@ -4282,6 +4547,19 @@
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4322,6 +4600,19 @@
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4362,6 +4653,19 @@
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>출혈</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4394,6 +4698,19 @@
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" t="n">
+        <v>5</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>열 · 감염</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🌡️</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4426,118 +4743,198 @@
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>열 · 감염</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🌡️</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>체온</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>🌡️</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>체온이 어떤가요?</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>🌡️ 열이 남</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>통증 동반?</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>통증 없음</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>고체온</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>고체온+통증없음</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" t="n">
+        <v>5</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>열 · 감염</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>🌡️</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>통증 동반?</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>통증 없음</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>고체온</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>고체온+통증없음</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>fever</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>체온</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>🌡️</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>체온이 어떤가요?</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>🌡️ 열이 남</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>통증 동반?</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>통증 있음</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>고체온</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>고체온+통증 있음</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" t="n">
+        <v>5</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>열 · 감염</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>🌡️</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>통증 동반?</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>통증 있음</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>고체온</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>고체온+통증 있음</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>temp</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>체온</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>🌡️</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>체온이 어떤가요?</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>🥶 체온이 낮음</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>통증 동반?</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>저체온</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>🥶</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="2" t="inlineStr"/>
-      <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>저체온</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>저체온</t>
-        </is>
-      </c>
       <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>열 · 감염</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🌡️</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -4570,6 +4967,19 @@
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>의식 · 신경</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -4610,6 +5020,19 @@
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -4650,70 +5073,125 @@
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>hyper</t>
+          <t>glu</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>혈당</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>🍬</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>혈당이 어떤가요?</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>🍬 혈당이 높음</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
           <t>고혈당</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>고혈당</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>🍬</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="2" t="inlineStr"/>
-      <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>고혈당</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>고혈당</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>hypo</t>
+          <t>glu</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>혈당</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>🍬</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>혈당이 어떤가요?</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>💉 혈당이 낮음</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
           <t>저혈당</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>💉</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
-      <c r="E32" s="2" t="inlineStr"/>
-      <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>저혈당</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>저혈당</t>
-        </is>
-      </c>
       <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" t="n">
+        <v>8</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>혈당</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>🍬</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -4754,6 +5232,19 @@
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>의식 · 신경</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -4794,6 +5285,19 @@
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" t="n">
+        <v>2</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>의식 · 신경</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -4822,6 +5326,19 @@
           <t>이상없음 → 바로 의식/낙상</t>
         </is>
       </c>
+      <c r="K35" t="n">
+        <v>10</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>🧩</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4864,6 +5381,19 @@
           <t>⚠️ 초안</t>
         </is>
       </c>
+      <c r="K36" t="n">
+        <v>9</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4906,6 +5436,19 @@
           <t>⚠️ 초안</t>
         </is>
       </c>
+      <c r="K37" t="n">
+        <v>9</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4948,6 +5491,19 @@
           <t>⚠️ 초안</t>
         </is>
       </c>
+      <c r="K38" t="n">
+        <v>9</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4990,6 +5546,19 @@
           <t>⚠️ 초안</t>
         </is>
       </c>
+      <c r="K39" t="n">
+        <v>9</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5032,6 +5601,19 @@
           <t>⚠️ 초안</t>
         </is>
       </c>
+      <c r="K40" t="n">
+        <v>9</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5074,6 +5656,19 @@
           <t>⚠️ 초안</t>
         </is>
       </c>
+      <c r="K41" t="n">
+        <v>9</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5106,6 +5701,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K42" t="n">
+        <v>7</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>배 · 소변 · 눈 · 귀</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>🫃</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5138,6 +5746,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K43" t="n">
+        <v>7</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>배 · 소변 · 눈 · 귀</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>🫃</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5170,6 +5791,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K44" t="n">
+        <v>7</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>배 · 소변 · 눈 · 귀</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>🫃</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5202,6 +5836,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K45" t="n">
+        <v>2</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>의식 · 신경</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5234,6 +5881,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K46" t="n">
+        <v>2</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>의식 · 신경</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5266,6 +5926,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K47" t="n">
+        <v>7</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>배 · 소변 · 눈 · 귀</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>🫃</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5298,6 +5971,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K48" t="n">
+        <v>6</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>다침 · 화상 · 피부</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5330,6 +6016,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>의식 · 신경</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>🧠</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5362,6 +6061,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K50" t="n">
+        <v>10</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>🧩</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5394,6 +6106,19 @@
           <t>⚠️ V4 이관</t>
         </is>
       </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5426,6 +6151,19 @@
           <t>커버리지 보완 260802</t>
         </is>
       </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>숨 · 가슴 · 순환</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>🫀</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5458,6 +6196,19 @@
           <t>커버리지 보완 260802</t>
         </is>
       </c>
+      <c r="K53" t="n">
+        <v>6</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>다침 · 화상 · 피부</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>🤕</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5490,6 +6241,19 @@
           <t>커버리지 보완 260802</t>
         </is>
       </c>
+      <c r="K54" t="n">
+        <v>10</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>🧩</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5532,6 +6296,19 @@
           <t>커버리지 2차 260802</t>
         </is>
       </c>
+      <c r="K55" t="n">
+        <v>9</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5574,6 +6351,19 @@
           <t>커버리지 2차 260802</t>
         </is>
       </c>
+      <c r="K56" t="n">
+        <v>9</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5616,6 +6406,19 @@
           <t>커버리지 2차 260802</t>
         </is>
       </c>
+      <c r="K57" t="n">
+        <v>9</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5658,6 +6461,19 @@
           <t>커버리지 2차 260802</t>
         </is>
       </c>
+      <c r="K58" t="n">
+        <v>9</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5700,6 +6516,19 @@
           <t>커버리지 2차 260802</t>
         </is>
       </c>
+      <c r="K59" t="n">
+        <v>9</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5742,6 +6571,19 @@
           <t>커버리지 2차 260802</t>
         </is>
       </c>
+      <c r="K60" t="n">
+        <v>9</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5784,6 +6626,19 @@
           <t>커버리지 2차 260802</t>
         </is>
       </c>
+      <c r="K61" t="n">
+        <v>9</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>소아 · 임신</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>👶</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5814,6 +6669,19 @@
       <c r="J62" t="inlineStr">
         <is>
           <t>외상 1경로 통합 260802</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>6</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>다침 · 화상 · 피부</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>🤕</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -5382,11 +5382,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5437,11 +5437,11 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -5492,11 +5492,11 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -5547,11 +5547,11 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -5602,11 +5602,11 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -5657,11 +5657,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>임신 · 산과</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>👶</t>
+          <t>🤰</t>
         </is>
       </c>
     </row>
@@ -6356,12 +6356,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>임신 · 산과</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>👶</t>
+          <t>🤰</t>
         </is>
       </c>
     </row>
@@ -6411,12 +6411,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>임신 · 산과</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>👶</t>
+          <t>🤰</t>
         </is>
       </c>
     </row>
@@ -6466,12 +6466,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>임신 · 산과</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>👶</t>
+          <t>🤰</t>
         </is>
       </c>
     </row>
@@ -6517,11 +6517,11 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6572,11 +6572,11 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6627,11 +6627,11 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>소아 · 임신</t>
+          <t>소아 환자</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>동물·사람</t>
+          <t>동물·사람·뱀 (마스터에 뱀 진술문 없음 → 소견으로 기록)</t>
         </is>
       </c>
     </row>
@@ -3378,6 +3378,256 @@
       <c r="I46" t="inlineStr">
         <is>
           <t>체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>물림</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>🐕</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>redness 있음/redness 없음</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>🩺 물린 자리가 붉은지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>발적</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>물림</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>🐕</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>edema 있음/edema 없음</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>🩺 물린 자리가 부었는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>부종</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>물림</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>🐕</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>통증 있음/통증 없음</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>"물린 곳이 아프세요?"</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>쏘임</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>🐝</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>edema 있음/edema 없음</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>🩺 쏘인 자리가 부었는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>부종</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>피부상황</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>쏘임</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>🐝</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>감염위험</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>통증 있음/통증 없음</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>"쏘인 곳이 아프세요?"</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>통증</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3628,6 +3628,564 @@
       <c r="J51" t="inlineStr">
         <is>
           <t>통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>황달</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>황달 있음/황달 없음</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>"피부가 노랗게 보이나요?"</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>성인·소아 공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>황달</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>공막의 황달 있음/공막의 황달 없음</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>🩺 눈 흰자가 노란지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>황달</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>🟡</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>황달이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>칼륨 높음</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>고칼륨혈증</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>혈중 potassium 수치 정상 이상임</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>🩺 혈중 potassium 결과가 정상보다 높나요?</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>칼륨 높음</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>고칼륨혈증</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>혈중 potassium 검사결과 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>2</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>칼륨 높음</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>고칼륨혈증</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>고칼륨식이 섭취 제한하도록 교육함</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>3</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>칼륨 낮음</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>저칼륨혈증</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>혈중 potassium 수치 정상 이하임</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>🩺 혈중 potassium 결과가 정상보다 낮나요?</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>칼륨 낮음</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>저칼륨혈증</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>혈중 potassium 검사결과 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>칼륨 낮음</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>🧪</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>저칼륨혈증</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>고칼륨식이 섭취 격려함</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>나트륨 높음</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>고나트륨혈증</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>혈중 sodium 수치 정상 이상임</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>🩺 혈중 sodium 결과가 정상보다 높나요?</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>나트륨 높음</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>고나트륨혈증</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>혈중 sodium 검사결과 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>나트륨 낮음</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>저나트륨혈증</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>혈중 sodium 수치 정상 이하임</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>🩺 혈중 sodium 결과가 정상보다 낮나요?</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>5</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>나트륨 낮음</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>저나트륨혈증</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>혈중 sodium 검사결과 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>나트륨 낮음</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>저나트륨혈증</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>sodium 섭취를 늘리도록 교육함</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>칩스 확인 필요</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3650,7 +3650,6 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
           <t>A&amp;E</t>
@@ -3696,7 +3695,6 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
           <t>A&amp;E</t>
@@ -3737,7 +3735,6 @@
           <t>🟡</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
           <t>P&amp;E</t>
@@ -3801,11 +3798,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>칼륨 높음</t>
+          <t>칼륨 낮음</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3815,17 +3812,27 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>고칼륨혈증</t>
+          <t>저칼륨혈증</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>혈중 potassium 검사결과 확인함</t>
+          <t>혈중 potassium 수치 정상 이하임</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>🩺 혈중 potassium 결과가 정상보다 낮나요?</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
     </row>
@@ -3836,36 +3843,41 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>칼륨 높음</t>
+          <t>나트륨 높음</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>🧪</t>
+          <t>🧂</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>고칼륨혈증</t>
+          <t>고나트륨혈증</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 제한하도록 교육함</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>칩스 확인 필요</t>
+          <t>혈중 sodium 수치 정상 이상임</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>🩺 혈중 sodium 결과가 정상보다 높나요?</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
     </row>
@@ -3876,21 +3888,21 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>칼륨 낮음</t>
+          <t>나트륨 낮음</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>🧪</t>
+          <t>🧂</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>저칼륨혈증</t>
+          <t>저나트륨혈증</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3900,12 +3912,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>혈중 potassium 수치 정상 이하임</t>
+          <t>혈중 sodium 수치 정상 이하임</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>🩺 혈중 potassium 결과가 정상보다 낮나요?</t>
+          <t>🩺 혈중 sodium 결과가 정상보다 낮나요?</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3921,11 +3933,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>칼륨 낮음</t>
+          <t>칼륨 높음</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3935,7 +3947,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>저칼륨혈증</t>
+          <t>고칼륨혈증</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3945,7 +3957,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>혈중 potassium 검사결과 확인함</t>
+          <t>심전도 변화를 확인함</t>
         </is>
       </c>
     </row>
@@ -3956,11 +3968,11 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>칼륨 낮음</t>
+          <t>칼륨 높음</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3970,7 +3982,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>저칼륨혈증</t>
+          <t>고칼륨혈증</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3980,12 +3992,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>고칼륨식이 섭취 격려함</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>칩스 확인 필요</t>
+          <t>불편감이 있는지 확인함</t>
         </is>
       </c>
     </row>
@@ -3996,41 +4003,31 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>나트륨 높음</t>
+          <t>칼륨 낮음</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>🧂</t>
+          <t>🧪</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>고나트륨혈증</t>
+          <t>저칼륨혈증</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이상임</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>🩺 혈중 sodium 결과가 정상보다 높나요?</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>심전도 변화를 확인함</t>
         </is>
       </c>
     </row>
@@ -4041,21 +4038,21 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>나트륨 높음</t>
+          <t>칼륨 낮음</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>🧂</t>
+          <t>🧪</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>고나트륨혈증</t>
+          <t>저칼륨혈증</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4065,7 +4062,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
+          <t>불편감이 있는지 확인함</t>
         </is>
       </c>
     </row>
@@ -4076,11 +4073,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>나트륨 낮음</t>
+          <t>나트륨 높음</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4090,27 +4087,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>저나트륨혈증</t>
+          <t>고나트륨혈증</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>혈중 sodium 수치 정상 이하임</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>🩺 혈중 sodium 결과가 정상보다 낮나요?</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>전해질 불균형 증상이 있는지 확인함</t>
         </is>
       </c>
     </row>
@@ -4121,11 +4108,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>나트륨 낮음</t>
+          <t>나트륨 높음</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4135,7 +4122,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>저나트륨혈증</t>
+          <t>고나트륨혈증</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4145,7 +4132,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>혈중 sodium 검사결과 확인함</t>
+          <t>의식수준 변화가 있는지 관찰함</t>
         </is>
       </c>
     </row>
@@ -4180,12 +4167,42 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>sodium 섭취를 늘리도록 교육함</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>칩스 확인 필요</t>
+          <t>전해질 불균형 증상이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>5</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>나트륨 낮음</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>🧂</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>저나트륨혈증</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>의식수준 변화가 있는지 관찰함</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4203,6 +4203,126 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>의식수준 변화가 있는지 관찰함</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>6</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>💓</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>부정맥 있음/부정맥 없음</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>🩺 심전도에 부정맥이 보이나요?</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>리듬 종류는 추후 추가 예정</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>6</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>💓</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>부정맥이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>6</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>💓</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>부정맥으로 인한 증상이 있는지 확인함</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -7641,7 +7641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L716"/>
+  <dimension ref="A1:L720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -35522,6 +35522,146 @@
       <c r="K716" t="inlineStr">
         <is>
           <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D717" t="n">
+        <v>8</v>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>신경학 경로는 무조건 근력 평가</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>중독</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D718" t="n">
+        <v>5</v>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>신경학 경로는 무조건 근력 평가</t>
+        </is>
+      </c>
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>중독위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>의식섬망</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D719" t="n">
+        <v>6</v>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>신경학 경로는 무조건 근력 평가</t>
+        </is>
+      </c>
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>조직관류저하:뇌</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Seizure</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>지금 Seizure 할 때</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D720" t="n">
+        <v>5</v>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>신경학 경로는 무조건 근력 평가</t>
+        </is>
+      </c>
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -2007,17 +2007,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>복부 압통 있음/복부 압통 없음</t>
+          <t>복부 통증 있음/복부 통증 없음</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>🩺 배를 눌렀을 때 아파하는지 확인하세요</t>
+          <t>"배가 아프세요?"</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>토글</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>복부 압통 → 복부 통증으로 통일</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4328,6 +4328,256 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>부정맥으로 인한 증상이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>7</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>부종 · 체중 증가</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>체액과다</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>edema 있음/edema 없음</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>🩺 부어 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>신부전·심부전 공통</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>7</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>부종 · 체중 증가</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>체액과다</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>체중 증가함/체중 감소함/체중 변화 없음</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>"평소보다 몸무게가 늘었나요?"</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>선택</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>7</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>부종 · 체중 증가</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>체액과다</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>소변량 감소함</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>🩺 소변량이 줄었나요?</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>마스터에 「변화 없음」 없음 → 줄었을 때만</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>7</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>부종 · 체중 증가</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>체액과다</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>수분섭취배설량 측정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>7</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>부종 · 체중 증가</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>체액과다</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>체중 측정함</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>7</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>부종 · 체중 증가</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>💧</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>체액과다</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>말초 부종 확인함</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -7896,7 +7896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L720"/>
+  <dimension ref="A1:L724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -35915,6 +35915,186 @@
         </is>
       </c>
       <c r="J720" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>통증</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>복부통증</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D721" t="n">
+        <v>7</v>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>복부 팽만 있음/복부 팽만 없음</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>🩺 배가 불러 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>장폐색 소견</t>
+        </is>
+      </c>
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>급성통증</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>소화기</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>5</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>복부 팽만 있음/복부 팽만 없음</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>🩺 배가 불러 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>장폐색 소견</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>체액부족위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D723" t="n">
+        <v>10</v>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>창백함</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>🩺 얼굴이 창백한지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>실신 소견 · 마스터에 음성 없음 → 체크</t>
+        </is>
+      </c>
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>어지럼</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="D724" t="n">
+        <v>11</v>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>발한 있음/발한 없음</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>🩺 식은땀이 나는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>실신 소견</t>
+        </is>
+      </c>
+      <c r="J724" t="inlineStr">
         <is>
           <t>신체손상위험</t>
         </is>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4578,6 +4578,251 @@
       <c r="G75" t="inlineStr">
         <is>
           <t>말초 부종 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>8</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>쇼크 의심</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>조직관류저하</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>혈압 저하됨</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>🩺 혈압이 떨어졌나요?</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>마스터에 「혈압 정상」 없음 → 떨어졌을 때만</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>8</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>쇼크 의심</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>조직관류저하</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>맥박수 증가됨</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>🩺 맥박이 빨라졌나요?</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>8</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>쇼크 의심</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>조직관류저하</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>A&amp;E</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>소변량 감소함</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>🩺 소변량이 줄었나요?</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>체크</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>8</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>쇼크 의심</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>조직관류저하</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>shock 증상(차고 축축한 피부, 혈압하강, 빈맥, 호흡수 증가, 혼수, 소변량 감소)이 있는지 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>8</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>쇼크 의심</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>조직관류저하</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>말초 관류를 확인함</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>추가상태</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>8</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>쇼크 의심</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>🩸</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>조직관류저하</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>활력징후 측정함</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -28981,7 +28981,7 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>조직관류저하</t>
         </is>
       </c>
     </row>
@@ -29071,7 +29071,7 @@
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>조직관류저하</t>
         </is>
       </c>
     </row>
@@ -29236,17 +29236,17 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>조직관류저하</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
         <is>
-          <t>⚠️ V4 이관</t>
+          <t>저혈압은 마스터 간호진단에 없음 → 조직관류저하</t>
         </is>
       </c>
       <c r="J541" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>조직관류저하</t>
         </is>
       </c>
     </row>
@@ -29281,7 +29281,7 @@
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>조직관류저하</t>
         </is>
       </c>
     </row>
@@ -29316,7 +29316,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>조직관류저하</t>
         </is>
       </c>
     </row>
@@ -29351,7 +29351,7 @@
       </c>
       <c r="J544" t="inlineStr">
         <is>
-          <t>저혈압</t>
+          <t>조직관류저하</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -26851,7 +26851,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>감각지각장애:시각,청각,촉각,미각,후각,운동감각</t>
         </is>
       </c>
     </row>
@@ -26896,7 +26896,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>감각지각장애:시각,청각,촉각,미각,후각,운동감각</t>
         </is>
       </c>
     </row>
@@ -26941,7 +26941,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>감각지각장애:시각,청각,촉각,미각,후각,운동감각</t>
         </is>
       </c>
     </row>
@@ -27101,17 +27101,17 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>감각지각장애:시각,청각,촉각,미각,후각,운동감각</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>★ 칩스확정 — 마스터는 통합형(시각,청각,촉각…)</t>
+          <t>마스터 원문 그대로 (시각만 떼어 쓰는 이름이 아님)</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>감각지각장애:시각,청각,촉각,미각,후각,운동감각</t>
         </is>
       </c>
     </row>
@@ -27146,7 +27146,7 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>감각지각장애:시각,청각,촉각,미각,후각,운동감각</t>
         </is>
       </c>
     </row>
@@ -27181,7 +27181,7 @@
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>감각지각장애 : 시각</t>
+          <t>감각지각장애:시각,청각,촉각,미각,후각,운동감각</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -8141,7 +8141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L721"/>
+  <dimension ref="A1:L722"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -23382,7 +23382,7 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -23452,7 +23452,7 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -36207,6 +36207,41 @@
       <c r="J721" t="inlineStr">
         <is>
           <t>비효율적수유</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>소아</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>소아-경련</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>P&amp;E</t>
+        </is>
+      </c>
+      <c r="D722" t="n">
+        <v>1</v>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>체온 측정함</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>소아 경련은 열성경련이 흔하다</t>
+        </is>
+      </c>
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>뇌손상 징후</t>
+          <t>두부·머리 외상·뇌손상 징후</t>
         </is>
       </c>
     </row>
@@ -1610,6 +1610,11 @@
           <t>신경학적 증상이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>두부·머리 외상·뇌손상 징후</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1655,6 +1660,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>안면·얼굴 열상</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1690,6 +1700,11 @@
           <t>상처 dressing 함</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>안면·얼굴 열상</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1735,6 +1750,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>경추·목·척추</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1780,6 +1800,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>경추·목·척추</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1815,6 +1840,11 @@
           <t>sensory motor circulation 확인함</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>경추·목·척추</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1860,6 +1890,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>흉부·갈비뼈·늑골</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1905,6 +1940,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>흉부·갈비뼈·늑골</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1940,6 +1980,11 @@
           <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>흉부·갈비뼈·늑골</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1975,6 +2020,11 @@
           <t>산소포화도 monitor 함</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>흉부·갈비뼈·늑골</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2022,7 +2072,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>복부 압통 → 복부 통증으로 통일</t>
+          <t>복부·배</t>
         </is>
       </c>
     </row>
@@ -2070,6 +2120,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>사지·상지·하지·골절</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2115,6 +2170,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>사지·상지·하지·골절</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2150,6 +2210,11 @@
           <t>sensory motor circulation 확인함</t>
         </is>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>사지·상지·하지·골절</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2197,7 +2262,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>동물·사람·뱀 (마스터에 뱀 진술문 없음 → 소견으로 기록)</t>
+          <t>개·고양이·동물·사람·뱀·교상 (마스터에 뱀 진술문 없음 → 소견으로 기록)</t>
         </is>
       </c>
     </row>
@@ -2235,6 +2300,11 @@
           <t>감염 증상이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>개·고양이·동물·사람·뱀·교상 (마스터에 뱀 진술문 없음 → 소견으로 기록)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2282,7 +2352,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>벌·곤충</t>
+          <t>벌·말벌·곤충·벌레·쏘였다</t>
         </is>
       </c>
     </row>
@@ -2320,6 +2390,11 @@
           <t>쏘인부위 침 제거함</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>벌·말벌·곤충·벌레·쏘였다</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2365,6 +2440,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>찢어짐·베임·칼·유리</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2400,6 +2480,11 @@
           <t>상처 dressing 함</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>찢어짐·베임·칼·유리</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2445,6 +2530,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>두드러기·알레르기·가려움</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2490,6 +2580,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>연조직염·빨갛게 부음</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2535,6 +2630,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>연조직염·빨갛게 부음</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2582,7 +2682,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>출혈경향 의심</t>
+          <t>타박·시퍼렇게·출혈경향 의심</t>
         </is>
       </c>
     </row>
@@ -2630,6 +2730,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>박힘·가시·유리·못</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2677,7 +2782,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>더운 환경 노출</t>
+          <t>더위·일사병·온열질환·더운 환경 노출</t>
         </is>
       </c>
     </row>
@@ -2715,6 +2820,11 @@
           <t>미온수 목욕 시행함</t>
         </is>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>더위·일사병·온열질환·더운 환경 노출</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2750,6 +2860,11 @@
           <t>덥거나 추운 환경에 노출되지 않도록 함</t>
         </is>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>더위·일사병·온열질환·더운 환경 노출</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2797,7 +2912,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>일사병·일광화상</t>
+          <t>일광화상·햇빛·일사병</t>
         </is>
       </c>
     </row>
@@ -2845,6 +2960,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>추위·언 손발·frostbite</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2880,6 +3000,11 @@
           <t>동상입지 않도록 교육함</t>
         </is>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>추위·언 손발·frostbite</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2927,7 +3052,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>물에 빠짐</t>
+          <t>물에 빠짐·익사·수영</t>
         </is>
       </c>
     </row>
@@ -2965,6 +3090,11 @@
           <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>물에 빠짐·익사·수영</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3000,6 +3130,11 @@
           <t>산소포화도 monitor 함</t>
         </is>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>물에 빠짐·익사·수영</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3035,6 +3170,11 @@
           <t>덥거나 추운 환경에 노출되지 않도록 함</t>
         </is>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>저체온·추위</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3080,6 +3220,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>산·알칼리·세제·약품</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3115,6 +3260,11 @@
           <t>상처 관찰함</t>
         </is>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>산·알칼리·세제·약품</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3162,7 +3312,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>입구·출구 상처</t>
+          <t>감전·전기·입구 출구 상처</t>
         </is>
       </c>
     </row>
@@ -3200,6 +3350,11 @@
           <t>상처 dressing 함</t>
         </is>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>감전·전기·입구 출구 상처</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3245,6 +3400,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>가스·연기·매연·흡입</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3280,6 +3440,11 @@
           <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>가스·연기·매연·흡입</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3315,6 +3480,11 @@
           <t>산소포화도 monitor 함</t>
         </is>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>가스·연기·매연·흡입</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3340,6 +3510,11 @@
           <t>중독위험</t>
         </is>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>음독·약 먹음·자살시도·중독</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3385,6 +3560,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>닿음·묻음</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3432,7 +3612,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>발적</t>
+          <t>개·고양이·동물·사람·뱀·교상 (마스터에 뱀 진술문 없음 → 소견으로 기록)</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3662,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>부종</t>
+          <t>개·고양이·동물·사람·뱀·교상 (마스터에 뱀 진술문 없음 → 소견으로 기록)</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3712,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>통증</t>
+          <t>개·고양이·동물·사람·뱀·교상 (마스터에 뱀 진술문 없음 → 소견으로 기록)</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3762,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>부종</t>
+          <t>벌·말벌·곤충·벌레·쏘였다</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3812,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>통증</t>
+          <t>벌·말벌·곤충·벌레·쏘였다</t>
         </is>
       </c>
     </row>
@@ -3677,7 +3857,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>성인·소아 공통</t>
+          <t>노랗다·눈 노랑·빌리루빈·성인 소아 공통</t>
         </is>
       </c>
     </row>
@@ -3720,6 +3900,11 @@
           <t>토글</t>
         </is>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>노랗다·눈 노랑·빌리루빈·성인 소아 공통</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3750,6 +3935,11 @@
           <t>황달이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>노랗다·눈 노랑·빌리루빈·성인 소아 공통</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3795,6 +3985,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>고칼륨·potassium·K 높음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3840,6 +4035,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>저칼륨·potassium·K 낮음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3885,6 +4085,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>고나트륨·sodium·Na 높음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3930,6 +4135,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>저나트륨·sodium·Na 낮음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3965,6 +4175,11 @@
           <t>심전도 변화를 확인함</t>
         </is>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>고칼륨·potassium·K 높음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4000,6 +4215,11 @@
           <t>불편감이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>고칼륨·potassium·K 높음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4035,6 +4255,11 @@
           <t>심전도 변화를 확인함</t>
         </is>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>저칼륨·potassium·K 낮음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4070,6 +4295,11 @@
           <t>불편감이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>저칼륨·potassium·K 낮음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4105,6 +4335,11 @@
           <t>전해질 불균형 증상이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>고나트륨·sodium·Na 높음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4140,6 +4375,11 @@
           <t>의식수준 변화가 있는지 관찰함</t>
         </is>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>고나트륨·sodium·Na 높음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4175,6 +4415,11 @@
           <t>전해질 불균형 증상이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>저나트륨·sodium·Na 낮음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4210,6 +4455,11 @@
           <t>의식수준 변화가 있는지 관찰함</t>
         </is>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>저나트륨·sodium·Na 낮음·전해질</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4257,7 +4507,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>리듬 종류는 추후 추가 예정</t>
+          <t>Af·afib·심전도·리듬·맥박 이상</t>
         </is>
       </c>
     </row>
@@ -4295,6 +4545,11 @@
           <t>부정맥이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Af·afib·심전도·리듬·맥박 이상</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4330,6 +4585,11 @@
           <t>부정맥으로 인한 증상이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Af·afib·심전도·리듬·맥박 이상</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4377,7 +4637,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>신부전·심부전 공통</t>
+          <t>붓다·체중·신부전·심부전·투석</t>
         </is>
       </c>
     </row>
@@ -4425,6 +4685,11 @@
           <t>선택</t>
         </is>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>붓다·체중·신부전·심부전·투석</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4472,7 +4737,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>마스터에 「변화 없음」 없음 → 줄었을 때만</t>
+          <t>붓다·체중·신부전·심부전·투석</t>
         </is>
       </c>
     </row>
@@ -4510,6 +4775,11 @@
           <t>수분섭취배설량 측정함</t>
         </is>
       </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>붓다·체중·신부전·심부전·투석</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4545,6 +4815,11 @@
           <t>체중 측정함</t>
         </is>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>붓다·체중·신부전·심부전·투석</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4580,6 +4855,11 @@
           <t>말초 부종 확인함</t>
         </is>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>붓다·체중·신부전·심부전·투석</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4627,7 +4907,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>마스터에 「혈압 정상」 없음 → 떨어졌을 때만</t>
+          <t>쇼크·혈압 떨어짐·저혈압</t>
         </is>
       </c>
     </row>
@@ -4675,6 +4955,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>쇼크·혈압 떨어짐·저혈압</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4720,6 +5005,11 @@
           <t>체크</t>
         </is>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>쇼크·혈압 떨어짐·저혈압</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4755,6 +5045,11 @@
           <t>shock 증상(차고 축축한 피부, 혈압하강, 빈맥, 호흡수 증가, 혼수, 소변량 감소)이 있는지 확인함</t>
         </is>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>쇼크·혈압 떨어짐·저혈압</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4790,6 +5085,11 @@
           <t>말초 관류를 확인함</t>
         </is>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>쇼크·혈압 떨어짐·저혈압</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4823,6 +5123,11 @@
       <c r="G81" t="inlineStr">
         <is>
           <t>활력징후 측정함</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>쇼크·혈압 떨어짐·저혈압</t>
         </is>
       </c>
     </row>

--- a/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
+++ b/3_서비스/NFH간호기록/data/간호기록_원본_260623.xlsx
@@ -8446,7 +8446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L722"/>
+  <dimension ref="A1:L721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -34318,25 +34318,15 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D666" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>수유 후 만족감 있음</t>
-        </is>
-      </c>
-      <c r="F666" t="inlineStr">
-        <is>
-          <t>🩺 먹고 나서 편안해 보이는지 관찰하세요</t>
-        </is>
-      </c>
-      <c r="G666" t="inlineStr">
-        <is>
-          <t>체크</t>
+          <t>비효율적수유</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -34363,7 +34353,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D667" t="n">
@@ -34371,7 +34361,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>비효율적수유</t>
+          <t>수유 중 아기의 피로 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -34402,11 +34392,11 @@
         </is>
       </c>
       <c r="D668" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>수유 중 아기의 피로 증상이 있는지 확인함</t>
+          <t>수유 방법에 대해 교육함</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -34428,20 +34418,30 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>소아-수유곤란</t>
+          <t>소아-무호흡</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D669" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>수유 방법에 대해 교육함</t>
+          <t>무호흡 있음/없음</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>"숨을 멈춘 적이 있나요?"</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>비효율적수유</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
     </row>
@@ -34472,16 +34472,16 @@
         </is>
       </c>
       <c r="D670" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>무호흡 있음/없음</t>
+          <t>청색증 있음/없음</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>"숨을 멈춘 적이 있나요?"</t>
+          <t>"입술이나 얼굴이 파래졌나요?"</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -34517,16 +34517,16 @@
         </is>
       </c>
       <c r="D671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>청색증 있음/없음</t>
+          <t>apnea alarm 울림/apnea alarm 울리지 않음</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>"입술이나 얼굴이 파래졌나요?"</t>
+          <t>🩺 무호흡 알람이 울렸는지 확인하세요</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -34558,25 +34558,15 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D672" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>apnea alarm 울림/apnea alarm 울리지 않음</t>
-        </is>
-      </c>
-      <c r="F672" t="inlineStr">
-        <is>
-          <t>🩺 무호흡 알람이 울렸는지 확인하세요</t>
-        </is>
-      </c>
-      <c r="G672" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>비효율적호흡양상</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -34603,7 +34593,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D673" t="n">
@@ -34611,7 +34601,7 @@
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>호흡곤란이 있는지 확인함</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -34642,11 +34632,11 @@
         </is>
       </c>
       <c r="D674" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>호흡곤란이 있는지 확인함</t>
+          <t>산소포화도 monitor 함</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -34677,11 +34667,11 @@
         </is>
       </c>
       <c r="D675" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>산소포화도 monitor 함</t>
+          <t>무호흡 monitor 시작함</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -34712,11 +34702,11 @@
         </is>
       </c>
       <c r="D676" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>무호흡 monitor 시작함</t>
+          <t>무호흡 지속 시간 측정함</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -34733,35 +34723,50 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>소아</t>
+          <t>외상</t>
         </is>
       </c>
       <c r="B677" t="inlineStr">
         <is>
-          <t>소아-무호흡</t>
+          <t>외상</t>
         </is>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D677" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>무호흡 지속 시간 측정함</t>
+          <t>신체손상 있음</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>🩺 다친 곳이 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>커버리지 2차 260802</t>
+          <t>외상 1경로 통합 260802</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>비효율적호흡양상</t>
+          <t>신체손상위험</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>외상부위</t>
         </is>
       </c>
     </row>
@@ -34782,21 +34787,21 @@
         </is>
       </c>
       <c r="D678" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>신체손상 있음</t>
+          <t>출혈 있음/없음</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>🩺 다친 곳이 있는지 확인하세요</t>
+          <t>"피가 나나요?"</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -34806,7 +34811,7 @@
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="L678" t="inlineStr">
@@ -34832,16 +34837,16 @@
         </is>
       </c>
       <c r="D679" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>출혈 있음/없음</t>
+          <t>찰과상 있음/없음</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>"피가 나나요?"</t>
+          <t>🩺 긁힌 상처를 확인하세요</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
@@ -34856,7 +34861,7 @@
       </c>
       <c r="J679" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="L679" t="inlineStr">
@@ -34882,16 +34887,16 @@
         </is>
       </c>
       <c r="D680" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>찰과상 있음/없음</t>
+          <t>edema 있음/없음</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>🩺 긁힌 상처를 확인하세요</t>
+          <t>🩺 다친 곳이 부었는지 확인하세요</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
@@ -34932,16 +34937,16 @@
         </is>
       </c>
       <c r="D681" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>edema 있음/없음</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>🩺 다친 곳이 부었는지 확인하세요</t>
+          <t>"다친 곳이 아프세요?"</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
@@ -34956,7 +34961,7 @@
       </c>
       <c r="J681" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="L681" t="inlineStr">
@@ -34978,7 +34983,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D682" t="n">
@@ -34986,17 +34991,7 @@
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F682" t="inlineStr">
-        <is>
-          <t>"다친 곳이 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G682" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>신체손상위험</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -35006,12 +35001,7 @@
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-      <c r="L682" t="inlineStr">
-        <is>
-          <t>외상부위</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -35028,7 +35018,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D683" t="n">
@@ -35036,7 +35026,7 @@
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>상처 관찰함</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -35067,11 +35057,11 @@
         </is>
       </c>
       <c r="D684" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>상처 관찰함</t>
+          <t>안전간호를 제공함</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -35098,7 +35088,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D685" t="n">
@@ -35106,7 +35096,7 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>안전간호를 제공함</t>
+          <t>출혈</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -35116,7 +35106,7 @@
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>출혈</t>
         </is>
       </c>
     </row>
@@ -35133,15 +35123,15 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>출혈 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -35172,11 +35162,11 @@
         </is>
       </c>
       <c r="D687" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>출혈 증상이 있는지 확인함</t>
+          <t>출혈양상 확인함</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -35203,15 +35193,15 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D688" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>출혈양상 확인함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -35221,7 +35211,7 @@
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>출혈</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -35238,15 +35228,15 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D689" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -35277,11 +35267,11 @@
         </is>
       </c>
       <c r="D690" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -35312,11 +35302,11 @@
         </is>
       </c>
       <c r="D691" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -35333,35 +35323,50 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>외상</t>
+          <t>피부</t>
         </is>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D692" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>피부 손상 있음</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>🩺 피부가 상했는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>체크</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>외상 1경로 통합 260802</t>
+          <t>피부 확장 260802</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>피부손상</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr">
+        <is>
+          <t>피부상황</t>
         </is>
       </c>
     </row>
@@ -35382,21 +35387,21 @@
         </is>
       </c>
       <c r="D693" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>피부 손상 있음</t>
+          <t>출혈 있음/없음</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>🩺 피부가 상했는지 확인하세요</t>
+          <t>"피가 나나요?"</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
@@ -35432,16 +35437,16 @@
         </is>
       </c>
       <c r="D694" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>출혈 있음/없음</t>
+          <t>통증 있음/없음</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>"피가 나나요?"</t>
+          <t>"그 부위가 아프세요?"</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
@@ -35456,7 +35461,7 @@
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>피부손상</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="L694" t="inlineStr">
@@ -35478,25 +35483,15 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D695" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
-        </is>
-      </c>
-      <c r="F695" t="inlineStr">
-        <is>
-          <t>"그 부위가 아프세요?"</t>
-        </is>
-      </c>
-      <c r="G695" t="inlineStr">
-        <is>
-          <t>토글</t>
+          <t>감염위험</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -35506,12 +35501,7 @@
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>급성통증</t>
-        </is>
-      </c>
-      <c r="L695" t="inlineStr">
-        <is>
-          <t>피부상황</t>
+          <t>감염위험</t>
         </is>
       </c>
     </row>
@@ -35528,15 +35518,15 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D696" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>피부 상태를 관찰함</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -35563,7 +35553,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D697" t="n">
@@ -35571,7 +35561,7 @@
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>피부 상태를 관찰함</t>
+          <t>급성통증</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -35581,7 +35571,7 @@
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>감염위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
@@ -35598,15 +35588,15 @@
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D698" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>통증을 인정해줌</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -35637,11 +35627,11 @@
         </is>
       </c>
       <c r="D699" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>통증을 인정해줌</t>
+          <t>통증 양상을 확인함</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -35672,11 +35662,11 @@
         </is>
       </c>
       <c r="D700" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>통증 양상을 확인함</t>
+          <t>통증을 관찰하기로 함</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -35693,30 +35683,40 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>피부</t>
+          <t>이비인후</t>
         </is>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D701" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>통증을 관찰하기로 함</t>
+          <t>통증 있음/없음</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>"아프세요?"</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>피부 확장 260802</t>
+          <t>통증 문항 260802</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
@@ -35728,12 +35728,12 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>심근경색 의심</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>이비인후</t>
+          <t>심근경색의심+통증없음</t>
         </is>
       </c>
       <c r="C702" t="inlineStr">
@@ -35742,16 +35742,16 @@
         </is>
       </c>
       <c r="D702" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>통증 있음/없음</t>
+          <t>부정맥 있음/부정맥 없음</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>"아프세요?"</t>
+          <t>🩺 심전도에 부정맥이 보이나요?</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
@@ -35761,12 +35761,17 @@
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>통증 문항 260802</t>
+          <t>심전도 판독 결과</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>부정맥</t>
+        </is>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
         </is>
       </c>
     </row>
@@ -35783,30 +35788,15 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D703" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>부정맥 있음/부정맥 없음</t>
-        </is>
-      </c>
-      <c r="F703" t="inlineStr">
-        <is>
-          <t>🩺 심전도에 부정맥이 보이나요?</t>
-        </is>
-      </c>
-      <c r="G703" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
-      <c r="I703" t="inlineStr">
-        <is>
-          <t>심전도 판독 결과</t>
+          <t>부정맥</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
@@ -35833,15 +35823,15 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D704" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>부정맥</t>
+          <t>부정맥이 있는지 확인함</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
@@ -35872,11 +35862,11 @@
         </is>
       </c>
       <c r="D705" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>부정맥이 있는지 확인함</t>
+          <t>부정맥으로 인한 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
@@ -35907,11 +35897,11 @@
         </is>
       </c>
       <c r="D706" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>부정맥으로 인한 증상이 있는지 확인함</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
@@ -35933,20 +35923,35 @@
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>심근경색의심+통증없음</t>
+          <t>심근경색의심+통증있음</t>
         </is>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D707" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>부정맥 있음/부정맥 없음</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>🩺 심전도에 부정맥이 보이나요?</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>토글</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>심전도 판독 결과</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
@@ -35973,30 +35978,15 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D708" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>부정맥 있음/부정맥 없음</t>
-        </is>
-      </c>
-      <c r="F708" t="inlineStr">
-        <is>
-          <t>🩺 심전도에 부정맥이 보이나요?</t>
-        </is>
-      </c>
-      <c r="G708" t="inlineStr">
-        <is>
-          <t>토글</t>
-        </is>
-      </c>
-      <c r="I708" t="inlineStr">
-        <is>
-          <t>심전도 판독 결과</t>
+          <t>부정맥</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
@@ -36023,15 +36013,15 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D709" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E709" t="inlineStr">
         <is>
-          <t>부정맥</t>
+          <t>부정맥이 있는지 확인함</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
@@ -36062,11 +36052,11 @@
         </is>
       </c>
       <c r="D710" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>부정맥이 있는지 확인함</t>
+          <t>부정맥으로 인한 증상이 있는지 확인함</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
@@ -36097,11 +36087,11 @@
         </is>
       </c>
       <c r="D711" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>부정맥으로 인한 증상이 있는지 확인함</t>
+          <t>EKG monitor 시작함</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
@@ -36118,12 +36108,12 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>심근경색 의심</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>심근경색의심+통증있음</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C712" t="inlineStr">
@@ -36136,29 +36126,29 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>EKG monitor 시작함</t>
+          <t>사지 근력 평가함</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>신경학 경로는 무조건 근력 평가</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
         <is>
-          <t>부정맥</t>
-        </is>
-      </c>
-      <c r="K712" t="inlineStr">
-        <is>
-          <t>부정맥 진단 신설 — 칩스 확인 필요</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C713" t="inlineStr">
@@ -36167,7 +36157,7 @@
         </is>
       </c>
       <c r="D713" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E713" t="inlineStr">
         <is>
@@ -36181,19 +36171,19 @@
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>중독위험</t>
         </is>
       </c>
     </row>
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>의식섬망</t>
         </is>
       </c>
       <c r="C714" t="inlineStr">
@@ -36202,7 +36192,7 @@
         </is>
       </c>
       <c r="D714" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E714" t="inlineStr">
         <is>
@@ -36216,19 +36206,19 @@
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>중독위험</t>
+          <t>조직관류저하:뇌</t>
         </is>
       </c>
     </row>
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>Seizure</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>의식섬망</t>
+          <t>지금 Seizure 할 때</t>
         </is>
       </c>
       <c r="C715" t="inlineStr">
@@ -36237,7 +36227,7 @@
         </is>
       </c>
       <c r="D715" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E715" t="inlineStr">
         <is>
@@ -36251,54 +36241,64 @@
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>조직관류저하:뇌</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>Seizure</t>
+          <t>통증</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>지금 Seizure 할 때</t>
+          <t>복부통증</t>
         </is>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>P&amp;E</t>
+          <t>A&amp;E</t>
         </is>
       </c>
       <c r="D716" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>사지 근력 평가함</t>
+          <t>복부 팽만 있음/복부 팽만 없음</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>🩺 배가 불러 있는지 확인하세요</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>토글</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>신경학 경로는 무조건 근력 평가</t>
+          <t>장폐색 소견</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>급성통증</t>
         </is>
       </c>
     </row>
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>통증</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>복부통증</t>
+          <t>소화기</t>
         </is>
       </c>
       <c r="C717" t="inlineStr">
@@ -36307,7 +36307,7 @@
         </is>
       </c>
       <c r="D717" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E717" t="inlineStr">
         <is>
@@ -36331,19 +36331,19 @@
       </c>
       <c r="J717" t="inlineStr">
         <is>
-          <t>급성통증</t>
+          <t>체액부족위험</t>
         </is>
       </c>
     </row>
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>소화기</t>
+          <t>어지럼</t>
         </is>
       </c>
       <c r="C718" t="inlineStr">
@@ -36352,31 +36352,31 @@
         </is>
       </c>
       <c r="D718" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>복부 팽만 있음/복부 팽만 없음</t>
+          <t>창백함</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>🩺 배가 불러 있는지 확인하세요</t>
+          <t>🩺 얼굴이 창백한지 확인하세요</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>체크</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>장폐색 소견</t>
+          <t>실신 소견 · 마스터에 음성 없음 → 체크</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>체액부족위험</t>
+          <t>신체손상위험</t>
         </is>
       </c>
     </row>
@@ -36397,26 +36397,26 @@
         </is>
       </c>
       <c r="D719" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E719" t="inlineStr">
         <is>
-          <t>창백함</t>
+          <t>발한 있음/발한 없음</t>
         </is>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>🩺 얼굴이 창백한지 확인하세요</t>
+          <t>🩺 식은땀이 나는지 확인하세요</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>체크</t>
+          <t>토글</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>실신 소견 · 마스터에 음성 없음 → 체크</t>
+          <t>실신 소견</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
@@ -36428,12 +36428,12 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>소아</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>어지럼</t>
+          <t>소아-황달</t>
         </is>
       </c>
       <c r="C720" t="inlineStr">
@@ -36442,31 +36442,31 @@
         </is>
       </c>
       <c r="D720" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>발한 있음/발한 없음</t>
+          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>🩺 식은땀이 나는지 확인하세요</t>
+          <t>🩺 아이 반응 정도를 확인하세요</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>토글</t>
+          <t>선택</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>실신 소견</t>
+          <t>축 처짐과 통합 — 관찰이 더 정확하다</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>신체손상위험</t>
+          <t>비효율적수유</t>
         </is>
       </c>
     </row>
@@ -36478,73 +36478,28 @@
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>소아-황달</t>
+          <t>소아-경련</t>
         </is>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>A&amp;E</t>
+          <t>P&amp;E</t>
         </is>
       </c>
       <c r="D721" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>울음소리 좋음/자극 주면 울음/반응 없음</t>
-        </is>
-      </c>
-      <c r="F721" t="inlineStr">
-        <is>
-          <t>🩺 아이 반응 정도를 확인하세요</t>
-        </is>
-      </c>
-      <c r="G721" t="inlineStr">
-        <is>
-          <t>선택</t>
+          <t>체온 측정함</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>축 처짐과 통합 — 관찰이 더 정확하다</t>
+          <t>소아 경련은 열성경련이 흔하다</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
-        <is>
-          <t>비효율적수유</t>
-        </is>
-      </c>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr">
-        <is>
-          <t>소아</t>
-        </is>
-      </c>
-      <c r="B722" t="inlineStr">
-        <is>
-          <t>소아-경련</t>
-        </is>
-      </c>
-      <c r="C722" t="inlineStr">
-        <is>
-          <t>P&amp;E</t>
-        </is>
-      </c>
-      <c r="D722" t="n">
-        <v>1</v>
-      </c>
-      <c r="E722" t="inlineStr">
-        <is>
-          <t>체온 측정함</t>
-        </is>
-      </c>
-      <c r="I722" t="inlineStr">
-        <is>
-          <t>소아 경련은 열성경련이 흔하다</t>
-        </is>
-      </c>
-      <c r="J722" t="inlineStr">
         <is>
           <t>신체손상위험</t>
         </is>
